--- a/Summary_Analysis/single_BERTopic_results_AI_summary.xlsx
+++ b/Summary_Analysis/single_BERTopic_results_AI_summary.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_said_dean</t>
+          <t>-1_law_indigenous_dean_report</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'said', 'dean', 'freedom', 'report', 'association', 'letter', 'harassment', 'process']</t>
+          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['Acadia University in Wolfville, Nova Scotia confirmed on September 7, 2018, that Rick Mehta, a tenured associate professor of psychology, had been dismissed. The firing took effect on August 31, 2018, following a formal investigation into complaints against him. Mehta had taught at Acadia for fifteen years, including large required courses such as Introductory Psychology and Research Design and Analysis, and had received teaching awards and positive student evaluations. He was also a self-styled firebrand for “academic free speech” who had stoked a national debate about free expression on campus by making controversial comments on social media and in the classroom.\n\nMehta was outspoken both on campus and online about a range of contentious issues, including decolonization, immigration, gender politics, and the Truth and Reconciliation Commission. He came under fire for saying multiculturalism is a scam, denying the wage gap between men and women, and dismissing the Truth and Reconciliation Commission as a vehicle for “endless apologies and compensation.” On Twitter, he retweeted a post saying it was “statistically impossible for all Native children to have had a negative experience with residential schools.” His defenders called his voice an antidote to political correctness run amok, while critics said his polarizing comments attacked marginalized people and perpetuated harmful stereotypes. The acrimonious debate spurred a Halifax-based activist to launch a petition demanding his removal, while a counter-petition called for him to stay in the classroom as a beacon of freedom of expression.\n\nThe university launched an external three-month investigation overseen by Dalhousie University professor emeritus Wayne MacKay, as well as an internal inquiry conducted by Acadia’s Dean of Science, Jeff Hooper. University spokesman Scott Roberts said he was unable to comment or “provide any elaboration” on the dismissal because it was a confidential personnel matter, and called the MacKay report a “privileged document.” The Acadia University Faculty Association said it was informed of the firing on August 31 and has since filed for arbitration. “The termination of a tenured professor is very serious, and the faculty association has filed for arbitration while its senior grievance officer and legal counsel examine the administration’s disciplinary procedures and evidence,” the association said in a statement. Mehta continued to receive his $112,527 annual salary and benefits pending the outcome of the arbitration.\n\nAn eight-page letter written by Acadia’s Vice-President Academic, Heather Hemming, on August 3, 2018, delivered a detailed review of the school’s grounds for disciplinary action against Mehta. The letter cited eight categories of inappropriate conduct: unprofessional and non-collegial conduct directed at students, faculty, and administration, including creation of a poisoned work environment; breaches of privacy in relation to students and colleagues; creation of a poisoned, intolerant teaching environment, particularly regarding sensitive issues of gender and race; making inappropriate and potentially discriminatory comments towards women and vulnerable groups; personal harassment and bullying of students, faculty and other members of the university community; significant deviations from the academic syllabus and significant use of irrelevant non-academic sources in class, resulting in failure to teach required course material; damaging the reputation of the institution by attacking the university and colleagues on social media; and unwillingness to recognize the harmful effects of actions on students and faculty.\n\nHemming wrote that it was “reprehensible” that Mehta posted to a publicly available Dropbox account a recording of one of his classes in which a student disclosed her rape experience. “This action further demonstrates your disregard for the privacy rights of students and suggests you are more concerned with public online support than the interests of students,” she wrote. The letter also stated that Mehta’s conduct toward students and colleagues created a “poisoned” work and teaching environment and that many members of the psychology department had expressed genuine concern for their safety. It cited an example where Mehta told an Intro to Psychology class that sexual assault survivors are not victims and women are assaulted because they put themselves in dangerous environments. Quoting the MacKay report, Hemming wrote that Mehta made numerous discriminatory or harassing posts on social media. “Indigenous peoples, racialized minorities, women, sexual identity and gender expression, immigrants and multiculturalism are all targets,” she wrote. The letter said a significant amount of class time, in some classes 90 percent or more, was spent on topics irrelevant or not connected to the course syllabus, and that Mehta had failed to deliver the course Acadia contracted him to teach. It also said that concerns, cautions, and counselling about the “harmful effects” of his teaching, interactions, and social media use had been brought to his attention but had fallen on deaf ears. “You seem to be under the impression that your rights of ‘free speech’ and academic freedom trump all other obligations to the university and members of the university community,” Hemming wrote.\n\nIn the letter of dismissal given to Mehta at his dismissal hearing, President Peter Ricketts stated that he was firing Mehta on the basis of issues that “were wide ranging and include failure to fulfill academic responsibilities, unprofessional conduct, breach of privacy, and harassment and intimidation of students and other members of the University community.” After the dismissal, Ricketts responded to a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship, saying the action was not taken in response to Mehta’s legitimate exercise of free speech or academic freedom. “He was not dismissed for his views but rather for his conduct towards other members of faculty, staff, and students,” Ricketts wrote. Ricketts said Mehta had been provided access to hundreds of pages of material from both the internal and external reports, as well as a lengthy list of specific reasons supporting the decision to dismiss him.\n\nMehta disputed the university’s account. He said the university gave him “broad and unspecified reasons” and that the reports relied in part on anonymous submissions and lacked methodology. He said he was only offered limited time to review the MacKay and Hooper reports before being fired, and was not allowed to have copies unless he signed an agreement preventing him from distributing confidential information or retaliating against complainants, which he called a “gag order.” Mehta said he never discriminated against or harassed students or colleagues. “I have never done any of the acts that have been attributed to me,” he said. He said “perspectives are subjective” and that the complaints came from a small number of students, while larger numbers of other students thought it was refreshing that he was trying to get them to think critically. He said he offered concessions before being fired: to move offices away from colleagues who were uncomfortable around him, to teach different courses, and not to be Facebook friends with students while they were in his courses, but the university was not interested. Mehta said he had no regrets about his comments, actions, or teaching style. He believed the real reason for his dismissal was a “culture war” taking place in universities, and that he was fired because he spoke out against the university’s new mission of “committing to social justice.” He said the university was using harassment and discrimination policies to suppress his dissent.\n\nSeveral outside voices weighed in. Mercer wrote in the Halifax Chronicle Herald that the three most troubling things about the firing were the secrecy surrounding Acadia’s decision, Acadia’s failure to address properly any valid complaint, and Acadia’s attack on freedom of expression on campus. Peter Wood, writing for the National Association of Scholars, described the firing as “How a Social Justice Mob Fired a Tenured Professor,” arguing that Mehta stood up for disinterested academic standards while Acadia rushed to a “social justice” agenda. In March, the Canadian Association of University Teachers appointed a committee to review how Acadia handled grievances against Mehta to determine whether his academic freedom had been breached or threatened. The Acadia University Faculty Association filed for arbitration, and Mehta said he was going into the arbitration process with resolve because the outcome would have national implications for academic freedom in Canada.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -499,17 +499,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -545,12 +545,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3_said_class_duval_lieutenant</t>
+          <t>3_class_gender_complaint_word</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['said', 'class', 'duval', 'lieutenant', 'lieutenant duval', 'st', 'gender', 'complaint', 'word', 'did']</t>
+          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4_freedom_york_noble_board</t>
+          <t>4_board_media_journals_release</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['freedom', 'york', 'noble', 'board', 'media', '2018', 'ubc', 'journals', 'release', 'did']</t>
+          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'dalhousie', 'control']</t>
+          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'control', 'bargaining']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -681,22 +681,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -731,22 +731,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -878,22 +878,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -925,12 +925,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4_freedom_york_noble_board</t>
+          <t>4_board_media_journals_release</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['freedom', 'york', 'noble', 'board', 'media', '2018', 'ubc', 'journals', 'release', 'did']</t>
+          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>freedom - york - noble - board - media - 2018 - ubc - journals - release - did</t>
+          <t>board - media - journals - release - trustees - governance - wall - suspension - president - grievance</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -973,12 +973,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4_freedom_york_noble_board</t>
+          <t>4_board_media_journals_release</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['freedom', 'york', 'noble', 'board', 'media', '2018', 'ubc', 'journals', 'release', 'did']</t>
+          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>freedom - york - noble - board - media - 2018 - ubc - journals - release - did</t>
+          <t>board - media - journals - release - trustees - governance - wall - suspension - president - grievance</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>health - freedom - consent - medical - committee - public - records - said - christian - informed</t>
+          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1067,22 +1067,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3_said_class_duval_lieutenant</t>
+          <t>3_class_gender_complaint_word</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>['said', 'class', 'duval', 'lieutenant', 'lieutenant duval', 'st', 'gender', 'complaint', 'word', 'did']</t>
+          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>said - class - duval - lieutenant - lieutenant duval - st - gender - complaint - word - did</t>
+          <t>class - gender - complaint - word - rights - investigation - views - complaints - 2015 - expression</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3_said_class_duval_lieutenant</t>
+          <t>3_class_gender_complaint_word</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>['said', 'class', 'duval', 'lieutenant', 'lieutenant duval', 'st', 'gender', 'complaint', 'word', 'did']</t>
+          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>said - class - duval - lieutenant - lieutenant duval - st - gender - complaint - word - did</t>
+          <t>class - gender - complaint - word - rights - investigation - views - complaints - 2015 - expression</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>health - freedom - consent - medical - committee - public - records - said - christian - informed</t>
+          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4_freedom_york_noble_board</t>
+          <t>4_board_media_journals_release</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>['freedom', 'york', 'noble', 'board', 'media', '2018', 'ubc', 'journals', 'release', 'did']</t>
+          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>freedom - york - noble - board - media - 2018 - ubc - journals - release - did</t>
+          <t>board - media - journals - release - trustees - governance - wall - suspension - president - grievance</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_said_dean</t>
+          <t>-1_law_indigenous_dean_report</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'said', 'dean', 'freedom', 'report', 'association', 'letter', 'harassment', 'process']</t>
+          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['Acadia University in Wolfville, Nova Scotia confirmed on September 7, 2018, that Rick Mehta, a tenured associate professor of psychology, had been dismissed. The firing took effect on August 31, 2018, following a formal investigation into complaints against him. Mehta had taught at Acadia for fifteen years, including large required courses such as Introductory Psychology and Research Design and Analysis, and had received teaching awards and positive student evaluations. He was also a self-styled firebrand for “academic free speech” who had stoked a national debate about free expression on campus by making controversial comments on social media and in the classroom.\n\nMehta was outspoken both on campus and online about a range of contentious issues, including decolonization, immigration, gender politics, and the Truth and Reconciliation Commission. He came under fire for saying multiculturalism is a scam, denying the wage gap between men and women, and dismissing the Truth and Reconciliation Commission as a vehicle for “endless apologies and compensation.” On Twitter, he retweeted a post saying it was “statistically impossible for all Native children to have had a negative experience with residential schools.” His defenders called his voice an antidote to political correctness run amok, while critics said his polarizing comments attacked marginalized people and perpetuated harmful stereotypes. The acrimonious debate spurred a Halifax-based activist to launch a petition demanding his removal, while a counter-petition called for him to stay in the classroom as a beacon of freedom of expression.\n\nThe university launched an external three-month investigation overseen by Dalhousie University professor emeritus Wayne MacKay, as well as an internal inquiry conducted by Acadia’s Dean of Science, Jeff Hooper. University spokesman Scott Roberts said he was unable to comment or “provide any elaboration” on the dismissal because it was a confidential personnel matter, and called the MacKay report a “privileged document.” The Acadia University Faculty Association said it was informed of the firing on August 31 and has since filed for arbitration. “The termination of a tenured professor is very serious, and the faculty association has filed for arbitration while its senior grievance officer and legal counsel examine the administration’s disciplinary procedures and evidence,” the association said in a statement. Mehta continued to receive his $112,527 annual salary and benefits pending the outcome of the arbitration.\n\nAn eight-page letter written by Acadia’s Vice-President Academic, Heather Hemming, on August 3, 2018, delivered a detailed review of the school’s grounds for disciplinary action against Mehta. The letter cited eight categories of inappropriate conduct: unprofessional and non-collegial conduct directed at students, faculty, and administration, including creation of a poisoned work environment; breaches of privacy in relation to students and colleagues; creation of a poisoned, intolerant teaching environment, particularly regarding sensitive issues of gender and race; making inappropriate and potentially discriminatory comments towards women and vulnerable groups; personal harassment and bullying of students, faculty and other members of the university community; significant deviations from the academic syllabus and significant use of irrelevant non-academic sources in class, resulting in failure to teach required course material; damaging the reputation of the institution by attacking the university and colleagues on social media; and unwillingness to recognize the harmful effects of actions on students and faculty.\n\nHemming wrote that it was “reprehensible” that Mehta posted to a publicly available Dropbox account a recording of one of his classes in which a student disclosed her rape experience. “This action further demonstrates your disregard for the privacy rights of students and suggests you are more concerned with public online support than the interests of students,” she wrote. The letter also stated that Mehta’s conduct toward students and colleagues created a “poisoned” work and teaching environment and that many members of the psychology department had expressed genuine concern for their safety. It cited an example where Mehta told an Intro to Psychology class that sexual assault survivors are not victims and women are assaulted because they put themselves in dangerous environments. Quoting the MacKay report, Hemming wrote that Mehta made numerous discriminatory or harassing posts on social media. “Indigenous peoples, racialized minorities, women, sexual identity and gender expression, immigrants and multiculturalism are all targets,” she wrote. The letter said a significant amount of class time, in some classes 90 percent or more, was spent on topics irrelevant or not connected to the course syllabus, and that Mehta had failed to deliver the course Acadia contracted him to teach. It also said that concerns, cautions, and counselling about the “harmful effects” of his teaching, interactions, and social media use had been brought to his attention but had fallen on deaf ears. “You seem to be under the impression that your rights of ‘free speech’ and academic freedom trump all other obligations to the university and members of the university community,” Hemming wrote.\n\nIn the letter of dismissal given to Mehta at his dismissal hearing, President Peter Ricketts stated that he was firing Mehta on the basis of issues that “were wide ranging and include failure to fulfill academic responsibilities, unprofessional conduct, breach of privacy, and harassment and intimidation of students and other members of the University community.” After the dismissal, Ricketts responded to a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship, saying the action was not taken in response to Mehta’s legitimate exercise of free speech or academic freedom. “He was not dismissed for his views but rather for his conduct towards other members of faculty, staff, and students,” Ricketts wrote. Ricketts said Mehta had been provided access to hundreds of pages of material from both the internal and external reports, as well as a lengthy list of specific reasons supporting the decision to dismiss him.\n\nMehta disputed the university’s account. He said the university gave him “broad and unspecified reasons” and that the reports relied in part on anonymous submissions and lacked methodology. He said he was only offered limited time to review the MacKay and Hooper reports before being fired, and was not allowed to have copies unless he signed an agreement preventing him from distributing confidential information or retaliating against complainants, which he called a “gag order.” Mehta said he never discriminated against or harassed students or colleagues. “I have never done any of the acts that have been attributed to me,” he said. He said “perspectives are subjective” and that the complaints came from a small number of students, while larger numbers of other students thought it was refreshing that he was trying to get them to think critically. He said he offered concessions before being fired: to move offices away from colleagues who were uncomfortable around him, to teach different courses, and not to be Facebook friends with students while they were in his courses, but the university was not interested. Mehta said he had no regrets about his comments, actions, or teaching style. He believed the real reason for his dismissal was a “culture war” taking place in universities, and that he was fired because he spoke out against the university’s new mission of “committing to social justice.” He said the university was using harassment and discrimination policies to suppress his dissent.\n\nSeveral outside voices weighed in. Mercer wrote in the Halifax Chronicle Herald that the three most troubling things about the firing were the secrecy surrounding Acadia’s decision, Acadia’s failure to address properly any valid complaint, and Acadia’s attack on freedom of expression on campus. Peter Wood, writing for the National Association of Scholars, described the firing as “How a Social Justice Mob Fired a Tenured Professor,” arguing that Mehta stood up for disinterested academic standards while Acadia rushed to a “social justice” agenda. In March, the Canadian Association of University Teachers appointed a committee to review how Acadia handled grievances against Mehta to determine whether his academic freedom had been breached or threatened. The Acadia University Faculty Association filed for arbitration, and Mehta said he was going into the arbitration process with resolve because the outcome would have national implications for academic freedom in Canada.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>law - indigenous - said - dean - freedom - report - association - letter - harassment - process</t>
+          <t>law - indigenous - dean - report - association - letter - harassment - process - work - hiring</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>health - freedom - consent - medical - committee - public - records - said - christian - informed</t>
+          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3_said_class_duval_lieutenant</t>
+          <t>3_class_gender_complaint_word</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>['said', 'class', 'duval', 'lieutenant', 'lieutenant duval', 'st', 'gender', 'complaint', 'word', 'did']</t>
+          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>said - class - duval - lieutenant - lieutenant duval - st - gender - complaint - word - did</t>
+          <t>class - gender - complaint - word - rights - investigation - views - complaints - 2015 - expression</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'dalhousie', 'control']</t>
+          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'control', 'bargaining']</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>course - notes - agreement - teaching - materials - employer - decision - request - dalhousie - control</t>
+          <t>course - notes - agreement - teaching - materials - employer - decision - request - control - bargaining</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1745,22 +1745,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_said_dean</t>
+          <t>-1_law_indigenous_dean_report</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'said', 'dean', 'freedom', 'report', 'association', 'letter', 'harassment', 'process']</t>
+          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['Acadia University in Wolfville, Nova Scotia confirmed on September 7, 2018, that Rick Mehta, a tenured associate professor of psychology, had been dismissed. The firing took effect on August 31, 2018, following a formal investigation into complaints against him. Mehta had taught at Acadia for fifteen years, including large required courses such as Introductory Psychology and Research Design and Analysis, and had received teaching awards and positive student evaluations. He was also a self-styled firebrand for “academic free speech” who had stoked a national debate about free expression on campus by making controversial comments on social media and in the classroom.\n\nMehta was outspoken both on campus and online about a range of contentious issues, including decolonization, immigration, gender politics, and the Truth and Reconciliation Commission. He came under fire for saying multiculturalism is a scam, denying the wage gap between men and women, and dismissing the Truth and Reconciliation Commission as a vehicle for “endless apologies and compensation.” On Twitter, he retweeted a post saying it was “statistically impossible for all Native children to have had a negative experience with residential schools.” His defenders called his voice an antidote to political correctness run amok, while critics said his polarizing comments attacked marginalized people and perpetuated harmful stereotypes. The acrimonious debate spurred a Halifax-based activist to launch a petition demanding his removal, while a counter-petition called for him to stay in the classroom as a beacon of freedom of expression.\n\nThe university launched an external three-month investigation overseen by Dalhousie University professor emeritus Wayne MacKay, as well as an internal inquiry conducted by Acadia’s Dean of Science, Jeff Hooper. University spokesman Scott Roberts said he was unable to comment or “provide any elaboration” on the dismissal because it was a confidential personnel matter, and called the MacKay report a “privileged document.” The Acadia University Faculty Association said it was informed of the firing on August 31 and has since filed for arbitration. “The termination of a tenured professor is very serious, and the faculty association has filed for arbitration while its senior grievance officer and legal counsel examine the administration’s disciplinary procedures and evidence,” the association said in a statement. Mehta continued to receive his $112,527 annual salary and benefits pending the outcome of the arbitration.\n\nAn eight-page letter written by Acadia’s Vice-President Academic, Heather Hemming, on August 3, 2018, delivered a detailed review of the school’s grounds for disciplinary action against Mehta. The letter cited eight categories of inappropriate conduct: unprofessional and non-collegial conduct directed at students, faculty, and administration, including creation of a poisoned work environment; breaches of privacy in relation to students and colleagues; creation of a poisoned, intolerant teaching environment, particularly regarding sensitive issues of gender and race; making inappropriate and potentially discriminatory comments towards women and vulnerable groups; personal harassment and bullying of students, faculty and other members of the university community; significant deviations from the academic syllabus and significant use of irrelevant non-academic sources in class, resulting in failure to teach required course material; damaging the reputation of the institution by attacking the university and colleagues on social media; and unwillingness to recognize the harmful effects of actions on students and faculty.\n\nHemming wrote that it was “reprehensible” that Mehta posted to a publicly available Dropbox account a recording of one of his classes in which a student disclosed her rape experience. “This action further demonstrates your disregard for the privacy rights of students and suggests you are more concerned with public online support than the interests of students,” she wrote. The letter also stated that Mehta’s conduct toward students and colleagues created a “poisoned” work and teaching environment and that many members of the psychology department had expressed genuine concern for their safety. It cited an example where Mehta told an Intro to Psychology class that sexual assault survivors are not victims and women are assaulted because they put themselves in dangerous environments. Quoting the MacKay report, Hemming wrote that Mehta made numerous discriminatory or harassing posts on social media. “Indigenous peoples, racialized minorities, women, sexual identity and gender expression, immigrants and multiculturalism are all targets,” she wrote. The letter said a significant amount of class time, in some classes 90 percent or more, was spent on topics irrelevant or not connected to the course syllabus, and that Mehta had failed to deliver the course Acadia contracted him to teach. It also said that concerns, cautions, and counselling about the “harmful effects” of his teaching, interactions, and social media use had been brought to his attention but had fallen on deaf ears. “You seem to be under the impression that your rights of ‘free speech’ and academic freedom trump all other obligations to the university and members of the university community,” Hemming wrote.\n\nIn the letter of dismissal given to Mehta at his dismissal hearing, President Peter Ricketts stated that he was firing Mehta on the basis of issues that “were wide ranging and include failure to fulfill academic responsibilities, unprofessional conduct, breach of privacy, and harassment and intimidation of students and other members of the University community.” After the dismissal, Ricketts responded to a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship, saying the action was not taken in response to Mehta’s legitimate exercise of free speech or academic freedom. “He was not dismissed for his views but rather for his conduct towards other members of faculty, staff, and students,” Ricketts wrote. Ricketts said Mehta had been provided access to hundreds of pages of material from both the internal and external reports, as well as a lengthy list of specific reasons supporting the decision to dismiss him.\n\nMehta disputed the university’s account. He said the university gave him “broad and unspecified reasons” and that the reports relied in part on anonymous submissions and lacked methodology. He said he was only offered limited time to review the MacKay and Hooper reports before being fired, and was not allowed to have copies unless he signed an agreement preventing him from distributing confidential information or retaliating against complainants, which he called a “gag order.” Mehta said he never discriminated against or harassed students or colleagues. “I have never done any of the acts that have been attributed to me,” he said. He said “perspectives are subjective” and that the complaints came from a small number of students, while larger numbers of other students thought it was refreshing that he was trying to get them to think critically. He said he offered concessions before being fired: to move offices away from colleagues who were uncomfortable around him, to teach different courses, and not to be Facebook friends with students while they were in his courses, but the university was not interested. Mehta said he had no regrets about his comments, actions, or teaching style. He believed the real reason for his dismissal was a “culture war” taking place in universities, and that he was fired because he spoke out against the university’s new mission of “committing to social justice.” He said the university was using harassment and discrimination policies to suppress his dissent.\n\nSeveral outside voices weighed in. Mercer wrote in the Halifax Chronicle Herald that the three most troubling things about the firing were the secrecy surrounding Acadia’s decision, Acadia’s failure to address properly any valid complaint, and Acadia’s attack on freedom of expression on campus. Peter Wood, writing for the National Association of Scholars, described the firing as “How a Social Justice Mob Fired a Tenured Professor,” arguing that Mehta stood up for disinterested academic standards while Acadia rushed to a “social justice” agenda. In March, the Canadian Association of University Teachers appointed a committee to review how Acadia handled grievances against Mehta to determine whether his academic freedom had been breached or threatened. The Acadia University Faculty Association filed for arbitration, and Mehta said he was going into the arbitration process with resolve because the outcome would have national implications for academic freedom in Canada.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>law - indigenous - said - dean - freedom - report - association - letter - harassment - process</t>
+          <t>law - indigenous - dean - report - association - letter - harassment - process - work - hiring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1793,22 +1793,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_said_dean</t>
+          <t>-1_law_indigenous_dean_report</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'said', 'dean', 'freedom', 'report', 'association', 'letter', 'harassment', 'process']</t>
+          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['Acadia University in Wolfville, Nova Scotia confirmed on September 7, 2018, that Rick Mehta, a tenured associate professor of psychology, had been dismissed. The firing took effect on August 31, 2018, following a formal investigation into complaints against him. Mehta had taught at Acadia for fifteen years, including large required courses such as Introductory Psychology and Research Design and Analysis, and had received teaching awards and positive student evaluations. He was also a self-styled firebrand for “academic free speech” who had stoked a national debate about free expression on campus by making controversial comments on social media and in the classroom.\n\nMehta was outspoken both on campus and online about a range of contentious issues, including decolonization, immigration, gender politics, and the Truth and Reconciliation Commission. He came under fire for saying multiculturalism is a scam, denying the wage gap between men and women, and dismissing the Truth and Reconciliation Commission as a vehicle for “endless apologies and compensation.” On Twitter, he retweeted a post saying it was “statistically impossible for all Native children to have had a negative experience with residential schools.” His defenders called his voice an antidote to political correctness run amok, while critics said his polarizing comments attacked marginalized people and perpetuated harmful stereotypes. The acrimonious debate spurred a Halifax-based activist to launch a petition demanding his removal, while a counter-petition called for him to stay in the classroom as a beacon of freedom of expression.\n\nThe university launched an external three-month investigation overseen by Dalhousie University professor emeritus Wayne MacKay, as well as an internal inquiry conducted by Acadia’s Dean of Science, Jeff Hooper. University spokesman Scott Roberts said he was unable to comment or “provide any elaboration” on the dismissal because it was a confidential personnel matter, and called the MacKay report a “privileged document.” The Acadia University Faculty Association said it was informed of the firing on August 31 and has since filed for arbitration. “The termination of a tenured professor is very serious, and the faculty association has filed for arbitration while its senior grievance officer and legal counsel examine the administration’s disciplinary procedures and evidence,” the association said in a statement. Mehta continued to receive his $112,527 annual salary and benefits pending the outcome of the arbitration.\n\nAn eight-page letter written by Acadia’s Vice-President Academic, Heather Hemming, on August 3, 2018, delivered a detailed review of the school’s grounds for disciplinary action against Mehta. The letter cited eight categories of inappropriate conduct: unprofessional and non-collegial conduct directed at students, faculty, and administration, including creation of a poisoned work environment; breaches of privacy in relation to students and colleagues; creation of a poisoned, intolerant teaching environment, particularly regarding sensitive issues of gender and race; making inappropriate and potentially discriminatory comments towards women and vulnerable groups; personal harassment and bullying of students, faculty and other members of the university community; significant deviations from the academic syllabus and significant use of irrelevant non-academic sources in class, resulting in failure to teach required course material; damaging the reputation of the institution by attacking the university and colleagues on social media; and unwillingness to recognize the harmful effects of actions on students and faculty.\n\nHemming wrote that it was “reprehensible” that Mehta posted to a publicly available Dropbox account a recording of one of his classes in which a student disclosed her rape experience. “This action further demonstrates your disregard for the privacy rights of students and suggests you are more concerned with public online support than the interests of students,” she wrote. The letter also stated that Mehta’s conduct toward students and colleagues created a “poisoned” work and teaching environment and that many members of the psychology department had expressed genuine concern for their safety. It cited an example where Mehta told an Intro to Psychology class that sexual assault survivors are not victims and women are assaulted because they put themselves in dangerous environments. Quoting the MacKay report, Hemming wrote that Mehta made numerous discriminatory or harassing posts on social media. “Indigenous peoples, racialized minorities, women, sexual identity and gender expression, immigrants and multiculturalism are all targets,” she wrote. The letter said a significant amount of class time, in some classes 90 percent or more, was spent on topics irrelevant or not connected to the course syllabus, and that Mehta had failed to deliver the course Acadia contracted him to teach. It also said that concerns, cautions, and counselling about the “harmful effects” of his teaching, interactions, and social media use had been brought to his attention but had fallen on deaf ears. “You seem to be under the impression that your rights of ‘free speech’ and academic freedom trump all other obligations to the university and members of the university community,” Hemming wrote.\n\nIn the letter of dismissal given to Mehta at his dismissal hearing, President Peter Ricketts stated that he was firing Mehta on the basis of issues that “were wide ranging and include failure to fulfill academic responsibilities, unprofessional conduct, breach of privacy, and harassment and intimidation of students and other members of the University community.” After the dismissal, Ricketts responded to a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship, saying the action was not taken in response to Mehta’s legitimate exercise of free speech or academic freedom. “He was not dismissed for his views but rather for his conduct towards other members of faculty, staff, and students,” Ricketts wrote. Ricketts said Mehta had been provided access to hundreds of pages of material from both the internal and external reports, as well as a lengthy list of specific reasons supporting the decision to dismiss him.\n\nMehta disputed the university’s account. He said the university gave him “broad and unspecified reasons” and that the reports relied in part on anonymous submissions and lacked methodology. He said he was only offered limited time to review the MacKay and Hooper reports before being fired, and was not allowed to have copies unless he signed an agreement preventing him from distributing confidential information or retaliating against complainants, which he called a “gag order.” Mehta said he never discriminated against or harassed students or colleagues. “I have never done any of the acts that have been attributed to me,” he said. He said “perspectives are subjective” and that the complaints came from a small number of students, while larger numbers of other students thought it was refreshing that he was trying to get them to think critically. He said he offered concessions before being fired: to move offices away from colleagues who were uncomfortable around him, to teach different courses, and not to be Facebook friends with students while they were in his courses, but the university was not interested. Mehta said he had no regrets about his comments, actions, or teaching style. He believed the real reason for his dismissal was a “culture war” taking place in universities, and that he was fired because he spoke out against the university’s new mission of “committing to social justice.” He said the university was using harassment and discrimination policies to suppress his dissent.\n\nSeveral outside voices weighed in. Mercer wrote in the Halifax Chronicle Herald that the three most troubling things about the firing were the secrecy surrounding Acadia’s decision, Acadia’s failure to address properly any valid complaint, and Acadia’s attack on freedom of expression on campus. Peter Wood, writing for the National Association of Scholars, described the firing as “How a Social Justice Mob Fired a Tenured Professor,” arguing that Mehta stood up for disinterested academic standards while Acadia rushed to a “social justice” agenda. In March, the Canadian Association of University Teachers appointed a committee to review how Acadia handled grievances against Mehta to determine whether his academic freedom had been breached or threatened. The Acadia University Faculty Association filed for arbitration, and Mehta said he was going into the arbitration process with resolve because the outcome would have national implications for academic freedom in Canada.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>law - indigenous - said - dean - freedom - report - association - letter - harassment - process</t>
+          <t>law - indigenous - dean - report - association - letter - harassment - process - work - hiring</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>health - freedom - consent - medical - committee - public - records - said - christian - informed</t>
+          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_said_dean</t>
+          <t>-1_law_indigenous_dean_report</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'said', 'dean', 'freedom', 'report', 'association', 'letter', 'harassment', 'process']</t>
+          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['Acadia University in Wolfville, Nova Scotia confirmed on September 7, 2018, that Rick Mehta, a tenured associate professor of psychology, had been dismissed. The firing took effect on August 31, 2018, following a formal investigation into complaints against him. Mehta had taught at Acadia for fifteen years, including large required courses such as Introductory Psychology and Research Design and Analysis, and had received teaching awards and positive student evaluations. He was also a self-styled firebrand for “academic free speech” who had stoked a national debate about free expression on campus by making controversial comments on social media and in the classroom.\n\nMehta was outspoken both on campus and online about a range of contentious issues, including decolonization, immigration, gender politics, and the Truth and Reconciliation Commission. He came under fire for saying multiculturalism is a scam, denying the wage gap between men and women, and dismissing the Truth and Reconciliation Commission as a vehicle for “endless apologies and compensation.” On Twitter, he retweeted a post saying it was “statistically impossible for all Native children to have had a negative experience with residential schools.” His defenders called his voice an antidote to political correctness run amok, while critics said his polarizing comments attacked marginalized people and perpetuated harmful stereotypes. The acrimonious debate spurred a Halifax-based activist to launch a petition demanding his removal, while a counter-petition called for him to stay in the classroom as a beacon of freedom of expression.\n\nThe university launched an external three-month investigation overseen by Dalhousie University professor emeritus Wayne MacKay, as well as an internal inquiry conducted by Acadia’s Dean of Science, Jeff Hooper. University spokesman Scott Roberts said he was unable to comment or “provide any elaboration” on the dismissal because it was a confidential personnel matter, and called the MacKay report a “privileged document.” The Acadia University Faculty Association said it was informed of the firing on August 31 and has since filed for arbitration. “The termination of a tenured professor is very serious, and the faculty association has filed for arbitration while its senior grievance officer and legal counsel examine the administration’s disciplinary procedures and evidence,” the association said in a statement. Mehta continued to receive his $112,527 annual salary and benefits pending the outcome of the arbitration.\n\nAn eight-page letter written by Acadia’s Vice-President Academic, Heather Hemming, on August 3, 2018, delivered a detailed review of the school’s grounds for disciplinary action against Mehta. The letter cited eight categories of inappropriate conduct: unprofessional and non-collegial conduct directed at students, faculty, and administration, including creation of a poisoned work environment; breaches of privacy in relation to students and colleagues; creation of a poisoned, intolerant teaching environment, particularly regarding sensitive issues of gender and race; making inappropriate and potentially discriminatory comments towards women and vulnerable groups; personal harassment and bullying of students, faculty and other members of the university community; significant deviations from the academic syllabus and significant use of irrelevant non-academic sources in class, resulting in failure to teach required course material; damaging the reputation of the institution by attacking the university and colleagues on social media; and unwillingness to recognize the harmful effects of actions on students and faculty.\n\nHemming wrote that it was “reprehensible” that Mehta posted to a publicly available Dropbox account a recording of one of his classes in which a student disclosed her rape experience. “This action further demonstrates your disregard for the privacy rights of students and suggests you are more concerned with public online support than the interests of students,” she wrote. The letter also stated that Mehta’s conduct toward students and colleagues created a “poisoned” work and teaching environment and that many members of the psychology department had expressed genuine concern for their safety. It cited an example where Mehta told an Intro to Psychology class that sexual assault survivors are not victims and women are assaulted because they put themselves in dangerous environments. Quoting the MacKay report, Hemming wrote that Mehta made numerous discriminatory or harassing posts on social media. “Indigenous peoples, racialized minorities, women, sexual identity and gender expression, immigrants and multiculturalism are all targets,” she wrote. The letter said a significant amount of class time, in some classes 90 percent or more, was spent on topics irrelevant or not connected to the course syllabus, and that Mehta had failed to deliver the course Acadia contracted him to teach. It also said that concerns, cautions, and counselling about the “harmful effects” of his teaching, interactions, and social media use had been brought to his attention but had fallen on deaf ears. “You seem to be under the impression that your rights of ‘free speech’ and academic freedom trump all other obligations to the university and members of the university community,” Hemming wrote.\n\nIn the letter of dismissal given to Mehta at his dismissal hearing, President Peter Ricketts stated that he was firing Mehta on the basis of issues that “were wide ranging and include failure to fulfill academic responsibilities, unprofessional conduct, breach of privacy, and harassment and intimidation of students and other members of the University community.” After the dismissal, Ricketts responded to a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship, saying the action was not taken in response to Mehta’s legitimate exercise of free speech or academic freedom. “He was not dismissed for his views but rather for his conduct towards other members of faculty, staff, and students,” Ricketts wrote. Ricketts said Mehta had been provided access to hundreds of pages of material from both the internal and external reports, as well as a lengthy list of specific reasons supporting the decision to dismiss him.\n\nMehta disputed the university’s account. He said the university gave him “broad and unspecified reasons” and that the reports relied in part on anonymous submissions and lacked methodology. He said he was only offered limited time to review the MacKay and Hooper reports before being fired, and was not allowed to have copies unless he signed an agreement preventing him from distributing confidential information or retaliating against complainants, which he called a “gag order.” Mehta said he never discriminated against or harassed students or colleagues. “I have never done any of the acts that have been attributed to me,” he said. He said “perspectives are subjective” and that the complaints came from a small number of students, while larger numbers of other students thought it was refreshing that he was trying to get them to think critically. He said he offered concessions before being fired: to move offices away from colleagues who were uncomfortable around him, to teach different courses, and not to be Facebook friends with students while they were in his courses, but the university was not interested. Mehta said he had no regrets about his comments, actions, or teaching style. He believed the real reason for his dismissal was a “culture war” taking place in universities, and that he was fired because he spoke out against the university’s new mission of “committing to social justice.” He said the university was using harassment and discrimination policies to suppress his dissent.\n\nSeveral outside voices weighed in. Mercer wrote in the Halifax Chronicle Herald that the three most troubling things about the firing were the secrecy surrounding Acadia’s decision, Acadia’s failure to address properly any valid complaint, and Acadia’s attack on freedom of expression on campus. Peter Wood, writing for the National Association of Scholars, described the firing as “How a Social Justice Mob Fired a Tenured Professor,” arguing that Mehta stood up for disinterested academic standards while Acadia rushed to a “social justice” agenda. In March, the Canadian Association of University Teachers appointed a committee to review how Acadia handled grievances against Mehta to determine whether his academic freedom had been breached or threatened. The Acadia University Faculty Association filed for arbitration, and Mehta said he was going into the arbitration process with resolve because the outcome would have national implications for academic freedom in Canada.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>law - indigenous - said - dean - freedom - report - association - letter - harassment - process</t>
+          <t>law - indigenous - dean - report - association - letter - harassment - process - work - hiring</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4_freedom_york_noble_board</t>
+          <t>4_board_media_journals_release</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>['freedom', 'york', 'noble', 'board', 'media', '2018', 'ubc', 'journals', 'release', 'did']</t>
+          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>freedom - york - noble - board - media - 2018 - ubc - journals - release - did</t>
+          <t>board - media - journals - release - trustees - governance - wall - suspension - president - grievance</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1988,29 +1988,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_said_dean</t>
+          <t>-1_law_indigenous_dean_report</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'said', 'dean', 'freedom', 'report', 'association', 'letter', 'harassment', 'process']</t>
+          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['Acadia University in Wolfville, Nova Scotia confirmed on September 7, 2018, that Rick Mehta, a tenured associate professor of psychology, had been dismissed. The firing took effect on August 31, 2018, following a formal investigation into complaints against him. Mehta had taught at Acadia for fifteen years, including large required courses such as Introductory Psychology and Research Design and Analysis, and had received teaching awards and positive student evaluations. He was also a self-styled firebrand for “academic free speech” who had stoked a national debate about free expression on campus by making controversial comments on social media and in the classroom.\n\nMehta was outspoken both on campus and online about a range of contentious issues, including decolonization, immigration, gender politics, and the Truth and Reconciliation Commission. He came under fire for saying multiculturalism is a scam, denying the wage gap between men and women, and dismissing the Truth and Reconciliation Commission as a vehicle for “endless apologies and compensation.” On Twitter, he retweeted a post saying it was “statistically impossible for all Native children to have had a negative experience with residential schools.” His defenders called his voice an antidote to political correctness run amok, while critics said his polarizing comments attacked marginalized people and perpetuated harmful stereotypes. The acrimonious debate spurred a Halifax-based activist to launch a petition demanding his removal, while a counter-petition called for him to stay in the classroom as a beacon of freedom of expression.\n\nThe university launched an external three-month investigation overseen by Dalhousie University professor emeritus Wayne MacKay, as well as an internal inquiry conducted by Acadia’s Dean of Science, Jeff Hooper. University spokesman Scott Roberts said he was unable to comment or “provide any elaboration” on the dismissal because it was a confidential personnel matter, and called the MacKay report a “privileged document.” The Acadia University Faculty Association said it was informed of the firing on August 31 and has since filed for arbitration. “The termination of a tenured professor is very serious, and the faculty association has filed for arbitration while its senior grievance officer and legal counsel examine the administration’s disciplinary procedures and evidence,” the association said in a statement. Mehta continued to receive his $112,527 annual salary and benefits pending the outcome of the arbitration.\n\nAn eight-page letter written by Acadia’s Vice-President Academic, Heather Hemming, on August 3, 2018, delivered a detailed review of the school’s grounds for disciplinary action against Mehta. The letter cited eight categories of inappropriate conduct: unprofessional and non-collegial conduct directed at students, faculty, and administration, including creation of a poisoned work environment; breaches of privacy in relation to students and colleagues; creation of a poisoned, intolerant teaching environment, particularly regarding sensitive issues of gender and race; making inappropriate and potentially discriminatory comments towards women and vulnerable groups; personal harassment and bullying of students, faculty and other members of the university community; significant deviations from the academic syllabus and significant use of irrelevant non-academic sources in class, resulting in failure to teach required course material; damaging the reputation of the institution by attacking the university and colleagues on social media; and unwillingness to recognize the harmful effects of actions on students and faculty.\n\nHemming wrote that it was “reprehensible” that Mehta posted to a publicly available Dropbox account a recording of one of his classes in which a student disclosed her rape experience. “This action further demonstrates your disregard for the privacy rights of students and suggests you are more concerned with public online support than the interests of students,” she wrote. The letter also stated that Mehta’s conduct toward students and colleagues created a “poisoned” work and teaching environment and that many members of the psychology department had expressed genuine concern for their safety. It cited an example where Mehta told an Intro to Psychology class that sexual assault survivors are not victims and women are assaulted because they put themselves in dangerous environments. Quoting the MacKay report, Hemming wrote that Mehta made numerous discriminatory or harassing posts on social media. “Indigenous peoples, racialized minorities, women, sexual identity and gender expression, immigrants and multiculturalism are all targets,” she wrote. The letter said a significant amount of class time, in some classes 90 percent or more, was spent on topics irrelevant or not connected to the course syllabus, and that Mehta had failed to deliver the course Acadia contracted him to teach. It also said that concerns, cautions, and counselling about the “harmful effects” of his teaching, interactions, and social media use had been brought to his attention but had fallen on deaf ears. “You seem to be under the impression that your rights of ‘free speech’ and academic freedom trump all other obligations to the university and members of the university community,” Hemming wrote.\n\nIn the letter of dismissal given to Mehta at his dismissal hearing, President Peter Ricketts stated that he was firing Mehta on the basis of issues that “were wide ranging and include failure to fulfill academic responsibilities, unprofessional conduct, breach of privacy, and harassment and intimidation of students and other members of the University community.” After the dismissal, Ricketts responded to a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship, saying the action was not taken in response to Mehta’s legitimate exercise of free speech or academic freedom. “He was not dismissed for his views but rather for his conduct towards other members of faculty, staff, and students,” Ricketts wrote. Ricketts said Mehta had been provided access to hundreds of pages of material from both the internal and external reports, as well as a lengthy list of specific reasons supporting the decision to dismiss him.\n\nMehta disputed the university’s account. He said the university gave him “broad and unspecified reasons” and that the reports relied in part on anonymous submissions and lacked methodology. He said he was only offered limited time to review the MacKay and Hooper reports before being fired, and was not allowed to have copies unless he signed an agreement preventing him from distributing confidential information or retaliating against complainants, which he called a “gag order.” Mehta said he never discriminated against or harassed students or colleagues. “I have never done any of the acts that have been attributed to me,” he said. He said “perspectives are subjective” and that the complaints came from a small number of students, while larger numbers of other students thought it was refreshing that he was trying to get them to think critically. He said he offered concessions before being fired: to move offices away from colleagues who were uncomfortable around him, to teach different courses, and not to be Facebook friends with students while they were in his courses, but the university was not interested. Mehta said he had no regrets about his comments, actions, or teaching style. He believed the real reason for his dismissal was a “culture war” taking place in universities, and that he was fired because he spoke out against the university’s new mission of “committing to social justice.” He said the university was using harassment and discrimination policies to suppress his dissent.\n\nSeveral outside voices weighed in. Mercer wrote in the Halifax Chronicle Herald that the three most troubling things about the firing were the secrecy surrounding Acadia’s decision, Acadia’s failure to address properly any valid complaint, and Acadia’s attack on freedom of expression on campus. Peter Wood, writing for the National Association of Scholars, described the firing as “How a Social Justice Mob Fired a Tenured Professor,” arguing that Mehta stood up for disinterested academic standards while Acadia rushed to a “social justice” agenda. In March, the Canadian Association of University Teachers appointed a committee to review how Acadia handled grievances against Mehta to determine whether his academic freedom had been breached or threatened. The Acadia University Faculty Association filed for arbitration, and Mehta said he was going into the arbitration process with resolve because the outcome would have national implications for academic freedom in Canada.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>law - indigenous - said - dean - freedom - report - association - letter - harassment - process</t>
+          <t>law - indigenous - dean - report - association - letter - harassment - process - work - hiring</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'dalhousie', 'control']</t>
+          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'control', 'bargaining']</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>course - notes - agreement - teaching - materials - employer - decision - request - dalhousie - control</t>
+          <t>course - notes - agreement - teaching - materials - employer - decision - request - control - bargaining</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2130,22 +2130,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2180,29 +2180,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_said_dean</t>
+          <t>-1_law_indigenous_dean_report</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'said', 'dean', 'freedom', 'report', 'association', 'letter', 'harassment', 'process']</t>
+          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['Acadia University in Wolfville, Nova Scotia confirmed on September 7, 2018, that Rick Mehta, a tenured associate professor of psychology, had been dismissed. The firing took effect on August 31, 2018, following a formal investigation into complaints against him. Mehta had taught at Acadia for fifteen years, including large required courses such as Introductory Psychology and Research Design and Analysis, and had received teaching awards and positive student evaluations. He was also a self-styled firebrand for “academic free speech” who had stoked a national debate about free expression on campus by making controversial comments on social media and in the classroom.\n\nMehta was outspoken both on campus and online about a range of contentious issues, including decolonization, immigration, gender politics, and the Truth and Reconciliation Commission. He came under fire for saying multiculturalism is a scam, denying the wage gap between men and women, and dismissing the Truth and Reconciliation Commission as a vehicle for “endless apologies and compensation.” On Twitter, he retweeted a post saying it was “statistically impossible for all Native children to have had a negative experience with residential schools.” His defenders called his voice an antidote to political correctness run amok, while critics said his polarizing comments attacked marginalized people and perpetuated harmful stereotypes. The acrimonious debate spurred a Halifax-based activist to launch a petition demanding his removal, while a counter-petition called for him to stay in the classroom as a beacon of freedom of expression.\n\nThe university launched an external three-month investigation overseen by Dalhousie University professor emeritus Wayne MacKay, as well as an internal inquiry conducted by Acadia’s Dean of Science, Jeff Hooper. University spokesman Scott Roberts said he was unable to comment or “provide any elaboration” on the dismissal because it was a confidential personnel matter, and called the MacKay report a “privileged document.” The Acadia University Faculty Association said it was informed of the firing on August 31 and has since filed for arbitration. “The termination of a tenured professor is very serious, and the faculty association has filed for arbitration while its senior grievance officer and legal counsel examine the administration’s disciplinary procedures and evidence,” the association said in a statement. Mehta continued to receive his $112,527 annual salary and benefits pending the outcome of the arbitration.\n\nAn eight-page letter written by Acadia’s Vice-President Academic, Heather Hemming, on August 3, 2018, delivered a detailed review of the school’s grounds for disciplinary action against Mehta. The letter cited eight categories of inappropriate conduct: unprofessional and non-collegial conduct directed at students, faculty, and administration, including creation of a poisoned work environment; breaches of privacy in relation to students and colleagues; creation of a poisoned, intolerant teaching environment, particularly regarding sensitive issues of gender and race; making inappropriate and potentially discriminatory comments towards women and vulnerable groups; personal harassment and bullying of students, faculty and other members of the university community; significant deviations from the academic syllabus and significant use of irrelevant non-academic sources in class, resulting in failure to teach required course material; damaging the reputation of the institution by attacking the university and colleagues on social media; and unwillingness to recognize the harmful effects of actions on students and faculty.\n\nHemming wrote that it was “reprehensible” that Mehta posted to a publicly available Dropbox account a recording of one of his classes in which a student disclosed her rape experience. “This action further demonstrates your disregard for the privacy rights of students and suggests you are more concerned with public online support than the interests of students,” she wrote. The letter also stated that Mehta’s conduct toward students and colleagues created a “poisoned” work and teaching environment and that many members of the psychology department had expressed genuine concern for their safety. It cited an example where Mehta told an Intro to Psychology class that sexual assault survivors are not victims and women are assaulted because they put themselves in dangerous environments. Quoting the MacKay report, Hemming wrote that Mehta made numerous discriminatory or harassing posts on social media. “Indigenous peoples, racialized minorities, women, sexual identity and gender expression, immigrants and multiculturalism are all targets,” she wrote. The letter said a significant amount of class time, in some classes 90 percent or more, was spent on topics irrelevant or not connected to the course syllabus, and that Mehta had failed to deliver the course Acadia contracted him to teach. It also said that concerns, cautions, and counselling about the “harmful effects” of his teaching, interactions, and social media use had been brought to his attention but had fallen on deaf ears. “You seem to be under the impression that your rights of ‘free speech’ and academic freedom trump all other obligations to the university and members of the university community,” Hemming wrote.\n\nIn the letter of dismissal given to Mehta at his dismissal hearing, President Peter Ricketts stated that he was firing Mehta on the basis of issues that “were wide ranging and include failure to fulfill academic responsibilities, unprofessional conduct, breach of privacy, and harassment and intimidation of students and other members of the University community.” After the dismissal, Ricketts responded to a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship, saying the action was not taken in response to Mehta’s legitimate exercise of free speech or academic freedom. “He was not dismissed for his views but rather for his conduct towards other members of faculty, staff, and students,” Ricketts wrote. Ricketts said Mehta had been provided access to hundreds of pages of material from both the internal and external reports, as well as a lengthy list of specific reasons supporting the decision to dismiss him.\n\nMehta disputed the university’s account. He said the university gave him “broad and unspecified reasons” and that the reports relied in part on anonymous submissions and lacked methodology. He said he was only offered limited time to review the MacKay and Hooper reports before being fired, and was not allowed to have copies unless he signed an agreement preventing him from distributing confidential information or retaliating against complainants, which he called a “gag order.” Mehta said he never discriminated against or harassed students or colleagues. “I have never done any of the acts that have been attributed to me,” he said. He said “perspectives are subjective” and that the complaints came from a small number of students, while larger numbers of other students thought it was refreshing that he was trying to get them to think critically. He said he offered concessions before being fired: to move offices away from colleagues who were uncomfortable around him, to teach different courses, and not to be Facebook friends with students while they were in his courses, but the university was not interested. Mehta said he had no regrets about his comments, actions, or teaching style. He believed the real reason for his dismissal was a “culture war” taking place in universities, and that he was fired because he spoke out against the university’s new mission of “committing to social justice.” He said the university was using harassment and discrimination policies to suppress his dissent.\n\nSeveral outside voices weighed in. Mercer wrote in the Halifax Chronicle Herald that the three most troubling things about the firing were the secrecy surrounding Acadia’s decision, Acadia’s failure to address properly any valid complaint, and Acadia’s attack on freedom of expression on campus. Peter Wood, writing for the National Association of Scholars, described the firing as “How a Social Justice Mob Fired a Tenured Professor,” arguing that Mehta stood up for disinterested academic standards while Acadia rushed to a “social justice” agenda. In March, the Canadian Association of University Teachers appointed a committee to review how Acadia handled grievances against Mehta to determine whether his academic freedom had been breached or threatened. The Acadia University Faculty Association filed for arbitration, and Mehta said he was going into the arbitration process with resolve because the outcome would have national implications for academic freedom in Canada.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>law - indigenous - said - dean - freedom - report - association - letter - harassment - process</t>
+          <t>law - indigenous - dean - report - association - letter - harassment - process - work - hiring</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>health - freedom - consent - medical - committee - public - records - said - christian - informed</t>
+          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>health - freedom - consent - medical - committee - public - records - said - christian - informed</t>
+          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>health - freedom - consent - medical - committee - public - records - said - christian - informed</t>
+          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'dalhousie', 'control']</t>
+          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'control', 'bargaining']</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>course - notes - agreement - teaching - materials - employer - decision - request - dalhousie - control</t>
+          <t>course - notes - agreement - teaching - materials - employer - decision - request - control - bargaining</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2_health_freedom_consent_medical</t>
+          <t>2_health_consent_medical_committee</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['health', 'freedom', 'consent', 'medical', 'committee', 'public', 'records', 'said', 'christian', 'informed']</t>
+          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>health - freedom - consent - medical - committee - public - records - said - christian - informed</t>
+          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2610,22 +2610,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2656,22 +2656,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3_said_class_duval_lieutenant</t>
+          <t>3_class_gender_complaint_word</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>['said', 'class', 'duval', 'lieutenant', 'lieutenant duval', 'st', 'gender', 'complaint', 'word', 'did']</t>
+          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>said - class - duval - lieutenant - lieutenant duval - st - gender - complaint - word - did</t>
+          <t>class - gender - complaint - word - rights - investigation - views - complaints - 2015 - expression</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2752,22 +2752,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1_said_freedom_comments_letter</t>
+          <t>1_comments_racism_letter_canada</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>['said', 'freedom', 'comments', 'letter', 'racism', 'canada', 'sherman', 'president', 'statement', 'people']</t>
+          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>["On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", "Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>said - freedom - comments - letter - racism - canada - sherman - president - statement - people</t>
+          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'noble', 'grievor', 'caut', 'freedom', 'public', 'applicants']</t>
+          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - noble - grievor - caut - freedom - public - applicants</t>
+          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2845,22 +2845,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_said_dean</t>
+          <t>-1_law_indigenous_dean_report</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'said', 'dean', 'freedom', 'report', 'association', 'letter', 'harassment', 'process']</t>
+          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['Acadia University in Wolfville, Nova Scotia confirmed on September 7, 2018, that Rick Mehta, a tenured associate professor of psychology, had been dismissed. The firing took effect on August 31, 2018, following a formal investigation into complaints against him. Mehta had taught at Acadia for fifteen years, including large required courses such as Introductory Psychology and Research Design and Analysis, and had received teaching awards and positive student evaluations. He was also a self-styled firebrand for “academic free speech” who had stoked a national debate about free expression on campus by making controversial comments on social media and in the classroom.\n\nMehta was outspoken both on campus and online about a range of contentious issues, including decolonization, immigration, gender politics, and the Truth and Reconciliation Commission. He came under fire for saying multiculturalism is a scam, denying the wage gap between men and women, and dismissing the Truth and Reconciliation Commission as a vehicle for “endless apologies and compensation.” On Twitter, he retweeted a post saying it was “statistically impossible for all Native children to have had a negative experience with residential schools.” His defenders called his voice an antidote to political correctness run amok, while critics said his polarizing comments attacked marginalized people and perpetuated harmful stereotypes. The acrimonious debate spurred a Halifax-based activist to launch a petition demanding his removal, while a counter-petition called for him to stay in the classroom as a beacon of freedom of expression.\n\nThe university launched an external three-month investigation overseen by Dalhousie University professor emeritus Wayne MacKay, as well as an internal inquiry conducted by Acadia’s Dean of Science, Jeff Hooper. University spokesman Scott Roberts said he was unable to comment or “provide any elaboration” on the dismissal because it was a confidential personnel matter, and called the MacKay report a “privileged document.” The Acadia University Faculty Association said it was informed of the firing on August 31 and has since filed for arbitration. “The termination of a tenured professor is very serious, and the faculty association has filed for arbitration while its senior grievance officer and legal counsel examine the administration’s disciplinary procedures and evidence,” the association said in a statement. Mehta continued to receive his $112,527 annual salary and benefits pending the outcome of the arbitration.\n\nAn eight-page letter written by Acadia’s Vice-President Academic, Heather Hemming, on August 3, 2018, delivered a detailed review of the school’s grounds for disciplinary action against Mehta. The letter cited eight categories of inappropriate conduct: unprofessional and non-collegial conduct directed at students, faculty, and administration, including creation of a poisoned work environment; breaches of privacy in relation to students and colleagues; creation of a poisoned, intolerant teaching environment, particularly regarding sensitive issues of gender and race; making inappropriate and potentially discriminatory comments towards women and vulnerable groups; personal harassment and bullying of students, faculty and other members of the university community; significant deviations from the academic syllabus and significant use of irrelevant non-academic sources in class, resulting in failure to teach required course material; damaging the reputation of the institution by attacking the university and colleagues on social media; and unwillingness to recognize the harmful effects of actions on students and faculty.\n\nHemming wrote that it was “reprehensible” that Mehta posted to a publicly available Dropbox account a recording of one of his classes in which a student disclosed her rape experience. “This action further demonstrates your disregard for the privacy rights of students and suggests you are more concerned with public online support than the interests of students,” she wrote. The letter also stated that Mehta’s conduct toward students and colleagues created a “poisoned” work and teaching environment and that many members of the psychology department had expressed genuine concern for their safety. It cited an example where Mehta told an Intro to Psychology class that sexual assault survivors are not victims and women are assaulted because they put themselves in dangerous environments. Quoting the MacKay report, Hemming wrote that Mehta made numerous discriminatory or harassing posts on social media. “Indigenous peoples, racialized minorities, women, sexual identity and gender expression, immigrants and multiculturalism are all targets,” she wrote. The letter said a significant amount of class time, in some classes 90 percent or more, was spent on topics irrelevant or not connected to the course syllabus, and that Mehta had failed to deliver the course Acadia contracted him to teach. It also said that concerns, cautions, and counselling about the “harmful effects” of his teaching, interactions, and social media use had been brought to his attention but had fallen on deaf ears. “You seem to be under the impression that your rights of ‘free speech’ and academic freedom trump all other obligations to the university and members of the university community,” Hemming wrote.\n\nIn the letter of dismissal given to Mehta at his dismissal hearing, President Peter Ricketts stated that he was firing Mehta on the basis of issues that “were wide ranging and include failure to fulfill academic responsibilities, unprofessional conduct, breach of privacy, and harassment and intimidation of students and other members of the University community.” After the dismissal, Ricketts responded to a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship, saying the action was not taken in response to Mehta’s legitimate exercise of free speech or academic freedom. “He was not dismissed for his views but rather for his conduct towards other members of faculty, staff, and students,” Ricketts wrote. Ricketts said Mehta had been provided access to hundreds of pages of material from both the internal and external reports, as well as a lengthy list of specific reasons supporting the decision to dismiss him.\n\nMehta disputed the university’s account. He said the university gave him “broad and unspecified reasons” and that the reports relied in part on anonymous submissions and lacked methodology. He said he was only offered limited time to review the MacKay and Hooper reports before being fired, and was not allowed to have copies unless he signed an agreement preventing him from distributing confidential information or retaliating against complainants, which he called a “gag order.” Mehta said he never discriminated against or harassed students or colleagues. “I have never done any of the acts that have been attributed to me,” he said. He said “perspectives are subjective” and that the complaints came from a small number of students, while larger numbers of other students thought it was refreshing that he was trying to get them to think critically. He said he offered concessions before being fired: to move offices away from colleagues who were uncomfortable around him, to teach different courses, and not to be Facebook friends with students while they were in his courses, but the university was not interested. Mehta said he had no regrets about his comments, actions, or teaching style. He believed the real reason for his dismissal was a “culture war” taking place in universities, and that he was fired because he spoke out against the university’s new mission of “committing to social justice.” He said the university was using harassment and discrimination policies to suppress his dissent.\n\nSeveral outside voices weighed in. Mercer wrote in the Halifax Chronicle Herald that the three most troubling things about the firing were the secrecy surrounding Acadia’s decision, Acadia’s failure to address properly any valid complaint, and Acadia’s attack on freedom of expression on campus. Peter Wood, writing for the National Association of Scholars, described the firing as “How a Social Justice Mob Fired a Tenured Professor,” arguing that Mehta stood up for disinterested academic standards while Acadia rushed to a “social justice” agenda. In March, the Canadian Association of University Teachers appointed a committee to review how Acadia handled grievances against Mehta to determine whether his academic freedom had been breached or threatened. The Acadia University Faculty Association filed for arbitration, and Mehta said he was going into the arbitration process with resolve because the outcome would have national implications for academic freedom in Canada.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>law - indigenous - said - dean - freedom - report - association - letter - harassment - process</t>
+          <t>law - indigenous - dean - report - association - letter - harassment - process - work - hiring</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3_said_class_duval_lieutenant</t>
+          <t>3_class_gender_complaint_word</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>['said', 'class', 'duval', 'lieutenant', 'lieutenant duval', 'st', 'gender', 'complaint', 'word', 'did']</t>
+          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>said - class - duval - lieutenant - lieutenant duval - st - gender - complaint - word - did</t>
+          <t>class - gender - complaint - word - rights - investigation - views - complaints - 2015 - expression</t>
         </is>
       </c>
       <c r="G48" t="n">

--- a/Summary_Analysis/single_BERTopic_results_AI_summary.xlsx
+++ b/Summary_Analysis/single_BERTopic_results_AI_summary.xlsx
@@ -449,21 +449,21 @@
         <v>-1</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_dean_report</t>
+          <t>-1_law_indigenous_september_rights</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
+          <t>['law', 'indigenous', 'september', 'rights', 'work', 'harassment', 'dean', 'hiring', 'law school', 'process']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.']</t>
         </is>
       </c>
     </row>
@@ -472,21 +472,21 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0_committee_president_board_hall</t>
+          <t>0_letter_comments_expression_wrote</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
+          <t>['letter', 'comments', 'expression', 'wrote', 'saying', 'views', 'social', 'statement', 'racism', 'class']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['The grievor, Chad Thompson, had been employed as an Assistant Professor at University College of the North (UCN) for approximately two years when he was terminated in August 2011 for insubordination, insolence and defiant behaviour in the context of his involvement on a search committee. The termination occurred following his role as Chair of the Selection Board for Competition No. 3145, a search to fill a full-time, regular Social Science Instructor position in the Faculty of Arts and Sciences. The grievor held a full-time tenure track position within the bargaining unit represented by the Manitoba Government and General Employees\' Union.\n\nNorma Baker, the grievor\'s spouse and Dean of the Faculty of Arts and Sciences, was initially involved in preparing the posting and reviewing applications, but then went on sick leave. Because of concern about delay, the Vice-President - Academic, Kathryn McNaughton, requested that the grievor chair the search committee. The committee shortlisted two candidates, Aaron Crowe and Jason Hildebrandt. Crowe was interviewed, while Hildebrandt was unavailable due to an injury. The search committee unanimously endorsed Crowe, pending reference checks. Although UCN policy provided that Human Resources would check references, there was discussion by the committee and it was decided that Baker, as an academic, should conduct the reference checks, with the input of Human Resources committee member Linda Hunt. Baker did conduct the reference checks of Crowe. Linda Hunt prepared the Selection Board Report and submitted it to Interim President Konrad Jonasson with the committee\'s recommendation to hire Crowe.\n\nBy e-mail of July 14, 2011, Jonasson refused to approve the recommendation. He raised concerns including an appearance of conflict of interest by having both Baker and the grievor involved, questions about the second candidate\'s inability to interview, the educational qualifications of the recommended candidate, and whether information regarding the candidate\'s PhD program was current. Jonasson offered two options: consider the search failed and start anew, or go back and review all candidates to determine if any of the three not granted interviews should be interviewed and whether the second candidate remained interested. The e-mail concluded that if the other three did not merit an interview and candidate 2 could not go forward, the search should be declared failed and restarted. Baker, the grievor, committee member Sandra Barber, and McNaughton interpreted this e-mail as a declaration of failed search. Jonasson testified that it was designed to indicate concerns and solicit additional information, and that he did not declare a failed search until a subsequent e-mail on July 15.\n\nOn July 15, 2011 at 8:54 a.m., the grievor directed an e-mail to Linda Hunt stating that he would not be submitting his notes and ratings for the LTF hiring process, that given the actions of the Interim President regarding competition 3145 he had no confidence that Mr. Jonasson would respect the policies and procedures of HR, and that he was unwilling to participate any further in this or any other hiring committee until he regained confidence in the process. The e-mail was copied to the head of Human Resources and to McNaughton, but not to Jonasson. The grievor testified that he was not attempting to hide anything, that he felt it was part of his role to speak out where he believed the governance of the institution to be in error, and that he did not regret sending the message, although he wished he had worded it more carefully.\n\nAt 9:14 a.m. on July 15, approximately twenty minutes after the e-mail to Hunt, the grievor sent an e-mail directly to Aaron Crowe, advising him that, as Chair of the Selection Committee, he was writing with deepest regret to inform him of the decision by Interim President Mr. Konrad Jonasson to reject the unanimous recommendation of the Selection Committee to offer him the position. The e-mail suggested that Crowe might wish to speak with Human Resources regarding UCN policy HR-03-0 and with MGEU regarding Article 11:04 in the collective agreement, and was copied to the Manager of Human Resources and two Union staff representatives, including Nelson. Jonasson considered this a violation of protocol and a breach of confidentiality of the selection process. The grievor acknowledged he was angry, that he felt Jonasson\'s decision was not just, that sending the e-mail was a "very stupid thing to do," and that he regretted having done so. Crowe, an internal candidate, subsequently grieved the failure to award him the position.\n\nBy letter of August 10, 2011, Jonasson issued Baker a disciplinary reprimand for various misconduct, including her involvement on the search committee, her involvement in contacting references, and her e-mail of July 15. Baker was out of scope and not in a position to grieve that discipline; she subsequently resigned her position with UCN. Jonasson met with the grievor and Union representative Nelson on July 27, 2011 to review concerns. There was an issue as to whether the grievor offered regret or an apology; Jonasson had no recollection of an apology, while the grievor believed he showed regret and offered an apology, and Nelson testified that the grievor apologized at least twice or perhaps three times. Subsequent to that meeting, the grievor\'s position was terminated by letter of August 17, 2011.\n\nThe letter of termination stated that the grievor\'s actions relating to competition no. 3145 were in fundamental breach of his employment obligations. It cited three reasons: first, without the knowledge or approval of Human Resources, he allowed Baker to continue to participate on the Selection Board after she withdrew and allowed her to contact references on behalf of UCN, which was a significant breach of trust and a clear breach of policy; second, the grievor made insolent allegations against the Interim President in his e-mail to Hunt, stating he had no confidence that Jonasson would respect HR policies and procedures; and third, the grievor violated UCN policy by sending an e-mail directly to the recommended candidate advising him of the rejection, copying representatives of the MGEU Union who were not employees of UCN, and highlighting sections of the Collective Agreement for the unsuccessful applicant. The letter asserted that the grievor\'s conduct was clearly intended to undermine the authority of the Interim President.\n\nThe Employer argued that the grievor was a short term employee who had been insubordinate, insolent and defiant without justification, that his evidence was misleading in an attempt to minimize what he had done, and that the e-mails were inappropriate and sent without justification. The Employer submitted that this was extreme insubordination striking at the heart of the employment relationship, that none of the normal factors of mitigation were present, and that dismissal was the appropriate response. The Employer noted that the grievor had not demonstrated exceptional financial hardship other than what one would normally anticipate from a termination, and argued that even if academic freedom were engaged, it was not used responsibly.\n\nThe Union asserted that while there was conduct deserving of discipline, there had been no progressive discipline and termination was simply too severe. The Union pointed out that the grievor had an unblemished record, that Jonasson acknowledged he had not looked at the grievor\'s prior clear record, and that another individual, Baker, had received only a written reprimand for similar conduct, demonstrating inconsistency in the application of discipline. The Union argued that the e-mail to Crowe was written in the heat of the moment, that the grievor accepted responsibility for his actions, that the reference checks were done with the involvement of Human Resources, and that the e-mail to Hunt was an expression of concern over the hiring process, related to the service component of his role and potentially within academic freedom under Article 72 of the Collective Agreement. The Union requested reinstatement and compensation, with a letter of reprimand as the appropriate discipline.\n\nThe arbitrator, R.A. Simpson, found that while the grievor\'s conduct was insubordinate and warranted discipline, termination was not justified. The arbitrator noted that although the grievor was entitled to consider the July 14 e-mail equivalent to a declaration of failed search, that did not excuse his subsequent conduct. The e-mail to Hunt, containing comments about the Interim President\'s respect for HR policies, had a degree of insolence amounting to insubordination and was not within the service component of the grievor\'s role or within the parameters of academic freedom, but considered in isolation, it could have been dealt with through perhaps a verbal or at most a written reprimand. The e-mail to Crowe was clearly insubordinate, involving a breach of confidentiality, disclosure of confidential information, an invitation to challenge the Employer\'s decision, and a defiance of and challenge to the Employer\'s authority. However, the arbitrator was not satisfied that the employment relationship was irreparably harmed or could not be successfully rehabilitated. The grievor was not a long term employee, but his record over two years was without blemish, he was not challenged on his evidence as to exceptional services he had provided, and dismissal would have a significant adverse effect upon his career. There was no evidence that progressive discipline short of termination was considered. The arbitrator accepted the Employer\'s argument that there was a significant difference between Baker\'s situation and the grievor\'s, with Baker communicating with colleagues and advocating for faculty and students, as opposed to the grievor communicating with an unsuccessful candidate and disclosing confidential information. Nevertheless, a lesser discipline could well have been sufficient to rehabilitate the employment relationship. The arbitrator substituted a two-month suspension without pay for the termination, stating that this was a significant penalty that should send a message that such behaviour would not be tolerated. The grievance was allowed, the termination rescinded, and a two-month suspension without pay substituted.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
         </is>
       </c>
     </row>
@@ -495,21 +495,21 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1_comments_racism_letter_canada</t>
+          <t>1_committee_president_board_public</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
+          <t>['committee', 'president', 'board', 'public', 'caut', 'applicants', 'hall', 'grievor', 'school', 'search']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>['Between March 2011 and July 2012, the University of Calgary (U of C) worked to secure a sponsorship from Enbridge, a Calgary-based oil and gas pipeline company, to establish a research institute at the Haskayne School of Business (HSB). Dr. Joe Arvai, a recently appointed faculty member, was asked to be director of what became the Enbridge Centre for Corporate Sustainability (ECCS). The sponsorship agreement, dated July 1, 2011, was between Enbridge and “The Governors of the University of Calgary,” committing $225,000 annually over ten years. However, planned activities were based on an annual budget of $500,000, more than double Enbridge’s financial outlay, creating an immediate funding shortfall that was supposed to be made up by additional corporate fundraising.\n\nDuring the establishment and launch of the ECCS, Arvai repeatedly raised concerns about Enbridge’s influence over the Centre’s academic mission. Emails disclosed through freedom of information requests showed that Enbridge exerted influence over the Centre’s name, the selection of partner institutions, the planning of the public launch, and the role of the director. Enbridge pressed for Central Michigan University (CMU) as a partner, in part because CMU had given Enbridge "very valuable advice" after the 2010 Kalamazoo River oil spill in Michigan; Arvai objected on academic grounds, saying CMU had only one faculty member in the relevant field, but was pressured to accept. HSB Dean Len Waverman told Arvai that “the monies we give to CMU are tiny – it won’t be viewed as a payoff,” and that “Elizabeth [Cannon] will have a fit if she sees this.” Enbridge also expressed concerns about Arvai’s appointment to a U.S. Environmental Protection Agency (EPA) Scientific Advisory Board, and the university delayed its announcement of that appointment so as not to “piss off Enbridge any more.” Arvai stated that “we cannot maintain our credibility as serious scholars/researchers if the sponsors can dictate the Centre’s agenda,” and that he could not serve as director if sponsors were allowed to meddle in academic activities.\n\nArvai was removed as ECCS director in March 2012. He later told the CAUT committee that he was removed one week after he informed Enbridge’s public relations firm, National Public Relations, of his opposition on scientific grounds to the Northern Gateway pipeline. In an email of March 19, 2012, Dean Waverman told Enbridge officials: “Joe Arvai is no longer Director of the Centre, there are too many conflicts and demands!” Arvai subsequently left the U of C and is now at the University of Michigan.\n\nA CBC News investigation in November 2015 prompted the Canadian Association of University Teachers (CAUT) to establish an Ad Hoc Investigatory Committee. In his first public statement, an opinion piece reprinted by CBC News, Arvai said the CBC had done “an exceptional job of getting the facts correct,” and that the post hoc suggestions that decisions setting up the Enbridge Centre were “transparent, legitimate, and free of corporate interference or conflict-of-interest” were as difficult for him to accept as they were in 2012. He said donors should be able to suggest, but not select, advisory individuals, and should have a voice in a centre’s name and mission, but should not require that support be limited to those sharing their “core values.”\n\nThe CAUT report, released in October 2017, made findings on conflict of interest, academic freedom, external influence, funding, governance, and the McMahon review. It found a “clear appearance of a conflict of interest” on the part of U of C President Elizabeth Cannon, who served on the Enbridge Income Fund Holdings Board for significant remuneration while president, and who failed to publicly recuse herself from Enbridge-related matters. The report found that Cannon intervened directly with Dean Waverman, telling him that Enbridge was “not very happy,” that she wanted a good relationship with Enbridge, and emphasizing “I am on one of their Boards!” The report also found that the U of C Board of Governors failed to review or approve the sponsorship agreement, despite being a party to it, and that Cannon’s reliance on an “administrative lapse” was an “unacceptable evasion of responsibility.”\n\nThe CAUT committee concluded that Dr. Arvai’s academic freedom was compromised as a result of the U of C’s mishandling of the Enbridge Centre, appearing to be due to a desire on the part of senior leadership to please a significant donor. It found that Enbridge sought to influence the Centre’s establishment and launch, and that university administrators failed to convey that this influence was inappropriate. The report found that Enbridge was given special access to academic staff, was allowed to recommend partners, and had extensive influence over the public launch. The committee found Arvai’s explanation for his departure credible and troubling. It also found that the sponsorship was “skewed in Enbridge’s favour” from the start, with unfunded promises made at the university’s risk and expense, creating a “cycle of dependency” and pressures to compromise academic integrity. It identified a “significant failure of collegial governance, accountability and oversight,” and warned of “worrying signs of a culture of silencing and reprisal at the U of C.”\n\nThe CAUT report was highly critical of the university’s own review, led by retired Justice Terrence McMahon. The Board of Governors had commissioned the McMahon review in November 2015; McMahon found no wrongdoing and cleared university officials, including President Cannon, and the board considered the matter closed. The CAUT committee, however, stated that it was misleading to describe the McMahon review as “independent” and “transparent,” because it was established, mandated, and staffed by the Board or its counsel, and because it did not acknowledge or discuss the central role of academic freedom. The committee said McMahon gave the benefit of the doubt to senior officials while subjecting Arvai and Waverman to damaging criticism, and that the review’s selective approach to confidentiality was inconsistent with fairness and thoroughness. The CAUT report made recommendations including prohibiting university presidents and senior officials from serving for remuneration on external corporate boards, reviewing Board governance, and releasing all documents provided to the McMahon review.\n\nFollowing the CAUT report, the University of Calgary Faculty Association, chaired by Sandra Hoenle, called on the provincial government to probe governance at the university. Hoenle wrote that one of the greatest concerns was “the domination of the senior administration in the governance processes,” and that the Board of Governors and Senior Administration had misapplied “for-profit corporate structures within a university collegial setting,” keeping decision-making behind closed doors. She said, “We’re not a corporation. Universities are not corporations.” Arvai welcomed the CAUT report and said it was “wholly appropriate for the faculty association to be asking for a provincial review.” Alberta’s Ministry of Advanced Education stated that conflict of interest was being examined at public boards, including academic freedom, through a review of agencies, boards, and commissions, and that “Academic freedom is a cornerstone of any university.” Hoenle said the provincial governance review had been truncated and should be expanded to specifically deal with issues identified in the CAUT and CBC investigations.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.']</t>
         </is>
       </c>
     </row>
@@ -518,21 +518,21 @@
         <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2_health_consent_medical_committee</t>
+          <t>2_report_clinical_records_committee</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
+          <t>['report', 'clinical', 'records', 'committee', 'consent', 'health', 'confidentiality', 'patients', 'medical', 'information']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['A prolonged and acrimonious dispute in Toronto involving internationally acclaimed blood researcher Dr. Nancy Olivieri, the Hospital for Sick Children (HSC), the University of Toronto, and the pharmaceutical manufacturer Apotex Inc. was resolved in a face-saving compromise in late January 1999, after earlier events had ignited a controversy over research ethics, patient safety, and academic freedom.\n\nThe dispute centred on clinical trials of deferiprone (L1), an experimental orally active iron-chelating agent being tested as an alternative to the standard but onerous deferoxamine (DFO) therapy for patients with thalassemia major, a transfusion-dependent blood disorder causing progressive iron loading of major organs. Dr. Olivieri, a specialist in hematology and internal medicine, was principal investigator of two Toronto trials: LA-03, a long-term efficacy and safety study, and LA-01, a randomized comparison trial versus DFO, co-sponsored by the Medical Research Council and Apotex. In 1996, Dr. Olivieri identified an unexpected risk in the LA-03 data: loss of sustained efficacy of L1 in a substantial proportion of patients, with hepatic iron concentrations (HIC) stabilizing or rising into ranges associated with iron-induced complications. Apotex disputed her interpretation and opposed informing patients. When HSC\'s Research Ethics Board (REB) directed Dr. Olivieri to revise patient information and consent forms to disclose this risk, Apotex abruptly terminated both Toronto trials on May 24, 1996, withdrew its drug from the hospital pharmacy, and issued legal warnings threatening legal action if she communicated the risk to patients, regulators, or the scientific community.\n\nFollowing the trial terminations, Dean Arnold Aberman of the University of Toronto\'s Faculty of Medicine mediated a new arrangement under Health Canada\'s Emergency Drug Release (EDR) program. Patients who had been in the former trial cohorts and wished to continue on L1 and were still considered to be benefiting could do so as patients under Dr. Olivieri\'s care, provided they were fully informed of the newly identified risk, accepted it, and agreed to monitoring tests including annual liver biopsy. The REB had no jurisdiction over this non-trial EDR treatment arrangement, and Dr. Olivieri, as "the practitioner" under EDR regulations, had reporting obligations only to patients, Apotex, and the Health Protection Branch. She nonetheless informed the REB that the trials had been terminated, and she later reported the loss-of-efficacy finding directly to the regulators despite continued legal warnings from Apotex.\n\nIn early February 1997, Dr. Olivieri and her collaborators, liver pathologist Dr. Ross Cameron and Dr. Gary Brittenham, identified a second, more serious unexpected risk through review of serial liver biopsy slides: progression of liver fibrosis in some patients, making L1 the probable cause of a "severe adverse reaction." She informed patients immediately, counselled them to interrupt use of the drug, and transferred them back to standard therapy in a timely and orderly fashion. She also informed Apotex and the federal regulators, sending her report to the FDA, HPB, and the health ministries of Italy and India. Apotex responded with further legal warnings, and Dr. Hugh O\'Brodovich, HSC\'s Pediatrician-in-Chief, intervened on February 19, 1997, questioning whether Dr. Olivieri had failed in an obligation to report the risk to the REB and to her department chief. Dr. Aideen Moore, the REB Chair, provided incorrect information suggesting that a research trial of L1 continued after May 1996, although both trials had in fact been terminated and patients were under EDR. Subsequent investigations determined that Dr. Olivieri had no obligation to report to the REB in these circumstances and that she had acted "in the best interests of her patients."\n\nThe controversy became public in August 1998 after Dr. Olivieri published her findings on loss of efficacy and toxicity in the New England Journal of Medicine. In September 1998, the HSC Board of Trustees unilaterally established a review conducted by Dr. Arnold Naimark. The Naimark Report, released December 9, 1998, incorrectly concluded that Dr. Olivieri had failed to report her concerns about L1 toxicity to the REB in a timely fashion. On the same day, the HSC Board directed its Medical Advisory Committee (MAC) to inquire into her conduct. On January 6, 1999, HSC removed Dr. Olivieri from her position as director of the hemoglobinopathy program without due process and issued "gag orders" to her and three supporters, Drs. Helen Chan, Peter Durie, and Brenda Gallie, restricting communication with the media. These actions prompted interventions by the Canadian Association of University Teachers (CAUT), the University of Toronto Faculty Association (UTFA), leading scientists Sir David Weatherall and Dr. David Nathan, and University President Robert Prichard. A marathon negotiating session on January 25, 1999 produced a settlement that restored Dr. Olivieri\'s full responsibility and authority over clinical care and research in hemoglobinopathies, withdrew the gag orders, changed her reporting relationships, and provided her with legal indemnification of $150,000 and coverage for potential legal action by Apotex.\n\nThe Medical Advisory Committee, using undisclosed allegations and testimony, principally from Dr. Gideon Koren, Dr. Olivieri\'s former co-investigator, and Dr. O\'Brodovich, referred a series of "concerns" about her conduct to the College of Physicians and Surgeons of Ontario (CPSO) and the University of Toronto in April 2000. Dr. Koren was later disciplined by HSC and the University on April 11, 2000 for "gross misconduct," including persistently lying about his authorship of anonymous letters disparaging Dr. Olivieri and her supporters; he admitted responsibility only after being identified by DNA evidence. The Health Professions Appeal and Review Board subsequently found that Dr. Koren\'s anonymous letter-writing campaign constituted "serious professional misconduct" and directed that the matter be referred to the CPSO Discipline Committee.\n\nIn October 2001, the independent CAUT Committee of Inquiry, chaired by Jon Thompson with Patricia Baird and Jocelyn Downie, published a detailed report exonerating Dr. Olivieri, faulting Apotex for attempting to suppress information on risks and to discredit her, faulting HSC and the University for failing to protect her academic freedom, and criticizing the Naimark Review and MAC proceedings for relying on incorrect and false information. On December 19, 2001, the CPSO Complaints Committee, assisted by an independent expert panel, concluded that "no further action is warranted against Dr. Olivieri," finding she did not fall below a reasonable standard of care in continuing to administer L1, in ordering liver biopsies, or in communicating with her department chief. The Committee specifically found her judgment in advising patients to undergo biopsies "not only reasonable, but commendable in the circumstances." On January 7, 2002, Dean David Naylor of the University of Toronto\'s Faculty of Medicine dismissed all related allegations, including the claim that Dr. Olivieri should have reported her conclusions on L1 toxicity to the REB.\n\nThe case was ultimately recognized for its impact on a critically important issue: the growing dependence of researchers, universities, and hospitals on corporate research funding and the need for policy safeguards to ensure that sponsors cannot restrict communication of identified risks, that confidentiality clauses in research contracts are not used to suppress findings of risk, and that research ethics boards, universities, and hospitals act robustly to defend academic freedom and the safety of trial participants and patients.', 'The Canadian Association of University Teachers (CAUT) established an Independent Committee of Inquiry, chaired by Professor Trudo Lemmens, with Dr. Thomas A. Ban and Dr. Louis C. Charland, to investigate the seizure of research records from the offices of Dr. Anne Duffy at the Institute of Mental Health Research (IMHR) in Ottawa on March 22, 2005. The Committee was mandated to investigate the sequence of events leading to and following the seizure, the institutional relationships between the University of Ottawa, the IMHR, and the Royal Ottawa Hospital (ROH), whether breaches of institutional responsibility or research ethics standards occurred, the impact on academic freedom and integrity, the impact on researchers, research subjects and institutions, and to make recommendations to prevent recurrence. The final report was submitted in March 2013 after delays caused by court proceedings and health issues.\n\nThe events began on March 11, 2005, when Dr. Duffy’s research coordinator told Sharyn Szick, Administrative Director of the IMHR, that a research assistant was scanning clinical charts and inserting printed copies into research records, and that informed consent forms were missing from some research records or had been signed after study initiation and backdated. Ms. Szick reported this to Dr. Zul Merali, President and CEO of the IMHR. On March 22, 2005, after a meeting attended by Ms. Szick, Dr. Keith Busby, Suzan Crozier, Carolyn Belzile, and Sharon Purvis, the decision was made to remove clinical charts from Dr. Duffy’s office and chart room. Dr. Paul Dagg, Director of Clinical Services, and Mr. Bruce Swan, CEO of the Royal Ottawa Health Care Group (ROHCG), authorized the removal of clinical charts based on allegations that clinical charts had been scanned and downloaded to hospital network drives, contrary to ROH policy and the Personal Health Information Protection Act (PHIPA). Once the clinical charts were relocated, Dr. Busby, at Dr. Merali’s request, conducted a “spot check” of approximately 20 research binders and reported that about five lacked consent forms behind the tab marked “consent.” Dr. Merali then ordered the immediate transfer of the research records of the bipolar team to a “secure location” at the ROH. Neither Dr. Duffy nor any member of her research team was present. Dr. Duffy learned of the removal the next morning from a note on her door.\n\nThe seized material included clinical charts, research records, personal files, and computer discs. According to Drs. Duffy and Grof, the records concerned more than 2,000 research subjects, including current and former patients and controls from Ontario and Nova Scotia. The records included studies conducted by Drs. Alda, Grof, and Duffy, involving long-term follow-up of families with bipolar disorder. The ROHCG Research Ethics Board (REB), chaired by Dr. Alan B. Douglass, was not consulted in advance, had received no complaint, and had not authorized the removal. Dr. Dagg’s investigation concluded on April 13, 2005 that no serious breaches of privacy with clinical charts had occurred, though he apologized for the removal.\n\nDrs. Duffy and Grof retained legal counsel on March 23, 2005, and commenced court proceedings for the return of the research records. They also filed a complaint with the Information and Privacy Commissioner of Ontario. On April 15, 2005, proceedings were adjourned and on April 18, 2005 an agreement was reached: the research records would be copied, originals returned, copies turned over to the REB without review, Dr. Merali would outline concerns, and the REB would appoint an independent reviewer. However, Dr. Duffy learned that Dr. Busby had already reviewed some records, contrary to her understanding of the agreement. Dr. Duffy then informed research subjects by e-mail that IMHR personnel had accessed personal information. The Information and Privacy Commissioner’s investigation was put on hold after objections from Dr. Duffy’s lawyers.\n\nIn May 2005, Drs. Duffy and Grof contacted CAUT, which established the Independent Committee of Inquiry. Committee interviews began in late summer 2005. Most institutional officials declined to participate on legal advice. A settlement was reached on October 19, 2005, which allowed Dr. Douglass to invite Dr. Padraig Darby, Chair of the REB of the Centre for Addiction and Mental Health, to review copies of the research records. Dr. Darby’s report, submitted November 10, 2006, found that only one of six studies had REB approval and that informed consent forms were missing from 77 of 252 records (30.5%). It was later clarified that all studies had approval letters on file that had not been provided to Dr. Darby. Drs. Duffy and Grof disputed the findings, reporting that only 11% of records lacked consent forms based on their review of the originals, and suggested that a former research assistant had failed to add consent forms to files. The Darby Report led to a second round of litigation, which ended in 2008 when the Canadian Medical Protective Association declined further funding and Drs. Duffy and Grof agreed to pay the other party’s legal costs.\n\nThe Committee’s own review of the original research records found that some consent forms identified as missing by Dr. Darby were present in the originals, and that new signed consent forms were present in records where originals were absent. Interviews with research subjects and parents of subjects whose original consent forms were missing showed that all were fully aware that they or their children were participating in Dr. Duffy’s research, understood the nature and purpose of the research, and had strong confidence in Dr. Duffy’s integrity.\n\nThe Committee concluded that the seizure of research records was in violation of research ethics standards. It emphasized a key distinction between informed consent obtained to protect research subjects from physical or psychological harm, and informed consent obtained to protect the privacy of research subjects and the confidentiality of sensitive health information. In the studies at issue, the consent forms represented a pledge by researchers to protect confidentiality. Seizing records in response to allegations of missing consent forms therefore violated the very essence of the informed consent. The “spot check” conducted by Dr. Busby was not a proper audit, as it lacked advance notice, defined objectives, scope, and researcher involvement, and was not carried out by the REB. The Committee found that the seizure was a disproportionate response, contrary to the principle of “proportionate review” under the Tri-Council Policy Statement (TCPS), and that institutional officials breached their responsibility by prioritizing the establishment of alleged wrongdoing over the protection of research subject privacy. The Committee attributed the seizure to ongoing tensions between Drs. Duffy and Grof and Drs. Merali and Bradwejn, and to the confounding of informed consent for privacy protection with informed consent for protection from harm.\n\nThe Committee’s recommendations included: clarifying that research records are in principle the property of the researcher; clearly defining the position of self-funded research teams and renegotiating responsibilities regularly; identifying for each research project whether informed consent is for protection from harm or for privacy and confidentiality; clarifying institutional responsibilities so that the REB that approved a project, not other institutional officials, ensures adherence to research ethics standards; and ensuring that seizure of research records is only a last resort when there is an immediate and serious threat to the wellbeing of research subjects, with procedures designed to respect the privacy and confidentiality of health information.', '# Summary: Suspension and Termination of Dr. Francis Christian\n\nDr. Francis Christian, a clinical professor of general surgery at the University of Saskatchewan (USask) and a practicing surgeon in Saskatoon with more than 20 years of experience, was suspended and terminated from his positions after publicly raising concerns about COVID-19 vaccination of children. As of June 2021, Christian served as Director of the Surgical Humanities Program (which he co-founded), Director of Quality and Patient Safety in the Department of Surgery, and Editor of the Journal of the Surgical Humanities. His roles overlapped with a contract position with the Saskatchewan Health Authority (SHA).\n\nOn June 17, 2021, Christian released a prepared statement to over 200 doctors and spoke at a press conference outside Walter Murray Collegiate in Saskatoon, appearing with a group called Concerned Parents Saskatchewan while a vaccine clinic was taking place at the high school. He declined to take questions from journalists. In his statement, Christian emphasized that he is a "very pro-vaccine physician" and is "pro-vaccine for my own family, including myself," citing the elimination of smallpox through vaccination. He stated he spoke "directly to parents and children" as "a physician, a surgeon and a fellow human being" and did not represent any group, the SHA, or the university.\n\nChristian invoked the "sacrosanct principle" of informed consent, arguing that patients must be made "fully aware of the risks of the medical intervention, the benefits of the intervention and if any alternatives exist to the intervention," particularly for "a new vaccine that has never before been tried in humans." He asserted this principle was "being consistently violated in this province for the m-RNA vaccine for our kids," claiming he had not met "a single vaccinated child or parent who has been adequately informed."\n\nChristian articulated eight points he argued parents and children must know before consenting: (1) that the mRNA vaccine is "a new, experimental vaccine design" never used in humans; (2) that the vaccines have not been fully authorized by Health Canada or the CDC, being under "interim authorization" in Canada and "emergency use authorization" in the US; (3) that while there is an emergency for the elderly, vulnerable, and health care workers—given that the mean age of COVID-19 deaths in Canada is 83.8—"Covid-19 does not pose a threat to our kids," with a death risk of less than 0.003%; (4) that children do not readily transmit the virus to adults; (5) that the mRNA vaccines have been "associated with several thousand deaths" in the US government\'s Vaccine Adverse Reporting System, which he called "a strong signal" that could not be ignored; (6) that there is a "real and significantly increased risk" of myocarditis (heart inflammation) in vaccinated children, leading the German national vaccine agency and the UK vaccine agency to not recommend the vaccine for healthy children; (7) that the benefit of the vaccine for children is "marginal at best," with an Absolute Risk Reduction of less than 2%; and (8) that Ivermectin is an alternative treatment. He urged authorities "to call a pause in the m-RNA vaccine roll-out to our kids" and stated that without informed consent, "the Nuremberg code is being violated." He also appeared in a video posted to the website BitChute that received nearly 70,000 views, in which he questioned the mainstream narrative about the pandemic, mocked restrictions, and called the vaccines "experimental injections."\n\nOn June 21, 2021, the Saskatchewan Health Authority and the College of Medicine wrote to Christian alleging they had "received information that you are engaging in activities designed to discourage and prevent children and adolescents from receiving Covid-19 vaccination contrary to the recommendations and pandemic-response efforts of Saskatchewan and Canadian public health authorities."\n\nOn June 23, 2021, Christian was called into a meeting with Dr. Preston Smith, Dean of the College of Medicine; Dr. Susan Shaw, Chief Medical Officer of the Saskatchewan Health Authority; and Dr. Brian Ulmer, Head of the Department of Surgery. He was informed of his immediate suspension from all faculty responsibilities and academic administrative roles, and that he would be fired from the university as of September 2021. The SHA terminated its contract with Christian, which was set to expire on September 21 following the required 90 days\' notice. Christian remained able to practice medicine and the university said it was not suspending payment for services he would have otherwise received during the investigation period. Christian recorded the 22-minute meeting and posted the audio online.\n\nDuring the meeting, Christian said, "You\'ve basically read indictments against me. These are the sort of panels that were set up in the Soviet Union and Nazi Germany against academics," adding, "I\'m not saying that you\'re Nazis or Soviets, but it\'s really disturbing, isn\'t it?" He stated he was one of many doctors being "silenced and censored," and told the officials, "You guys are living in a dystopian bubble. The truth will come out and when that bubble bursts, you guys are going to be in big trouble." Shaw expressed concern that Christian was "a highly intelligent man" who was "not making intelligent decisions," and Christian was offered supports if he was feeling distressed, which he declined.\n\nIn a statement, Dean Smith said the University "encourages public debate of important societal issues," but noted that per USask\'s Medical Faculty Policy, "our medical faculty are subject to the ethical and professional standards governing the practice of medicine." Smith told Global News that "when somebody is saying things that are at such great variance with all of our experts and worldwide experts and public safety is involved and could be jeopardized through these differences of view, I think we have to recognize that that\'s a special situation that requires urgent and extraordinary action." The SHA stated that "health system leaders are expected to be committed to fact-based, scientifically driven public messaging" and that leaders who depart "in favour of conspiracy theories put lives at risk by potentially discouraging uptake on life-saving vaccines."\n\nThe Justice Centre for Constitutional Freedoms announced it was representing Christian in his appeals and before the College of Physicians and Surgeons of Saskatchewan, against a complaint objecting to his advocacy for informed consent. Litigation Director Jay Cameron said the termination was "a violation of his charter-protected right to freedom of thought, belief, opinion and expression, and a betrayal of the principles of scientific inquiry," and described "a clear pattern of highly competent and skilled medical doctors in very esteemed positions being taken down and censored or even fired, for practicing proper science and medicine." The Justice Centre also drew comparisons to its representation of Dr. Chris Milburn in Nova Scotia, who faced disciplinary proceedings over an opinion column.\n\nOn June 30, 2021, the Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Dean Smith requesting an explanation of "how Dr Christian\'s suspension is not a violation of his academic freedom and how his suspension will not tend to create a chilly climate for expression on campus." SAFS argued that "nothing that has been reported should draw any discipline at all" and that "academic freedom protects his rights to have them and to express them publicly," noting the importance of professors being "free to question received wisdom and official policy" during a pandemic.']</t>
+          <t>['A prolonged and acrimonious dispute in Toronto involving internationally acclaimed blood researcher Dr. Nancy Olivieri, the Hospital for Sick Children (HSC), the University of Toronto, and the pharmaceutical manufacturer Apotex Inc. was resolved in a face-saving compromise in late January 1999, after earlier events had ignited a controversy over research ethics, patient safety, and academic freedom.\n\nThe dispute centred on clinical trials of deferiprone (L1), an experimental orally active iron-chelating agent being tested as an alternative to the standard but onerous deferoxamine (DFO) therapy for patients with thalassemia major, a transfusion-dependent blood disorder causing progressive iron loading of major organs. Dr. Olivieri, a specialist in hematology and internal medicine, was principal investigator of two Toronto trials: LA-03, a long-term efficacy and safety study, and LA-01, a randomized comparison trial versus DFO, co-sponsored by the Medical Research Council and Apotex. In 1996, Dr. Olivieri identified an unexpected risk in the LA-03 data: loss of sustained efficacy of L1 in a substantial proportion of patients, with hepatic iron concentrations (HIC) stabilizing or rising into ranges associated with iron-induced complications. Apotex disputed her interpretation and opposed informing patients. When HSC\'s Research Ethics Board (REB) directed Dr. Olivieri to revise patient information and consent forms to disclose this risk, Apotex abruptly terminated both Toronto trials on May 24, 1996, withdrew its drug from the hospital pharmacy, and issued legal warnings threatening legal action if she communicated the risk to patients, regulators, or the scientific community.\n\nFollowing the trial terminations, Dean Arnold Aberman of the University of Toronto\'s Faculty of Medicine mediated a new arrangement under Health Canada\'s Emergency Drug Release (EDR) program. Patients who had been in the former trial cohorts and wished to continue on L1 and were still considered to be benefiting could do so as patients under Dr. Olivieri\'s care, provided they were fully informed of the newly identified risk, accepted it, and agreed to monitoring tests including annual liver biopsy. The REB had no jurisdiction over this non-trial EDR treatment arrangement, and Dr. Olivieri, as "the practitioner" under EDR regulations, had reporting obligations only to patients, Apotex, and the Health Protection Branch. She nonetheless informed the REB that the trials had been terminated, and she later reported the loss-of-efficacy finding directly to the regulators despite continued legal warnings from Apotex.\n\nIn early February 1997, Dr. Olivieri and her collaborators, liver pathologist Dr. Ross Cameron and Dr. Gary Brittenham, identified a second, more serious unexpected risk through review of serial liver biopsy slides: progression of liver fibrosis in some patients, making L1 the probable cause of a "severe adverse reaction." She informed patients immediately, counselled them to interrupt use of the drug, and transferred them back to standard therapy in a timely and orderly fashion. She also informed Apotex and the federal regulators, sending her report to the FDA, HPB, and the health ministries of Italy and India. Apotex responded with further legal warnings, and Dr. Hugh O\'Brodovich, HSC\'s Pediatrician-in-Chief, intervened on February 19, 1997, questioning whether Dr. Olivieri had failed in an obligation to report the risk to the REB and to her department chief. Dr. Aideen Moore, the REB Chair, provided incorrect information suggesting that a research trial of L1 continued after May 1996, although both trials had in fact been terminated and patients were under EDR. Subsequent investigations determined that Dr. Olivieri had no obligation to report to the REB in these circumstances and that she had acted "in the best interests of her patients."\n\nThe controversy became public in August 1998 after Dr. Olivieri published her findings on loss of efficacy and toxicity in the New England Journal of Medicine. In September 1998, the HSC Board of Trustees unilaterally established a review conducted by Dr. Arnold Naimark. The Naimark Report, released December 9, 1998, incorrectly concluded that Dr. Olivieri had failed to report her concerns about L1 toxicity to the REB in a timely fashion. On the same day, the HSC Board directed its Medical Advisory Committee (MAC) to inquire into her conduct. On January 6, 1999, HSC removed Dr. Olivieri from her position as director of the hemoglobinopathy program without due process and issued "gag orders" to her and three supporters, Drs. Helen Chan, Peter Durie, and Brenda Gallie, restricting communication with the media. These actions prompted interventions by the Canadian Association of University Teachers (CAUT), the University of Toronto Faculty Association (UTFA), leading scientists Sir David Weatherall and Dr. David Nathan, and University President Robert Prichard. A marathon negotiating session on January 25, 1999 produced a settlement that restored Dr. Olivieri\'s full responsibility and authority over clinical care and research in hemoglobinopathies, withdrew the gag orders, changed her reporting relationships, and provided her with legal indemnification of $150,000 and coverage for potential legal action by Apotex.\n\nThe Medical Advisory Committee, using undisclosed allegations and testimony, principally from Dr. Gideon Koren, Dr. Olivieri\'s former co-investigator, and Dr. O\'Brodovich, referred a series of "concerns" about her conduct to the College of Physicians and Surgeons of Ontario (CPSO) and the University of Toronto in April 2000. Dr. Koren was later disciplined by HSC and the University on April 11, 2000 for "gross misconduct," including persistently lying about his authorship of anonymous letters disparaging Dr. Olivieri and her supporters; he admitted responsibility only after being identified by DNA evidence. The Health Professions Appeal and Review Board subsequently found that Dr. Koren\'s anonymous letter-writing campaign constituted "serious professional misconduct" and directed that the matter be referred to the CPSO Discipline Committee.\n\nIn October 2001, the independent CAUT Committee of Inquiry, chaired by Jon Thompson with Patricia Baird and Jocelyn Downie, published a detailed report exonerating Dr. Olivieri, faulting Apotex for attempting to suppress information on risks and to discredit her, faulting HSC and the University for failing to protect her academic freedom, and criticizing the Naimark Review and MAC proceedings for relying on incorrect and false information. On December 19, 2001, the CPSO Complaints Committee, assisted by an independent expert panel, concluded that "no further action is warranted against Dr. Olivieri," finding she did not fall below a reasonable standard of care in continuing to administer L1, in ordering liver biopsies, or in communicating with her department chief. The Committee specifically found her judgment in advising patients to undergo biopsies "not only reasonable, but commendable in the circumstances." On January 7, 2002, Dean David Naylor of the University of Toronto\'s Faculty of Medicine dismissed all related allegations, including the claim that Dr. Olivieri should have reported her conclusions on L1 toxicity to the REB.\n\nThe case was ultimately recognized for its impact on a critically important issue: the growing dependence of researchers, universities, and hospitals on corporate research funding and the need for policy safeguards to ensure that sponsors cannot restrict communication of identified risks, that confidentiality clauses in research contracts are not used to suppress findings of risk, and that research ethics boards, universities, and hospitals act robustly to defend academic freedom and the safety of trial participants and patients.', 'The Canadian Association of University Teachers (CAUT) established an Independent Committee of Inquiry, chaired by Professor Trudo Lemmens, with Dr. Thomas A. Ban and Dr. Louis C. Charland, to investigate the seizure of research records from the offices of Dr. Anne Duffy at the Institute of Mental Health Research (IMHR) in Ottawa on March 22, 2005. The Committee was mandated to investigate the sequence of events leading to and following the seizure, the institutional relationships between the University of Ottawa, the IMHR, and the Royal Ottawa Hospital (ROH), whether breaches of institutional responsibility or research ethics standards occurred, the impact on academic freedom and integrity, the impact on researchers, research subjects and institutions, and to make recommendations to prevent recurrence. The final report was submitted in March 2013 after delays caused by court proceedings and health issues.\n\nThe events began on March 11, 2005, when Dr. Duffy’s research coordinator told Sharyn Szick, Administrative Director of the IMHR, that a research assistant was scanning clinical charts and inserting printed copies into research records, and that informed consent forms were missing from some research records or had been signed after study initiation and backdated. Ms. Szick reported this to Dr. Zul Merali, President and CEO of the IMHR. On March 22, 2005, after a meeting attended by Ms. Szick, Dr. Keith Busby, Suzan Crozier, Carolyn Belzile, and Sharon Purvis, the decision was made to remove clinical charts from Dr. Duffy’s office and chart room. Dr. Paul Dagg, Director of Clinical Services, and Mr. Bruce Swan, CEO of the Royal Ottawa Health Care Group (ROHCG), authorized the removal of clinical charts based on allegations that clinical charts had been scanned and downloaded to hospital network drives, contrary to ROH policy and the Personal Health Information Protection Act (PHIPA). Once the clinical charts were relocated, Dr. Busby, at Dr. Merali’s request, conducted a “spot check” of approximately 20 research binders and reported that about five lacked consent forms behind the tab marked “consent.” Dr. Merali then ordered the immediate transfer of the research records of the bipolar team to a “secure location” at the ROH. Neither Dr. Duffy nor any member of her research team was present. Dr. Duffy learned of the removal the next morning from a note on her door.\n\nThe seized material included clinical charts, research records, personal files, and computer discs. According to Drs. Duffy and Grof, the records concerned more than 2,000 research subjects, including current and former patients and controls from Ontario and Nova Scotia. The records included studies conducted by Drs. Alda, Grof, and Duffy, involving long-term follow-up of families with bipolar disorder. The ROHCG Research Ethics Board (REB), chaired by Dr. Alan B. Douglass, was not consulted in advance, had received no complaint, and had not authorized the removal. Dr. Dagg’s investigation concluded on April 13, 2005 that no serious breaches of privacy with clinical charts had occurred, though he apologized for the removal.\n\nDrs. Duffy and Grof retained legal counsel on March 23, 2005, and commenced court proceedings for the return of the research records. They also filed a complaint with the Information and Privacy Commissioner of Ontario. On April 15, 2005, proceedings were adjourned and on April 18, 2005 an agreement was reached: the research records would be copied, originals returned, copies turned over to the REB without review, Dr. Merali would outline concerns, and the REB would appoint an independent reviewer. However, Dr. Duffy learned that Dr. Busby had already reviewed some records, contrary to her understanding of the agreement. Dr. Duffy then informed research subjects by e-mail that IMHR personnel had accessed personal information. The Information and Privacy Commissioner’s investigation was put on hold after objections from Dr. Duffy’s lawyers.\n\nIn May 2005, Drs. Duffy and Grof contacted CAUT, which established the Independent Committee of Inquiry. Committee interviews began in late summer 2005. Most institutional officials declined to participate on legal advice. A settlement was reached on October 19, 2005, which allowed Dr. Douglass to invite Dr. Padraig Darby, Chair of the REB of the Centre for Addiction and Mental Health, to review copies of the research records. Dr. Darby’s report, submitted November 10, 2006, found that only one of six studies had REB approval and that informed consent forms were missing from 77 of 252 records (30.5%). It was later clarified that all studies had approval letters on file that had not been provided to Dr. Darby. Drs. Duffy and Grof disputed the findings, reporting that only 11% of records lacked consent forms based on their review of the originals, and suggested that a former research assistant had failed to add consent forms to files. The Darby Report led to a second round of litigation, which ended in 2008 when the Canadian Medical Protective Association declined further funding and Drs. Duffy and Grof agreed to pay the other party’s legal costs.\n\nThe Committee’s own review of the original research records found that some consent forms identified as missing by Dr. Darby were present in the originals, and that new signed consent forms were present in records where originals were absent. Interviews with research subjects and parents of subjects whose original consent forms were missing showed that all were fully aware that they or their children were participating in Dr. Duffy’s research, understood the nature and purpose of the research, and had strong confidence in Dr. Duffy’s integrity.\n\nThe Committee concluded that the seizure of research records was in violation of research ethics standards. It emphasized a key distinction between informed consent obtained to protect research subjects from physical or psychological harm, and informed consent obtained to protect the privacy of research subjects and the confidentiality of sensitive health information. In the studies at issue, the consent forms represented a pledge by researchers to protect confidentiality. Seizing records in response to allegations of missing consent forms therefore violated the very essence of the informed consent. The “spot check” conducted by Dr. Busby was not a proper audit, as it lacked advance notice, defined objectives, scope, and researcher involvement, and was not carried out by the REB. The Committee found that the seizure was a disproportionate response, contrary to the principle of “proportionate review” under the Tri-Council Policy Statement (TCPS), and that institutional officials breached their responsibility by prioritizing the establishment of alleged wrongdoing over the protection of research subject privacy. The Committee attributed the seizure to ongoing tensions between Drs. Duffy and Grof and Drs. Merali and Bradwejn, and to the confounding of informed consent for privacy protection with informed consent for protection from harm.\n\nThe Committee’s recommendations included: clarifying that research records are in principle the property of the researcher; clearly defining the position of self-funded research teams and renegotiating responsibilities regularly; identifying for each research project whether informed consent is for protection from harm or for privacy and confidentiality; clarifying institutional responsibilities so that the REB that approved a project, not other institutional officials, ensures adherence to research ethics standards; and ensuring that seizure of research records is only a last resort when there is an immediate and serious threat to the wellbeing of research subjects, with procedures designed to respect the privacy and confidentiality of health information.', 'A prolonged and bitter dispute at Halifax’s Capital District Health Authority (CDHA) and Dalhousie University involved three physicians—Drs. Gabrielle Horne, Michael Goodyear, and Bassam A. Nassar. All held joint academic and hospital appointments. An Independent Committee of Inquiry established by the Canadian Association of University Teachers found that their cases arose from “interpersonal disagreements” that escalated because of serious flaws in bylaws, policies, procedures, and institutional culture. The Committee concluded that the damage was caused by a “collective and systemic failure” at CDHA/Dalhousie, not by individual errors, and that none of the three doctors was ultimately found to have committed wrongdoing when their cases received fair hearings.\n\nA central problem was the absence of academic freedom from the Affiliation Agreement between Dalhousie and CDHA. This meant academic freedom had no formal role in the relationship, leaving clinical faculty vulnerable. The Committee also found that “collegiality” was undefined and misused; it was applied in vague, personality-based ways that related to perceptions of “congeniality” rather than professional competence. In all three cases, allegations of lacking collegiality were used against the doctors. The doctors’ remuneration came through the Alternate Funding Plan (AFP) or group practice plans, which gave Department Chiefs extraordinary power over income with inadequate appeal rights. Appointments were not tenured, but were Continuing Appointments with Periodic Review (CAPR), which did not protect academic freedom.\n\nThe CDHA Medical Staff (Disciplinary) Bylaws were central to the cases of Drs. Horne and Goodyear. The Bylaws allowed summary variation of privileges by a Department Chief, but did not require natural justice or procedural fairness at the District Medical Advisory Committee (DMAC) or Privileges Review Committee (PRC) stages. Only the CDHA Board hearing provided those protections. The Bylaws set a maximum of fifty-one days before a case would go to the Board, but in practice the processes lasted years because the parties agreed to waive time limits. The Committee found that the Bylaws were “in many ways unsuited to productive solutions” and that variations of privileges should be reserved for egregious cases. It also criticized the lack of grievance procedures, income maintenance, and any binding process to implement Board rulings.\n\nIn Dr. Nassar’s case, the Disciplinary Bylaws were not invoked. His problems began with conflicts with the Chief of Pathology over privatized laboratory services and perceived conflicts of interest. He faced a letter of reprimand, a harassment complaint that was quashed by the Nova Scotia Supreme Court because no valid bylaws were in force, and a recommendation that his CAPR appointment not be renewed based on allegations about “collegiality” and “personal integrity.” His complaint of a hostile work environment was not resolved, and he spent years in litigation. An addendum to the Inquiry report later noted that Dr. Nassar reached a “mutually satisfactory settlement” with the Capital District Health Authority.\n\nDr. Horne was a cardiologist and clinical researcher whose privileges were summarily varied on October 21, 2002, by the Chief of Medicine. She was removed from clinical services where team care was the model, including the Heart Function Clinic, and enrollment in her research clinical trials was halted. The stated reason was concern about her ability to maintain “appropriate professional interaction in a team care model of service delivery.” Her research had all required Research Ethics Board approvals, and when her protocols were eventually presented to a special meeting of the clinical trials group, no safety issues were identified. A mediated settlement was reached in June 2003, but CDHA did not implement it; the PRC asserted the CEO lacked authority, and the courts agreed. The CDHA Board ruled in September 2006 that there was insufficient reason to invoke the “emergency variation” and ordered Dr. Horne restored to the status she held before the variation. By then, her research program had been destroyed. Dr. Horne subsequently won a jury verdict in the Nova Scotia Supreme Court of $1.4 million—described as the highest amount ever awarded in Canadian history for “loss of reputation and career”—plus more than $167,000 in legal fees. The jury found that her loss of privileges constituted “bad faith or malice.” Dr. Ken West called it “a classic case of workplace bullying.” The Nova Scotia Court of Appeal later reduced the award to $800,000, while the $167,000 for legal fees remained.\n\nDr. Goodyear, a medical oncologist, had his privileges restricted on October 10, 2002, and then suspended on January 9, 2003, after disagreements with colleagues over new cancer treatment protocols, including use of the “Douillard protocol” rather than the “Saltz regimen.” He was accused of failure to function in a “collegial team framework” and of exposing patients to risk. His income was reduced to 15% of its previous level through the AFP while the case was still pending. The CDHA Board did not rule until January 26, 2009—more than six years after the original variation—finding that there was “no basis to vary or suspend the privileges of Dr. Michael Goodyear” and ordering him restored to his October 9, 2002 status. However, by then he had been out of practice so long that a reintegration plan was required. Two CDHA oncologists who had testified against him were appointed as mentors, creating a reasonable apprehension of bias. Dr. Goodyear was ultimately denied a full medical licence and his oncology career was ended.\n\nThe provincial government later released documents showing that over $1 million in taxpayer money was spent on outside lawyers during the disciplinary process involving Dr. Horne, from 2002 onwards. The $1,024,649.67 was shared among four Halifax law firms: Boyne Clarke, Patterson Palmer, Stewart McKelvey, and Wickwire Holm. The Nova Scotia government had long refused to release the figures until Information Commissioner Tricia Ralph found the Department of Health “did not meet its burden to prove the information was exempt from disclosure.” The costs of defending the subsequent lawsuit and appeal remained secret, with the Nova Scotia Health Organizations Protective Association refusing to disclose “commercially sensitive information.” Dr. Horne said the figure was “extremely upsetting” and that it was likely “a small fraction of what was actually spent.”\n\nThe Independent Committee of Inquiry made numerous recommendations, including replacing the Affiliation Agreement with a “Cooperative Partnership,” protecting academic freedom, converting CAPR appointments into tenure-stream appointments, creating a formal Policy on Variation of Privileges, establishing discipline and grievance policies with final and binding arbitration, and ensuring effective representation for medical staff. It also recommended new external independent resources for defining and assessing clinical practice standards, and prompt fair settlements for the three doctors. The Committee concluded that “justice has been too long delayed.”']</t>
         </is>
       </c>
     </row>
@@ -541,21 +541,21 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3_class_gender_complaint_word</t>
+          <t>3_media_board_release_journals</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
+          <t>['media', 'board', 'release', 'journals', 'trustees', 'governance', 'wall', 'suspension', 'committee', 'grievance']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['In late March 2020, Kathleen Lowrey, an associate professor of anthropology at the University of Alberta, was dismissed from her administrative role as the Department of Anthropology’s associate chair of undergraduate programs. Lowrey had held the position since the start of the 2019-20 academic year, with the appointment normally running three years. Her dismissal was the result of informal, anonymous complaints made by one or more students to the University’s Office of Safe Disclosure and Human Rights and to the Dean of Students, André Costopolous. The students alleged that Lowrey’s “gender critical” views on sex and gender made them feel “unsafe” and caused them “harm,” and that her presence in the role could drive students away from choosing anthropology as a major. Lowrey was told it did not matter whether the claims against her were true. She was not given specific charges, was not given a hearing, and the complainants were not identified.\n\nLowrey describes herself as a gender-critical feminist. Her core views include the positions that biological sex is real, that men cannot get pregnant, that lesbians don’t have penises, and that transgender identity should not trump biological sex for policy decisions. She had publicly expressed those views by publishing an article on the website Feminist Current, posting signs and material on her office door, and teaching a January 2020 course, “Anthropology of Women,” in which she told students on the first day that they would read material currently out of fashion in academia and that they did not have to agree with her. She said she believed none of the complaints came from students who actually took the class. Lowrey was also told she had discouraged students from organizing Pride events, a claim she denied, and which led her to conclude the complaints centred on her views.\n\nWhen asked to resign, Lowrey refused, insisting that if the university wished to dismiss her from the service role it would need to put its reasons in writing. Dean of Arts Lesley Cormack subsequently sent her a letter on March 24, 2020, stating that she was no longer “effective” in the role and that “it is not in the best interests of the students or the university” for her to carry on. The letter did not specify how the university reached that conclusion. University spokesperson Hallie Brodie said Lowrey’s academic appointment as associate professor had not changed, cited privacy reasons for not commenting on the administrative role, and said the university had no further comment.\n\nThe case generated extensive commentary and controversy. Carolyn Sale, writing for the Centre for Free Expression blog at Ryerson University, argued that the University of Alberta was endorsing ideological conformity and that the process was akin to “McCarthyite” proceedings or ex officio proceedings during the English Reformation, in which accused heretics could be punished based on secret disclosures never made public. Sale contended that there is no such thing as a “safe” learning environment if “safe” means never encountering disagreeable views, and that academic freedom applies to all aspects of a professor’s work, conventionally defined as 40% teaching, 40% research, and 20% service. She also criticized the university’s concern that Lowrey’s views could have financial consequences for the department under a budget model where government funding follows students, and the university’s reasoning that not dismissing Lowrey would make students feel the university cared more about supporting the professor than about them.\n\nMark Mercer, president of the Society for Academic Freedom and Scholarship, wrote to Dean Cormack asking her to reinstate Lowrey, warning that removing her would discourage faculty from assuming service roles and could harm teaching and academic integrity. Peter Wood, president of the National Association of Scholars, later wrote a public open letter to Steve Patten, the new Dean of Arts, urging the university to reverse its decision. Wood called Lowrey’s view that humans are sexually binary a biological fact, and argued that removing her from her position communicated to faculty that responsible expression of accurate information would be punished if it irritated enough students or administrators. Columnists Lorne Gunter and Barbara Kay defended Lowrey’s freedom of expression even while disagreeing with her views, with Gunter calling the dismissal a “witch-hunt mentality” and Kay noting that Lowrey was concerned the university had taken the position that “saying you don’t think a person can change sex is a firing offence.”\n\nStudent and faculty reactions were divided. Elizabeth Sawchuk, a Banting postdoctoral fellow and adjunct professor, said she had no problem with Lowrey exploring gender and sexuality in scholarship, but found the images on Lowrey’s door offensive and not academically appropriate, and said they harmed trans and non-binary students and colleagues. Chris Beasley, president of the Organization of Arts Students and Interdisciplinary Studies, said the removal was a positive result for students and that campus must remain a safe space. Joel Agarwal, president of the U of A Students’ Union, said professors are guaranteed academic freedom but that it does not give them immunity from discipline for behaviour that would lead to discipline in any other workplace. An anonymous student said Lowrey’s social media posts on Spinster, where she welcomed students searching her feed for “hate speech,” made the student fear bringing concerns forward. Another anonymous student said Lowrey disrupted a student-led queer anthropology event with “anti-trans remarks” and argued directly with a trans man in the room. Lowrey said she had attended the event to listen, but felt she needed to speak up, remained polite and careful, and believed some faculty members did not like being confronted.\n\nLowrey herself published an essay in Quillette describing her journey from South American anthropology to gender-critical feminism, noting that a decade earlier she might have joined campaigns to cancel other academics. She said that during the 2019-20 academic year the University of Alberta introduced sweeping equity, diversity, and inclusion policies that she believed could be used to silence feminist women. She noted she was the only member of the university’s General Faculties Council to vote against the new EDI policy, which included a focus on gender at the expense of sex. She said the conflict was unavoidable because contemporary gender ideology requires active affirmation that men can become women and vice versa, and that refusing to assent is treated as doing active harm to trans-identified individuals. She expressed concern for non-tenured university employees and for students afraid to voice shared opinions.\n\nA grievance was filed by Lowrey and the Association of Academic Staff of the University of Alberta, the academic staff union. The union alleged that the university breached the collective bargaining agreement by failing to uphold academic freedom and by exercising management rights in an unfair, unreasonable, inequitable, and non-arbitrary manner. An arbitrator sided with the university, finding that Lowrey was removed not because of her academic views but because she was a “protagonist in a dispute” that prevented her from effectively serving as associate chair. The Alberta Labour Relations Board upheld that decision. In November 2024, the Alberta Court of Appeal dismissed the union’s appeal, ruling that it raised no question of law. Justice Dawn Pentelechuk wrote that the arbitrator had drawn a rational and transparently articulated line between Lowrey’s academic views, which were not the basis for the university’s decision, and her suitability to carry out the role given the circumstances that had developed. The court said the union’s argument was largely a complaint about the interpretation and weight given to the evidence, not an identifiable legal error.\n\nThroughout the controversy, Lowrey maintained that her dismissal from the service role was a violation of academic freedom. She said the university had taken the position that if a professor is not specifically covered by academic freedom, that person can be fired, which she called terrifying and horrible. She said the implications were dangerous because the debate over biological sex and gender identity is a live issue in Canadian democracy. Supporters of Lowrey argued that unorthodox or controversial views must be actively debated and never suppressed, and that universities must not become homes for orthodoxy or dogma. Critics argued that Lowrey’s methods of communicating her views, including her office door and social media posts, created an exclusionary and toxic environment and went beyond legitimate academic discussion.', 'Students at Bishop’s University in Sherbrooke, Que., have alleged that sociology professor Dr. Cheryl Gosselin has used derogatory and discriminatory language in her classroom for years. Multiple students spoke to CTV News and to The Campus, the university’s independent student newspaper, describing incidents involving racist, homophobic and Islamophobic comments, slurs, stereotyping and dismissive responses when students raised concerns. The allegations prompted an internal university memo, a review of complaint processes, reassignment of Gosselin’s winter 2025 classes, and statements from Quebec’s Higher Education Ministry.\n\nSociology student Malik Kessouagni, who said he took three classes with Gosselin, alleged that she spoke about how Black women “react” and said she “didn’t really like Black women” while staring at a Black woman in the class. Kessouagni also alleged that Gosselin discussed the stereotype about Black men with large penises while staring at him and a friend, as they were the only Black people present. Marie-May Lamothe, another sociology student, said she witnessed discriminatory comments about the LGBTQIA2S+ community as recently as November 2024. She said Gosselin used the “F” slur in class, repeating it six or seven times, and that there was “an audible gasp from the classroom.” Lamothe also alleged that Gosselin misgendered non-binary authors, called Arab men sexist, argued that women who wear the hijab “slut shame” Caucasian women, and freely used the “N” word and the “F” slur when discussing readings or lectures about Black and LGBTQIA+ communities. The Campus’s investigation identified the class as a first-year Gender and Sociology course (SOC129) and the date as November 12, 2024. Students said Gosselin used the slur while quoting Joel Mittleman’s 2022 article, “Homophobic Bullying as Gender Policing: Population-Based Evidence,” which contains the uncensored slur, and then kept repeating it while asking questions like “what does this mean, f-g.” Students described the discomfort in the room, and Allister Coursol noted that “no one was answering.” Aaliyah Wilburn, a political science student, said she raised her hand to ask Gosselin to consider the repercussions of using such strong language, but felt dismissed: “She basically blew me off. Told me I was incorrect, and basically, she made me feel dumb for saying something.” Kessouagni recalled Gosselin’s defence: “It’s not a word that she uses on a daily basis.” He said, “Regardless of the fact if you use it on a daily basis or not, you still used it. Therefore, it’s still an issue and you do not want to hold yourself accountable.” Sociology student Rory Point-Du-Jour, who took a class with Gosselin in 2022, said Gosselin was “not really apologetic or regretful” and told students “you guys kind of just have to deal with it.”\n\nWilburn reported the incident to the university’s Equity, Diversity and Inclusion (EDI) department and later lodged a formal complaint against Gosselin. She said the EDI response felt like they were “trying to find reasons and excuses for why Cheryl was saying the things that she was saying” and argued that there is “no excuse” and that the university should “hold your teachers accountable.” The Campus reported that Wilburn had not received recent information on whether the complaint was still in process. Andrew Webster, Vice-Principal Academics and Research, said he could not comment on the status of the complaint because of Quebec and Canadian privacy laws, while adding that complaints are taken “very seriously.”\n\nThe students also described earlier complaints. Markayza Mitchell, a sociology student, told The Campus about an incident in winter 2023 when she raised concerns in Gosselin’s first-year Quebec Society course about the lack of Indigenous representation. According to Mitchell, Gosselin said she shouldn’t impose her perspective on the rest of the class and pointed to the door, telling her she could leave. Mitchell said she “didn’t feel respected at all” and later dropped the class, which affected her ability to graduate. Leana Ceresoli, who became Social Science Senator in May 2024, said she had been made aware of Gosselin’s controversy through informal complaints about separate undisclosed incidents in Gosselin’s 2023 Quebec Society course. Ceresoli relayed these concerns to Roser Rise, then Student Representative Council Vice-President of Academic Affairs, and Rise said she worked with Webster to create a more clearly defined structure for formal complaints. However, the students who complained informally did not wish to pursue the formal process. Ceresoli, who was a teaching assistant for Gosselin’s fall 2024 Gender and Society course, was not in class when the slur was allegedly used and said she was surprised students had not told her.\n\nThe Bishop’s University Students’ Representative Council (SRC) said it was not aware of any formal complaints against Gosselin and encouraged students to contact the Office of the Dean or another relevant administrative office to file a formal report. Bishop’s University initially said it “cannot comment, discuss or disclose any confidential or personal information” and that it holds “itself and its faculty and staff to the highest standards.” Communications manager Sonia Patenaude said the university acts swiftly if concerns are raised and follows due process. After the CTV News report was published, an internal memo signed by Principal Sébastien Lebel-Grenier and vice-principals was sent to students and staff. The memo recognized that members of the community might find the media report “challenging and emotionally straining.” It said complaints “should be discussed with the professor, the program chair, the dean, or the ombudsperson” and that reports or complaints would be treated confidentially and investigated fairly. The university said it would “be pursuing a conversation in Senate, starting at its Jan. 24 meeting, on ways to better communicate resources and processes available to students” and would “also be examining how our processes can be improved.” The memo also said universities are “places of learning through the free and open discussion of sometimes difficult or challenging subjects and ideas,” and that professors must pursue truth and disseminate knowledge responsibly within a “safe and respectful environment.” It lamented that its “internal processes are not sufficiently known or understood, or may be seen as insufficient.”\n\nQuebec’s Higher Education Ministry called the allegations “worrying” in the first CTV article, with spokesperson Simon Savignac saying, “Discriminatory comments cannot be tolerated” and inviting students to lodge complaints through official channels. The ministry later said it was “shocked” by the allegations and in close communication with the university. During the January 24 Senate meeting, Webster proposed integrating a link to university resources into course syllabi to standardize communication, but the proposal turned into a debate on professorial autonomy and administrative overreach. Webster said the proposal would be revisited by the Academic Standing Admissions Policy committee and intended to be brought back to Senate.\n\nFollowing the CTV report, Gosselin’s winter 2025 classes — Sociology of the Body (SOC219) and Quebec Society (SOC102) — were cancelled on January 14. On January 16, Gosselin taught both classes without acknowledging the article. The following week, the classes were taken over by Dr. Travis Smith from the sports studies department and Dr. David Webster from the history department. Gosselin did not respond to requests for comment; Andrew Webster said she had no wish to comment and preferred not to be contacted further. Students such as Lamothe continued to call for real consequences, saying Gosselin “needs to face a real repercussion and realize that this is an actual incident that means a lot.” The students also expressed concern that a white student might think, “OK, if my professor is saying this, I should be able to say it too,” and that derogatory terms used so freely in a classroom are “really appalling.”', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
+          <t>['The documents concern David Noble, a historian and critic of technology and education, and a full professor in the Division of Social Sciences in the Faculty of Arts at York University. The central events described are the November 2004 distribution by Noble of a flyer on York’s campus, the University’s public condemnation of that flyer, and the subsequent grievance arbitration between York University and the York University Faculty Association (YUFA). Additional documents describe a separate controversy involving Noble’s rejected appointment to the J.S. Woodsworth Chair in Humanities at Simon Fraser University, and provide biographical background on Noble’s career and activism.\n\n**The Flyer and the Media Release**\n\nOn Thursday, November 18, 2004, at a film screening sponsored by the student group Solidarity for Palestinian Human Rights (SPHR), Noble distributed an unsigned two-page document entitled "THE YORK UNIVERSITY FOUNDATION: THE TAIL THAT WAGS THE DOG (SUGGESTIONS FOR FURTHER RESEARCH)". The flyer alleged that the York University Foundation (YUF), established in 2002, operates as "the tail that wags the dog" of York University, guiding administration decision-making through fundraising considerations. It further alleged that the YUF was "biased by the presence and influence of staunch pro-Israel lobbyists, activists, and fundraising agencies," and it listed members of the YUF Board of Directors along with their affiliations with Jewish organizations such as the United Jewish Appeal Federation of Greater Toronto (UJA), the United Israel Appeal of Canada (UIA), and the Mount Sinai Hospital Foundation (MSHF). The flyer connected these affiliations to decisions by the University to discipline pro-Palestinian activists, including the suspension of student Daniel Freeman-Maloy, and to the proposed Argonaut football stadium at York. Noble testified that he had prepared the document as part of academic research and had distributed it to students in his classes before attending the SPHR film screening.\n\nOn Friday, November 19, 2004, York University issued a Media Release entitled "York University, Hillel, SPHR Denounce Material Targeting Jewish Community Members." The Media Release, posted on York’s website and sent to major Canadian news outlets, quoted York President Lorna Marsden stating that York "strongly condemns this highly offensive material, which singles out certain members of the York community on the basis of their ethnicity and alleged political views, including philanthropic volunteers who serve on the board of the York University Foundation." It also quoted representatives of SPHR and Hillel at York denouncing the material. The Media Release did not name Noble, but a separate media release from the Canadian Jewish Congress (CJC), issued at about the same time, expressly identified "York University sociology Professor David Noble" and condemned his statements as "appalling" and as "antisemitism, vaguely disguised as anti-Israel rhetoric." Newspaper articles in the Globe and Mail and Toronto Star followed, reporting on the controversy.\n\nNoble testified that upon learning of the Media Release he felt "deeply offended," "outraged," "under assault," "shocked," "stunned," "astonished," and "blind-sided" to have been "labelled an anti-semite" by his own University, particularly because he is Jewish and the son of a Polish immigrant father. He subsequently demanded an apology from York and the CJC and threatened legal action.\n\n**The Grievance and Arbitration**\n\nOn November 29, 2004, YUFA filed a grievance on Noble’s behalf. The grievance alleged that the University had discriminated against Noble on the basis of his political beliefs and/or non-conforming personal or social behaviour contrary to Article 3.01 of the collective agreement, and had violated Article 10.01 by failing to protect and promote academic freedom and by libelling the grievor in the Media Release. The grievance requested a declaration, an apology, distribution of a corrective media release, and damages in the amount of $10,000,000.00.\n\nThe arbitration was heard by sole arbitrator Russell Goodfellow. Ten witnesses gave evidence, and the parties made extensive submissions on defamation and academic freedom. In his award dated September 26, 2007, the arbitrator found that York had breached Article 10.01 of the collective agreement. He noted that Richard Fisher, York’s Chief Marketing and Communications Officer, was responsible for the University’s response and testified that he did not view the pamphlet as having any "academic" aspect, did not consider the Collective Agreement or Article 10.01, did not consult York’s labour relations department, and had limited knowledge of the concept of academic freedom. The arbitrator held that the University’s Media Release, with its implied accusations of racism and bigotry and its implicit suggestion that no student should be exposed to Noble’s material, was a clear violation of Noble’s academic freedom. The arbitrator emphasized that the University failed to contact Noble or YUFA before issuing the release, and that the release had the effect of making the pamphlet a matter of public interest while leaving Noble identifiable to the media through the CJC and others.\n\nThe arbitrator dismissed the defamation claim on its merits. He applied the two-part test from *Knupffer v. London Express Newspaper Ltd.*: whether the article was capable of referring to the plaintiff, and whether reasonable people who know the plaintiff would conclude that it referred to him. The arbitrator found that the Media Release commented exclusively on the "material," did not identify Noble directly or indirectly, and preserved the anonymity that was a feature of Noble’s own pamphlet. Even read in light of surrounding circumstances, including the University’s "nudge, nudge, wink, wink" approach of directing inquiries to others, the Media Release was not "of and concerning" Noble. The claim for defamation was therefore dismissed. The arbitrator made brief remarks on the defence of fair comment, noting that there was at least some basis for the view that the material did "single out" or "target" Jewish members of the York community, but he did not need to decide the defence.\n\nThe arbitrator’s remedies were: a declaration that the University breached Article 10.01; an order that the University forthwith remove the Media Release from its website; and an award of damages to Noble in the amount of $2,500.00. The arbitrator declined to order an apology.\n\n**Simon Fraser University Appointment and Biographical Background**\n\nA separate set of events concerns Noble’s appointment to the J.S. Woodsworth Chair in Humanities at Simon Fraser University (SFU). Noble alleged his academic freedom was violated when SFU’s administration overturned the recommendation of the department of humanities that he be appointed and directed the department to undertake a new search. The Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee appointed an independent committee of inquiry to investigate, composed of Howard Pawley and Gordon Shrimpton. More than 120 leading American academics protested the cancellation, and Burnaby-Douglas MP Svend Robinson wrote to SFU’s president expressing concern. SFU Vice-President Academic John Waterhouse denied that the administration intervened on political grounds, citing errors in the hiring procedure and insufficient references; these statements were disputed by history professor Lawrin Armstrong, a member of the search committee. SFU also named an independent reviewer to investigate.\n\nNoble’s biography describes him as a historian and critic of technology, science, and education. He obtained degrees from the University of Florida and the University of Rochester, taught at MIT, the Smithsonian Institution, Drexel University, and York University, and was known for works such as *America by Design* and *Forces of Production*. He was denied tenure at MIT, and throughout his career he criticized the corporatization of universities. He received the Joe A. Callaway Award for Civic Courage in 1998. He died suddenly on December 27, 2010, from septic shock and kidney failure caused by pneumonia.', 'Thompson Rivers University (TRU) in Kamloops, B.C., suspended economics professor Derek Pyne for one year without pay or benefits on July 16, 2020, over a Facebook post he made on June 10, 2020. Pyne, who teaches in the School of Business and Economics, said the suspension was the second time TRU had disciplined him in connection with an academic freedom dispute. He said he was surprised by the university’s action. “I did not think that even TRU would be foolish enough to go after me for such an obvious issue of academic freedom, given how much bad publicity they generated when they attacked my academic freedom in the past.”\n\nPyne’s first suspension came in 2018, after he published research into so-called predatory journals. His paper, “The Rewards of Predatory Publications at a Small Business School,” was published by the University of Toronto Press Journal of Scholarly Publishing. In it, he claimed that more than half of the faculty members in the TRU department of Business and Economics had published papers in illegitimate journals to advance their careers. Pyne said he was banned from campus in May 2018 and suspended in July 2018. TRU’s then-interim president, Christine Bovis-Cnossen, said at the time that the discipline was not related to his research but that she could not comment further due to employment and privacy law. Pyne was reinstated in January 2019. A committee of investigation established by the Canadian Association of University Teachers (CAUT) concluded in November 2019 that TRU’s administration had breached Pyne’s academic freedom and his privacy. The committee found that TRU “appears to suffer a broad institutional weakness when it comes to understanding academic freedom,” and that the university failed to understand academic freedom beyond a “narrow application to support faculty members’ freedom to pursue what they expect to be fruitful avenues of research and publish their results.” The committee recommended that TRU review its human resources practices to ensure academic freedom was properly understood and protected. TRU did not participate in the investigation, saying CAUT did not have authority or jurisdiction to probe issues covered by the collective agreement.\n\nThe Facebook post that led to the latest suspension praised the Brock University Faculty Association (BUFA) for supporting Tomas Hudlicky, a chemistry professor at Brock University who had been at the centre of controversy. Hudlicky had written an essay in the chemistry journal Angewandte Chemie that criticized employment equity hiring and commented on skills transfer between “masters and apprentices.” The journal retracted the essay after backlash, and Brock University apologized, saying the essay did not reflect the university’s values. BUFA published a statement supporting academic freedom. In his June 10 Facebook post, Pyne wrote: “Some good news for a change. Unlike Thompson Rivers University Faculty Association, it seems that some university unions are not opposed to academic freedom. One can debate some of the details of the following statement but the bottom line is that it comes out in support of academic freedom, even when it goes against the university, and the union’s, positions.” In a comment, Pyne tagged the Federation of Post-Secondary Educators and several members of TRU’s Faculty Association (TRUFA). He also predicted that TRUFA members would “go running” to Larry Phillips, the executive director of human resources at TRU, to defend them. The post was shared three times.\n\nAccording to Pyne, two complainants told TRU that being tagged in the post led to them losing sleep, and one claimed she needed time off work to recover. A union executive member and steward filed the harassment complaint. Pyne said he was called to a human resources meeting with Phillips, who read him a four-page letter from TRU president Brett Fairbairn. Pyne was told he had been suspended for one year with no pay and no benefits, and he was also cut off from his TRU email account, which he said contains information he requires. He said he did not have a last chance to access his work email.\n\nTRU spokesperson Darshan Lindsay said the university could not provide specific information on personnel matters due to employment and privacy laws, but stated: “We want to be clear that matters involving Dr. Pyne are not about the exercise of academic freedom.” Lindsay added that TRU fully supports academic freedom, “including the ability to conduct independent research, freely communicate knowledge and the results of research and scholarship, and respectfully debate differences.” She also said it was “unlikely the university would suspend an employee for a single social media post,” and that employees have avenues for appeal through their union or the British Columbia Labour Relations Board. Fairbairn made the same points in a letter dated July 28, 2020, in response to an inquiry from the Society for Academic Freedom and Scholarship (SAFS).\n\nThe SAFS, an organization dedicated to defending academic freedom and the merit principle in higher education, sent a letter to TRU on July 27, 2020. Mark Mercer, the society’s president and a philosophy professor at Saint Mary’s University, said Pyne’s suspension was “a serious violation of his academic freedom.” The letter argued that Pyne’s right to criticize both TRU and his faculty association is protected by Article 9.6 of the TRU Collective Agreement. Mercer also wrote that “providing people an opportunity to know what one is thinking cannot be a case of harassment, especially when the people Dr Pyne tagged on Facebook were union officials.” He said denying Pyne the use of his office, university email address, and other university resources would severely impede his work as a scholar, and demanded that TRU explain why its action was not an attack on academic standards and values.\n\nPyne said appealing his suspension through his union made little sense because it was a union executive member and steward who filed the complaint that led to his suspension. However, after the suspension, Pyne received correspondence from TRUFA, including a copy of a grievance that listed academic freedom as a ground. Pyne said TRUFA had previously opposed action on academic freedom grounds, and that if the union was serious about the new grievance, “it really will change things.” TRUFA was demanding that the suspension be rescinded and that Pyne be reinstated with full retroactive salary and benefits. A previous complaint Pyne filed with the BC Labour Relations Board had been dismissed in July 2019, and his appeal was denied; the board said it lacked jurisdiction under Section 12 of the province’s labour code to determine whether academic freedom rights had been violated, and that such rights were a matter for arbitration under the TRU-TRUFA collective agreement.\n\nPyne said he was unsure of his next steps and had asked several organizations for advice. He said universities need to respect academic freedom, stating: “I think that the public has a right to know how tax dollars are being misused by a public institution. More generally, I think academic freedom is essential for the advancement of knowledge.” He also said: “At some point, a line has to be drawn or academic freedom will only be a right on paper.”', 'Thompson Rivers University (TRU) in Kamloops, B.C. became the centre of a controversy involving predatory academic publishing and academic freedom after economics professor Derek Pyne conducted research on so-called “predatory journals”—publications that claim to be peer reviewed but in reality publish articles in exchange for fees paid by authors, often with little or no scrutiny. Pyne, an associate professor in TRU’s School of Business and Economics, began researching the rewards for faculty who published in such journals, and in April 2017 published a peer-reviewed article, “The Rewards of Predatory Publications at a Small Business School,” in the Journal of Scholarly Publishing, a publication of the University of Toronto Press. His study reported that about half of more than three dozen faculty and administrators in the school had published in suspect journals, sometimes frequently, and that such publications were linked to promotions, research awards, and financial remuneration. Although the article did not name TRU, it became known that the school studied was TRU’s School of Business and Economics. Pyne also wrote an opinion piece for the Ottawa Citizen in April 2017 titled “Are universities complicit in predatory publishing?” and later gave interviews to The New York Times, The Economist, and other international media.\n\nPyne had communicated his findings and concerns to TRU administrators, including the dean, provost, and others, before publication. He said his communications created friction with the dean and that the university made no attempt to discuss, verify, or address the issue. His research was supported financially by TRU’s Office of Research and Graduate Studies. During the same period, Pyne publicly questioned the quality of the School of Business and Economics and its new professional master’s degree programs, including comments posted on a local media website. His department passed motions criticizing those comments. Complaints about Pyne led to multiple human resources processes. In June 2016 he received a formal notice of discipline related to communications with colleagues and administrators. In December 2017 a research misconduct complaint was filed against him under TRU’s Integrity in Research and Scholarship policy; it was later determined to be unfounded, but another similar complaint was filed shortly afterward. Pyne was required to undergo a psychological examination, which took place on June 4, 2018; the resulting report found no evidence of mental illness.\n\nOn May 17, 2018, Pyne was notified he was prohibited from being on campus, though he was still expected to perform his regular duties. On May 30, TRU’s human resources department accused him of making “defamatory and insubordinate” comments. On June 15, during a consultation process for an internal candidate for associate dean, Pyne submitted feedback that discussed the candidate’s publications in allegedly predatory journals. The university responded by accusing him of “defamatory language and accusations.” On July 17, 2018, Pyne was suspended indefinitely without pay, with written notification on July 23. TRU stated the suspension was based on insubordination and inappropriate, threatening, and defamatory statements. Pyne contended his statements were factual. After the Thompson Rivers University Faculty Association (TRUFA) became aware of the suspension, it was reduced to a two-week suspension ending July 31, and TRUFA filed a grievance. TRU later restored Pyne’s pay after media coverage, but he remained banned from teaching and from campus except in limited circumstances. The university declined to explain the reasons for its actions, citing privacy laws and the need to protect the personal information of employees.\n\nThe Canadian Association of University Teachers (CAUT) became aware of Pyne’s case through media coverage and, after reviewing initial evidence, established an ad hoc investigatory committee on October 30, 2018, to investigate whether TRU violated Pyne’s academic freedom and whether the suspension was appropriate. The committee was chaired by Mark Mac Lean of the University of British Columbia and included Carla Graebner of Simon Fraser University. TRU declined to participate, with interim president Christine Bovis-Cnossen stating that CAUT had no authority or jurisdiction to investigate matters covered by the collective agreement, and that the appropriate process would be a grievance filed by TRUFA. TRUFA did not file an academic freedom grievance. Pyne also filed a complaint under Section 12 of the B.C. Labour Code alleging TRUFA breached its duty of fair representation; that complaint was dismissed by the Labour Board, which noted it did not have jurisdiction to determine academic freedom violations.\n\nTRU’s interim president issued public statements asserting that “Action taken against Dr. Pyne was not related to his specific research, the dissemination of his research, or the exercising of his right to academic freedom.” She said academic freedom was fully protected under the collective agreement and that faculty hired or promoted at TRU go through a robust peer review process. Some academics, including UBC professor Michael Byers and Mark Mercer of the Society for Academic Freedom and Scholarship, called for transparency or government intervention. The B.C. government declined to intervene, citing the University Act provision that a minister must not interfere in the exercise of powers conferred on a university. TRU also complained to the Vancouver Sun about its coverage, saying the newspaper misrepresented TRU by failing to include the university’s full statement.\n\nThe CAUT investigatory committee released its report in November 2019. It concluded that TRU appeared to suffer from a broad institutional weakness in understanding academic freedom beyond its narrow application to research and publication. It found significant breaches of Pyne’s academic freedom with respect to the administration’s responses to his intramural and extramural communications criticizing the School of Business and Economics, its programs, and its faculty. The committee held that the collective agreement’s Article 9.6 on academic freedom created a positive obligation on the parties to consider academic freedom in any case involving speech from faculty members, and that the failure to do so denied Pyne procedural fairness. It found no evidence that any person at TRU interfered with Pyne’s actual research, but it concluded that the decision to suspend him was not made on a sound basis. It also found serious breaches of Pyne’s privacy by both TRU and TRUFA, particularly with respect to the circulation of his psychological report. The report identified emergent themes including the “pathologizing of dissent,” failures of human resources processes to respect academic freedom, failures to protect medical privacy, and a failure of academic governance with respect to considering predatory journals in tenure and promotion decisions. It made recommendations that TRU complete an academic freedom policy, review HR practices, manage conflicts of interest, remove constraints on Pyne’s speech, and have the Senate Tenure and Promotion Committee review the use of predatory publications in tenure and promotion.\n\nThe controversy also drew attention to the broader phenomenon of predatory publishing. Jeffrey Beall, a former University of Colorado librarian, created a database of about 12,000 questionable journals, and the Texas company Cabell’s compiled a similar list of almost 9,000 journals. A sting operation by John Bohannon, described in The Economist, found that 69 percent of journals chosen from a blacklist offered to publish a fake paper for a fee, and 38 percent of supposedly trustworthy whitelisted open-access journals also accepted it. Estimates cited in the documents indicated that articles published in disputed journals grew from about 53,000 in 2010 to more than 400,000 annually. The debate over predatory journals has increasingly shifted from the idea that authors are victims to the view that many academics knowingly use them to inflate publication records and advance careers. Pyne’s case became a symbol of the risks of exposing such practices, especially for faculty who challenge their own institutions. TRU’s incoming president, Brett Fairbairn, who took office in December 2018, had previously resigned as provost at the University of Saskatchewan after suspending a professor who criticized administration budget cuts, raising further concerns about academic freedom at TRU.']</t>
         </is>
       </c>
     </row>
@@ -564,21 +564,21 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4_board_media_journals_release</t>
+          <t>4_christian_public_health_covid19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
+          <t>['christian', 'public', 'health', 'covid19', 'children', 'western', 'public health', 'medicine', 'provost', 'scientific']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['The documents concern David Noble, a historian and critic of technology and education, and a full professor in the Division of Social Sciences in the Faculty of Arts at York University. The central events described are the November 2004 distribution by Noble of a flyer on York’s campus, the University’s public condemnation of that flyer, and the subsequent grievance arbitration between York University and the York University Faculty Association (YUFA). Additional documents describe a separate controversy involving Noble’s rejected appointment to the J.S. Woodsworth Chair in Humanities at Simon Fraser University, and provide biographical background on Noble’s career and activism.\n\n**The Flyer and the Media Release**\n\nOn Thursday, November 18, 2004, at a film screening sponsored by the student group Solidarity for Palestinian Human Rights (SPHR), Noble distributed an unsigned two-page document entitled "THE YORK UNIVERSITY FOUNDATION: THE TAIL THAT WAGS THE DOG (SUGGESTIONS FOR FURTHER RESEARCH)". The flyer alleged that the York University Foundation (YUF), established in 2002, operates as "the tail that wags the dog" of York University, guiding administration decision-making through fundraising considerations. It further alleged that the YUF was "biased by the presence and influence of staunch pro-Israel lobbyists, activists, and fundraising agencies," and it listed members of the YUF Board of Directors along with their affiliations with Jewish organizations such as the United Jewish Appeal Federation of Greater Toronto (UJA), the United Israel Appeal of Canada (UIA), and the Mount Sinai Hospital Foundation (MSHF). The flyer connected these affiliations to decisions by the University to discipline pro-Palestinian activists, including the suspension of student Daniel Freeman-Maloy, and to the proposed Argonaut football stadium at York. Noble testified that he had prepared the document as part of academic research and had distributed it to students in his classes before attending the SPHR film screening.\n\nOn Friday, November 19, 2004, York University issued a Media Release entitled "York University, Hillel, SPHR Denounce Material Targeting Jewish Community Members." The Media Release, posted on York’s website and sent to major Canadian news outlets, quoted York President Lorna Marsden stating that York "strongly condemns this highly offensive material, which singles out certain members of the York community on the basis of their ethnicity and alleged political views, including philanthropic volunteers who serve on the board of the York University Foundation." It also quoted representatives of SPHR and Hillel at York denouncing the material. The Media Release did not name Noble, but a separate media release from the Canadian Jewish Congress (CJC), issued at about the same time, expressly identified "York University sociology Professor David Noble" and condemned his statements as "appalling" and as "antisemitism, vaguely disguised as anti-Israel rhetoric." Newspaper articles in the Globe and Mail and Toronto Star followed, reporting on the controversy.\n\nNoble testified that upon learning of the Media Release he felt "deeply offended," "outraged," "under assault," "shocked," "stunned," "astonished," and "blind-sided" to have been "labelled an anti-semite" by his own University, particularly because he is Jewish and the son of a Polish immigrant father. He subsequently demanded an apology from York and the CJC and threatened legal action.\n\n**The Grievance and Arbitration**\n\nOn November 29, 2004, YUFA filed a grievance on Noble’s behalf. The grievance alleged that the University had discriminated against Noble on the basis of his political beliefs and/or non-conforming personal or social behaviour contrary to Article 3.01 of the collective agreement, and had violated Article 10.01 by failing to protect and promote academic freedom and by libelling the grievor in the Media Release. The grievance requested a declaration, an apology, distribution of a corrective media release, and damages in the amount of $10,000,000.00.\n\nThe arbitration was heard by sole arbitrator Russell Goodfellow. Ten witnesses gave evidence, and the parties made extensive submissions on defamation and academic freedom. In his award dated September 26, 2007, the arbitrator found that York had breached Article 10.01 of the collective agreement. He noted that Richard Fisher, York’s Chief Marketing and Communications Officer, was responsible for the University’s response and testified that he did not view the pamphlet as having any "academic" aspect, did not consider the Collective Agreement or Article 10.01, did not consult York’s labour relations department, and had limited knowledge of the concept of academic freedom. The arbitrator held that the University’s Media Release, with its implied accusations of racism and bigotry and its implicit suggestion that no student should be exposed to Noble’s material, was a clear violation of Noble’s academic freedom. The arbitrator emphasized that the University failed to contact Noble or YUFA before issuing the release, and that the release had the effect of making the pamphlet a matter of public interest while leaving Noble identifiable to the media through the CJC and others.\n\nThe arbitrator dismissed the defamation claim on its merits. He applied the two-part test from *Knupffer v. London Express Newspaper Ltd.*: whether the article was capable of referring to the plaintiff, and whether reasonable people who know the plaintiff would conclude that it referred to him. The arbitrator found that the Media Release commented exclusively on the "material," did not identify Noble directly or indirectly, and preserved the anonymity that was a feature of Noble’s own pamphlet. Even read in light of surrounding circumstances, including the University’s "nudge, nudge, wink, wink" approach of directing inquiries to others, the Media Release was not "of and concerning" Noble. The claim for defamation was therefore dismissed. The arbitrator made brief remarks on the defence of fair comment, noting that there was at least some basis for the view that the material did "single out" or "target" Jewish members of the York community, but he did not need to decide the defence.\n\nThe arbitrator’s remedies were: a declaration that the University breached Article 10.01; an order that the University forthwith remove the Media Release from its website; and an award of damages to Noble in the amount of $2,500.00. The arbitrator declined to order an apology.\n\n**Simon Fraser University Appointment and Biographical Background**\n\nA separate set of events concerns Noble’s appointment to the J.S. Woodsworth Chair in Humanities at Simon Fraser University (SFU). Noble alleged his academic freedom was violated when SFU’s administration overturned the recommendation of the department of humanities that he be appointed and directed the department to undertake a new search. The Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee appointed an independent committee of inquiry to investigate, composed of Howard Pawley and Gordon Shrimpton. More than 120 leading American academics protested the cancellation, and Burnaby-Douglas MP Svend Robinson wrote to SFU’s president expressing concern. SFU Vice-President Academic John Waterhouse denied that the administration intervened on political grounds, citing errors in the hiring procedure and insufficient references; these statements were disputed by history professor Lawrin Armstrong, a member of the search committee. SFU also named an independent reviewer to investigate.\n\nNoble’s biography describes him as a historian and critic of technology, science, and education. He obtained degrees from the University of Florida and the University of Rochester, taught at MIT, the Smithsonian Institution, Drexel University, and York University, and was known for works such as *America by Design* and *Forces of Production*. He was denied tenure at MIT, and throughout his career he criticized the corporatization of universities. He received the Joe A. Callaway Award for Civic Courage in 1998. He died suddenly on December 27, 2010, from septic shock and kidney failure caused by pneumonia.', 'Thompson Rivers University (TRU) in Kamloops, B.C., suspended economics professor Derek Pyne for one year without pay or benefits on July 16, 2020, over a Facebook post he made on June 10, 2020. Pyne, who teaches in the School of Business and Economics, said the suspension was the second time TRU had disciplined him in connection with an academic freedom dispute. He said he was surprised by the university’s action. “I did not think that even TRU would be foolish enough to go after me for such an obvious issue of academic freedom, given how much bad publicity they generated when they attacked my academic freedom in the past.”\n\nPyne’s first suspension came in 2018, after he published research into so-called predatory journals. His paper, “The Rewards of Predatory Publications at a Small Business School,” was published by the University of Toronto Press Journal of Scholarly Publishing. In it, he claimed that more than half of the faculty members in the TRU department of Business and Economics had published papers in illegitimate journals to advance their careers. Pyne said he was banned from campus in May 2018 and suspended in July 2018. TRU’s then-interim president, Christine Bovis-Cnossen, said at the time that the discipline was not related to his research but that she could not comment further due to employment and privacy law. Pyne was reinstated in January 2019. A committee of investigation established by the Canadian Association of University Teachers (CAUT) concluded in November 2019 that TRU’s administration had breached Pyne’s academic freedom and his privacy. The committee found that TRU “appears to suffer a broad institutional weakness when it comes to understanding academic freedom,” and that the university failed to understand academic freedom beyond a “narrow application to support faculty members’ freedom to pursue what they expect to be fruitful avenues of research and publish their results.” The committee recommended that TRU review its human resources practices to ensure academic freedom was properly understood and protected. TRU did not participate in the investigation, saying CAUT did not have authority or jurisdiction to probe issues covered by the collective agreement.\n\nThe Facebook post that led to the latest suspension praised the Brock University Faculty Association (BUFA) for supporting Tomas Hudlicky, a chemistry professor at Brock University who had been at the centre of controversy. Hudlicky had written an essay in the chemistry journal Angewandte Chemie that criticized employment equity hiring and commented on skills transfer between “masters and apprentices.” The journal retracted the essay after backlash, and Brock University apologized, saying the essay did not reflect the university’s values. BUFA published a statement supporting academic freedom. In his June 10 Facebook post, Pyne wrote: “Some good news for a change. Unlike Thompson Rivers University Faculty Association, it seems that some university unions are not opposed to academic freedom. One can debate some of the details of the following statement but the bottom line is that it comes out in support of academic freedom, even when it goes against the university, and the union’s, positions.” In a comment, Pyne tagged the Federation of Post-Secondary Educators and several members of TRU’s Faculty Association (TRUFA). He also predicted that TRUFA members would “go running” to Larry Phillips, the executive director of human resources at TRU, to defend them. The post was shared three times.\n\nAccording to Pyne, two complainants told TRU that being tagged in the post led to them losing sleep, and one claimed she needed time off work to recover. A union executive member and steward filed the harassment complaint. Pyne said he was called to a human resources meeting with Phillips, who read him a four-page letter from TRU president Brett Fairbairn. Pyne was told he had been suspended for one year with no pay and no benefits, and he was also cut off from his TRU email account, which he said contains information he requires. He said he did not have a last chance to access his work email.\n\nTRU spokesperson Darshan Lindsay said the university could not provide specific information on personnel matters due to employment and privacy laws, but stated: “We want to be clear that matters involving Dr. Pyne are not about the exercise of academic freedom.” Lindsay added that TRU fully supports academic freedom, “including the ability to conduct independent research, freely communicate knowledge and the results of research and scholarship, and respectfully debate differences.” She also said it was “unlikely the university would suspend an employee for a single social media post,” and that employees have avenues for appeal through their union or the British Columbia Labour Relations Board. Fairbairn made the same points in a letter dated July 28, 2020, in response to an inquiry from the Society for Academic Freedom and Scholarship (SAFS).\n\nThe SAFS, an organization dedicated to defending academic freedom and the merit principle in higher education, sent a letter to TRU on July 27, 2020. Mark Mercer, the society’s president and a philosophy professor at Saint Mary’s University, said Pyne’s suspension was “a serious violation of his academic freedom.” The letter argued that Pyne’s right to criticize both TRU and his faculty association is protected by Article 9.6 of the TRU Collective Agreement. Mercer also wrote that “providing people an opportunity to know what one is thinking cannot be a case of harassment, especially when the people Dr Pyne tagged on Facebook were union officials.” He said denying Pyne the use of his office, university email address, and other university resources would severely impede his work as a scholar, and demanded that TRU explain why its action was not an attack on academic standards and values.\n\nPyne said appealing his suspension through his union made little sense because it was a union executive member and steward who filed the complaint that led to his suspension. However, after the suspension, Pyne received correspondence from TRUFA, including a copy of a grievance that listed academic freedom as a ground. Pyne said TRUFA had previously opposed action on academic freedom grounds, and that if the union was serious about the new grievance, “it really will change things.” TRUFA was demanding that the suspension be rescinded and that Pyne be reinstated with full retroactive salary and benefits. A previous complaint Pyne filed with the BC Labour Relations Board had been dismissed in July 2019, and his appeal was denied; the board said it lacked jurisdiction under Section 12 of the province’s labour code to determine whether academic freedom rights had been violated, and that such rights were a matter for arbitration under the TRU-TRUFA collective agreement.\n\nPyne said he was unsure of his next steps and had asked several organizations for advice. He said universities need to respect academic freedom, stating: “I think that the public has a right to know how tax dollars are being misused by a public institution. More generally, I think academic freedom is essential for the advancement of knowledge.” He also said: “At some point, a line has to be drawn or academic freedom will only be a right on paper.”', 'Thompson Rivers University (TRU) in Kamloops, B.C. became the centre of a controversy involving predatory academic publishing and academic freedom after economics professor Derek Pyne conducted research on so-called “predatory journals”—publications that claim to be peer reviewed but in reality publish articles in exchange for fees paid by authors, often with little or no scrutiny. Pyne, an associate professor in TRU’s School of Business and Economics, began researching the rewards for faculty who published in such journals, and in April 2017 published a peer-reviewed article, “The Rewards of Predatory Publications at a Small Business School,” in the Journal of Scholarly Publishing, a publication of the University of Toronto Press. His study reported that about half of more than three dozen faculty and administrators in the school had published in suspect journals, sometimes frequently, and that such publications were linked to promotions, research awards, and financial remuneration. Although the article did not name TRU, it became known that the school studied was TRU’s School of Business and Economics. Pyne also wrote an opinion piece for the Ottawa Citizen in April 2017 titled “Are universities complicit in predatory publishing?” and later gave interviews to The New York Times, The Economist, and other international media.\n\nPyne had communicated his findings and concerns to TRU administrators, including the dean, provost, and others, before publication. He said his communications created friction with the dean and that the university made no attempt to discuss, verify, or address the issue. His research was supported financially by TRU’s Office of Research and Graduate Studies. During the same period, Pyne publicly questioned the quality of the School of Business and Economics and its new professional master’s degree programs, including comments posted on a local media website. His department passed motions criticizing those comments. Complaints about Pyne led to multiple human resources processes. In June 2016 he received a formal notice of discipline related to communications with colleagues and administrators. In December 2017 a research misconduct complaint was filed against him under TRU’s Integrity in Research and Scholarship policy; it was later determined to be unfounded, but another similar complaint was filed shortly afterward. Pyne was required to undergo a psychological examination, which took place on June 4, 2018; the resulting report found no evidence of mental illness.\n\nOn May 17, 2018, Pyne was notified he was prohibited from being on campus, though he was still expected to perform his regular duties. On May 30, TRU’s human resources department accused him of making “defamatory and insubordinate” comments. On June 15, during a consultation process for an internal candidate for associate dean, Pyne submitted feedback that discussed the candidate’s publications in allegedly predatory journals. The university responded by accusing him of “defamatory language and accusations.” On July 17, 2018, Pyne was suspended indefinitely without pay, with written notification on July 23. TRU stated the suspension was based on insubordination and inappropriate, threatening, and defamatory statements. Pyne contended his statements were factual. After the Thompson Rivers University Faculty Association (TRUFA) became aware of the suspension, it was reduced to a two-week suspension ending July 31, and TRUFA filed a grievance. TRU later restored Pyne’s pay after media coverage, but he remained banned from teaching and from campus except in limited circumstances. The university declined to explain the reasons for its actions, citing privacy laws and the need to protect the personal information of employees.\n\nThe Canadian Association of University Teachers (CAUT) became aware of Pyne’s case through media coverage and, after reviewing initial evidence, established an ad hoc investigatory committee on October 30, 2018, to investigate whether TRU violated Pyne’s academic freedom and whether the suspension was appropriate. The committee was chaired by Mark Mac Lean of the University of British Columbia and included Carla Graebner of Simon Fraser University. TRU declined to participate, with interim president Christine Bovis-Cnossen stating that CAUT had no authority or jurisdiction to investigate matters covered by the collective agreement, and that the appropriate process would be a grievance filed by TRUFA. TRUFA did not file an academic freedom grievance. Pyne also filed a complaint under Section 12 of the B.C. Labour Code alleging TRUFA breached its duty of fair representation; that complaint was dismissed by the Labour Board, which noted it did not have jurisdiction to determine academic freedom violations.\n\nTRU’s interim president issued public statements asserting that “Action taken against Dr. Pyne was not related to his specific research, the dissemination of his research, or the exercising of his right to academic freedom.” She said academic freedom was fully protected under the collective agreement and that faculty hired or promoted at TRU go through a robust peer review process. Some academics, including UBC professor Michael Byers and Mark Mercer of the Society for Academic Freedom and Scholarship, called for transparency or government intervention. The B.C. government declined to intervene, citing the University Act provision that a minister must not interfere in the exercise of powers conferred on a university. TRU also complained to the Vancouver Sun about its coverage, saying the newspaper misrepresented TRU by failing to include the university’s full statement.\n\nThe CAUT investigatory committee released its report in November 2019. It concluded that TRU appeared to suffer from a broad institutional weakness in understanding academic freedom beyond its narrow application to research and publication. It found significant breaches of Pyne’s academic freedom with respect to the administration’s responses to his intramural and extramural communications criticizing the School of Business and Economics, its programs, and its faculty. The committee held that the collective agreement’s Article 9.6 on academic freedom created a positive obligation on the parties to consider academic freedom in any case involving speech from faculty members, and that the failure to do so denied Pyne procedural fairness. It found no evidence that any person at TRU interfered with Pyne’s actual research, but it concluded that the decision to suspend him was not made on a sound basis. It also found serious breaches of Pyne’s privacy by both TRU and TRUFA, particularly with respect to the circulation of his psychological report. The report identified emergent themes including the “pathologizing of dissent,” failures of human resources processes to respect academic freedom, failures to protect medical privacy, and a failure of academic governance with respect to considering predatory journals in tenure and promotion decisions. It made recommendations that TRU complete an academic freedom policy, review HR practices, manage conflicts of interest, remove constraints on Pyne’s speech, and have the Senate Tenure and Promotion Committee review the use of predatory publications in tenure and promotion.\n\nThe controversy also drew attention to the broader phenomenon of predatory publishing. Jeffrey Beall, a former University of Colorado librarian, created a database of about 12,000 questionable journals, and the Texas company Cabell’s compiled a similar list of almost 9,000 journals. A sting operation by John Bohannon, described in The Economist, found that 69 percent of journals chosen from a blacklist offered to publish a fake paper for a fee, and 38 percent of supposedly trustworthy whitelisted open-access journals also accepted it. Estimates cited in the documents indicated that articles published in disputed journals grew from about 53,000 in 2010 to more than 400,000 annually. The debate over predatory journals has increasingly shifted from the idea that authors are victims to the view that many academics knowingly use them to inflate publication records and advance careers. Pyne’s case became a symbol of the risks of exposing such practices, especially for faculty who challenge their own institutions. TRU’s incoming president, Brett Fairbairn, who took office in December 2018, had previously resigned as provost at the University of Saskatchewan after suspending a professor who criticized administration budget cuts, raising further concerns about academic freedom at TRU.']</t>
+          <t>['Patrick Provost, a professor at Université Laval in Quebec, became the subject of academic-freedom controversy after making public comments critical of mRNA COVID-19 vaccines. According to a June 30, 2022 article by The Canadian Press, Provost, a professor of microbiology and immunology who studies micro RNA — small molecules that help regulate genes — was suspended for eight weeks without pay on June 14, 2022. The suspension stemmed from comments he made in December 2021 at a conference organized by Reinfo Covid Quebec, a group that has criticized COVID-19 public health measures and been accused of spreading misinformation about vaccines. At that conference, Provost said he believed the risks of COVID-19 vaccination in children outweigh the benefits because of potential side-effects from mRNA vaccines, which use messenger RNA created in a lab to teach cells how to make a protein. Following the conference, Provost sent an email to all professors at Université Laval encouraging them to share their knowledge and expertise with the public, referencing his December speech. That email led to a complaint from a colleague. A university committee consisting of a lawyer and two experts concluded that his comments were biased and that he did not analyze his data rigorously or present his information objectively.\n\nProvost defended his actions, saying, "I was just doing what I was hired to do. I had some concerns about something, I searched the literature and I prepared a speech, delivered it to the public. Being censored for doing what I\'ve been trained to do — and hired to do — well, it\'s hard to believe." He also said, "As soon as you raise some concerns about vaccines, or side-effects, or complications related to vaccines, then it\'s worse than the N-word. You\'re condemned by the media, by the government and you\'re chased and put down." He added that because he expressed opinions that went against the government narrative, he was suspended.\n\nSimon Viviers, vice-president of the Université Laval faculty union, said the union had filed a grievance over the suspension. "For us, this is an attack on academic freedom," he said. "To allow (a university) to judge the validity of the comments made by a university professor in public and to sanction him in this manner is extremely problematic." Viviers said the university should not have used a research integrity committee to judge whether Provost\'s comments were valid. The union did not take a position on the comments themselves, only on how Provost was treated. Viviers worried that the suspension could have a dissuasive effect, "even lead to self-censorship."\n\nDavid Robinson, executive director of the Canadian Association of University Teachers, said professors should be disciplined only for comments that amount to incompetence or that violate legal limits to speech, such as libel laws. "We have to have a high tolerance for academic freedom and diversity of viewpoints," he said. He added that "naysayers" and "gadflies" need to be tolerated because they sometimes turn out to be right. Robinson cited the example of researchers who first suggested that some ulcers are caused by bacterial infection — they were dismissed by the scientific community, but the evidence eventually proved them correct. "That\'s what the university is all about — it\'s all about disagreements and it\'s through disagreements and debate, and challenging evidence that\'s presented by someone else that we eventually reach some common understanding," he said. "But we shouldn\'t stifle that debate."\n\nHowever, Dr. Mathieu Nadeau-Vallée, a medical resident at Université de Montréal with a PhD in immunology, said Provost is not an expert in the mRNA technology used in the Pfizer and Moderna COVID-19 vaccines, or in the vaccination of children. "This person doesn\'t really have the expertise to speak about all this," Nadeau-Vallée said. "He\'s a biochemistry professor; he doesn\'t study messenger RNA, he studies small RNA. It\'s not at all the same area of research. So this is a person who is expressing themselves about a subject that they\'re not really an expert in and is speaking against the scientific consensus on that subject." Nadeau-Vallée said COVID-19 vaccines and public health measures have saved lives and that academic freedom means being able to speak about any subject but does not mean that false things can be said. He said anyone who wants to speak against the scientific consensus has to show scientific evidence.\n\nAccording to local news reports, Provost was one of two professors suspended by Université Laval for anti-vaccine comments. The university declined to comment on either suspension, the union said it was not aware of the second case, and the second professor named in news reports did not respond to requests for comment. Quebec Higher Education Minister Danielle McCann said in an emailed statement that the suspensions were examples justifying the government\'s adoption earlier that month of a bill protecting academic freedom. The bill gave all universities in the province one year to create an academic freedom policy and establish a committee responsible for supervising its implementation. McCann said she was calling on Université Laval — and the province\'s other universities — to establish those policies as soon as possible. "These situations demonstrate the relevance and importance of adopting this law," she said.\n\nA later letter dated June 4, 2024, from the Society for Academic Freedom and Scholarship (SAFS) addressed the ongoing case. The letter was sent by Robert G. Thomas, President of SAFS, to Dr. Sophie D’Amours, Rector of Université Laval, at 2325, rue de l\'Université, Québec. The letter expressed concerns regarding the "recent firing" of Professor Patrick Provost at Université Laval. According to multiple media reports, as stated in the letter, Provost had been disciplined, suspended and more recently fired for his public criticisms around the use of mRNA COVID vaccines. SAFS wrote that this turn of events was regrettable not only for what it did to interfere with Provost\'s academic freedom but also because of its potential effect on the wider community. The letter argued that academic institutions maintain public trust through their disinterested search for truth and openness to scholarly critique, and that if ultimate conclusions appear preordained and certain orthodoxies may not be questioned, universities could rightly be seen as places of dogma rather than empirical investigation. SAFS stated that firing Provost sent a clear message to researchers to tread carefully when entering certain debates, creating a chill on the expression of heterodox positions, particularly in science, and impeding the discovery of new understandings. The organization respectfully requested a response from the Rector and said it would post the response along with the letter on its website. The letter was copied to Hon. Pascale Déry, MNA, Minister of Higher Education, and Marie-Hélène Parizeau, President of SPUL.', 'A dispute at Western University in London, Ontario, has centered on the limits of academic freedom in the context of COVID-19. Donald Welsh, a professor of physiology at the Schulich School of Medicine and Dentistry, has regularly tweeted and retweeted information challenging the effectiveness of COVID-19 vaccines and other public health measures. In a January 7 tweet, Welsh wrote that he suspected the health minister understood that "C19 vaccines are ineffective at mitigating infection, transmission and death" and that this "seems more like a political rather than a scientific stance." On January 13, he tweeted that "every aspect of Canada\'s public response to C19 was devoid of sound scientific reasoning." On January 23, responding to a tweet by Dr. Nathan Stall about low vaccination rates among children, Welsh wrote: "There is no need to vaccinate those who aren\'t susceptible. This is the standard practice in most of the world." That tweet drew a response from Dr. Genevieve Eastabrook, an associate professor in maternal-fetal medicine who also works at Schulich, who wrote: "This individual knows nothing about preventative medicine, vaccination or public health. Yet again, I am embarrassed to work at the same institution as this person."\n\nWelsh\'s colleague Jacob Shelley, who holds a joint appointment with Western\'s Faculty of Law and the School of Health Studies and directs the school\'s Health Ethics, Law &amp; Policy lab, accused Welsh of hiding behind the protections of academic freedom to spread misinformation about the effectiveness of COVID-19 vaccines. Shelley argued that "academic freedom comes with academic responsibilities," meaning "having integrity in our research, not just to say whatever the hell we want." He said any academic\'s public statements should have to withstand scrutiny from their peers in the same way a PhD student\'s dissertation is tested. In Shelley\'s view, Welsh\'s tweets "are not reliable information," "are not scientific," and "would not get through a peer review." Shelley had previously challenged Welsh\'s opinions on Twitter, but Welsh blocked Shelley, and Shelley\'s responses were no longer included in the threads. Shelley also said that other professors often notify him of Welsh\'s tweets in hopes he will challenge them, but they are often afraid to enter the fray themselves for fear it will be career limiting. "A lot of people are afraid to speak out because there could be consequences," Shelley said, adding that he had been told, "You should be careful because the central administration won\'t forget and this will come back to bite you."\n\nWestern University told CBC News that Welsh\'s views "do not align with the views of the Schulich School of Medicine &amp; Dentistry or Western University," and that the university is "disappointed that Don Welsh has decided to take the position that he has." The statement also said that while Welsh\'s views "contradict the position of public health and the university," there was not much the university could do about it. "As employees of the university, individual faculty members have the freedom to express their opinions and beliefs, and those views are their own and do not represent the views of the school or university," the statement said, adding that the school "continues to support all public health measures related to the ongoing pandemic." While a neonatal nurse at London Health Sciences Centre was fired last year for organizing anti-lockdown rallies and challenging public health measures such as lockdowns and masking, Welsh\'s comments are protected by academic freedom. The underlying principle is that professors should not have their research and writings influenced by fear of reprisals from their employer.\n\nWelsh, in an email to CBC News, stood by his right to state his own opinions, pointing to the statement on his Twitter profile page that the opinions stated are Welsh\'s own and do not represent Schulich or the university. He said discussion around the best public health responses to COVID-19 "is never settled and it would be incorrect to present it as such. That is why the conversation continues to evolve on places like Twitter. This process is organic and debate is fundamental." Shelley agreed that the debate should be more robust, but said the ivory tower world of academia is often averse to controversy and guided by a "don\'t rock the boat" mentality.\n\nIn response to the controversy, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members and others dedicated to the defense of academic freedom and the merit principle in higher education, sent a letter dated 4 February 2022 to Alan Shepard, President and Vice-Chancellor of Western University. The letter, written by SAFS president Mark Mercer and signed by the board of directors and past presidents, commends Western for stating publicly that "individual faculty members have the freedom to express their opinions and beliefs." The letter notes that Western professors and others had urged Western to violate the academic freedom of Donald Welsh, and that Western rejected these appeals. SAFS stated that Western has demonstrated that it understands that academic freedom is essential to the mission of the university, for it enables new ideas to be spoken and to be debated robustly. Those who disagree with Dr. Welsh are free to criticize his views and defend their own. In the absence of academic freedom, the public could not trust what academics say, as people would be suspicious that their research was guided by the need to come to approved conclusions. SAFS respectfully asked Shepard to respond to the letter and, with permission, to post the response along with the letter on the SAFS website. The letter was copied to several Western vice-provosts and deans, including the Dean of the Schulich School of Medicine &amp; Dentistry, Dr. John Yoo. The central issue remains whether academic freedom protects a faculty member\'s public comments on COVID-19 even when those comments contradict public health guidance and are seen by colleagues as misinformation. Western\'s position is that individual faculty members have the freedom to express their opinions and beliefs, and that those views are their own and do not represent the views of the school or university, while Shelley and others argue that academic freedom entails academic responsibilities and that false or unreliable claims should face peer scrutiny.', '# Summary: Suspension and Termination of Dr. Francis Christian\n\nDr. Francis Christian, a clinical professor of general surgery at the University of Saskatchewan (USask) and a practicing surgeon in Saskatoon with more than 20 years of experience, was suspended and terminated from his positions after publicly raising concerns about COVID-19 vaccination of children. As of June 2021, Christian served as Director of the Surgical Humanities Program (which he co-founded), Director of Quality and Patient Safety in the Department of Surgery, and Editor of the Journal of the Surgical Humanities. His roles overlapped with a contract position with the Saskatchewan Health Authority (SHA).\n\nOn June 17, 2021, Christian released a prepared statement to over 200 doctors and spoke at a press conference outside Walter Murray Collegiate in Saskatoon, appearing with a group called Concerned Parents Saskatchewan while a vaccine clinic was taking place at the high school. He declined to take questions from journalists. In his statement, Christian emphasized that he is a "very pro-vaccine physician" and is "pro-vaccine for my own family, including myself," citing the elimination of smallpox through vaccination. He stated he spoke "directly to parents and children" as "a physician, a surgeon and a fellow human being" and did not represent any group, the SHA, or the university.\n\nChristian invoked the "sacrosanct principle" of informed consent, arguing that patients must be made "fully aware of the risks of the medical intervention, the benefits of the intervention and if any alternatives exist to the intervention," particularly for "a new vaccine that has never before been tried in humans." He asserted this principle was "being consistently violated in this province for the m-RNA vaccine for our kids," claiming he had not met "a single vaccinated child or parent who has been adequately informed."\n\nChristian articulated eight points he argued parents and children must know before consenting: (1) that the mRNA vaccine is "a new, experimental vaccine design" never used in humans; (2) that the vaccines have not been fully authorized by Health Canada or the CDC, being under "interim authorization" in Canada and "emergency use authorization" in the US; (3) that while there is an emergency for the elderly, vulnerable, and health care workers—given that the mean age of COVID-19 deaths in Canada is 83.8—"Covid-19 does not pose a threat to our kids," with a death risk of less than 0.003%; (4) that children do not readily transmit the virus to adults; (5) that the mRNA vaccines have been "associated with several thousand deaths" in the US government\'s Vaccine Adverse Reporting System, which he called "a strong signal" that could not be ignored; (6) that there is a "real and significantly increased risk" of myocarditis (heart inflammation) in vaccinated children, leading the German national vaccine agency and the UK vaccine agency to not recommend the vaccine for healthy children; (7) that the benefit of the vaccine for children is "marginal at best," with an Absolute Risk Reduction of less than 2%; and (8) that Ivermectin is an alternative treatment. He urged authorities "to call a pause in the m-RNA vaccine roll-out to our kids" and stated that without informed consent, "the Nuremberg code is being violated." He also appeared in a video posted to the website BitChute that received nearly 70,000 views, in which he questioned the mainstream narrative about the pandemic, mocked restrictions, and called the vaccines "experimental injections."\n\nOn June 21, 2021, the Saskatchewan Health Authority and the College of Medicine wrote to Christian alleging they had "received information that you are engaging in activities designed to discourage and prevent children and adolescents from receiving Covid-19 vaccination contrary to the recommendations and pandemic-response efforts of Saskatchewan and Canadian public health authorities."\n\nOn June 23, 2021, Christian was called into a meeting with Dr. Preston Smith, Dean of the College of Medicine; Dr. Susan Shaw, Chief Medical Officer of the Saskatchewan Health Authority; and Dr. Brian Ulmer, Head of the Department of Surgery. He was informed of his immediate suspension from all faculty responsibilities and academic administrative roles, and that he would be fired from the university as of September 2021. The SHA terminated its contract with Christian, which was set to expire on September 21 following the required 90 days\' notice. Christian remained able to practice medicine and the university said it was not suspending payment for services he would have otherwise received during the investigation period. Christian recorded the 22-minute meeting and posted the audio online.\n\nDuring the meeting, Christian said, "You\'ve basically read indictments against me. These are the sort of panels that were set up in the Soviet Union and Nazi Germany against academics," adding, "I\'m not saying that you\'re Nazis or Soviets, but it\'s really disturbing, isn\'t it?" He stated he was one of many doctors being "silenced and censored," and told the officials, "You guys are living in a dystopian bubble. The truth will come out and when that bubble bursts, you guys are going to be in big trouble." Shaw expressed concern that Christian was "a highly intelligent man" who was "not making intelligent decisions," and Christian was offered supports if he was feeling distressed, which he declined.\n\nIn a statement, Dean Smith said the University "encourages public debate of important societal issues," but noted that per USask\'s Medical Faculty Policy, "our medical faculty are subject to the ethical and professional standards governing the practice of medicine." Smith told Global News that "when somebody is saying things that are at such great variance with all of our experts and worldwide experts and public safety is involved and could be jeopardized through these differences of view, I think we have to recognize that that\'s a special situation that requires urgent and extraordinary action." The SHA stated that "health system leaders are expected to be committed to fact-based, scientifically driven public messaging" and that leaders who depart "in favour of conspiracy theories put lives at risk by potentially discouraging uptake on life-saving vaccines."\n\nThe Justice Centre for Constitutional Freedoms announced it was representing Christian in his appeals and before the College of Physicians and Surgeons of Saskatchewan, against a complaint objecting to his advocacy for informed consent. Litigation Director Jay Cameron said the termination was "a violation of his charter-protected right to freedom of thought, belief, opinion and expression, and a betrayal of the principles of scientific inquiry," and described "a clear pattern of highly competent and skilled medical doctors in very esteemed positions being taken down and censored or even fired, for practicing proper science and medicine." The Justice Centre also drew comparisons to its representation of Dr. Chris Milburn in Nova Scotia, who faced disciplinary proceedings over an opinion column.\n\nOn June 30, 2021, the Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Dean Smith requesting an explanation of "how Dr Christian\'s suspension is not a violation of his academic freedom and how his suspension will not tend to create a chilly climate for expression on campus." SAFS argued that "nothing that has been reported should draw any discipline at all" and that "academic freedom protects his rights to have them and to express them publicly," noting the importance of professors being "free to question received wisdom and official policy" during a pandemic.']</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'employer', 'decision', 'request', 'control', 'bargaining']</t>
+          <t>['course', 'notes', 'agreement', 'teaching', 'materials', 'decision', 'request', 'employer', 'control', 'bargaining']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['On 30 March 2020, Mark Mercer, PhD, President of the Society for Academic Freedom and Scholarship (SAFS), wrote to Leslie Phillmore, PhD, Acting Associate Dean (Academic) of the Faculty of Science at Dalhousie University, expressing concern about Dalhousie’s decision of 19 March 2020 to remove Gábor Lukács as instructor from his section of Math 1115. SAFS is described as an organization of university faculty members and others dedicated to the defense of academic freedom and the merit principle in higher education.\n\nSAFS offered three grounds for concern. First, the decision appeared inconsistent with the principle that professors of courses are well positioned to make sound and fair pedagogical decisions. According to the letter, professors are granted a large sphere of freedom in teaching their courses in part because being close to their students enables them to find effective ways to teach in the specific circumstances of their classrooms. Dr. Lukács judged that once the course was moved online, fairness and student motivation required abandoning the standard grading scheme in favour of Pass/Fail. SAFS argued that a professor’s informed and conscientious decision should not be overruled unless that decision clearly puts something important at serious risk. The letter also stated that it was far from clear that, in the context of online teaching and evaluation, the Pass/Fail system would have been in any way unfair to students. Indeed, the system Dr. Lukács intended to use was very close to the new grade options announced by Teri Balser, Dalhousie’s Provost, on 26 March. Those options, in turn, were informed by recent thinking about how best to promote learning and respect the integrity of academic standards under conditions of social distancing and online teaching and evaluating.\n\nSecond, SAFS stated that Dr. Lukács was removed from his course despite the fact that he was actively seeking a resolution to the conflict over his grading decision. He had been ordered to reinstall his previous grading system and was given a very short deadline by which to comply; that deadline passed while he was discussing the matter with the Program Director. SAFS argued that the deadline could have been extended until Dr. Lukács was in a proper position to respond, and that in any case an arrangement for assigning grades could have been found that would have left Dr. Lukács the teacher in the course. The letter further suggested that Dalhousie’s unwillingness to wait until a professor had consulted with relevant officers would seem to put at risk collegial relations between the university’s administration and its professors. It also questioned why Dr. Lukács was forbidden from having contact with his students, stating that this order could serve no pedagogical purpose.\n\nThird, SAFS argued that students in the class would be distracted and puzzled by the change of instructors and would have to get used to a new teaching style. Removing Dr. Lukács could not, therefore, have been in the best interests of the students. Continuity and consistency were described as always pedagogically valuable, but more valuable than ever under the present challenging circumstances. The letter concluded that if the decision to remove Dr. Lukács stood, Dalhousie would appear to have done a disservice to respect for informed and conscientious teaching decisions, to Dr. Lukács himself, to relations between the administration and professors, and to the students in Dr. Lukács’s section of Math 1115. SAFS respectfully requested a response and asked permission to post the response along with the letter on its website.\n\nThe letter was copied to Deep Saini, President of Dalhousie University; Teri Balser, Provost and Vice-President Academic; Jeannette Janssen, Chair of the Department of Mathematics and Statistics; and Gábor Lukács, Department of Mathematics and Statistics.\n\nOn 31 March 2020, Leslie Phillmore, PhD, Associate Dean Academic (Acting) of the Faculty of Science, responded to Dr. Mercer. In her response, Dr. Phillmore stated that she could not comment on decisions made with respect to individual employees, but assured him that Dalhousie University recognizes the importance of maintaining academic freedom in teaching, research and scholarship. She also stated that Dr. Mercer was welcome to post the response on the SAFS website. The response was copied to the same recipients as the SAFS letter: Deep Saini, Teri Balser, Jeannette Janssen, and Gábor Lukács.\n\nThe correspondence as a whole documents a dispute at Dalhousie University concerning the removal of a faculty member from a course after he changed the grading scheme to Pass/Fail following the move to online teaching. SAFS defended the professor’s pedagogical judgment, criticized the timing and manner of the removal, and emphasized the potential harm to students. Dalhousie’s response declined to comment on the individual personnel decision while affirming the university’s general commitment to academic freedom.', 'The University of British Columbia Faculty Association (UBCFA) grieved against the University of British Columbia after the university required Professor Mary Bryson to sign an individual contract transferring copyright ownership in course materials for a new online Master of Educational Technology (MET) program. An arbitrator, James E. Dorsey, Q.C., issued a 97-page award on February 18, 2004, finding in favour of the union and Dr. Bryson on all counts. The university appealed to the B.C. Labour Relations Board, which upheld the arbitrator’s ruling and rejected each of the university’s grounds of appeal.\n\nThe dispute arose in the context of faculty ownership of copyright in course materials. The arbitrator noted that, under the Copyright Act, an author is presumptively the first owner of copyright, but works made in the course of employment are owned by the employer in the absence of an agreement to the contrary. However, in the university context, it is accepted that academic authors have copyright ownership of their writings unless they agree to assign it. This is characterized as the “academic or teacher exception” to the presumption of first ownership in the employer, or as an implied agreement based on custom, tradition, and shared understanding. Ownership of copyright by academic authors is important to support, foster, and preserve academic freedom. UBC Policy #88 also recognizes that ownership of and intellectual property rights to “literary works” produced by those connected with the University are vested in the individuals involved.\n\nThe Master of Educational Technology program was a joint degree offered online with the Tec de Monterrey. It was the first degree offered entirely at a distance by UBC and was intended to be fully cost recoverable. Course development for the program was managed through the Distance Education and Technology (DET) unit, which used a team-based project management approach. Faculty members developing courses were asked to sign a “MET Letter of Agreement for the Production, Development and Delivery of an Online Course” that required them to assign copyright to the university. The agreement gave the university, acting in its discretion, the right to decide which materials contributed by an author would be used in the course, the right to use materials without attributing authorship, and the right to revise or modify materials without the author’s consent.\n\nDr. Bryson, a tenured professor in the Department of Educational and Counselling Psychology and Special Education, was assigned in May 2002 to develop the core course ETEC 512 Application of Learning Theories to Instruction as part of her regular teaching load. In September 2002, she first learned of the contract from Dr. Jim Gaskell, the MET Coordinator. She objected to the contract on grounds of academic freedom and the artificial distinction between author materials and course materials. She believed the contract reduced her role to providing content and gave the university undue control and a right of censorship. She refused to sign and was removed from the assignment. The UBCFA advised members not to sign individual contracts, taking the position that the university was required to bargain with the association as the sole bargaining agent.\n\nThe union filed grievances alleging that the university violated Article 3 of the Agreement on the Framework for Collective Bargaining by negotiating directly with bargaining unit members over terms and conditions of employment, and violated Articles 4 and 12 by removing Dr. Bryson because of her membership in and activities on behalf of the association. The arbitrator found that intellectual property rights, and specifically copyright, are terms and conditions of employment. Because of the importance of the expression of ideas to academic freedom and the presumptive first ownership of copyright in faculty, issues related to copyright are part of the core of the relationship between employer and employee. The arbitrator concluded that the scope of the union’s exclusive bargaining authority includes the right to negotiate about matters related to copyright ownership of bargaining unit employees in works made in the course of their employment. He found that the university negotiated directly with individual faculty members contrary to Article 3.\n\nThe arbitrator also found that Dr. Bryson was removed from the assignment given to her by her department head because she was insisting on doing this portion of her assigned teaching in accordance with the terms of the collective agreement. The decision to remove her was punishment for her refusal to agree to work under terms different from those in the collective agreement. The arbitrator held that every bargaining unit member has a right, and perhaps a responsibility, to ensure the university complies with the collective agreement, and that refusing to make private agreements to different conditions of employment is an activity on behalf of the bargaining agent. He found that Dr. Bryson was removed because of her membership in and activities on behalf of the Faculty Association, contrary to Article 4 of the Framework Agreement. As a remedy, the arbitrator ordered the university to assign Dr. Bryson, as part of her regular teaching load, the development and teaching of ETEC 531 with Dr. Petrina.\n\nThe university appealed the decision to the B.C. Labour Relations Board. The UBCFA was determined to see the arbitrator’s decision upheld. The labour board rejected each of the university’s grounds of appeal and upheld the arbitrator’s ruling. The UBCFA president described the original ruling as a landmark victory for academic freedom and faculty rights, and the CAUT president said the decision strengthens everyone’s academic freedom and intellectual property rights. The case was seen as part of a broader struggle against the “unbundling” and commoditization of teaching in online education, and as confirming that faculty, not administrators, determine the content and spirit of courses.', 'Dr. Steven Lukits, a full-time associate professor of English at the Royal Military College of Canada in Kingston, Ontario, and a member of the University Teaching bargaining unit represented by the Canadian Military Colleges Faculty Association, filed a grievance after being ordered to produce his handwritten course notes in response to an Access to Information request. On March 22, 2013, the Access to Information Coordinator at the Canadian Defence Academy received a request for the course materials, lecture slides, handouts, course packages, and handwritten notes prepared for or by Dr. Lukits for the course English ENE 453 (War Literature II), taught between September 2012 and March 18, 2013.\n\nDr. Lukits initially discussed the request with then-Principal Dr. Joel Sokolsky. They agreed that all materials already available to students would be handed over, but Dr. Sokolsky told him not to turn over the course notes. The principal’s office sought a legal opinion from the local judge advocate general, who advised that because the course notes were created while Dr. Lukits was employed by the Crown to teach, they were considered co-owned by the Crown and subject to compliance with the ATI request. In April 2013, the CMCFA wrote to the principal taking the position that the documents did not constitute “a record under the control of the institution” under section 4(1) of the Access to Information Act, and that by custom and law such documents were in the custody and control of Professor Lukits. Principal Sokolsky wrote to the commandant and to the Chief of Military Personnel supporting the grievor’s position, stating that the normal practice of the College was to treat course notes as the personal property of the individual and not under the control of the College, and warning that acceding to the request would set a troubling precedent and call into question academic freedom at RMC. A briefing note dated April 9, 2013 similarly recommended that the course notes be exempted from the ATI request.\n\nDespite these representations, by a letter dated October 29, 2013, the Commander of the Canadian Defence Academy ordered that the grievor comply with the complete requirement of the ATI request. In the summer of 2013, Harry Cole replaced Dr. Sokolsky as principal; he showed the grievor the order and told him he had to obey it. On November 28, 2013, the grievor filed a grievance alleging that the order to produce the course notes contravened articles 5, 6.01, and 8.01 of the collective agreement. He complied with the order and produced the course notes under express reservation of rights and under threat of discipline. The course notes were held by the employer and were not released pending the grievance and adjudication process.\n\nThe employer objected to the jurisdiction of the adjudicator, arguing that the matter fell within the ambit of the Access to Information Act. That objection was dismissed in a preliminary decision, 2017 PSLREB 6. At the hearing on the merits, held in Kingston on February 2 and 3, 2017, the grievor testified and called three witnesses, all professors who were teaching or had taught at the College: Dr. Douglas Delaney, Dr. Jane Boulden, and Dr. Elizabeth Jane Errington. The employer called one witness, John O’Connell, deputy director of the Department of National Defence Access to Information and Privacy Office, who testified that the course notes were employer records because the College is part of DND.\n\nThe professors’ evidence was consistent: they believed their lecture notes were their personal property; the College did not require them to prepare course notes; the notes were in point-form format used as an aide-memoire; the College did not require them to produce the notes to anyone; the College imposed no standards for making or storing them; they were not aware that the College used the notes or integrated them into its records; they were not aware of any reliance by the College on the notes; they stored the notes on College premises; and some kept them while others destroyed them at the end of the year. The grievor testified that his course notes were original to him, personal, private, tentative, and unfinished, and that he used them as aide-memoires and for research ideas. No evidence was submitted contradicting this testimony. The adjudicator found the test for control set out in Canada (Information Commissioner) v. Canada (National Defence), as affirmed by the Supreme Court of Canada, was not met. Under that test, even where a record relates to a departmental matter, all relevant factors must be considered to determine whether the government institution could reasonably expect to obtain a copy upon request, including the substantive content of the record, the circumstances in which it was created, and the legal relationship between the institution and the record holder. Relying also on Canada (Privacy Commissioner) v. Canada (Labour Relations Board), the adjudicator held that the fact that the notes were kept on the employer’s premises did not bring them within the institution’s control.\n\nThe adjudicator concluded that the professors, not the College, maintained control over the course notes, and therefore the notes were not subject to the Access to Information Act. He also found that the grievance fell within his jurisdiction under section 209(1)(a) of the Federal Public Sector Labour Relations Act because it related to the interpretation or application of the collective agreement. Article 8.01 of the collective agreement preserves past practices where the agreement is silent on working conditions. The collective agreement was silent on who controls professors’ course notes, and the evidence established that, before and after the agreement, course notes were consistently treated as the personal property of the individual professor. The grievor therefore established the past practice on a balance of probabilities. The adjudicator further accepted that the order to produce the course notes breached article 5 of the collective agreement, which protects academic freedom. Ordering production of material created for and in the course of teaching and research that is otherwise protected by the principle of academic freedom was a breach of academic freedom. The special mission of the College, under clause 5.06, does not diminish the academic freedom of university teachers.\n\nThe decision, Lukits v. Treasury Board (Department of National Defence), 2019 FPSLREB 32, was released on March 13, 2019. The Board allowed the grievance, found that the employer breached the collective agreement, ordered the employer to return to the grievor all copies of the course notes, and ordered that the course notes entered into evidence be sealed. The CMCFA summarized the result as confirming that members own their notes and cannot be compelled to produce them to satisfy an ATI request because they are not records under the control of the Government of Canada, and that such a request would violate both past practice and academic freedom. The case has been noted as significant for confirming that teaching materials developed by an academic that are not otherwise available to the institution are protected by academic freedom, and that the location of academic records, such as storage on institutional premises or electronic systems, is not determinative of institutional custody or control.']</t>
+          <t>['On 30 March 2020, Mark Mercer, PhD, President of the Society for Academic Freedom and Scholarship (SAFS), wrote to Leslie Phillmore, PhD, Acting Associate Dean (Academic) of the Faculty of Science at Dalhousie University, expressing concern about Dalhousie’s decision of 19 March 2020 to remove Gábor Lukács as instructor from his section of Math 1115. SAFS is described as an organization of university faculty members and others dedicated to the defense of academic freedom and the merit principle in higher education.\n\nSAFS offered three grounds for concern. First, the decision appeared inconsistent with the principle that professors of courses are well positioned to make sound and fair pedagogical decisions. According to the letter, professors are granted a large sphere of freedom in teaching their courses in part because being close to their students enables them to find effective ways to teach in the specific circumstances of their classrooms. Dr. Lukács judged that once the course was moved online, fairness and student motivation required abandoning the standard grading scheme in favour of Pass/Fail. SAFS argued that a professor’s informed and conscientious decision should not be overruled unless that decision clearly puts something important at serious risk. The letter also stated that it was far from clear that, in the context of online teaching and evaluation, the Pass/Fail system would have been in any way unfair to students. Indeed, the system Dr. Lukács intended to use was very close to the new grade options announced by Teri Balser, Dalhousie’s Provost, on 26 March. Those options, in turn, were informed by recent thinking about how best to promote learning and respect the integrity of academic standards under conditions of social distancing and online teaching and evaluating.\n\nSecond, SAFS stated that Dr. Lukács was removed from his course despite the fact that he was actively seeking a resolution to the conflict over his grading decision. He had been ordered to reinstall his previous grading system and was given a very short deadline by which to comply; that deadline passed while he was discussing the matter with the Program Director. SAFS argued that the deadline could have been extended until Dr. Lukács was in a proper position to respond, and that in any case an arrangement for assigning grades could have been found that would have left Dr. Lukács the teacher in the course. The letter further suggested that Dalhousie’s unwillingness to wait until a professor had consulted with relevant officers would seem to put at risk collegial relations between the university’s administration and its professors. It also questioned why Dr. Lukács was forbidden from having contact with his students, stating that this order could serve no pedagogical purpose.\n\nThird, SAFS argued that students in the class would be distracted and puzzled by the change of instructors and would have to get used to a new teaching style. Removing Dr. Lukács could not, therefore, have been in the best interests of the students. Continuity and consistency were described as always pedagogically valuable, but more valuable than ever under the present challenging circumstances. The letter concluded that if the decision to remove Dr. Lukács stood, Dalhousie would appear to have done a disservice to respect for informed and conscientious teaching decisions, to Dr. Lukács himself, to relations between the administration and professors, and to the students in Dr. Lukács’s section of Math 1115. SAFS respectfully requested a response and asked permission to post the response along with the letter on its website.\n\nThe letter was copied to Deep Saini, President of Dalhousie University; Teri Balser, Provost and Vice-President Academic; Jeannette Janssen, Chair of the Department of Mathematics and Statistics; and Gábor Lukács, Department of Mathematics and Statistics.\n\nOn 31 March 2020, Leslie Phillmore, PhD, Associate Dean Academic (Acting) of the Faculty of Science, responded to Dr. Mercer. In her response, Dr. Phillmore stated that she could not comment on decisions made with respect to individual employees, but assured him that Dalhousie University recognizes the importance of maintaining academic freedom in teaching, research and scholarship. She also stated that Dr. Mercer was welcome to post the response on the SAFS website. The response was copied to the same recipients as the SAFS letter: Deep Saini, Teri Balser, Jeannette Janssen, and Gábor Lukács.\n\nThe correspondence as a whole documents a dispute at Dalhousie University concerning the removal of a faculty member from a course after he changed the grading scheme to Pass/Fail following the move to online teaching. SAFS defended the professor’s pedagogical judgment, criticized the timing and manner of the removal, and emphasized the potential harm to students. Dalhousie’s response declined to comment on the individual personnel decision while affirming the university’s general commitment to academic freedom.', 'Dr. Steven Lukits, a full-time associate professor of English at the Royal Military College of Canada in Kingston, Ontario, and a member of the University Teaching bargaining unit represented by the Canadian Military Colleges Faculty Association, filed a grievance after being ordered to produce his handwritten course notes in response to an Access to Information request. On March 22, 2013, the Access to Information Coordinator at the Canadian Defence Academy received a request for the course materials, lecture slides, handouts, course packages, and handwritten notes prepared for or by Dr. Lukits for the course English ENE 453 (War Literature II), taught between September 2012 and March 18, 2013.\n\nDr. Lukits initially discussed the request with then-Principal Dr. Joel Sokolsky. They agreed that all materials already available to students would be handed over, but Dr. Sokolsky told him not to turn over the course notes. The principal’s office sought a legal opinion from the local judge advocate general, who advised that because the course notes were created while Dr. Lukits was employed by the Crown to teach, they were considered co-owned by the Crown and subject to compliance with the ATI request. In April 2013, the CMCFA wrote to the principal taking the position that the documents did not constitute “a record under the control of the institution” under section 4(1) of the Access to Information Act, and that by custom and law such documents were in the custody and control of Professor Lukits. Principal Sokolsky wrote to the commandant and to the Chief of Military Personnel supporting the grievor’s position, stating that the normal practice of the College was to treat course notes as the personal property of the individual and not under the control of the College, and warning that acceding to the request would set a troubling precedent and call into question academic freedom at RMC. A briefing note dated April 9, 2013 similarly recommended that the course notes be exempted from the ATI request.\n\nDespite these representations, by a letter dated October 29, 2013, the Commander of the Canadian Defence Academy ordered that the grievor comply with the complete requirement of the ATI request. In the summer of 2013, Harry Cole replaced Dr. Sokolsky as principal; he showed the grievor the order and told him he had to obey it. On November 28, 2013, the grievor filed a grievance alleging that the order to produce the course notes contravened articles 5, 6.01, and 8.01 of the collective agreement. He complied with the order and produced the course notes under express reservation of rights and under threat of discipline. The course notes were held by the employer and were not released pending the grievance and adjudication process.\n\nThe employer objected to the jurisdiction of the adjudicator, arguing that the matter fell within the ambit of the Access to Information Act. That objection was dismissed in a preliminary decision, 2017 PSLREB 6. At the hearing on the merits, held in Kingston on February 2 and 3, 2017, the grievor testified and called three witnesses, all professors who were teaching or had taught at the College: Dr. Douglas Delaney, Dr. Jane Boulden, and Dr. Elizabeth Jane Errington. The employer called one witness, John O’Connell, deputy director of the Department of National Defence Access to Information and Privacy Office, who testified that the course notes were employer records because the College is part of DND.\n\nThe professors’ evidence was consistent: they believed their lecture notes were their personal property; the College did not require them to prepare course notes; the notes were in point-form format used as an aide-memoire; the College did not require them to produce the notes to anyone; the College imposed no standards for making or storing them; they were not aware that the College used the notes or integrated them into its records; they were not aware of any reliance by the College on the notes; they stored the notes on College premises; and some kept them while others destroyed them at the end of the year. The grievor testified that his course notes were original to him, personal, private, tentative, and unfinished, and that he used them as aide-memoires and for research ideas. No evidence was submitted contradicting this testimony. The adjudicator found the test for control set out in Canada (Information Commissioner) v. Canada (National Defence), as affirmed by the Supreme Court of Canada, was not met. Under that test, even where a record relates to a departmental matter, all relevant factors must be considered to determine whether the government institution could reasonably expect to obtain a copy upon request, including the substantive content of the record, the circumstances in which it was created, and the legal relationship between the institution and the record holder. Relying also on Canada (Privacy Commissioner) v. Canada (Labour Relations Board), the adjudicator held that the fact that the notes were kept on the employer’s premises did not bring them within the institution’s control.\n\nThe adjudicator concluded that the professors, not the College, maintained control over the course notes, and therefore the notes were not subject to the Access to Information Act. He also found that the grievance fell within his jurisdiction under section 209(1)(a) of the Federal Public Sector Labour Relations Act because it related to the interpretation or application of the collective agreement. Article 8.01 of the collective agreement preserves past practices where the agreement is silent on working conditions. The collective agreement was silent on who controls professors’ course notes, and the evidence established that, before and after the agreement, course notes were consistently treated as the personal property of the individual professor. The grievor therefore established the past practice on a balance of probabilities. The adjudicator further accepted that the order to produce the course notes breached article 5 of the collective agreement, which protects academic freedom. Ordering production of material created for and in the course of teaching and research that is otherwise protected by the principle of academic freedom was a breach of academic freedom. The special mission of the College, under clause 5.06, does not diminish the academic freedom of university teachers.\n\nThe decision, Lukits v. Treasury Board (Department of National Defence), 2019 FPSLREB 32, was released on March 13, 2019. The Board allowed the grievance, found that the employer breached the collective agreement, ordered the employer to return to the grievor all copies of the course notes, and ordered that the course notes entered into evidence be sealed. The CMCFA summarized the result as confirming that members own their notes and cannot be compelled to produce them to satisfy an ATI request because they are not records under the control of the Government of Canada, and that such a request would violate both past practice and academic freedom. The case has been noted as significant for confirming that teaching materials developed by an academic that are not otherwise available to the institution are protected by academic freedom, and that the location of academic records, such as storage on institutional premises or electronic systems, is not determinative of institutional custody or control.', 'The University of British Columbia Faculty Association (UBCFA) grieved against the University of British Columbia after the university required Professor Mary Bryson to sign an individual contract transferring copyright ownership in course materials for a new online Master of Educational Technology (MET) program. An arbitrator, James E. Dorsey, Q.C., issued a 97-page award on February 18, 2004, finding in favour of the union and Dr. Bryson on all counts. The university appealed to the B.C. Labour Relations Board, which upheld the arbitrator’s ruling and rejected each of the university’s grounds of appeal.\n\nThe dispute arose in the context of faculty ownership of copyright in course materials. The arbitrator noted that, under the Copyright Act, an author is presumptively the first owner of copyright, but works made in the course of employment are owned by the employer in the absence of an agreement to the contrary. However, in the university context, it is accepted that academic authors have copyright ownership of their writings unless they agree to assign it. This is characterized as the “academic or teacher exception” to the presumption of first ownership in the employer, or as an implied agreement based on custom, tradition, and shared understanding. Ownership of copyright by academic authors is important to support, foster, and preserve academic freedom. UBC Policy #88 also recognizes that ownership of and intellectual property rights to “literary works” produced by those connected with the University are vested in the individuals involved.\n\nThe Master of Educational Technology program was a joint degree offered online with the Tec de Monterrey. It was the first degree offered entirely at a distance by UBC and was intended to be fully cost recoverable. Course development for the program was managed through the Distance Education and Technology (DET) unit, which used a team-based project management approach. Faculty members developing courses were asked to sign a “MET Letter of Agreement for the Production, Development and Delivery of an Online Course” that required them to assign copyright to the university. The agreement gave the university, acting in its discretion, the right to decide which materials contributed by an author would be used in the course, the right to use materials without attributing authorship, and the right to revise or modify materials without the author’s consent.\n\nDr. Bryson, a tenured professor in the Department of Educational and Counselling Psychology and Special Education, was assigned in May 2002 to develop the core course ETEC 512 Application of Learning Theories to Instruction as part of her regular teaching load. In September 2002, she first learned of the contract from Dr. Jim Gaskell, the MET Coordinator. She objected to the contract on grounds of academic freedom and the artificial distinction between author materials and course materials. She believed the contract reduced her role to providing content and gave the university undue control and a right of censorship. She refused to sign and was removed from the assignment. The UBCFA advised members not to sign individual contracts, taking the position that the university was required to bargain with the association as the sole bargaining agent.\n\nThe union filed grievances alleging that the university violated Article 3 of the Agreement on the Framework for Collective Bargaining by negotiating directly with bargaining unit members over terms and conditions of employment, and violated Articles 4 and 12 by removing Dr. Bryson because of her membership in and activities on behalf of the association. The arbitrator found that intellectual property rights, and specifically copyright, are terms and conditions of employment. Because of the importance of the expression of ideas to academic freedom and the presumptive first ownership of copyright in faculty, issues related to copyright are part of the core of the relationship between employer and employee. The arbitrator concluded that the scope of the union’s exclusive bargaining authority includes the right to negotiate about matters related to copyright ownership of bargaining unit employees in works made in the course of their employment. He found that the university negotiated directly with individual faculty members contrary to Article 3.\n\nThe arbitrator also found that Dr. Bryson was removed from the assignment given to her by her department head because she was insisting on doing this portion of her assigned teaching in accordance with the terms of the collective agreement. The decision to remove her was punishment for her refusal to agree to work under terms different from those in the collective agreement. The arbitrator held that every bargaining unit member has a right, and perhaps a responsibility, to ensure the university complies with the collective agreement, and that refusing to make private agreements to different conditions of employment is an activity on behalf of the bargaining agent. He found that Dr. Bryson was removed because of her membership in and activities on behalf of the Faculty Association, contrary to Article 4 of the Framework Agreement. As a remedy, the arbitrator ordered the university to assign Dr. Bryson, as part of her regular teaching load, the development and teaching of ETEC 531 with Dr. Petrina.\n\nThe university appealed the decision to the B.C. Labour Relations Board. The UBCFA was determined to see the arbitrator’s decision upheld. The labour board rejected each of the university’s grounds of appeal and upheld the arbitrator’s ruling. The UBCFA president described the original ruling as a landmark victory for academic freedom and faculty rights, and the CAUT president said the decision strengthens everyone’s academic freedom and intellectual property rights. The case was seen as part of a broader struggle against the “unbundling” and commoditization of teaching in online education, and as confirming that faculty, not administrators, determine the content and spirit of courses.']</t>
         </is>
       </c>
     </row>
@@ -677,26 +677,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1_comments_racism_letter_canada</t>
+          <t>0_letter_comments_expression_wrote</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
+          <t>['letter', 'comments', 'expression', 'wrote', 'saying', 'views', 'social', 'statement', 'racism', 'class']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
+          <t>letter - comments - expression - wrote - saying - views - social - statement - racism - class</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -727,26 +727,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1_comments_racism_letter_canada</t>
+          <t>0_letter_comments_expression_wrote</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
+          <t>['letter', 'comments', 'expression', 'wrote', 'saying', 'views', 'social', 'statement', 'racism', 'class']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
+          <t>letter - comments - expression - wrote - saying - views - social - statement - racism - class</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -777,30 +777,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0_committee_president_board_hall</t>
+          <t>1_committee_president_board_public</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
+          <t>['committee', 'president', 'board', 'public', 'caut', 'applicants', 'hall', 'grievor', 'school', 'search']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['The grievor, Chad Thompson, had been employed as an Assistant Professor at University College of the North (UCN) for approximately two years when he was terminated in August 2011 for insubordination, insolence and defiant behaviour in the context of his involvement on a search committee. The termination occurred following his role as Chair of the Selection Board for Competition No. 3145, a search to fill a full-time, regular Social Science Instructor position in the Faculty of Arts and Sciences. The grievor held a full-time tenure track position within the bargaining unit represented by the Manitoba Government and General Employees\' Union.\n\nNorma Baker, the grievor\'s spouse and Dean of the Faculty of Arts and Sciences, was initially involved in preparing the posting and reviewing applications, but then went on sick leave. Because of concern about delay, the Vice-President - Academic, Kathryn McNaughton, requested that the grievor chair the search committee. The committee shortlisted two candidates, Aaron Crowe and Jason Hildebrandt. Crowe was interviewed, while Hildebrandt was unavailable due to an injury. The search committee unanimously endorsed Crowe, pending reference checks. Although UCN policy provided that Human Resources would check references, there was discussion by the committee and it was decided that Baker, as an academic, should conduct the reference checks, with the input of Human Resources committee member Linda Hunt. Baker did conduct the reference checks of Crowe. Linda Hunt prepared the Selection Board Report and submitted it to Interim President Konrad Jonasson with the committee\'s recommendation to hire Crowe.\n\nBy e-mail of July 14, 2011, Jonasson refused to approve the recommendation. He raised concerns including an appearance of conflict of interest by having both Baker and the grievor involved, questions about the second candidate\'s inability to interview, the educational qualifications of the recommended candidate, and whether information regarding the candidate\'s PhD program was current. Jonasson offered two options: consider the search failed and start anew, or go back and review all candidates to determine if any of the three not granted interviews should be interviewed and whether the second candidate remained interested. The e-mail concluded that if the other three did not merit an interview and candidate 2 could not go forward, the search should be declared failed and restarted. Baker, the grievor, committee member Sandra Barber, and McNaughton interpreted this e-mail as a declaration of failed search. Jonasson testified that it was designed to indicate concerns and solicit additional information, and that he did not declare a failed search until a subsequent e-mail on July 15.\n\nOn July 15, 2011 at 8:54 a.m., the grievor directed an e-mail to Linda Hunt stating that he would not be submitting his notes and ratings for the LTF hiring process, that given the actions of the Interim President regarding competition 3145 he had no confidence that Mr. Jonasson would respect the policies and procedures of HR, and that he was unwilling to participate any further in this or any other hiring committee until he regained confidence in the process. The e-mail was copied to the head of Human Resources and to McNaughton, but not to Jonasson. The grievor testified that he was not attempting to hide anything, that he felt it was part of his role to speak out where he believed the governance of the institution to be in error, and that he did not regret sending the message, although he wished he had worded it more carefully.\n\nAt 9:14 a.m. on July 15, approximately twenty minutes after the e-mail to Hunt, the grievor sent an e-mail directly to Aaron Crowe, advising him that, as Chair of the Selection Committee, he was writing with deepest regret to inform him of the decision by Interim President Mr. Konrad Jonasson to reject the unanimous recommendation of the Selection Committee to offer him the position. The e-mail suggested that Crowe might wish to speak with Human Resources regarding UCN policy HR-03-0 and with MGEU regarding Article 11:04 in the collective agreement, and was copied to the Manager of Human Resources and two Union staff representatives, including Nelson. Jonasson considered this a violation of protocol and a breach of confidentiality of the selection process. The grievor acknowledged he was angry, that he felt Jonasson\'s decision was not just, that sending the e-mail was a "very stupid thing to do," and that he regretted having done so. Crowe, an internal candidate, subsequently grieved the failure to award him the position.\n\nBy letter of August 10, 2011, Jonasson issued Baker a disciplinary reprimand for various misconduct, including her involvement on the search committee, her involvement in contacting references, and her e-mail of July 15. Baker was out of scope and not in a position to grieve that discipline; she subsequently resigned her position with UCN. Jonasson met with the grievor and Union representative Nelson on July 27, 2011 to review concerns. There was an issue as to whether the grievor offered regret or an apology; Jonasson had no recollection of an apology, while the grievor believed he showed regret and offered an apology, and Nelson testified that the grievor apologized at least twice or perhaps three times. Subsequent to that meeting, the grievor\'s position was terminated by letter of August 17, 2011.\n\nThe letter of termination stated that the grievor\'s actions relating to competition no. 3145 were in fundamental breach of his employment obligations. It cited three reasons: first, without the knowledge or approval of Human Resources, he allowed Baker to continue to participate on the Selection Board after she withdrew and allowed her to contact references on behalf of UCN, which was a significant breach of trust and a clear breach of policy; second, the grievor made insolent allegations against the Interim President in his e-mail to Hunt, stating he had no confidence that Jonasson would respect HR policies and procedures; and third, the grievor violated UCN policy by sending an e-mail directly to the recommended candidate advising him of the rejection, copying representatives of the MGEU Union who were not employees of UCN, and highlighting sections of the Collective Agreement for the unsuccessful applicant. The letter asserted that the grievor\'s conduct was clearly intended to undermine the authority of the Interim President.\n\nThe Employer argued that the grievor was a short term employee who had been insubordinate, insolent and defiant without justification, that his evidence was misleading in an attempt to minimize what he had done, and that the e-mails were inappropriate and sent without justification. The Employer submitted that this was extreme insubordination striking at the heart of the employment relationship, that none of the normal factors of mitigation were present, and that dismissal was the appropriate response. The Employer noted that the grievor had not demonstrated exceptional financial hardship other than what one would normally anticipate from a termination, and argued that even if academic freedom were engaged, it was not used responsibly.\n\nThe Union asserted that while there was conduct deserving of discipline, there had been no progressive discipline and termination was simply too severe. The Union pointed out that the grievor had an unblemished record, that Jonasson acknowledged he had not looked at the grievor\'s prior clear record, and that another individual, Baker, had received only a written reprimand for similar conduct, demonstrating inconsistency in the application of discipline. The Union argued that the e-mail to Crowe was written in the heat of the moment, that the grievor accepted responsibility for his actions, that the reference checks were done with the involvement of Human Resources, and that the e-mail to Hunt was an expression of concern over the hiring process, related to the service component of his role and potentially within academic freedom under Article 72 of the Collective Agreement. The Union requested reinstatement and compensation, with a letter of reprimand as the appropriate discipline.\n\nThe arbitrator, R.A. Simpson, found that while the grievor\'s conduct was insubordinate and warranted discipline, termination was not justified. The arbitrator noted that although the grievor was entitled to consider the July 14 e-mail equivalent to a declaration of failed search, that did not excuse his subsequent conduct. The e-mail to Hunt, containing comments about the Interim President\'s respect for HR policies, had a degree of insolence amounting to insubordination and was not within the service component of the grievor\'s role or within the parameters of academic freedom, but considered in isolation, it could have been dealt with through perhaps a verbal or at most a written reprimand. The e-mail to Crowe was clearly insubordinate, involving a breach of confidentiality, disclosure of confidential information, an invitation to challenge the Employer\'s decision, and a defiance of and challenge to the Employer\'s authority. However, the arbitrator was not satisfied that the employment relationship was irreparably harmed or could not be successfully rehabilitated. The grievor was not a long term employee, but his record over two years was without blemish, he was not challenged on his evidence as to exceptional services he had provided, and dismissal would have a significant adverse effect upon his career. There was no evidence that progressive discipline short of termination was considered. The arbitrator accepted the Employer\'s argument that there was a significant difference between Baker\'s situation and the grievor\'s, with Baker communicating with colleagues and advocating for faculty and students, as opposed to the grievor communicating with an unsuccessful candidate and disclosing confidential information. Nevertheless, a lesser discipline could well have been sufficient to rehabilitate the employment relationship. The arbitrator substituted a two-month suspension without pay for the termination, stating that this was a significant penalty that should send a message that such behaviour would not be tolerated. The grievance was allowed, the termination rescinded, and a two-month suspension without pay substituted.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.']</t>
+          <t>['Between March 2011 and July 2012, the University of Calgary (U of C) worked to secure a sponsorship from Enbridge, a Calgary-based oil and gas pipeline company, to establish a research institute at the Haskayne School of Business (HSB). Dr. Joe Arvai, a recently appointed faculty member, was asked to be director of what became the Enbridge Centre for Corporate Sustainability (ECCS). The sponsorship agreement, dated July 1, 2011, was between Enbridge and “The Governors of the University of Calgary,” committing $225,000 annually over ten years. However, planned activities were based on an annual budget of $500,000, more than double Enbridge’s financial outlay, creating an immediate funding shortfall that was supposed to be made up by additional corporate fundraising.\n\nDuring the establishment and launch of the ECCS, Arvai repeatedly raised concerns about Enbridge’s influence over the Centre’s academic mission. Emails disclosed through freedom of information requests showed that Enbridge exerted influence over the Centre’s name, the selection of partner institutions, the planning of the public launch, and the role of the director. Enbridge pressed for Central Michigan University (CMU) as a partner, in part because CMU had given Enbridge "very valuable advice" after the 2010 Kalamazoo River oil spill in Michigan; Arvai objected on academic grounds, saying CMU had only one faculty member in the relevant field, but was pressured to accept. HSB Dean Len Waverman told Arvai that “the monies we give to CMU are tiny – it won’t be viewed as a payoff,” and that “Elizabeth [Cannon] will have a fit if she sees this.” Enbridge also expressed concerns about Arvai’s appointment to a U.S. Environmental Protection Agency (EPA) Scientific Advisory Board, and the university delayed its announcement of that appointment so as not to “piss off Enbridge any more.” Arvai stated that “we cannot maintain our credibility as serious scholars/researchers if the sponsors can dictate the Centre’s agenda,” and that he could not serve as director if sponsors were allowed to meddle in academic activities.\n\nArvai was removed as ECCS director in March 2012. He later told the CAUT committee that he was removed one week after he informed Enbridge’s public relations firm, National Public Relations, of his opposition on scientific grounds to the Northern Gateway pipeline. In an email of March 19, 2012, Dean Waverman told Enbridge officials: “Joe Arvai is no longer Director of the Centre, there are too many conflicts and demands!” Arvai subsequently left the U of C and is now at the University of Michigan.\n\nA CBC News investigation in November 2015 prompted the Canadian Association of University Teachers (CAUT) to establish an Ad Hoc Investigatory Committee. In his first public statement, an opinion piece reprinted by CBC News, Arvai said the CBC had done “an exceptional job of getting the facts correct,” and that the post hoc suggestions that decisions setting up the Enbridge Centre were “transparent, legitimate, and free of corporate interference or conflict-of-interest” were as difficult for him to accept as they were in 2012. He said donors should be able to suggest, but not select, advisory individuals, and should have a voice in a centre’s name and mission, but should not require that support be limited to those sharing their “core values.”\n\nThe CAUT report, released in October 2017, made findings on conflict of interest, academic freedom, external influence, funding, governance, and the McMahon review. It found a “clear appearance of a conflict of interest” on the part of U of C President Elizabeth Cannon, who served on the Enbridge Income Fund Holdings Board for significant remuneration while president, and who failed to publicly recuse herself from Enbridge-related matters. The report found that Cannon intervened directly with Dean Waverman, telling him that Enbridge was “not very happy,” that she wanted a good relationship with Enbridge, and emphasizing “I am on one of their Boards!” The report also found that the U of C Board of Governors failed to review or approve the sponsorship agreement, despite being a party to it, and that Cannon’s reliance on an “administrative lapse” was an “unacceptable evasion of responsibility.”\n\nThe CAUT committee concluded that Dr. Arvai’s academic freedom was compromised as a result of the U of C’s mishandling of the Enbridge Centre, appearing to be due to a desire on the part of senior leadership to please a significant donor. It found that Enbridge sought to influence the Centre’s establishment and launch, and that university administrators failed to convey that this influence was inappropriate. The report found that Enbridge was given special access to academic staff, was allowed to recommend partners, and had extensive influence over the public launch. The committee found Arvai’s explanation for his departure credible and troubling. It also found that the sponsorship was “skewed in Enbridge’s favour” from the start, with unfunded promises made at the university’s risk and expense, creating a “cycle of dependency” and pressures to compromise academic integrity. It identified a “significant failure of collegial governance, accountability and oversight,” and warned of “worrying signs of a culture of silencing and reprisal at the U of C.”\n\nThe CAUT report was highly critical of the university’s own review, led by retired Justice Terrence McMahon. The Board of Governors had commissioned the McMahon review in November 2015; McMahon found no wrongdoing and cleared university officials, including President Cannon, and the board considered the matter closed. The CAUT committee, however, stated that it was misleading to describe the McMahon review as “independent” and “transparent,” because it was established, mandated, and staffed by the Board or its counsel, and because it did not acknowledge or discuss the central role of academic freedom. The committee said McMahon gave the benefit of the doubt to senior officials while subjecting Arvai and Waverman to damaging criticism, and that the review’s selective approach to confidentiality was inconsistent with fairness and thoroughness. The CAUT report made recommendations including prohibiting university presidents and senior officials from serving for remuneration on external corporate boards, reviewing Board governance, and releasing all documents provided to the McMahon review.\n\nFollowing the CAUT report, the University of Calgary Faculty Association, chaired by Sandra Hoenle, called on the provincial government to probe governance at the university. Hoenle wrote that one of the greatest concerns was “the domination of the senior administration in the governance processes,” and that the Board of Governors and Senior Administration had misapplied “for-profit corporate structures within a university collegial setting,” keeping decision-making behind closed doors. She said, “We’re not a corporation. Universities are not corporations.” Arvai welcomed the CAUT report and said it was “wholly appropriate for the faculty association to be asking for a provincial review.” Alberta’s Ministry of Advanced Education stated that conflict of interest was being examined at public boards, including academic freedom, through a review of agencies, boards, and commissions, and that “Academic freedom is a cornerstone of any university.” Hoenle said the provincial governance review had been truncated and should be expanded to specifically deal with issues identified in the CAUT and CBC investigations.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
+          <t>committee - president - board - public - caut - applicants - hall - grievor - school - search</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7521296605070661</v>
+        <v>1</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -824,30 +824,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0_committee_president_board_hall</t>
+          <t>1_committee_president_board_public</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
+          <t>['committee', 'president', 'board', 'public', 'caut', 'applicants', 'hall', 'grievor', 'school', 'search']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['The grievor, Chad Thompson, had been employed as an Assistant Professor at University College of the North (UCN) for approximately two years when he was terminated in August 2011 for insubordination, insolence and defiant behaviour in the context of his involvement on a search committee. The termination occurred following his role as Chair of the Selection Board for Competition No. 3145, a search to fill a full-time, regular Social Science Instructor position in the Faculty of Arts and Sciences. The grievor held a full-time tenure track position within the bargaining unit represented by the Manitoba Government and General Employees\' Union.\n\nNorma Baker, the grievor\'s spouse and Dean of the Faculty of Arts and Sciences, was initially involved in preparing the posting and reviewing applications, but then went on sick leave. Because of concern about delay, the Vice-President - Academic, Kathryn McNaughton, requested that the grievor chair the search committee. The committee shortlisted two candidates, Aaron Crowe and Jason Hildebrandt. Crowe was interviewed, while Hildebrandt was unavailable due to an injury. The search committee unanimously endorsed Crowe, pending reference checks. Although UCN policy provided that Human Resources would check references, there was discussion by the committee and it was decided that Baker, as an academic, should conduct the reference checks, with the input of Human Resources committee member Linda Hunt. Baker did conduct the reference checks of Crowe. Linda Hunt prepared the Selection Board Report and submitted it to Interim President Konrad Jonasson with the committee\'s recommendation to hire Crowe.\n\nBy e-mail of July 14, 2011, Jonasson refused to approve the recommendation. He raised concerns including an appearance of conflict of interest by having both Baker and the grievor involved, questions about the second candidate\'s inability to interview, the educational qualifications of the recommended candidate, and whether information regarding the candidate\'s PhD program was current. Jonasson offered two options: consider the search failed and start anew, or go back and review all candidates to determine if any of the three not granted interviews should be interviewed and whether the second candidate remained interested. The e-mail concluded that if the other three did not merit an interview and candidate 2 could not go forward, the search should be declared failed and restarted. Baker, the grievor, committee member Sandra Barber, and McNaughton interpreted this e-mail as a declaration of failed search. Jonasson testified that it was designed to indicate concerns and solicit additional information, and that he did not declare a failed search until a subsequent e-mail on July 15.\n\nOn July 15, 2011 at 8:54 a.m., the grievor directed an e-mail to Linda Hunt stating that he would not be submitting his notes and ratings for the LTF hiring process, that given the actions of the Interim President regarding competition 3145 he had no confidence that Mr. Jonasson would respect the policies and procedures of HR, and that he was unwilling to participate any further in this or any other hiring committee until he regained confidence in the process. The e-mail was copied to the head of Human Resources and to McNaughton, but not to Jonasson. The grievor testified that he was not attempting to hide anything, that he felt it was part of his role to speak out where he believed the governance of the institution to be in error, and that he did not regret sending the message, although he wished he had worded it more carefully.\n\nAt 9:14 a.m. on July 15, approximately twenty minutes after the e-mail to Hunt, the grievor sent an e-mail directly to Aaron Crowe, advising him that, as Chair of the Selection Committee, he was writing with deepest regret to inform him of the decision by Interim President Mr. Konrad Jonasson to reject the unanimous recommendation of the Selection Committee to offer him the position. The e-mail suggested that Crowe might wish to speak with Human Resources regarding UCN policy HR-03-0 and with MGEU regarding Article 11:04 in the collective agreement, and was copied to the Manager of Human Resources and two Union staff representatives, including Nelson. Jonasson considered this a violation of protocol and a breach of confidentiality of the selection process. The grievor acknowledged he was angry, that he felt Jonasson\'s decision was not just, that sending the e-mail was a "very stupid thing to do," and that he regretted having done so. Crowe, an internal candidate, subsequently grieved the failure to award him the position.\n\nBy letter of August 10, 2011, Jonasson issued Baker a disciplinary reprimand for various misconduct, including her involvement on the search committee, her involvement in contacting references, and her e-mail of July 15. Baker was out of scope and not in a position to grieve that discipline; she subsequently resigned her position with UCN. Jonasson met with the grievor and Union representative Nelson on July 27, 2011 to review concerns. There was an issue as to whether the grievor offered regret or an apology; Jonasson had no recollection of an apology, while the grievor believed he showed regret and offered an apology, and Nelson testified that the grievor apologized at least twice or perhaps three times. Subsequent to that meeting, the grievor\'s position was terminated by letter of August 17, 2011.\n\nThe letter of termination stated that the grievor\'s actions relating to competition no. 3145 were in fundamental breach of his employment obligations. It cited three reasons: first, without the knowledge or approval of Human Resources, he allowed Baker to continue to participate on the Selection Board after she withdrew and allowed her to contact references on behalf of UCN, which was a significant breach of trust and a clear breach of policy; second, the grievor made insolent allegations against the Interim President in his e-mail to Hunt, stating he had no confidence that Jonasson would respect HR policies and procedures; and third, the grievor violated UCN policy by sending an e-mail directly to the recommended candidate advising him of the rejection, copying representatives of the MGEU Union who were not employees of UCN, and highlighting sections of the Collective Agreement for the unsuccessful applicant. The letter asserted that the grievor\'s conduct was clearly intended to undermine the authority of the Interim President.\n\nThe Employer argued that the grievor was a short term employee who had been insubordinate, insolent and defiant without justification, that his evidence was misleading in an attempt to minimize what he had done, and that the e-mails were inappropriate and sent without justification. The Employer submitted that this was extreme insubordination striking at the heart of the employment relationship, that none of the normal factors of mitigation were present, and that dismissal was the appropriate response. The Employer noted that the grievor had not demonstrated exceptional financial hardship other than what one would normally anticipate from a termination, and argued that even if academic freedom were engaged, it was not used responsibly.\n\nThe Union asserted that while there was conduct deserving of discipline, there had been no progressive discipline and termination was simply too severe. The Union pointed out that the grievor had an unblemished record, that Jonasson acknowledged he had not looked at the grievor\'s prior clear record, and that another individual, Baker, had received only a written reprimand for similar conduct, demonstrating inconsistency in the application of discipline. The Union argued that the e-mail to Crowe was written in the heat of the moment, that the grievor accepted responsibility for his actions, that the reference checks were done with the involvement of Human Resources, and that the e-mail to Hunt was an expression of concern over the hiring process, related to the service component of his role and potentially within academic freedom under Article 72 of the Collective Agreement. The Union requested reinstatement and compensation, with a letter of reprimand as the appropriate discipline.\n\nThe arbitrator, R.A. Simpson, found that while the grievor\'s conduct was insubordinate and warranted discipline, termination was not justified. The arbitrator noted that although the grievor was entitled to consider the July 14 e-mail equivalent to a declaration of failed search, that did not excuse his subsequent conduct. The e-mail to Hunt, containing comments about the Interim President\'s respect for HR policies, had a degree of insolence amounting to insubordination and was not within the service component of the grievor\'s role or within the parameters of academic freedom, but considered in isolation, it could have been dealt with through perhaps a verbal or at most a written reprimand. The e-mail to Crowe was clearly insubordinate, involving a breach of confidentiality, disclosure of confidential information, an invitation to challenge the Employer\'s decision, and a defiance of and challenge to the Employer\'s authority. However, the arbitrator was not satisfied that the employment relationship was irreparably harmed or could not be successfully rehabilitated. The grievor was not a long term employee, but his record over two years was without blemish, he was not challenged on his evidence as to exceptional services he had provided, and dismissal would have a significant adverse effect upon his career. There was no evidence that progressive discipline short of termination was considered. The arbitrator accepted the Employer\'s argument that there was a significant difference between Baker\'s situation and the grievor\'s, with Baker communicating with colleagues and advocating for faculty and students, as opposed to the grievor communicating with an unsuccessful candidate and disclosing confidential information. Nevertheless, a lesser discipline could well have been sufficient to rehabilitate the employment relationship. The arbitrator substituted a two-month suspension without pay for the termination, stating that this was a significant penalty that should send a message that such behaviour would not be tolerated. The grievance was allowed, the termination rescinded, and a two-month suspension without pay substituted.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.']</t>
+          <t>['Between March 2011 and July 2012, the University of Calgary (U of C) worked to secure a sponsorship from Enbridge, a Calgary-based oil and gas pipeline company, to establish a research institute at the Haskayne School of Business (HSB). Dr. Joe Arvai, a recently appointed faculty member, was asked to be director of what became the Enbridge Centre for Corporate Sustainability (ECCS). The sponsorship agreement, dated July 1, 2011, was between Enbridge and “The Governors of the University of Calgary,” committing $225,000 annually over ten years. However, planned activities were based on an annual budget of $500,000, more than double Enbridge’s financial outlay, creating an immediate funding shortfall that was supposed to be made up by additional corporate fundraising.\n\nDuring the establishment and launch of the ECCS, Arvai repeatedly raised concerns about Enbridge’s influence over the Centre’s academic mission. Emails disclosed through freedom of information requests showed that Enbridge exerted influence over the Centre’s name, the selection of partner institutions, the planning of the public launch, and the role of the director. Enbridge pressed for Central Michigan University (CMU) as a partner, in part because CMU had given Enbridge "very valuable advice" after the 2010 Kalamazoo River oil spill in Michigan; Arvai objected on academic grounds, saying CMU had only one faculty member in the relevant field, but was pressured to accept. HSB Dean Len Waverman told Arvai that “the monies we give to CMU are tiny – it won’t be viewed as a payoff,” and that “Elizabeth [Cannon] will have a fit if she sees this.” Enbridge also expressed concerns about Arvai’s appointment to a U.S. Environmental Protection Agency (EPA) Scientific Advisory Board, and the university delayed its announcement of that appointment so as not to “piss off Enbridge any more.” Arvai stated that “we cannot maintain our credibility as serious scholars/researchers if the sponsors can dictate the Centre’s agenda,” and that he could not serve as director if sponsors were allowed to meddle in academic activities.\n\nArvai was removed as ECCS director in March 2012. He later told the CAUT committee that he was removed one week after he informed Enbridge’s public relations firm, National Public Relations, of his opposition on scientific grounds to the Northern Gateway pipeline. In an email of March 19, 2012, Dean Waverman told Enbridge officials: “Joe Arvai is no longer Director of the Centre, there are too many conflicts and demands!” Arvai subsequently left the U of C and is now at the University of Michigan.\n\nA CBC News investigation in November 2015 prompted the Canadian Association of University Teachers (CAUT) to establish an Ad Hoc Investigatory Committee. In his first public statement, an opinion piece reprinted by CBC News, Arvai said the CBC had done “an exceptional job of getting the facts correct,” and that the post hoc suggestions that decisions setting up the Enbridge Centre were “transparent, legitimate, and free of corporate interference or conflict-of-interest” were as difficult for him to accept as they were in 2012. He said donors should be able to suggest, but not select, advisory individuals, and should have a voice in a centre’s name and mission, but should not require that support be limited to those sharing their “core values.”\n\nThe CAUT report, released in October 2017, made findings on conflict of interest, academic freedom, external influence, funding, governance, and the McMahon review. It found a “clear appearance of a conflict of interest” on the part of U of C President Elizabeth Cannon, who served on the Enbridge Income Fund Holdings Board for significant remuneration while president, and who failed to publicly recuse herself from Enbridge-related matters. The report found that Cannon intervened directly with Dean Waverman, telling him that Enbridge was “not very happy,” that she wanted a good relationship with Enbridge, and emphasizing “I am on one of their Boards!” The report also found that the U of C Board of Governors failed to review or approve the sponsorship agreement, despite being a party to it, and that Cannon’s reliance on an “administrative lapse” was an “unacceptable evasion of responsibility.”\n\nThe CAUT committee concluded that Dr. Arvai’s academic freedom was compromised as a result of the U of C’s mishandling of the Enbridge Centre, appearing to be due to a desire on the part of senior leadership to please a significant donor. It found that Enbridge sought to influence the Centre’s establishment and launch, and that university administrators failed to convey that this influence was inappropriate. The report found that Enbridge was given special access to academic staff, was allowed to recommend partners, and had extensive influence over the public launch. The committee found Arvai’s explanation for his departure credible and troubling. It also found that the sponsorship was “skewed in Enbridge’s favour” from the start, with unfunded promises made at the university’s risk and expense, creating a “cycle of dependency” and pressures to compromise academic integrity. It identified a “significant failure of collegial governance, accountability and oversight,” and warned of “worrying signs of a culture of silencing and reprisal at the U of C.”\n\nThe CAUT report was highly critical of the university’s own review, led by retired Justice Terrence McMahon. The Board of Governors had commissioned the McMahon review in November 2015; McMahon found no wrongdoing and cleared university officials, including President Cannon, and the board considered the matter closed. The CAUT committee, however, stated that it was misleading to describe the McMahon review as “independent” and “transparent,” because it was established, mandated, and staffed by the Board or its counsel, and because it did not acknowledge or discuss the central role of academic freedom. The committee said McMahon gave the benefit of the doubt to senior officials while subjecting Arvai and Waverman to damaging criticism, and that the review’s selective approach to confidentiality was inconsistent with fairness and thoroughness. The CAUT report made recommendations including prohibiting university presidents and senior officials from serving for remuneration on external corporate boards, reviewing Board governance, and releasing all documents provided to the McMahon review.\n\nFollowing the CAUT report, the University of Calgary Faculty Association, chaired by Sandra Hoenle, called on the provincial government to probe governance at the university. Hoenle wrote that one of the greatest concerns was “the domination of the senior administration in the governance processes,” and that the Board of Governors and Senior Administration had misapplied “for-profit corporate structures within a university collegial setting,” keeping decision-making behind closed doors. She said, “We’re not a corporation. Universities are not corporations.” Arvai welcomed the CAUT report and said it was “wholly appropriate for the faculty association to be asking for a provincial review.” Alberta’s Ministry of Advanced Education stated that conflict of interest was being examined at public boards, including academic freedom, through a review of agencies, boards, and commissions, and that “Academic freedom is a cornerstone of any university.” Hoenle said the provincial governance review had been truncated and should be expanded to specifically deal with issues identified in the CAUT and CBC investigations.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
+          <t>committee - president - board - public - caut - applicants - hall - grievor - school - search</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8625191710265493</v>
+        <v>1</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -874,33 +874,33 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1_comments_racism_letter_canada</t>
+          <t>0_letter_comments_expression_wrote</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
+          <t>['letter', 'comments', 'expression', 'wrote', 'saying', 'views', 'social', 'statement', 'racism', 'class']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
+          <t>letter - comments - expression - wrote - saying - views - social - statement - racism - class</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4_board_media_journals_release</t>
+          <t>3_media_board_release_journals</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
+          <t>['media', 'board', 'release', 'journals', 'trustees', 'governance', 'wall', 'suspension', 'committee', 'grievance']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>board - media - journals - release - trustees - governance - wall - suspension - president - grievance</t>
+          <t>media - board - release - journals - trustees - governance - wall - suspension - committee - grievance</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4_board_media_journals_release</t>
+          <t>3_media_board_release_journals</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
+          <t>['media', 'board', 'release', 'journals', 'trustees', 'governance', 'wall', 'suspension', 'committee', 'grievance']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>board - media - journals - release - trustees - governance - wall - suspension - president - grievance</t>
+          <t>media - board - release - journals - trustees - governance - wall - suspension - committee - grievance</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2_health_consent_medical_committee</t>
+          <t>4_christian_public_health_covid19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
+          <t>['christian', 'public', 'health', 'covid19', 'children', 'western', 'public health', 'medicine', 'provost', 'scientific']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['A prolonged and acrimonious dispute in Toronto involving internationally acclaimed blood researcher Dr. Nancy Olivieri, the Hospital for Sick Children (HSC), the University of Toronto, and the pharmaceutical manufacturer Apotex Inc. was resolved in a face-saving compromise in late January 1999, after earlier events had ignited a controversy over research ethics, patient safety, and academic freedom.\n\nThe dispute centred on clinical trials of deferiprone (L1), an experimental orally active iron-chelating agent being tested as an alternative to the standard but onerous deferoxamine (DFO) therapy for patients with thalassemia major, a transfusion-dependent blood disorder causing progressive iron loading of major organs. Dr. Olivieri, a specialist in hematology and internal medicine, was principal investigator of two Toronto trials: LA-03, a long-term efficacy and safety study, and LA-01, a randomized comparison trial versus DFO, co-sponsored by the Medical Research Council and Apotex. In 1996, Dr. Olivieri identified an unexpected risk in the LA-03 data: loss of sustained efficacy of L1 in a substantial proportion of patients, with hepatic iron concentrations (HIC) stabilizing or rising into ranges associated with iron-induced complications. Apotex disputed her interpretation and opposed informing patients. When HSC\'s Research Ethics Board (REB) directed Dr. Olivieri to revise patient information and consent forms to disclose this risk, Apotex abruptly terminated both Toronto trials on May 24, 1996, withdrew its drug from the hospital pharmacy, and issued legal warnings threatening legal action if she communicated the risk to patients, regulators, or the scientific community.\n\nFollowing the trial terminations, Dean Arnold Aberman of the University of Toronto\'s Faculty of Medicine mediated a new arrangement under Health Canada\'s Emergency Drug Release (EDR) program. Patients who had been in the former trial cohorts and wished to continue on L1 and were still considered to be benefiting could do so as patients under Dr. Olivieri\'s care, provided they were fully informed of the newly identified risk, accepted it, and agreed to monitoring tests including annual liver biopsy. The REB had no jurisdiction over this non-trial EDR treatment arrangement, and Dr. Olivieri, as "the practitioner" under EDR regulations, had reporting obligations only to patients, Apotex, and the Health Protection Branch. She nonetheless informed the REB that the trials had been terminated, and she later reported the loss-of-efficacy finding directly to the regulators despite continued legal warnings from Apotex.\n\nIn early February 1997, Dr. Olivieri and her collaborators, liver pathologist Dr. Ross Cameron and Dr. Gary Brittenham, identified a second, more serious unexpected risk through review of serial liver biopsy slides: progression of liver fibrosis in some patients, making L1 the probable cause of a "severe adverse reaction." She informed patients immediately, counselled them to interrupt use of the drug, and transferred them back to standard therapy in a timely and orderly fashion. She also informed Apotex and the federal regulators, sending her report to the FDA, HPB, and the health ministries of Italy and India. Apotex responded with further legal warnings, and Dr. Hugh O\'Brodovich, HSC\'s Pediatrician-in-Chief, intervened on February 19, 1997, questioning whether Dr. Olivieri had failed in an obligation to report the risk to the REB and to her department chief. Dr. Aideen Moore, the REB Chair, provided incorrect information suggesting that a research trial of L1 continued after May 1996, although both trials had in fact been terminated and patients were under EDR. Subsequent investigations determined that Dr. Olivieri had no obligation to report to the REB in these circumstances and that she had acted "in the best interests of her patients."\n\nThe controversy became public in August 1998 after Dr. Olivieri published her findings on loss of efficacy and toxicity in the New England Journal of Medicine. In September 1998, the HSC Board of Trustees unilaterally established a review conducted by Dr. Arnold Naimark. The Naimark Report, released December 9, 1998, incorrectly concluded that Dr. Olivieri had failed to report her concerns about L1 toxicity to the REB in a timely fashion. On the same day, the HSC Board directed its Medical Advisory Committee (MAC) to inquire into her conduct. On January 6, 1999, HSC removed Dr. Olivieri from her position as director of the hemoglobinopathy program without due process and issued "gag orders" to her and three supporters, Drs. Helen Chan, Peter Durie, and Brenda Gallie, restricting communication with the media. These actions prompted interventions by the Canadian Association of University Teachers (CAUT), the University of Toronto Faculty Association (UTFA), leading scientists Sir David Weatherall and Dr. David Nathan, and University President Robert Prichard. A marathon negotiating session on January 25, 1999 produced a settlement that restored Dr. Olivieri\'s full responsibility and authority over clinical care and research in hemoglobinopathies, withdrew the gag orders, changed her reporting relationships, and provided her with legal indemnification of $150,000 and coverage for potential legal action by Apotex.\n\nThe Medical Advisory Committee, using undisclosed allegations and testimony, principally from Dr. Gideon Koren, Dr. Olivieri\'s former co-investigator, and Dr. O\'Brodovich, referred a series of "concerns" about her conduct to the College of Physicians and Surgeons of Ontario (CPSO) and the University of Toronto in April 2000. Dr. Koren was later disciplined by HSC and the University on April 11, 2000 for "gross misconduct," including persistently lying about his authorship of anonymous letters disparaging Dr. Olivieri and her supporters; he admitted responsibility only after being identified by DNA evidence. The Health Professions Appeal and Review Board subsequently found that Dr. Koren\'s anonymous letter-writing campaign constituted "serious professional misconduct" and directed that the matter be referred to the CPSO Discipline Committee.\n\nIn October 2001, the independent CAUT Committee of Inquiry, chaired by Jon Thompson with Patricia Baird and Jocelyn Downie, published a detailed report exonerating Dr. Olivieri, faulting Apotex for attempting to suppress information on risks and to discredit her, faulting HSC and the University for failing to protect her academic freedom, and criticizing the Naimark Review and MAC proceedings for relying on incorrect and false information. On December 19, 2001, the CPSO Complaints Committee, assisted by an independent expert panel, concluded that "no further action is warranted against Dr. Olivieri," finding she did not fall below a reasonable standard of care in continuing to administer L1, in ordering liver biopsies, or in communicating with her department chief. The Committee specifically found her judgment in advising patients to undergo biopsies "not only reasonable, but commendable in the circumstances." On January 7, 2002, Dean David Naylor of the University of Toronto\'s Faculty of Medicine dismissed all related allegations, including the claim that Dr. Olivieri should have reported her conclusions on L1 toxicity to the REB.\n\nThe case was ultimately recognized for its impact on a critically important issue: the growing dependence of researchers, universities, and hospitals on corporate research funding and the need for policy safeguards to ensure that sponsors cannot restrict communication of identified risks, that confidentiality clauses in research contracts are not used to suppress findings of risk, and that research ethics boards, universities, and hospitals act robustly to defend academic freedom and the safety of trial participants and patients.', 'The Canadian Association of University Teachers (CAUT) established an Independent Committee of Inquiry, chaired by Professor Trudo Lemmens, with Dr. Thomas A. Ban and Dr. Louis C. Charland, to investigate the seizure of research records from the offices of Dr. Anne Duffy at the Institute of Mental Health Research (IMHR) in Ottawa on March 22, 2005. The Committee was mandated to investigate the sequence of events leading to and following the seizure, the institutional relationships between the University of Ottawa, the IMHR, and the Royal Ottawa Hospital (ROH), whether breaches of institutional responsibility or research ethics standards occurred, the impact on academic freedom and integrity, the impact on researchers, research subjects and institutions, and to make recommendations to prevent recurrence. The final report was submitted in March 2013 after delays caused by court proceedings and health issues.\n\nThe events began on March 11, 2005, when Dr. Duffy’s research coordinator told Sharyn Szick, Administrative Director of the IMHR, that a research assistant was scanning clinical charts and inserting printed copies into research records, and that informed consent forms were missing from some research records or had been signed after study initiation and backdated. Ms. Szick reported this to Dr. Zul Merali, President and CEO of the IMHR. On March 22, 2005, after a meeting attended by Ms. Szick, Dr. Keith Busby, Suzan Crozier, Carolyn Belzile, and Sharon Purvis, the decision was made to remove clinical charts from Dr. Duffy’s office and chart room. Dr. Paul Dagg, Director of Clinical Services, and Mr. Bruce Swan, CEO of the Royal Ottawa Health Care Group (ROHCG), authorized the removal of clinical charts based on allegations that clinical charts had been scanned and downloaded to hospital network drives, contrary to ROH policy and the Personal Health Information Protection Act (PHIPA). Once the clinical charts were relocated, Dr. Busby, at Dr. Merali’s request, conducted a “spot check” of approximately 20 research binders and reported that about five lacked consent forms behind the tab marked “consent.” Dr. Merali then ordered the immediate transfer of the research records of the bipolar team to a “secure location” at the ROH. Neither Dr. Duffy nor any member of her research team was present. Dr. Duffy learned of the removal the next morning from a note on her door.\n\nThe seized material included clinical charts, research records, personal files, and computer discs. According to Drs. Duffy and Grof, the records concerned more than 2,000 research subjects, including current and former patients and controls from Ontario and Nova Scotia. The records included studies conducted by Drs. Alda, Grof, and Duffy, involving long-term follow-up of families with bipolar disorder. The ROHCG Research Ethics Board (REB), chaired by Dr. Alan B. Douglass, was not consulted in advance, had received no complaint, and had not authorized the removal. Dr. Dagg’s investigation concluded on April 13, 2005 that no serious breaches of privacy with clinical charts had occurred, though he apologized for the removal.\n\nDrs. Duffy and Grof retained legal counsel on March 23, 2005, and commenced court proceedings for the return of the research records. They also filed a complaint with the Information and Privacy Commissioner of Ontario. On April 15, 2005, proceedings were adjourned and on April 18, 2005 an agreement was reached: the research records would be copied, originals returned, copies turned over to the REB without review, Dr. Merali would outline concerns, and the REB would appoint an independent reviewer. However, Dr. Duffy learned that Dr. Busby had already reviewed some records, contrary to her understanding of the agreement. Dr. Duffy then informed research subjects by e-mail that IMHR personnel had accessed personal information. The Information and Privacy Commissioner’s investigation was put on hold after objections from Dr. Duffy’s lawyers.\n\nIn May 2005, Drs. Duffy and Grof contacted CAUT, which established the Independent Committee of Inquiry. Committee interviews began in late summer 2005. Most institutional officials declined to participate on legal advice. A settlement was reached on October 19, 2005, which allowed Dr. Douglass to invite Dr. Padraig Darby, Chair of the REB of the Centre for Addiction and Mental Health, to review copies of the research records. Dr. Darby’s report, submitted November 10, 2006, found that only one of six studies had REB approval and that informed consent forms were missing from 77 of 252 records (30.5%). It was later clarified that all studies had approval letters on file that had not been provided to Dr. Darby. Drs. Duffy and Grof disputed the findings, reporting that only 11% of records lacked consent forms based on their review of the originals, and suggested that a former research assistant had failed to add consent forms to files. The Darby Report led to a second round of litigation, which ended in 2008 when the Canadian Medical Protective Association declined further funding and Drs. Duffy and Grof agreed to pay the other party’s legal costs.\n\nThe Committee’s own review of the original research records found that some consent forms identified as missing by Dr. Darby were present in the originals, and that new signed consent forms were present in records where originals were absent. Interviews with research subjects and parents of subjects whose original consent forms were missing showed that all were fully aware that they or their children were participating in Dr. Duffy’s research, understood the nature and purpose of the research, and had strong confidence in Dr. Duffy’s integrity.\n\nThe Committee concluded that the seizure of research records was in violation of research ethics standards. It emphasized a key distinction between informed consent obtained to protect research subjects from physical or psychological harm, and informed consent obtained to protect the privacy of research subjects and the confidentiality of sensitive health information. In the studies at issue, the consent forms represented a pledge by researchers to protect confidentiality. Seizing records in response to allegations of missing consent forms therefore violated the very essence of the informed consent. The “spot check” conducted by Dr. Busby was not a proper audit, as it lacked advance notice, defined objectives, scope, and researcher involvement, and was not carried out by the REB. The Committee found that the seizure was a disproportionate response, contrary to the principle of “proportionate review” under the Tri-Council Policy Statement (TCPS), and that institutional officials breached their responsibility by prioritizing the establishment of alleged wrongdoing over the protection of research subject privacy. The Committee attributed the seizure to ongoing tensions between Drs. Duffy and Grof and Drs. Merali and Bradwejn, and to the confounding of informed consent for privacy protection with informed consent for protection from harm.\n\nThe Committee’s recommendations included: clarifying that research records are in principle the property of the researcher; clearly defining the position of self-funded research teams and renegotiating responsibilities regularly; identifying for each research project whether informed consent is for protection from harm or for privacy and confidentiality; clarifying institutional responsibilities so that the REB that approved a project, not other institutional officials, ensures adherence to research ethics standards; and ensuring that seizure of research records is only a last resort when there is an immediate and serious threat to the wellbeing of research subjects, with procedures designed to respect the privacy and confidentiality of health information.', '# Summary: Suspension and Termination of Dr. Francis Christian\n\nDr. Francis Christian, a clinical professor of general surgery at the University of Saskatchewan (USask) and a practicing surgeon in Saskatoon with more than 20 years of experience, was suspended and terminated from his positions after publicly raising concerns about COVID-19 vaccination of children. As of June 2021, Christian served as Director of the Surgical Humanities Program (which he co-founded), Director of Quality and Patient Safety in the Department of Surgery, and Editor of the Journal of the Surgical Humanities. His roles overlapped with a contract position with the Saskatchewan Health Authority (SHA).\n\nOn June 17, 2021, Christian released a prepared statement to over 200 doctors and spoke at a press conference outside Walter Murray Collegiate in Saskatoon, appearing with a group called Concerned Parents Saskatchewan while a vaccine clinic was taking place at the high school. He declined to take questions from journalists. In his statement, Christian emphasized that he is a "very pro-vaccine physician" and is "pro-vaccine for my own family, including myself," citing the elimination of smallpox through vaccination. He stated he spoke "directly to parents and children" as "a physician, a surgeon and a fellow human being" and did not represent any group, the SHA, or the university.\n\nChristian invoked the "sacrosanct principle" of informed consent, arguing that patients must be made "fully aware of the risks of the medical intervention, the benefits of the intervention and if any alternatives exist to the intervention," particularly for "a new vaccine that has never before been tried in humans." He asserted this principle was "being consistently violated in this province for the m-RNA vaccine for our kids," claiming he had not met "a single vaccinated child or parent who has been adequately informed."\n\nChristian articulated eight points he argued parents and children must know before consenting: (1) that the mRNA vaccine is "a new, experimental vaccine design" never used in humans; (2) that the vaccines have not been fully authorized by Health Canada or the CDC, being under "interim authorization" in Canada and "emergency use authorization" in the US; (3) that while there is an emergency for the elderly, vulnerable, and health care workers—given that the mean age of COVID-19 deaths in Canada is 83.8—"Covid-19 does not pose a threat to our kids," with a death risk of less than 0.003%; (4) that children do not readily transmit the virus to adults; (5) that the mRNA vaccines have been "associated with several thousand deaths" in the US government\'s Vaccine Adverse Reporting System, which he called "a strong signal" that could not be ignored; (6) that there is a "real and significantly increased risk" of myocarditis (heart inflammation) in vaccinated children, leading the German national vaccine agency and the UK vaccine agency to not recommend the vaccine for healthy children; (7) that the benefit of the vaccine for children is "marginal at best," with an Absolute Risk Reduction of less than 2%; and (8) that Ivermectin is an alternative treatment. He urged authorities "to call a pause in the m-RNA vaccine roll-out to our kids" and stated that without informed consent, "the Nuremberg code is being violated." He also appeared in a video posted to the website BitChute that received nearly 70,000 views, in which he questioned the mainstream narrative about the pandemic, mocked restrictions, and called the vaccines "experimental injections."\n\nOn June 21, 2021, the Saskatchewan Health Authority and the College of Medicine wrote to Christian alleging they had "received information that you are engaging in activities designed to discourage and prevent children and adolescents from receiving Covid-19 vaccination contrary to the recommendations and pandemic-response efforts of Saskatchewan and Canadian public health authorities."\n\nOn June 23, 2021, Christian was called into a meeting with Dr. Preston Smith, Dean of the College of Medicine; Dr. Susan Shaw, Chief Medical Officer of the Saskatchewan Health Authority; and Dr. Brian Ulmer, Head of the Department of Surgery. He was informed of his immediate suspension from all faculty responsibilities and academic administrative roles, and that he would be fired from the university as of September 2021. The SHA terminated its contract with Christian, which was set to expire on September 21 following the required 90 days\' notice. Christian remained able to practice medicine and the university said it was not suspending payment for services he would have otherwise received during the investigation period. Christian recorded the 22-minute meeting and posted the audio online.\n\nDuring the meeting, Christian said, "You\'ve basically read indictments against me. These are the sort of panels that were set up in the Soviet Union and Nazi Germany against academics," adding, "I\'m not saying that you\'re Nazis or Soviets, but it\'s really disturbing, isn\'t it?" He stated he was one of many doctors being "silenced and censored," and told the officials, "You guys are living in a dystopian bubble. The truth will come out and when that bubble bursts, you guys are going to be in big trouble." Shaw expressed concern that Christian was "a highly intelligent man" who was "not making intelligent decisions," and Christian was offered supports if he was feeling distressed, which he declined.\n\nIn a statement, Dean Smith said the University "encourages public debate of important societal issues," but noted that per USask\'s Medical Faculty Policy, "our medical faculty are subject to the ethical and professional standards governing the practice of medicine." Smith told Global News that "when somebody is saying things that are at such great variance with all of our experts and worldwide experts and public safety is involved and could be jeopardized through these differences of view, I think we have to recognize that that\'s a special situation that requires urgent and extraordinary action." The SHA stated that "health system leaders are expected to be committed to fact-based, scientifically driven public messaging" and that leaders who depart "in favour of conspiracy theories put lives at risk by potentially discouraging uptake on life-saving vaccines."\n\nThe Justice Centre for Constitutional Freedoms announced it was representing Christian in his appeals and before the College of Physicians and Surgeons of Saskatchewan, against a complaint objecting to his advocacy for informed consent. Litigation Director Jay Cameron said the termination was "a violation of his charter-protected right to freedom of thought, belief, opinion and expression, and a betrayal of the principles of scientific inquiry," and described "a clear pattern of highly competent and skilled medical doctors in very esteemed positions being taken down and censored or even fired, for practicing proper science and medicine." The Justice Centre also drew comparisons to its representation of Dr. Chris Milburn in Nova Scotia, who faced disciplinary proceedings over an opinion column.\n\nOn June 30, 2021, the Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Dean Smith requesting an explanation of "how Dr Christian\'s suspension is not a violation of his academic freedom and how his suspension will not tend to create a chilly climate for expression on campus." SAFS argued that "nothing that has been reported should draw any discipline at all" and that "academic freedom protects his rights to have them and to express them publicly," noting the importance of professors being "free to question received wisdom and official policy" during a pandemic.']</t>
+          <t>['Patrick Provost, a professor at Université Laval in Quebec, became the subject of academic-freedom controversy after making public comments critical of mRNA COVID-19 vaccines. According to a June 30, 2022 article by The Canadian Press, Provost, a professor of microbiology and immunology who studies micro RNA — small molecules that help regulate genes — was suspended for eight weeks without pay on June 14, 2022. The suspension stemmed from comments he made in December 2021 at a conference organized by Reinfo Covid Quebec, a group that has criticized COVID-19 public health measures and been accused of spreading misinformation about vaccines. At that conference, Provost said he believed the risks of COVID-19 vaccination in children outweigh the benefits because of potential side-effects from mRNA vaccines, which use messenger RNA created in a lab to teach cells how to make a protein. Following the conference, Provost sent an email to all professors at Université Laval encouraging them to share their knowledge and expertise with the public, referencing his December speech. That email led to a complaint from a colleague. A university committee consisting of a lawyer and two experts concluded that his comments were biased and that he did not analyze his data rigorously or present his information objectively.\n\nProvost defended his actions, saying, "I was just doing what I was hired to do. I had some concerns about something, I searched the literature and I prepared a speech, delivered it to the public. Being censored for doing what I\'ve been trained to do — and hired to do — well, it\'s hard to believe." He also said, "As soon as you raise some concerns about vaccines, or side-effects, or complications related to vaccines, then it\'s worse than the N-word. You\'re condemned by the media, by the government and you\'re chased and put down." He added that because he expressed opinions that went against the government narrative, he was suspended.\n\nSimon Viviers, vice-president of the Université Laval faculty union, said the union had filed a grievance over the suspension. "For us, this is an attack on academic freedom," he said. "To allow (a university) to judge the validity of the comments made by a university professor in public and to sanction him in this manner is extremely problematic." Viviers said the university should not have used a research integrity committee to judge whether Provost\'s comments were valid. The union did not take a position on the comments themselves, only on how Provost was treated. Viviers worried that the suspension could have a dissuasive effect, "even lead to self-censorship."\n\nDavid Robinson, executive director of the Canadian Association of University Teachers, said professors should be disciplined only for comments that amount to incompetence or that violate legal limits to speech, such as libel laws. "We have to have a high tolerance for academic freedom and diversity of viewpoints," he said. He added that "naysayers" and "gadflies" need to be tolerated because they sometimes turn out to be right. Robinson cited the example of researchers who first suggested that some ulcers are caused by bacterial infection — they were dismissed by the scientific community, but the evidence eventually proved them correct. "That\'s what the university is all about — it\'s all about disagreements and it\'s through disagreements and debate, and challenging evidence that\'s presented by someone else that we eventually reach some common understanding," he said. "But we shouldn\'t stifle that debate."\n\nHowever, Dr. Mathieu Nadeau-Vallée, a medical resident at Université de Montréal with a PhD in immunology, said Provost is not an expert in the mRNA technology used in the Pfizer and Moderna COVID-19 vaccines, or in the vaccination of children. "This person doesn\'t really have the expertise to speak about all this," Nadeau-Vallée said. "He\'s a biochemistry professor; he doesn\'t study messenger RNA, he studies small RNA. It\'s not at all the same area of research. So this is a person who is expressing themselves about a subject that they\'re not really an expert in and is speaking against the scientific consensus on that subject." Nadeau-Vallée said COVID-19 vaccines and public health measures have saved lives and that academic freedom means being able to speak about any subject but does not mean that false things can be said. He said anyone who wants to speak against the scientific consensus has to show scientific evidence.\n\nAccording to local news reports, Provost was one of two professors suspended by Université Laval for anti-vaccine comments. The university declined to comment on either suspension, the union said it was not aware of the second case, and the second professor named in news reports did not respond to requests for comment. Quebec Higher Education Minister Danielle McCann said in an emailed statement that the suspensions were examples justifying the government\'s adoption earlier that month of a bill protecting academic freedom. The bill gave all universities in the province one year to create an academic freedom policy and establish a committee responsible for supervising its implementation. McCann said she was calling on Université Laval — and the province\'s other universities — to establish those policies as soon as possible. "These situations demonstrate the relevance and importance of adopting this law," she said.\n\nA later letter dated June 4, 2024, from the Society for Academic Freedom and Scholarship (SAFS) addressed the ongoing case. The letter was sent by Robert G. Thomas, President of SAFS, to Dr. Sophie D’Amours, Rector of Université Laval, at 2325, rue de l\'Université, Québec. The letter expressed concerns regarding the "recent firing" of Professor Patrick Provost at Université Laval. According to multiple media reports, as stated in the letter, Provost had been disciplined, suspended and more recently fired for his public criticisms around the use of mRNA COVID vaccines. SAFS wrote that this turn of events was regrettable not only for what it did to interfere with Provost\'s academic freedom but also because of its potential effect on the wider community. The letter argued that academic institutions maintain public trust through their disinterested search for truth and openness to scholarly critique, and that if ultimate conclusions appear preordained and certain orthodoxies may not be questioned, universities could rightly be seen as places of dogma rather than empirical investigation. SAFS stated that firing Provost sent a clear message to researchers to tread carefully when entering certain debates, creating a chill on the expression of heterodox positions, particularly in science, and impeding the discovery of new understandings. The organization respectfully requested a response from the Rector and said it would post the response along with the letter on its website. The letter was copied to Hon. Pascale Déry, MNA, Minister of Higher Education, and Marie-Hélène Parizeau, President of SPUL.', 'A dispute at Western University in London, Ontario, has centered on the limits of academic freedom in the context of COVID-19. Donald Welsh, a professor of physiology at the Schulich School of Medicine and Dentistry, has regularly tweeted and retweeted information challenging the effectiveness of COVID-19 vaccines and other public health measures. In a January 7 tweet, Welsh wrote that he suspected the health minister understood that "C19 vaccines are ineffective at mitigating infection, transmission and death" and that this "seems more like a political rather than a scientific stance." On January 13, he tweeted that "every aspect of Canada\'s public response to C19 was devoid of sound scientific reasoning." On January 23, responding to a tweet by Dr. Nathan Stall about low vaccination rates among children, Welsh wrote: "There is no need to vaccinate those who aren\'t susceptible. This is the standard practice in most of the world." That tweet drew a response from Dr. Genevieve Eastabrook, an associate professor in maternal-fetal medicine who also works at Schulich, who wrote: "This individual knows nothing about preventative medicine, vaccination or public health. Yet again, I am embarrassed to work at the same institution as this person."\n\nWelsh\'s colleague Jacob Shelley, who holds a joint appointment with Western\'s Faculty of Law and the School of Health Studies and directs the school\'s Health Ethics, Law &amp; Policy lab, accused Welsh of hiding behind the protections of academic freedom to spread misinformation about the effectiveness of COVID-19 vaccines. Shelley argued that "academic freedom comes with academic responsibilities," meaning "having integrity in our research, not just to say whatever the hell we want." He said any academic\'s public statements should have to withstand scrutiny from their peers in the same way a PhD student\'s dissertation is tested. In Shelley\'s view, Welsh\'s tweets "are not reliable information," "are not scientific," and "would not get through a peer review." Shelley had previously challenged Welsh\'s opinions on Twitter, but Welsh blocked Shelley, and Shelley\'s responses were no longer included in the threads. Shelley also said that other professors often notify him of Welsh\'s tweets in hopes he will challenge them, but they are often afraid to enter the fray themselves for fear it will be career limiting. "A lot of people are afraid to speak out because there could be consequences," Shelley said, adding that he had been told, "You should be careful because the central administration won\'t forget and this will come back to bite you."\n\nWestern University told CBC News that Welsh\'s views "do not align with the views of the Schulich School of Medicine &amp; Dentistry or Western University," and that the university is "disappointed that Don Welsh has decided to take the position that he has." The statement also said that while Welsh\'s views "contradict the position of public health and the university," there was not much the university could do about it. "As employees of the university, individual faculty members have the freedom to express their opinions and beliefs, and those views are their own and do not represent the views of the school or university," the statement said, adding that the school "continues to support all public health measures related to the ongoing pandemic." While a neonatal nurse at London Health Sciences Centre was fired last year for organizing anti-lockdown rallies and challenging public health measures such as lockdowns and masking, Welsh\'s comments are protected by academic freedom. The underlying principle is that professors should not have their research and writings influenced by fear of reprisals from their employer.\n\nWelsh, in an email to CBC News, stood by his right to state his own opinions, pointing to the statement on his Twitter profile page that the opinions stated are Welsh\'s own and do not represent Schulich or the university. He said discussion around the best public health responses to COVID-19 "is never settled and it would be incorrect to present it as such. That is why the conversation continues to evolve on places like Twitter. This process is organic and debate is fundamental." Shelley agreed that the debate should be more robust, but said the ivory tower world of academia is often averse to controversy and guided by a "don\'t rock the boat" mentality.\n\nIn response to the controversy, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members and others dedicated to the defense of academic freedom and the merit principle in higher education, sent a letter dated 4 February 2022 to Alan Shepard, President and Vice-Chancellor of Western University. The letter, written by SAFS president Mark Mercer and signed by the board of directors and past presidents, commends Western for stating publicly that "individual faculty members have the freedom to express their opinions and beliefs." The letter notes that Western professors and others had urged Western to violate the academic freedom of Donald Welsh, and that Western rejected these appeals. SAFS stated that Western has demonstrated that it understands that academic freedom is essential to the mission of the university, for it enables new ideas to be spoken and to be debated robustly. Those who disagree with Dr. Welsh are free to criticize his views and defend their own. In the absence of academic freedom, the public could not trust what academics say, as people would be suspicious that their research was guided by the need to come to approved conclusions. SAFS respectfully asked Shepard to respond to the letter and, with permission, to post the response along with the letter on the SAFS website. The letter was copied to several Western vice-provosts and deans, including the Dean of the Schulich School of Medicine &amp; Dentistry, Dr. John Yoo. The central issue remains whether academic freedom protects a faculty member\'s public comments on COVID-19 even when those comments contradict public health guidance and are seen by colleagues as misinformation. Western\'s position is that individual faculty members have the freedom to express their opinions and beliefs, and that those views are their own and do not represent the views of the school or university, while Shelley and others argue that academic freedom entails academic responsibilities and that false or unreliable claims should face peer scrutiny.', '# Summary: Suspension and Termination of Dr. Francis Christian\n\nDr. Francis Christian, a clinical professor of general surgery at the University of Saskatchewan (USask) and a practicing surgeon in Saskatoon with more than 20 years of experience, was suspended and terminated from his positions after publicly raising concerns about COVID-19 vaccination of children. As of June 2021, Christian served as Director of the Surgical Humanities Program (which he co-founded), Director of Quality and Patient Safety in the Department of Surgery, and Editor of the Journal of the Surgical Humanities. His roles overlapped with a contract position with the Saskatchewan Health Authority (SHA).\n\nOn June 17, 2021, Christian released a prepared statement to over 200 doctors and spoke at a press conference outside Walter Murray Collegiate in Saskatoon, appearing with a group called Concerned Parents Saskatchewan while a vaccine clinic was taking place at the high school. He declined to take questions from journalists. In his statement, Christian emphasized that he is a "very pro-vaccine physician" and is "pro-vaccine for my own family, including myself," citing the elimination of smallpox through vaccination. He stated he spoke "directly to parents and children" as "a physician, a surgeon and a fellow human being" and did not represent any group, the SHA, or the university.\n\nChristian invoked the "sacrosanct principle" of informed consent, arguing that patients must be made "fully aware of the risks of the medical intervention, the benefits of the intervention and if any alternatives exist to the intervention," particularly for "a new vaccine that has never before been tried in humans." He asserted this principle was "being consistently violated in this province for the m-RNA vaccine for our kids," claiming he had not met "a single vaccinated child or parent who has been adequately informed."\n\nChristian articulated eight points he argued parents and children must know before consenting: (1) that the mRNA vaccine is "a new, experimental vaccine design" never used in humans; (2) that the vaccines have not been fully authorized by Health Canada or the CDC, being under "interim authorization" in Canada and "emergency use authorization" in the US; (3) that while there is an emergency for the elderly, vulnerable, and health care workers—given that the mean age of COVID-19 deaths in Canada is 83.8—"Covid-19 does not pose a threat to our kids," with a death risk of less than 0.003%; (4) that children do not readily transmit the virus to adults; (5) that the mRNA vaccines have been "associated with several thousand deaths" in the US government\'s Vaccine Adverse Reporting System, which he called "a strong signal" that could not be ignored; (6) that there is a "real and significantly increased risk" of myocarditis (heart inflammation) in vaccinated children, leading the German national vaccine agency and the UK vaccine agency to not recommend the vaccine for healthy children; (7) that the benefit of the vaccine for children is "marginal at best," with an Absolute Risk Reduction of less than 2%; and (8) that Ivermectin is an alternative treatment. He urged authorities "to call a pause in the m-RNA vaccine roll-out to our kids" and stated that without informed consent, "the Nuremberg code is being violated." He also appeared in a video posted to the website BitChute that received nearly 70,000 views, in which he questioned the mainstream narrative about the pandemic, mocked restrictions, and called the vaccines "experimental injections."\n\nOn June 21, 2021, the Saskatchewan Health Authority and the College of Medicine wrote to Christian alleging they had "received information that you are engaging in activities designed to discourage and prevent children and adolescents from receiving Covid-19 vaccination contrary to the recommendations and pandemic-response efforts of Saskatchewan and Canadian public health authorities."\n\nOn June 23, 2021, Christian was called into a meeting with Dr. Preston Smith, Dean of the College of Medicine; Dr. Susan Shaw, Chief Medical Officer of the Saskatchewan Health Authority; and Dr. Brian Ulmer, Head of the Department of Surgery. He was informed of his immediate suspension from all faculty responsibilities and academic administrative roles, and that he would be fired from the university as of September 2021. The SHA terminated its contract with Christian, which was set to expire on September 21 following the required 90 days\' notice. Christian remained able to practice medicine and the university said it was not suspending payment for services he would have otherwise received during the investigation period. Christian recorded the 22-minute meeting and posted the audio online.\n\nDuring the meeting, Christian said, "You\'ve basically read indictments against me. These are the sort of panels that were set up in the Soviet Union and Nazi Germany against academics," adding, "I\'m not saying that you\'re Nazis or Soviets, but it\'s really disturbing, isn\'t it?" He stated he was one of many doctors being "silenced and censored," and told the officials, "You guys are living in a dystopian bubble. The truth will come out and when that bubble bursts, you guys are going to be in big trouble." Shaw expressed concern that Christian was "a highly intelligent man" who was "not making intelligent decisions," and Christian was offered supports if he was feeling distressed, which he declined.\n\nIn a statement, Dean Smith said the University "encourages public debate of important societal issues," but noted that per USask\'s Medical Faculty Policy, "our medical faculty are subject to the ethical and professional standards governing the practice of medicine." Smith told Global News that "when somebody is saying things that are at such great variance with all of our experts and worldwide experts and public safety is involved and could be jeopardized through these differences of view, I think we have to recognize that that\'s a special situation that requires urgent and extraordinary action." The SHA stated that "health system leaders are expected to be committed to fact-based, scientifically driven public messaging" and that leaders who depart "in favour of conspiracy theories put lives at risk by potentially discouraging uptake on life-saving vaccines."\n\nThe Justice Centre for Constitutional Freedoms announced it was representing Christian in his appeals and before the College of Physicians and Surgeons of Saskatchewan, against a complaint objecting to his advocacy for informed consent. Litigation Director Jay Cameron said the termination was "a violation of his charter-protected right to freedom of thought, belief, opinion and expression, and a betrayal of the principles of scientific inquiry," and described "a clear pattern of highly competent and skilled medical doctors in very esteemed positions being taken down and censored or even fired, for practicing proper science and medicine." The Justice Centre also drew comparisons to its representation of Dr. Chris Milburn in Nova Scotia, who faced disciplinary proceedings over an opinion column.\n\nOn June 30, 2021, the Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Dean Smith requesting an explanation of "how Dr Christian\'s suspension is not a violation of his academic freedom and how his suspension will not tend to create a chilly climate for expression on campus." SAFS argued that "nothing that has been reported should draw any discipline at all" and that "academic freedom protects his rights to have them and to express them publicly," noting the importance of professors being "free to question received wisdom and official policy" during a pandemic.']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
+          <t>christian - public - health - covid19 - children - western - public health - medicine - provost - scientific</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1063,26 +1063,26 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1_comments_racism_letter_canada</t>
+          <t>0_letter_comments_expression_wrote</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['comments', 'racism', 'letter', 'canada', 'sherman', 'statement', 'president', 'people', 'speech', 'white']</t>
+          <t>['letter', 'comments', 'expression', 'wrote', 'saying', 'views', 'social', 'statement', 'racism', 'class']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", "On June 8, 2020, Dr. David Lesbarrères, Dean of the Faculty of Graduate Studies at Laurentian University in Sudbury, Ontario, posted a tweet that triggered a major controversy. Lesbarrères, a French evolutionary ecologist and biologist who had been appointed dean for a five-year term in July 2016, was responding to a tweet from Peter Soroye, a Black PhD biology student at the University of Ottawa, who had described being on the receiving end of a racist comment. In his own tweet, Lesbarrères wrote: “And shockingly enough on our campuses, even white males receive racist comments about their past. Why can’t we all see that we were once a monkey, let alone bacteria?” He ended the post with the hashtag “#AllLivesMatters” (sic).\n\nThe tweet was quickly condemned by members of the Laurentian community. Some of Lesbarrères’s Twitter followers expressed hurt and anger, and as the tweet was reposted on social media, the reaction intensified. Many people viewed the hashtag #AllLivesMatter as a criticism of the Black Lives Matter movement, since it is often used by detractors of that movement. On June 9, Lesbarrères deleted the tweet and issued an apology on Twitter: “Last night, I issued a tweet that hurt many people. I apologize for my words and understand that I must educate myself further about #BlackLivesMatter and Tweeter (sic). I didn't know that # existed and now realize it is rooted in values I do not hold and that I strongly condemn.” He added: “I pledge to continue to educate myself, continue the fight for inclusivity and against racism, and I apologize to all people I have hurt.”\n\nOn the same day, Laurentian University president Dr. Robert Haché issued a statement on the university’s website. He said: “Yesterday, our Dean of Graduate Studies issued an inappropriate and offensive tweet. He has since apologized publicly for his comments which, by his own admission, have hurt many people in our Laurentian community and beyond. The University is following-up on this expeditiously and with the utmost care and attention.” Haché also wrote: “That said, I wish to reiterate that I condemn any racism on campus. Laurentian is a campus that does its utmost to ensure that we are safe and inclusive.” The statement listed resources available to students, staff and faculty, including counselling services, the Indigenous Sharing and Learning Centre, the keep.me.SAFE program for international students, the Employee and Family Assistance Program, and the Equity, Diversity and Human Rights Office.\n\nLaurentian’s Graduate Students’ Association tweeted a call to action demanding that the school make the dean’s consequences public. Aaron St. Pierre, president of the Laurentian Graduate Student Association, said many graduate students were “deeply upset” by the comments. He said the association was happy that Laurentian had committed itself to addressing systemic racism and saw the dean stepping down as a step towards that. The association suggested that mandatory training be implemented for all Laurentian staff and increased funding for the Equity, Diversity, and Human Rights Department.\n\nOn June 22, Haché announced that Lesbarrères would be stepping down from his role. His statement read: “Further to my statement of June 9th condemning racism on campus, today I wish to communicate with the Laurentian community that Dr. David Lesbarrères will be stepping down from his day-to-day functions as Dean of the Faculty of Graduate Studies for an indeterminate period, effective immediately.” Interim arrangements for leadership of the Faculty of Graduate Studies were to be communicated shortly, with the functions of the Dean overseen by the Vice-President, Academic and Provost, Dr. Serge Demers. It was expected that Lesbarrères would return to his previous position as an assistant professor in the department of biology, although he had no scheduled classes that term. Laurentian confirmed that Lesbarrères remained a professor.\n\nFollowing his departure, a number of colleagues, students, and outside organizations came to Lesbarrères’s defence. Jason Lepojarvi, an assistant professor of religious studies at Thorneloe University, described Lesbarrères as “a wonderful guy who has been mistreated” and a victim of cancel culture, defined as withdrawing support for people or businesses after they have done or said something considered objectionable or offensive. Guy Chamberland, chair of the department of ancient studies at Thorneloe, said he had studied Lesbarrères’s Twitter account dating back two years and found no evidence of racism. Mery Martinez Garcia, a biology professor originally from Colombia, said: “David is a biologist who believes all life matters. People know David is not a racist but they are afraid to speak out.” Charles Ramcharan, an assistant professor in the School of Environment, wrote a letter to the editor calling Lesbarrères’s suspension “a miscarriage of justice.” He said Lesbarrères had been “a strong voice for students who are black, Indigenous, and people of colour (BIPOC), an ally in the fight for equality, and a person in a position where his ideals and energies can be transformative.” Ramcharan noted that Lesbarrères had helped get Ontario Graduate Scholarships and Teaching Assistantships extended to international students, worked tirelessly to care for international students trapped during COVID-19, housed an Iranian student in his home, and helped a refugee student find safe shelter. Ramcharan compared the treatment of Lesbarrères to the French and Russian revolutions, saying: “In David’s case, we have put the wrong person on the guillotine.”\n\nOn September 3, 2020, three professors—Guy Chamberland, Mery Martinez Garcia, and Jason Lepojarvi—published an op-ed in The Sudbury Star arguing that Lesbarrères had been unfairly treated. They admitted the tweet was “terribly timed” and “poorly worded,” but said he had accidentally stepped on “a cultural landmine” by using a hashtag he did not understand. They called the reaction an example of “callout culture” or “cancel culture,” and wrote: “To go after innocent scapegoats like this comes across as a diversion, a mockery of justice, and is painfully divisive.” They also criticized the punishment as sending Lesbarrères on “administrative leave for cultural ‘re-education’ somewhere, we assume, in the Gulag.” They endorsed a student-led petition to have Lesbarrères reinstated as dean. The petition, started by students, gathered about 180 signatures from students and faculty. It stated that the reaction was unnecessary given Lesbarrères’s reputation for being inclusive and respectful, and that his apology was swift once he realized he had unintentionally used a hashtag that he did not know was racist in nature. The petition cited activities such as canoe expeditions and snowshoeing treks organized for international students.\n\nBlack Lives Matter Sudbury responded with disappointment to the op-ed. Co-chair Ra’anaa Brown, a recent Laurentian graduate, said the movement’s administrators were “deceived” and “disappointed” by the letter and the professors who signed it. She said: “It’s important that people in positions of authority know social justice issues. Maybe [David Lesbarrères] doesn’t know, but it’s important that he knows that saying All Lives Matter is a racism issue. It’s not correct at all.” Brown also said the reference to the Gulag in the op-ed diminished the experience of students who have experienced racism at Laurentian and elsewhere. She called on Laurentian to do more to create an environment where students feel protected, including creating scholarships to financially support racialized minority students.\n\nOn September 9, 2020, the Society for Academic Freedom and Scholarship (SAFS), an organization of university faculty members dedicated to the defence of academic freedom and the merit principle, wrote to President Haché urging that Lesbarrères be reinstated immediately. The letter, signed by SAFS president Mark Mercer, argued that Lesbarrères’s tweet “was not inappropriate in any way” and simply expressed shock at racist comments directed against white students while asking that we remember our common descent or common humanity. The letter said that those who disagree with the tweet are free to criticize it, and that no one is harmed by hearing a view they do not like. It warned that the treatment of Lesbarrères would create “a chilly climate on campus for expression and discussion” and make it difficult for Laurentian to recruit high-quality administrators. SAFS encouraged Laurentian to reinstate Lesbarrères, apologize for betraying academic values, and make a statement affirming freedom of expression on campus. The letter asked Haché to respond and requested permission to post the response on the SAFS website.\n\nLaurentian University’s director of communications, Isabelle Bourgeault-Tasse, said the university could not comment on whether Lesbarrères might be returned to his role as dean, since it was a personnel matter. She said: “Laurentian University is committed to providing a safe, inclusive and welcoming environment for all of our students, faculty and staff in support of our bilingual and tri-cultural mandate.” She also noted that the Laurentian Senate had established a new committee on racism and discrimination in June, and that a working group was tasked with creating a safe physical space for Black, Indigenous, and people of colour on campus.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>comments - racism - letter - canada - sherman - statement - president - people - speech - white</t>
+          <t>letter - comments - expression - wrote - saying - views - social - statement - racism - class</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1110,26 +1110,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3_class_gender_complaint_word</t>
+          <t>0_letter_comments_expression_wrote</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
+          <t>['letter', 'comments', 'expression', 'wrote', 'saying', 'views', 'social', 'statement', 'racism', 'class']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['In late March 2020, Kathleen Lowrey, an associate professor of anthropology at the University of Alberta, was dismissed from her administrative role as the Department of Anthropology’s associate chair of undergraduate programs. Lowrey had held the position since the start of the 2019-20 academic year, with the appointment normally running three years. Her dismissal was the result of informal, anonymous complaints made by one or more students to the University’s Office of Safe Disclosure and Human Rights and to the Dean of Students, André Costopolous. The students alleged that Lowrey’s “gender critical” views on sex and gender made them feel “unsafe” and caused them “harm,” and that her presence in the role could drive students away from choosing anthropology as a major. Lowrey was told it did not matter whether the claims against her were true. She was not given specific charges, was not given a hearing, and the complainants were not identified.\n\nLowrey describes herself as a gender-critical feminist. Her core views include the positions that biological sex is real, that men cannot get pregnant, that lesbians don’t have penises, and that transgender identity should not trump biological sex for policy decisions. She had publicly expressed those views by publishing an article on the website Feminist Current, posting signs and material on her office door, and teaching a January 2020 course, “Anthropology of Women,” in which she told students on the first day that they would read material currently out of fashion in academia and that they did not have to agree with her. She said she believed none of the complaints came from students who actually took the class. Lowrey was also told she had discouraged students from organizing Pride events, a claim she denied, and which led her to conclude the complaints centred on her views.\n\nWhen asked to resign, Lowrey refused, insisting that if the university wished to dismiss her from the service role it would need to put its reasons in writing. Dean of Arts Lesley Cormack subsequently sent her a letter on March 24, 2020, stating that she was no longer “effective” in the role and that “it is not in the best interests of the students or the university” for her to carry on. The letter did not specify how the university reached that conclusion. University spokesperson Hallie Brodie said Lowrey’s academic appointment as associate professor had not changed, cited privacy reasons for not commenting on the administrative role, and said the university had no further comment.\n\nThe case generated extensive commentary and controversy. Carolyn Sale, writing for the Centre for Free Expression blog at Ryerson University, argued that the University of Alberta was endorsing ideological conformity and that the process was akin to “McCarthyite” proceedings or ex officio proceedings during the English Reformation, in which accused heretics could be punished based on secret disclosures never made public. Sale contended that there is no such thing as a “safe” learning environment if “safe” means never encountering disagreeable views, and that academic freedom applies to all aspects of a professor’s work, conventionally defined as 40% teaching, 40% research, and 20% service. She also criticized the university’s concern that Lowrey’s views could have financial consequences for the department under a budget model where government funding follows students, and the university’s reasoning that not dismissing Lowrey would make students feel the university cared more about supporting the professor than about them.\n\nMark Mercer, president of the Society for Academic Freedom and Scholarship, wrote to Dean Cormack asking her to reinstate Lowrey, warning that removing her would discourage faculty from assuming service roles and could harm teaching and academic integrity. Peter Wood, president of the National Association of Scholars, later wrote a public open letter to Steve Patten, the new Dean of Arts, urging the university to reverse its decision. Wood called Lowrey’s view that humans are sexually binary a biological fact, and argued that removing her from her position communicated to faculty that responsible expression of accurate information would be punished if it irritated enough students or administrators. Columnists Lorne Gunter and Barbara Kay defended Lowrey’s freedom of expression even while disagreeing with her views, with Gunter calling the dismissal a “witch-hunt mentality” and Kay noting that Lowrey was concerned the university had taken the position that “saying you don’t think a person can change sex is a firing offence.”\n\nStudent and faculty reactions were divided. Elizabeth Sawchuk, a Banting postdoctoral fellow and adjunct professor, said she had no problem with Lowrey exploring gender and sexuality in scholarship, but found the images on Lowrey’s door offensive and not academically appropriate, and said they harmed trans and non-binary students and colleagues. Chris Beasley, president of the Organization of Arts Students and Interdisciplinary Studies, said the removal was a positive result for students and that campus must remain a safe space. Joel Agarwal, president of the U of A Students’ Union, said professors are guaranteed academic freedom but that it does not give them immunity from discipline for behaviour that would lead to discipline in any other workplace. An anonymous student said Lowrey’s social media posts on Spinster, where she welcomed students searching her feed for “hate speech,” made the student fear bringing concerns forward. Another anonymous student said Lowrey disrupted a student-led queer anthropology event with “anti-trans remarks” and argued directly with a trans man in the room. Lowrey said she had attended the event to listen, but felt she needed to speak up, remained polite and careful, and believed some faculty members did not like being confronted.\n\nLowrey herself published an essay in Quillette describing her journey from South American anthropology to gender-critical feminism, noting that a decade earlier she might have joined campaigns to cancel other academics. She said that during the 2019-20 academic year the University of Alberta introduced sweeping equity, diversity, and inclusion policies that she believed could be used to silence feminist women. She noted she was the only member of the university’s General Faculties Council to vote against the new EDI policy, which included a focus on gender at the expense of sex. She said the conflict was unavoidable because contemporary gender ideology requires active affirmation that men can become women and vice versa, and that refusing to assent is treated as doing active harm to trans-identified individuals. She expressed concern for non-tenured university employees and for students afraid to voice shared opinions.\n\nA grievance was filed by Lowrey and the Association of Academic Staff of the University of Alberta, the academic staff union. The union alleged that the university breached the collective bargaining agreement by failing to uphold academic freedom and by exercising management rights in an unfair, unreasonable, inequitable, and non-arbitrary manner. An arbitrator sided with the university, finding that Lowrey was removed not because of her academic views but because she was a “protagonist in a dispute” that prevented her from effectively serving as associate chair. The Alberta Labour Relations Board upheld that decision. In November 2024, the Alberta Court of Appeal dismissed the union’s appeal, ruling that it raised no question of law. Justice Dawn Pentelechuk wrote that the arbitrator had drawn a rational and transparently articulated line between Lowrey’s academic views, which were not the basis for the university’s decision, and her suitability to carry out the role given the circumstances that had developed. The court said the union’s argument was largely a complaint about the interpretation and weight given to the evidence, not an identifiable legal error.\n\nThroughout the controversy, Lowrey maintained that her dismissal from the service role was a violation of academic freedom. She said the university had taken the position that if a professor is not specifically covered by academic freedom, that person can be fired, which she called terrifying and horrible. She said the implications were dangerous because the debate over biological sex and gender identity is a live issue in Canadian democracy. Supporters of Lowrey argued that unorthodox or controversial views must be actively debated and never suppressed, and that universities must not become homes for orthodoxy or dogma. Critics argued that Lowrey’s methods of communicating her views, including her office door and social media posts, created an exclusionary and toxic environment and went beyond legitimate academic discussion.', 'Students at Bishop’s University in Sherbrooke, Que., have alleged that sociology professor Dr. Cheryl Gosselin has used derogatory and discriminatory language in her classroom for years. Multiple students spoke to CTV News and to The Campus, the university’s independent student newspaper, describing incidents involving racist, homophobic and Islamophobic comments, slurs, stereotyping and dismissive responses when students raised concerns. The allegations prompted an internal university memo, a review of complaint processes, reassignment of Gosselin’s winter 2025 classes, and statements from Quebec’s Higher Education Ministry.\n\nSociology student Malik Kessouagni, who said he took three classes with Gosselin, alleged that she spoke about how Black women “react” and said she “didn’t really like Black women” while staring at a Black woman in the class. Kessouagni also alleged that Gosselin discussed the stereotype about Black men with large penises while staring at him and a friend, as they were the only Black people present. Marie-May Lamothe, another sociology student, said she witnessed discriminatory comments about the LGBTQIA2S+ community as recently as November 2024. She said Gosselin used the “F” slur in class, repeating it six or seven times, and that there was “an audible gasp from the classroom.” Lamothe also alleged that Gosselin misgendered non-binary authors, called Arab men sexist, argued that women who wear the hijab “slut shame” Caucasian women, and freely used the “N” word and the “F” slur when discussing readings or lectures about Black and LGBTQIA+ communities. The Campus’s investigation identified the class as a first-year Gender and Sociology course (SOC129) and the date as November 12, 2024. Students said Gosselin used the slur while quoting Joel Mittleman’s 2022 article, “Homophobic Bullying as Gender Policing: Population-Based Evidence,” which contains the uncensored slur, and then kept repeating it while asking questions like “what does this mean, f-g.” Students described the discomfort in the room, and Allister Coursol noted that “no one was answering.” Aaliyah Wilburn, a political science student, said she raised her hand to ask Gosselin to consider the repercussions of using such strong language, but felt dismissed: “She basically blew me off. Told me I was incorrect, and basically, she made me feel dumb for saying something.” Kessouagni recalled Gosselin’s defence: “It’s not a word that she uses on a daily basis.” He said, “Regardless of the fact if you use it on a daily basis or not, you still used it. Therefore, it’s still an issue and you do not want to hold yourself accountable.” Sociology student Rory Point-Du-Jour, who took a class with Gosselin in 2022, said Gosselin was “not really apologetic or regretful” and told students “you guys kind of just have to deal with it.”\n\nWilburn reported the incident to the university’s Equity, Diversity and Inclusion (EDI) department and later lodged a formal complaint against Gosselin. She said the EDI response felt like they were “trying to find reasons and excuses for why Cheryl was saying the things that she was saying” and argued that there is “no excuse” and that the university should “hold your teachers accountable.” The Campus reported that Wilburn had not received recent information on whether the complaint was still in process. Andrew Webster, Vice-Principal Academics and Research, said he could not comment on the status of the complaint because of Quebec and Canadian privacy laws, while adding that complaints are taken “very seriously.”\n\nThe students also described earlier complaints. Markayza Mitchell, a sociology student, told The Campus about an incident in winter 2023 when she raised concerns in Gosselin’s first-year Quebec Society course about the lack of Indigenous representation. According to Mitchell, Gosselin said she shouldn’t impose her perspective on the rest of the class and pointed to the door, telling her she could leave. Mitchell said she “didn’t feel respected at all” and later dropped the class, which affected her ability to graduate. Leana Ceresoli, who became Social Science Senator in May 2024, said she had been made aware of Gosselin’s controversy through informal complaints about separate undisclosed incidents in Gosselin’s 2023 Quebec Society course. Ceresoli relayed these concerns to Roser Rise, then Student Representative Council Vice-President of Academic Affairs, and Rise said she worked with Webster to create a more clearly defined structure for formal complaints. However, the students who complained informally did not wish to pursue the formal process. Ceresoli, who was a teaching assistant for Gosselin’s fall 2024 Gender and Society course, was not in class when the slur was allegedly used and said she was surprised students had not told her.\n\nThe Bishop’s University Students’ Representative Council (SRC) said it was not aware of any formal complaints against Gosselin and encouraged students to contact the Office of the Dean or another relevant administrative office to file a formal report. Bishop’s University initially said it “cannot comment, discuss or disclose any confidential or personal information” and that it holds “itself and its faculty and staff to the highest standards.” Communications manager Sonia Patenaude said the university acts swiftly if concerns are raised and follows due process. After the CTV News report was published, an internal memo signed by Principal Sébastien Lebel-Grenier and vice-principals was sent to students and staff. The memo recognized that members of the community might find the media report “challenging and emotionally straining.” It said complaints “should be discussed with the professor, the program chair, the dean, or the ombudsperson” and that reports or complaints would be treated confidentially and investigated fairly. The university said it would “be pursuing a conversation in Senate, starting at its Jan. 24 meeting, on ways to better communicate resources and processes available to students” and would “also be examining how our processes can be improved.” The memo also said universities are “places of learning through the free and open discussion of sometimes difficult or challenging subjects and ideas,” and that professors must pursue truth and disseminate knowledge responsibly within a “safe and respectful environment.” It lamented that its “internal processes are not sufficiently known or understood, or may be seen as insufficient.”\n\nQuebec’s Higher Education Ministry called the allegations “worrying” in the first CTV article, with spokesperson Simon Savignac saying, “Discriminatory comments cannot be tolerated” and inviting students to lodge complaints through official channels. The ministry later said it was “shocked” by the allegations and in close communication with the university. During the January 24 Senate meeting, Webster proposed integrating a link to university resources into course syllabi to standardize communication, but the proposal turned into a debate on professorial autonomy and administrative overreach. Webster said the proposal would be revisited by the Academic Standing Admissions Policy committee and intended to be brought back to Senate.\n\nFollowing the CTV report, Gosselin’s winter 2025 classes — Sociology of the Body (SOC219) and Quebec Society (SOC102) — were cancelled on January 14. On January 16, Gosselin taught both classes without acknowledging the article. The following week, the classes were taken over by Dr. Travis Smith from the sports studies department and Dr. David Webster from the history department. Gosselin did not respond to requests for comment; Andrew Webster said she had no wish to comment and preferred not to be contacted further. Students such as Lamothe continued to call for real consequences, saying Gosselin “needs to face a real repercussion and realize that this is an actual incident that means a lot.” The students also expressed concern that a white student might think, “OK, if my professor is saying this, I should be able to say it too,” and that derogatory terms used so freely in a classroom are “really appalling.”', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>class - gender - complaint - word - rights - investigation - views - complaints - 2015 - expression</t>
+          <t>letter - comments - expression - wrote - saying - views - social - statement - racism - class</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1160,33 +1160,33 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0_committee_president_board_hall</t>
+          <t>1_committee_president_board_public</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
+          <t>['committee', 'president', 'board', 'public', 'caut', 'applicants', 'hall', 'grievor', 'school', 'search']</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['The grievor, Chad Thompson, had been employed as an Assistant Professor at University College of the North (UCN) for approximately two years when he was terminated in August 2011 for insubordination, insolence and defiant behaviour in the context of his involvement on a search committee. The termination occurred following his role as Chair of the Selection Board for Competition No. 3145, a search to fill a full-time, regular Social Science Instructor position in the Faculty of Arts and Sciences. The grievor held a full-time tenure track position within the bargaining unit represented by the Manitoba Government and General Employees\' Union.\n\nNorma Baker, the grievor\'s spouse and Dean of the Faculty of Arts and Sciences, was initially involved in preparing the posting and reviewing applications, but then went on sick leave. Because of concern about delay, the Vice-President - Academic, Kathryn McNaughton, requested that the grievor chair the search committee. The committee shortlisted two candidates, Aaron Crowe and Jason Hildebrandt. Crowe was interviewed, while Hildebrandt was unavailable due to an injury. The search committee unanimously endorsed Crowe, pending reference checks. Although UCN policy provided that Human Resources would check references, there was discussion by the committee and it was decided that Baker, as an academic, should conduct the reference checks, with the input of Human Resources committee member Linda Hunt. Baker did conduct the reference checks of Crowe. Linda Hunt prepared the Selection Board Report and submitted it to Interim President Konrad Jonasson with the committee\'s recommendation to hire Crowe.\n\nBy e-mail of July 14, 2011, Jonasson refused to approve the recommendation. He raised concerns including an appearance of conflict of interest by having both Baker and the grievor involved, questions about the second candidate\'s inability to interview, the educational qualifications of the recommended candidate, and whether information regarding the candidate\'s PhD program was current. Jonasson offered two options: consider the search failed and start anew, or go back and review all candidates to determine if any of the three not granted interviews should be interviewed and whether the second candidate remained interested. The e-mail concluded that if the other three did not merit an interview and candidate 2 could not go forward, the search should be declared failed and restarted. Baker, the grievor, committee member Sandra Barber, and McNaughton interpreted this e-mail as a declaration of failed search. Jonasson testified that it was designed to indicate concerns and solicit additional information, and that he did not declare a failed search until a subsequent e-mail on July 15.\n\nOn July 15, 2011 at 8:54 a.m., the grievor directed an e-mail to Linda Hunt stating that he would not be submitting his notes and ratings for the LTF hiring process, that given the actions of the Interim President regarding competition 3145 he had no confidence that Mr. Jonasson would respect the policies and procedures of HR, and that he was unwilling to participate any further in this or any other hiring committee until he regained confidence in the process. The e-mail was copied to the head of Human Resources and to McNaughton, but not to Jonasson. The grievor testified that he was not attempting to hide anything, that he felt it was part of his role to speak out where he believed the governance of the institution to be in error, and that he did not regret sending the message, although he wished he had worded it more carefully.\n\nAt 9:14 a.m. on July 15, approximately twenty minutes after the e-mail to Hunt, the grievor sent an e-mail directly to Aaron Crowe, advising him that, as Chair of the Selection Committee, he was writing with deepest regret to inform him of the decision by Interim President Mr. Konrad Jonasson to reject the unanimous recommendation of the Selection Committee to offer him the position. The e-mail suggested that Crowe might wish to speak with Human Resources regarding UCN policy HR-03-0 and with MGEU regarding Article 11:04 in the collective agreement, and was copied to the Manager of Human Resources and two Union staff representatives, including Nelson. Jonasson considered this a violation of protocol and a breach of confidentiality of the selection process. The grievor acknowledged he was angry, that he felt Jonasson\'s decision was not just, that sending the e-mail was a "very stupid thing to do," and that he regretted having done so. Crowe, an internal candidate, subsequently grieved the failure to award him the position.\n\nBy letter of August 10, 2011, Jonasson issued Baker a disciplinary reprimand for various misconduct, including her involvement on the search committee, her involvement in contacting references, and her e-mail of July 15. Baker was out of scope and not in a position to grieve that discipline; she subsequently resigned her position with UCN. Jonasson met with the grievor and Union representative Nelson on July 27, 2011 to review concerns. There was an issue as to whether the grievor offered regret or an apology; Jonasson had no recollection of an apology, while the grievor believed he showed regret and offered an apology, and Nelson testified that the grievor apologized at least twice or perhaps three times. Subsequent to that meeting, the grievor\'s position was terminated by letter of August 17, 2011.\n\nThe letter of termination stated that the grievor\'s actions relating to competition no. 3145 were in fundamental breach of his employment obligations. It cited three reasons: first, without the knowledge or approval of Human Resources, he allowed Baker to continue to participate on the Selection Board after she withdrew and allowed her to contact references on behalf of UCN, which was a significant breach of trust and a clear breach of policy; second, the grievor made insolent allegations against the Interim President in his e-mail to Hunt, stating he had no confidence that Jonasson would respect HR policies and procedures; and third, the grievor violated UCN policy by sending an e-mail directly to the recommended candidate advising him of the rejection, copying representatives of the MGEU Union who were not employees of UCN, and highlighting sections of the Collective Agreement for the unsuccessful applicant. The letter asserted that the grievor\'s conduct was clearly intended to undermine the authority of the Interim President.\n\nThe Employer argued that the grievor was a short term employee who had been insubordinate, insolent and defiant without justification, that his evidence was misleading in an attempt to minimize what he had done, and that the e-mails were inappropriate and sent without justification. The Employer submitted that this was extreme insubordination striking at the heart of the employment relationship, that none of the normal factors of mitigation were present, and that dismissal was the appropriate response. The Employer noted that the grievor had not demonstrated exceptional financial hardship other than what one would normally anticipate from a termination, and argued that even if academic freedom were engaged, it was not used responsibly.\n\nThe Union asserted that while there was conduct deserving of discipline, there had been no progressive discipline and termination was simply too severe. The Union pointed out that the grievor had an unblemished record, that Jonasson acknowledged he had not looked at the grievor\'s prior clear record, and that another individual, Baker, had received only a written reprimand for similar conduct, demonstrating inconsistency in the application of discipline. The Union argued that the e-mail to Crowe was written in the heat of the moment, that the grievor accepted responsibility for his actions, that the reference checks were done with the involvement of Human Resources, and that the e-mail to Hunt was an expression of concern over the hiring process, related to the service component of his role and potentially within academic freedom under Article 72 of the Collective Agreement. The Union requested reinstatement and compensation, with a letter of reprimand as the appropriate discipline.\n\nThe arbitrator, R.A. Simpson, found that while the grievor\'s conduct was insubordinate and warranted discipline, termination was not justified. The arbitrator noted that although the grievor was entitled to consider the July 14 e-mail equivalent to a declaration of failed search, that did not excuse his subsequent conduct. The e-mail to Hunt, containing comments about the Interim President\'s respect for HR policies, had a degree of insolence amounting to insubordination and was not within the service component of the grievor\'s role or within the parameters of academic freedom, but considered in isolation, it could have been dealt with through perhaps a verbal or at most a written reprimand. The e-mail to Crowe was clearly insubordinate, involving a breach of confidentiality, disclosure of confidential information, an invitation to challenge the Employer\'s decision, and a defiance of and challenge to the Employer\'s authority. However, the arbitrator was not satisfied that the employment relationship was irreparably harmed or could not be successfully rehabilitated. The grievor was not a long term employee, but his record over two years was without blemish, he was not challenged on his evidence as to exceptional services he had provided, and dismissal would have a significant adverse effect upon his career. There was no evidence that progressive discipline short of termination was considered. The arbitrator accepted the Employer\'s argument that there was a significant difference between Baker\'s situation and the grievor\'s, with Baker communicating with colleagues and advocating for faculty and students, as opposed to the grievor communicating with an unsuccessful candidate and disclosing confidential information. Nevertheless, a lesser discipline could well have been sufficient to rehabilitate the employment relationship. The arbitrator substituted a two-month suspension without pay for the termination, stating that this was a significant penalty that should send a message that such behaviour would not be tolerated. The grievance was allowed, the termination rescinded, and a two-month suspension without pay substituted.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.']</t>
+          <t>['Between March 2011 and July 2012, the University of Calgary (U of C) worked to secure a sponsorship from Enbridge, a Calgary-based oil and gas pipeline company, to establish a research institute at the Haskayne School of Business (HSB). Dr. Joe Arvai, a recently appointed faculty member, was asked to be director of what became the Enbridge Centre for Corporate Sustainability (ECCS). The sponsorship agreement, dated July 1, 2011, was between Enbridge and “The Governors of the University of Calgary,” committing $225,000 annually over ten years. However, planned activities were based on an annual budget of $500,000, more than double Enbridge’s financial outlay, creating an immediate funding shortfall that was supposed to be made up by additional corporate fundraising.\n\nDuring the establishment and launch of the ECCS, Arvai repeatedly raised concerns about Enbridge’s influence over the Centre’s academic mission. Emails disclosed through freedom of information requests showed that Enbridge exerted influence over the Centre’s name, the selection of partner institutions, the planning of the public launch, and the role of the director. Enbridge pressed for Central Michigan University (CMU) as a partner, in part because CMU had given Enbridge "very valuable advice" after the 2010 Kalamazoo River oil spill in Michigan; Arvai objected on academic grounds, saying CMU had only one faculty member in the relevant field, but was pressured to accept. HSB Dean Len Waverman told Arvai that “the monies we give to CMU are tiny – it won’t be viewed as a payoff,” and that “Elizabeth [Cannon] will have a fit if she sees this.” Enbridge also expressed concerns about Arvai’s appointment to a U.S. Environmental Protection Agency (EPA) Scientific Advisory Board, and the university delayed its announcement of that appointment so as not to “piss off Enbridge any more.” Arvai stated that “we cannot maintain our credibility as serious scholars/researchers if the sponsors can dictate the Centre’s agenda,” and that he could not serve as director if sponsors were allowed to meddle in academic activities.\n\nArvai was removed as ECCS director in March 2012. He later told the CAUT committee that he was removed one week after he informed Enbridge’s public relations firm, National Public Relations, of his opposition on scientific grounds to the Northern Gateway pipeline. In an email of March 19, 2012, Dean Waverman told Enbridge officials: “Joe Arvai is no longer Director of the Centre, there are too many conflicts and demands!” Arvai subsequently left the U of C and is now at the University of Michigan.\n\nA CBC News investigation in November 2015 prompted the Canadian Association of University Teachers (CAUT) to establish an Ad Hoc Investigatory Committee. In his first public statement, an opinion piece reprinted by CBC News, Arvai said the CBC had done “an exceptional job of getting the facts correct,” and that the post hoc suggestions that decisions setting up the Enbridge Centre were “transparent, legitimate, and free of corporate interference or conflict-of-interest” were as difficult for him to accept as they were in 2012. He said donors should be able to suggest, but not select, advisory individuals, and should have a voice in a centre’s name and mission, but should not require that support be limited to those sharing their “core values.”\n\nThe CAUT report, released in October 2017, made findings on conflict of interest, academic freedom, external influence, funding, governance, and the McMahon review. It found a “clear appearance of a conflict of interest” on the part of U of C President Elizabeth Cannon, who served on the Enbridge Income Fund Holdings Board for significant remuneration while president, and who failed to publicly recuse herself from Enbridge-related matters. The report found that Cannon intervened directly with Dean Waverman, telling him that Enbridge was “not very happy,” that she wanted a good relationship with Enbridge, and emphasizing “I am on one of their Boards!” The report also found that the U of C Board of Governors failed to review or approve the sponsorship agreement, despite being a party to it, and that Cannon’s reliance on an “administrative lapse” was an “unacceptable evasion of responsibility.”\n\nThe CAUT committee concluded that Dr. Arvai’s academic freedom was compromised as a result of the U of C’s mishandling of the Enbridge Centre, appearing to be due to a desire on the part of senior leadership to please a significant donor. It found that Enbridge sought to influence the Centre’s establishment and launch, and that university administrators failed to convey that this influence was inappropriate. The report found that Enbridge was given special access to academic staff, was allowed to recommend partners, and had extensive influence over the public launch. The committee found Arvai’s explanation for his departure credible and troubling. It also found that the sponsorship was “skewed in Enbridge’s favour” from the start, with unfunded promises made at the university’s risk and expense, creating a “cycle of dependency” and pressures to compromise academic integrity. It identified a “significant failure of collegial governance, accountability and oversight,” and warned of “worrying signs of a culture of silencing and reprisal at the U of C.”\n\nThe CAUT report was highly critical of the university’s own review, led by retired Justice Terrence McMahon. The Board of Governors had commissioned the McMahon review in November 2015; McMahon found no wrongdoing and cleared university officials, including President Cannon, and the board considered the matter closed. The CAUT committee, however, stated that it was misleading to describe the McMahon review as “independent” and “transparent,” because it was established, mandated, and staffed by the Board or its counsel, and because it did not acknowledge or discuss the central role of academic freedom. The committee said McMahon gave the benefit of the doubt to senior officials while subjecting Arvai and Waverman to damaging criticism, and that the review’s selective approach to confidentiality was inconsistent with fairness and thoroughness. The CAUT report made recommendations including prohibiting university presidents and senior officials from serving for remuneration on external corporate boards, reviewing Board governance, and releasing all documents provided to the McMahon review.\n\nFollowing the CAUT report, the University of Calgary Faculty Association, chaired by Sandra Hoenle, called on the provincial government to probe governance at the university. Hoenle wrote that one of the greatest concerns was “the domination of the senior administration in the governance processes,” and that the Board of Governors and Senior Administration had misapplied “for-profit corporate structures within a university collegial setting,” keeping decision-making behind closed doors. She said, “We’re not a corporation. Universities are not corporations.” Arvai welcomed the CAUT report and said it was “wholly appropriate for the faculty association to be asking for a provincial review.” Alberta’s Ministry of Advanced Education stated that conflict of interest was being examined at public boards, including academic freedom, through a review of agencies, boards, and commissions, and that “Academic freedom is a cornerstone of any university.” Hoenle said the provincial governance review had been truncated and should be expanded to specifically deal with issues identified in the CAUT and CBC investigations.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
+          <t>committee - president - board - public - caut - applicants - hall - grievor - school - search</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1207,33 +1207,33 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3_class_gender_complaint_word</t>
+          <t>0_letter_comments_expression_wrote</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>['class', 'gender', 'complaint', 'word', 'rights', 'investigation', 'views', 'complaints', '2015', 'expression']</t>
+          <t>['letter', 'comments', 'expression', 'wrote', 'saying', 'views', 'social', 'statement', 'racism', 'class']</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['In late March 2020, Kathleen Lowrey, an associate professor of anthropology at the University of Alberta, was dismissed from her administrative role as the Department of Anthropology’s associate chair of undergraduate programs. Lowrey had held the position since the start of the 2019-20 academic year, with the appointment normally running three years. Her dismissal was the result of informal, anonymous complaints made by one or more students to the University’s Office of Safe Disclosure and Human Rights and to the Dean of Students, André Costopolous. The students alleged that Lowrey’s “gender critical” views on sex and gender made them feel “unsafe” and caused them “harm,” and that her presence in the role could drive students away from choosing anthropology as a major. Lowrey was told it did not matter whether the claims against her were true. She was not given specific charges, was not given a hearing, and the complainants were not identified.\n\nLowrey describes herself as a gender-critical feminist. Her core views include the positions that biological sex is real, that men cannot get pregnant, that lesbians don’t have penises, and that transgender identity should not trump biological sex for policy decisions. She had publicly expressed those views by publishing an article on the website Feminist Current, posting signs and material on her office door, and teaching a January 2020 course, “Anthropology of Women,” in which she told students on the first day that they would read material currently out of fashion in academia and that they did not have to agree with her. She said she believed none of the complaints came from students who actually took the class. Lowrey was also told she had discouraged students from organizing Pride events, a claim she denied, and which led her to conclude the complaints centred on her views.\n\nWhen asked to resign, Lowrey refused, insisting that if the university wished to dismiss her from the service role it would need to put its reasons in writing. Dean of Arts Lesley Cormack subsequently sent her a letter on March 24, 2020, stating that she was no longer “effective” in the role and that “it is not in the best interests of the students or the university” for her to carry on. The letter did not specify how the university reached that conclusion. University spokesperson Hallie Brodie said Lowrey’s academic appointment as associate professor had not changed, cited privacy reasons for not commenting on the administrative role, and said the university had no further comment.\n\nThe case generated extensive commentary and controversy. Carolyn Sale, writing for the Centre for Free Expression blog at Ryerson University, argued that the University of Alberta was endorsing ideological conformity and that the process was akin to “McCarthyite” proceedings or ex officio proceedings during the English Reformation, in which accused heretics could be punished based on secret disclosures never made public. Sale contended that there is no such thing as a “safe” learning environment if “safe” means never encountering disagreeable views, and that academic freedom applies to all aspects of a professor’s work, conventionally defined as 40% teaching, 40% research, and 20% service. She also criticized the university’s concern that Lowrey’s views could have financial consequences for the department under a budget model where government funding follows students, and the university’s reasoning that not dismissing Lowrey would make students feel the university cared more about supporting the professor than about them.\n\nMark Mercer, president of the Society for Academic Freedom and Scholarship, wrote to Dean Cormack asking her to reinstate Lowrey, warning that removing her would discourage faculty from assuming service roles and could harm teaching and academic integrity. Peter Wood, president of the National Association of Scholars, later wrote a public open letter to Steve Patten, the new Dean of Arts, urging the university to reverse its decision. Wood called Lowrey’s view that humans are sexually binary a biological fact, and argued that removing her from her position communicated to faculty that responsible expression of accurate information would be punished if it irritated enough students or administrators. Columnists Lorne Gunter and Barbara Kay defended Lowrey’s freedom of expression even while disagreeing with her views, with Gunter calling the dismissal a “witch-hunt mentality” and Kay noting that Lowrey was concerned the university had taken the position that “saying you don’t think a person can change sex is a firing offence.”\n\nStudent and faculty reactions were divided. Elizabeth Sawchuk, a Banting postdoctoral fellow and adjunct professor, said she had no problem with Lowrey exploring gender and sexuality in scholarship, but found the images on Lowrey’s door offensive and not academically appropriate, and said they harmed trans and non-binary students and colleagues. Chris Beasley, president of the Organization of Arts Students and Interdisciplinary Studies, said the removal was a positive result for students and that campus must remain a safe space. Joel Agarwal, president of the U of A Students’ Union, said professors are guaranteed academic freedom but that it does not give them immunity from discipline for behaviour that would lead to discipline in any other workplace. An anonymous student said Lowrey’s social media posts on Spinster, where she welcomed students searching her feed for “hate speech,” made the student fear bringing concerns forward. Another anonymous student said Lowrey disrupted a student-led queer anthropology event with “anti-trans remarks” and argued directly with a trans man in the room. Lowrey said she had attended the event to listen, but felt she needed to speak up, remained polite and careful, and believed some faculty members did not like being confronted.\n\nLowrey herself published an essay in Quillette describing her journey from South American anthropology to gender-critical feminism, noting that a decade earlier she might have joined campaigns to cancel other academics. She said that during the 2019-20 academic year the University of Alberta introduced sweeping equity, diversity, and inclusion policies that she believed could be used to silence feminist women. She noted she was the only member of the university’s General Faculties Council to vote against the new EDI policy, which included a focus on gender at the expense of sex. She said the conflict was unavoidable because contemporary gender ideology requires active affirmation that men can become women and vice versa, and that refusing to assent is treated as doing active harm to trans-identified individuals. She expressed concern for non-tenured university employees and for students afraid to voice shared opinions.\n\nA grievance was filed by Lowrey and the Association of Academic Staff of the University of Alberta, the academic staff union. The union alleged that the university breached the collective bargaining agreement by failing to uphold academic freedom and by exercising management rights in an unfair, unreasonable, inequitable, and non-arbitrary manner. An arbitrator sided with the university, finding that Lowrey was removed not because of her academic views but because she was a “protagonist in a dispute” that prevented her from effectively serving as associate chair. The Alberta Labour Relations Board upheld that decision. In November 2024, the Alberta Court of Appeal dismissed the union’s appeal, ruling that it raised no question of law. Justice Dawn Pentelechuk wrote that the arbitrator had drawn a rational and transparently articulated line between Lowrey’s academic views, which were not the basis for the university’s decision, and her suitability to carry out the role given the circumstances that had developed. The court said the union’s argument was largely a complaint about the interpretation and weight given to the evidence, not an identifiable legal error.\n\nThroughout the controversy, Lowrey maintained that her dismissal from the service role was a violation of academic freedom. She said the university had taken the position that if a professor is not specifically covered by academic freedom, that person can be fired, which she called terrifying and horrible. She said the implications were dangerous because the debate over biological sex and gender identity is a live issue in Canadian democracy. Supporters of Lowrey argued that unorthodox or controversial views must be actively debated and never suppressed, and that universities must not become homes for orthodoxy or dogma. Critics argued that Lowrey’s methods of communicating her views, including her office door and social media posts, created an exclusionary and toxic environment and went beyond legitimate academic discussion.', 'Students at Bishop’s University in Sherbrooke, Que., have alleged that sociology professor Dr. Cheryl Gosselin has used derogatory and discriminatory language in her classroom for years. Multiple students spoke to CTV News and to The Campus, the university’s independent student newspaper, describing incidents involving racist, homophobic and Islamophobic comments, slurs, stereotyping and dismissive responses when students raised concerns. The allegations prompted an internal university memo, a review of complaint processes, reassignment of Gosselin’s winter 2025 classes, and statements from Quebec’s Higher Education Ministry.\n\nSociology student Malik Kessouagni, who said he took three classes with Gosselin, alleged that she spoke about how Black women “react” and said she “didn’t really like Black women” while staring at a Black woman in the class. Kessouagni also alleged that Gosselin discussed the stereotype about Black men with large penises while staring at him and a friend, as they were the only Black people present. Marie-May Lamothe, another sociology student, said she witnessed discriminatory comments about the LGBTQIA2S+ community as recently as November 2024. She said Gosselin used the “F” slur in class, repeating it six or seven times, and that there was “an audible gasp from the classroom.” Lamothe also alleged that Gosselin misgendered non-binary authors, called Arab men sexist, argued that women who wear the hijab “slut shame” Caucasian women, and freely used the “N” word and the “F” slur when discussing readings or lectures about Black and LGBTQIA+ communities. The Campus’s investigation identified the class as a first-year Gender and Sociology course (SOC129) and the date as November 12, 2024. Students said Gosselin used the slur while quoting Joel Mittleman’s 2022 article, “Homophobic Bullying as Gender Policing: Population-Based Evidence,” which contains the uncensored slur, and then kept repeating it while asking questions like “what does this mean, f-g.” Students described the discomfort in the room, and Allister Coursol noted that “no one was answering.” Aaliyah Wilburn, a political science student, said she raised her hand to ask Gosselin to consider the repercussions of using such strong language, but felt dismissed: “She basically blew me off. Told me I was incorrect, and basically, she made me feel dumb for saying something.” Kessouagni recalled Gosselin’s defence: “It’s not a word that she uses on a daily basis.” He said, “Regardless of the fact if you use it on a daily basis or not, you still used it. Therefore, it’s still an issue and you do not want to hold yourself accountable.” Sociology student Rory Point-Du-Jour, who took a class with Gosselin in 2022, said Gosselin was “not really apologetic or regretful” and told students “you guys kind of just have to deal with it.”\n\nWilburn reported the incident to the university’s Equity, Diversity and Inclusion (EDI) department and later lodged a formal complaint against Gosselin. She said the EDI response felt like they were “trying to find reasons and excuses for why Cheryl was saying the things that she was saying” and argued that there is “no excuse” and that the university should “hold your teachers accountable.” The Campus reported that Wilburn had not received recent information on whether the complaint was still in process. Andrew Webster, Vice-Principal Academics and Research, said he could not comment on the status of the complaint because of Quebec and Canadian privacy laws, while adding that complaints are taken “very seriously.”\n\nThe students also described earlier complaints. Markayza Mitchell, a sociology student, told The Campus about an incident in winter 2023 when she raised concerns in Gosselin’s first-year Quebec Society course about the lack of Indigenous representation. According to Mitchell, Gosselin said she shouldn’t impose her perspective on the rest of the class and pointed to the door, telling her she could leave. Mitchell said she “didn’t feel respected at all” and later dropped the class, which affected her ability to graduate. Leana Ceresoli, who became Social Science Senator in May 2024, said she had been made aware of Gosselin’s controversy through informal complaints about separate undisclosed incidents in Gosselin’s 2023 Quebec Society course. Ceresoli relayed these concerns to Roser Rise, then Student Representative Council Vice-President of Academic Affairs, and Rise said she worked with Webster to create a more clearly defined structure for formal complaints. However, the students who complained informally did not wish to pursue the formal process. Ceresoli, who was a teaching assistant for Gosselin’s fall 2024 Gender and Society course, was not in class when the slur was allegedly used and said she was surprised students had not told her.\n\nThe Bishop’s University Students’ Representative Council (SRC) said it was not aware of any formal complaints against Gosselin and encouraged students to contact the Office of the Dean or another relevant administrative office to file a formal report. Bishop’s University initially said it “cannot comment, discuss or disclose any confidential or personal information” and that it holds “itself and its faculty and staff to the highest standards.” Communications manager Sonia Patenaude said the university acts swiftly if concerns are raised and follows due process. After the CTV News report was published, an internal memo signed by Principal Sébastien Lebel-Grenier and vice-principals was sent to students and staff. The memo recognized that members of the community might find the media report “challenging and emotionally straining.” It said complaints “should be discussed with the professor, the program chair, the dean, or the ombudsperson” and that reports or complaints would be treated confidentially and investigated fairly. The university said it would “be pursuing a conversation in Senate, starting at its Jan. 24 meeting, on ways to better communicate resources and processes available to students” and would “also be examining how our processes can be improved.” The memo also said universities are “places of learning through the free and open discussion of sometimes difficult or challenging subjects and ideas,” and that professors must pursue truth and disseminate knowledge responsibly within a “safe and respectful environment.” It lamented that its “internal processes are not sufficiently known or understood, or may be seen as insufficient.”\n\nQuebec’s Higher Education Ministry called the allegations “worrying” in the first CTV article, with spokesperson Simon Savignac saying, “Discriminatory comments cannot be tolerated” and inviting students to lodge complaints through official channels. The ministry later said it was “shocked” by the allegations and in close communication with the university. During the January 24 Senate meeting, Webster proposed integrating a link to university resources into course syllabi to standardize communication, but the proposal turned into a debate on professorial autonomy and administrative overreach. Webster said the proposal would be revisited by the Academic Standing Admissions Policy committee and intended to be brought back to Senate.\n\nFollowing the CTV report, Gosselin’s winter 2025 classes — Sociology of the Body (SOC219) and Quebec Society (SOC102) — were cancelled on January 14. On January 16, Gosselin taught both classes without acknowledging the article. The following week, the classes were taken over by Dr. Travis Smith from the sports studies department and Dr. David Webster from the history department. Gosselin did not respond to requests for comment; Andrew Webster said she had no wish to comment and preferred not to be contacted further. Students such as Lamothe continued to call for real consequences, saying Gosselin “needs to face a real repercussion and realize that this is an actual incident that means a lot.” The students also expressed concern that a white student might think, “OK, if my professor is saying this, I should be able to say it too,” and that derogatory terms used so freely in a classroom are “really appalling.”', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
+          <t>["Rima Azar, an associate professor of health psychology at Mount Allison University, was the subject of an internal review and public controversy in February 2021 over comments posted on her personal blog, “Bambi’s Afkar,” which she had started in July 2019. Azar, who was born in Lebanon during the civil war and later immigrated to Canada, used the blog to weigh in on matters including systemic racism, sexual violence, gender, colonization, freedom of expression, university policies, teaching in a multicultural society, and climate change. In posts, she denied the existence of systemic racism in New Brunswick and Canada, writing: “NB is NOT racist. Canada is NOT racist. We do not have ‘systemic’ racism or ‘systemic’ discrimination. We just have systemic naivety because we are a young country and because we want to save the world.” She cited activist Husoni Raymond, a founder of Black Lives Matter Fredericton and recipient of the Tom McCann Memorial Trophy from St. Thomas University, as evidence that New Brunswick was not racist, asking: “If NB is as racist as you are claiming, would one of its prestigious universities be honouring you like that?” Raymond responded on Twitter: “So one Black person wins an award and that means there’s no racism? Disappointing to see a professor who’s still ignorant to what racism is and will be using her power within the institution to uphold racists ideologies. Racism IS in Canada. Racism IS in NB.” Azar also labelled Black Lives Matter a “radical” movement, argued that Canada is not a “patriarchy” afflicted by “rape culture,” and made comments about “ISIS practices in Syria.” She also wrote critically about the Divest MtA movement and named student Helen Yao.\n\nThe blog came to the attention of the Mount Allison community in February 2021 after a former student Tweeting under the name “Izzy” assembled excerpts from Azar’s past posts. Mount Allison Students’ Union president Jonathan Ferguson said the union received multiple complaints from students about the blog, including concerns that Azar was “denying systemic racism in New Brunswick or in Canada, talking about BIPOC students in unkind ways, labelling Black Lives Matter a radical group — stuff that doesn't run in line with the values of our institution at all.” On February 22, 2021, acting vice-president Anne Comfort and provost Jeff Hennessy sent a statement to students, faculty, and staff acknowledging the complaints, saying: “We neither support nor agree with the inappropriate comments that have been posted to this blog,” and that the university had initiated “internal review processes.” The statement recognized that the comments were “hurtful” and said concerns had been raised by the Mount Allison Students’ Union, the Black Students Advisor &amp; Diversity Educator, the Indigenous Affairs Co-ordinator, and the Indigenous Student Support Group. The university said it would address the issues “without delay.” Ferguson commented, “freedom of speech doesn't mean amnesty from consequences.”\n\nThe Mount Allison Black Students’ Union issued a statement saying it was “deeply offended by Dr. Azar’s comments and believes she has no place teaching at Mount Allison University,” adding: “No student should fear discrimination by a professor.” The statement said Canadian institutions are “founded on colonialism and white supremacy.” Divest MtA joined the call for Azar’s removal, saying freedom of speech does not absolve her from consequences, especially given her position of power in healthcare and psychology.\n\nStudents also shared personal experiences. Zoë Wright, a fifth-year student and Two-Spirit Indigenous person, said that during a first-year class with Azar she introduced herself and asked that Azar use they/them pronouns, and that Azar replied, “No, I don’t believe in other identities.” Wright said the response was “really jarring” and contributed to delaying her public coming out, and that she reported the incident after the blog controversy emerged. Wright called for education, dialogue, and sensitivity training, and noted that the blog had been written anonymously, suggesting Azar lacked trust in her peers and colleagues. Helen Yao, named in Azar’s blog, said Azar appears committed to “denying the existence of structural inequality,” using personal anecdotes to make generalizations about everyone’s lived experiences, and she questioned Azar’s qualifications to teach about social determinants of health.\n\nCBC News reported on the controversy, including articles by Marie Sutherland. The Moncton Times &amp; Transcript also reported on Azar’s comments. Columnist Jonathan Kay, in the National Post, defended Azar, describing her as an Arab-Canadian, polyglot, foster parent, civil-war survivor, and proud Canadian, and criticized what he described as a mob of self-styled “intersectionalists” and white “settlers” denouncing her. He quoted tweets including one from a “privileged cis white 50-year-old woman” asking, “How is (it) that I understand systemic racism and she doesn’t? She needs to be removed immediately!” and another from a user expressing the hope that Azar “will lose her job.” Kay noted that Azar had tenure and would likely not be fired.\n\nThe Society for Academic Freedom and Scholarship (SAFS), a group of Canadian professors led by Mark Mercer, sent a letter to Mount Allison president Jean-Paul Boudreau calling the university’s statement an “egregious violation” of Azar’s academic freedom and an expression of “cancel culture.” The letter said Azar’s blog comments “concern matters of public and academic importance” and that “Mount Allison has no legitimate reason to look into Dr Azar’s postings.” SAFS cited the collective agreement stating that faculty members are entitled to “freedom in carrying out research and creative activity, and in publishing the results thereof; freedom of teaching and of discussion; freedom to criticize the university and the faculty association; and freedom from institutional censorship.” Mercer said universities should not hold party lines and should treat the controversy as a “teachable moment.” Mount Allison acknowledged receipt of the letter but made no further comment. Azar declined to comment on the internal review, saying she was ill and awaiting medical test results.\n\nThe university later announced that an independent investigator had reviewed complaints from students alleging discriminatory conduct, under Mount Allison’s Racism and Racial Harassment Policy. The investigator made “significant findings requiring action.” A decision was rendered and communicated to Azar and the Mount Allison Faculty Association. The university supported the investigator’s recommendation of equity, diversity, and inclusion training for Azar and offered to pay the costs. The university stated that Azar “will not be teaching this coming fall term,” and that the decision fell within the university’s rights under the collective agreement. The university said further processes under the collective agreement might unfold and that it would not provide further specifics.\n\nOn April 8, 2022, Mount Allison University, the Mount Allison Faculty Association, and Professor Rima Azar announced that “all matters in dispute between them have been resolved.” The parties agreed that the university had received student complaints and taken them seriously pursuant to the Policy on Workplace Harassment and the Anti-Racism Policy, and that such complaints from students need to be taken seriously. They agreed that fostering a respectful and inclusive learning environment, while also recognizing academic freedom, was of the utmost importance, and said no further commentary would be offered.", 'Dougal MacDonald, an assistant lecturer (also described as a sessional instructor) in the Faculty of Education at the University of Alberta, sparked a major controversy in late November 2019 with remarks he posted on his personal Facebook page. In a post made on November 20 at 12:55 a.m., MacDonald described the Holodomor—the 1932–33 famine in Soviet Ukraine recognized by the Canadian Parliament, most Canadian legislatures, and 16 United Nations member states as a genocide against the Ukrainian people created by Joseph Stalin and the Soviet Union—as a “lie” and a “myth.” He claimed that the Nazis created the “myth” in 1933 as a way to “discredit the Soviet Union,” and that Prime Minister Justin Trudeau and the Alberta legislature repeat the “lie” every year. MacDonald also wrote that “former Nazi collaborators and their spawn” in Canada “have long led the phony Holodomor campaign,” building “reactionary domestic organizations” with the help of the Canadian state. His post was captured in screenshots by The Gateway, the university’s student newspaper.\n\nThe Ukrainian Students’ Society (USS) at the University of Alberta responded swiftly, issuing a statement and a letter to President David Turpin on November 26. The USS said it was “extremely disturbed and ashamed” that a university faculty member had expressed this “hateful behaviour,” and called for MacDonald’s “immediate reprimand and termination from the U of A.” They characterized his comments as “anti-Ukrainian hate speech and denial of the Holodomor.” The USS engaged the Ukrainian Canadian Students’ Union (SUSK) and asked students, staff, and community members to email the dean of education and the university president. The Ukrainian Canadian Congress also called for MacDonald’s “immediate censure and termination,” while the Jewish Federation of Edmonton condemned his statements as “dangerous” revisionist history.\n\nThe University of Alberta initially responded through Deputy Provost Wendy Rogers, speaking on behalf of President Turpin. She said the university was “carefully monitoring this matter” while “balancing many interests and obligations.” She emphasized that MacDonald’s views did not represent those of the university and that, as a private citizen, he had the right to express his opinion, with others having the right to critique or debate it. Rogers noted the university understood he had not expressed these views in the context of his employment, and pointed to supports available at the Office of the Dean of Students. The statement did not mention any disciplinary action.\n\nMacDonald defended his comments, saying he stood by them and had done his “due diligence researching into the origins of what is called the holodomor.” He declined to debate “irrational assertions,” and described freedom of speech as a fundamental human right. He later issued a longer statement arguing that “free and public debate on issues, especially controversial issues, is a healthy aspect of our society” and that he would not have his voice silenced. He cited George Bernard Shaw, H.G. Wells, Walter Duranty, and others as historical figures who questioned the official account, and referenced Douglas Tottle’s 1987 book *Fraud, Famine and Fascism* and West Virginia University professor Mark Tauger. In a later response to The Gateway, he said scholars continue to debate whether the Holodomor was “man-made, intentional, and genocidal” or “nature-made, unintentional, and ethnicity-blind,” and that he took the latter position. MacDonald had run as the Marxist-Leninist Party of Canada candidate in Edmonton-Strathcona in the 2019 federal election, receiving 77 votes.\n\nAlberta Premier Jason Kenney weighed in without naming MacDonald, tweeting that he was “sad to see some in Canada still engaged in this genocide denial” and posting video of a speech in which he condemned “Western, supposedly-progressive voices who were complicit in one of history’s great cover-ups.” He described those voices as “the useful idiots of whom Lenin wrote—Westerners who purposefully lied about one of the great acts of mass murder in human history.” A Holodomor survivor, 89-year-old Leo Korownyk, publicly challenged MacDonald, saying “I was born there, I lived there, where was the professor?” and that “some of my relatives starved to death”—calling the university’s claim that it was a personal opinion unacceptable.\n\nThe Students’ Union (UASU), led by President Akanksha Bhatnagar, issued a statement on November 28 condemning MacDonald’s denial and calling on him to “take back his statements or resign,” while also calling on the university to condemn his remarks. That statement itself drew opposition from academics who invoked freedom of expression. On December 1, Kevin Kane, president of the Association of Academic Staff, said the call for retraction “can be seen as pressure for retroactive self-censorship” and was inconsistent with freedom of expression. On December 2, a letter signed by 43 professors and other academics across faculties—including arts, education, law, medicine, business, science, and Augustana—stated that MacDonald’s comments were protected by the university’s policies on freedom of expression and by academic freedom for extramural expression. The letter quoted the newly approved U of A statement: “It is for individuals, not the institution, to make those judgments for themselves and to act not by seeking to suppress expression, but by openly and vigorously contesting the ideas they oppose.” The academics argued that the learning environment is not made safe by preventing another’s exercise of freedom of expression, but is fundamentally undermined by suppression of ideas.\n\nA peaceful protest was held December 2 outside the South Academic Building, organized by the USS and supported by SUSK, the Ukrainian Canadian Congress Alberta Provincial Council, and the Ukrainian Canadian Congress Edmonton Branch. Protesters carried signs reading “Holodomor is a genocide.” USS president Megan Brownlee and SUSK’s Andriy Prichliak said the issue was not free speech but hate speech targeting the Ukrainian-Canadian community. Jars Balan, director of the Canadian Institute of Ukrainian Studies, said there was “nothing new” about MacDonald’s comments; they reflected a “long-standing strategy of the Soviet government to dismiss, to smear, to silence” critics. Balan also noted MacDonald had previously made similar claims in *The Marxist-Leninist Weekly* and suggested the university should determine whether MacDonald used his classroom as a platform. Bhatnagar attended and stressed solidarity, saying the Students’ Union stood with the USS in calling on the university to condemn the remarks.\n\nOn December 6, the university issued a formal statement signed by President Turpin, Dean of Education Jennifer Tupper, Dean of Arts Lesley Cormack, and Jars Balan. The statement declared that “the deliberate starvation of millions of Ukrainians by the Stalinist regime in 1932–33 is a fact established by scholars,” and that research by the Canadian Institute of Ukrainian Studies and its Holodomor Research and Education Consortium had demonstrated “the Holodomor was an act of genocide.” It outlined initiatives including launching a Rapid Research Response project hosted by the Kule Institute for Advanced Studies to create an educational website, hosting the Holodomor Bus, displaying teaching materials in the Faculty of Education, and holding an annual Holodomor Lecture. The statement said MacDonald had a right to free expression but that his views did not represent the university. It made no mention of reprimand or termination. The deans of Arts and Education also issued a joint statement stating categorically that MacDonald’s claim was “not true” and affirming that the university stands with the Ukrainian community in insisting on the reality of the Holodomor as a genocide causing intergenerational trauma.\n\nThe Society for Academic Freedom and Scholarship (SAFS), in a letter to President Turpin, commended the U of A for refusing to sanction MacDonald but criticized two elements: the university’s insistence that MacDonald spoke as a private citizen, since academics possess freedom of extramural utterance; and the university’s desire to announce an official position on a historical event, which SAFS said was contrary to the principle that universities themselves take no stance on substantive matters. The Ukrainian Students’ Society said it appreciated the university’s commitment to education and awareness but was “ultimately disappointed” by the lack of disciplinary action against MacDonald. Brownlee said that “freedom of speech and freedom of expression are not limitless,” and that MacDonald was using those freedoms to defend comments “equivalent to hate speech, defamation, and libel.” The university continued to hold that MacDonald’s comments were made as a private citizen and were protected expression, while the controversy highlighted the tension between free expression and the condemnation of genocide denial on campus.', 'On September 23, 2020, Verushka Lieutenant-Duval, a part-time professor in the Faculty of Arts at the University of Ottawa, used the word “nigger” in full during an online lecture in her course ART 3317, Art and Gender. She was teaching queer theory and explaining the concept of “subversive resignification,” the process by which insulting words are reappropriated, emptied of their original meaning, and turned into powerful markers of identity. She gave “queer,” “cripple” through Crip theory, and the “n-word,” resignified by the Black community, as examples. According to a later account by University of Ottawa president and vice-chancellor Jacques Frémont, a student who is a person of colour emailed Lieutenant-Duval after the class to state that many students were deeply hurt and to ask that the word not be used again in class. Lieutenant-Duval apologized to the student by email and invited students to discuss the issue in the next class. One student subsequently posted the apology email on Twitter on September 30 with the caption “@uOttawa pls teach your professors to not say the n word so i don’t have to THANKS!!” The post quickly sparked outrage on social media.\n\nFaculty of Arts Dean Kevin Kee issued a statement on October 2 saying the language was “offensive and completely unacceptable in our classrooms and on our campus,” and that the faculty was looking into the matter. The university removed Lieutenant-Duval from her teaching duties pending an investigation. Frémont later said this was an administrative suspension with pay that lasted one business day, not a disciplinary suspension. Lieutenant-Duval missed several classes and returned to teaching on October 16. The university also created a new section of the course for students who did not wish to continue with the original professor. Lieutenant-Duval later told Radio-Canada that only one student chose to remain in her class.\n\nThe controversy produced a large academic backlash. A letter signed by 579 CEGEP and university professors, written by Mathieu Gauthier of Cégep Garneau and Murielle Chapuis of Cégep Lionel-Groulx, denounced a “serious precedent which attacks academic freedom head-on.” The letter said the University of Ottawa was “on the wrong target” and that racism is not tackled “by punishing and prohibiting the teaching of words, works and authors who, on the contrary, reveal it and explicitly combat it.” A separate open letter from 34 current and retired University of Ottawa professors, published on October 16, argued that two elements had been confused in the affair: racism on campus, microaggressions, and discrimination against minorities must be denounced; and the role of university education is to nourish reflection, develop critical thinking, and allow everyone, regardless of position, the right to speak. The professors asked how, without the word, one can teach Raoul Peck’s film *I Am Not Your Negro*, the artistic movement of Négritude associated with Léopold Sédar Senghor and Aimé Césaire, Pierre Vallières’s *White Negroes of America*, Michèle Lalonde’s poem “Speak white,” the work of Toni Morrison, or Dany Laferrière’s *How to Make Love with a Nigger Without Getting Tired*. They noted that this was the third time the use and mention of words had been confused, after the cases of CBC’s Wendy Mesley and Concordia University professor Catherine Russell.\n\nThe University of Ottawa Students’ Union (UOSU) released a statement saying it was “deeply disturbed” by the open letter defending the use of racial slurs in classrooms and by a La Presse column by Isabelle Hachey that supported Lieutenant-Duval. The union called on the university to denounce the signing professors “not just through words, but through actions,” and emphasized solidarity with Black-led student groups. The statement was supported and endorsed by 20 other recognized student governments.\n\nRector Jacques Frémont broke his silence on October 19 with a message to the university community. He said that “members of dominant groups simply do not have the legitimacy to decide what constitutes micro-aggression.” He stated that Lieutenant-Duval had remained an employee of the university, that she was free to continue teaching while enjoying her full academic freedom, and that the creation of a new section of the course was “a necessary step to accommodate and respect the rights of all.” He also said the right to freedom of expression and the right to dignity are not contradictory but complementary.\n\nThe Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Frémont asking why any action had been taken against Lieutenant-Duval, why she was not reinstated immediately, and why a new section of the course was created. The letter argued that “mentioning a word is not using it” and that “there is no slur without a slurring.” It said the complaint should have been explained to students as groundless.\n\nThe 34 signatories of the professors’ open letter then became the targets of a cyberbullying campaign. According to Le Devoir, a tweet said the teachers “supported the use of the N word in class” and added “we will cyberbully them.” Lucie Hotte, a full professor in the French department, said she received hundreds of tweets calling her racist and demanding her dismissal and “re-education.” Maxime Prévost, director of the French department, said faculty did not feel safe, especially after Lieutenant-Duval’s address was posted on social networks. Marc-François Bernier described the movement as an “ideological guerrilla” and said fundamental principles were being dropped to please customers. The Ottawa police said no complaint had been received and no investigation had been launched.\n\nLieutenant-Duval also spoke publicly, apologizing to the Black community and to anyone she had hurt. She said she regretted using the word and that if she had known it should not be spoken in an academic course, she would have found another way. She said the controversy had been blown out of proportion by people taking extreme positions, and she expressed fear for her personal safety because her name, phone number, and home address had been posted online. She said she was proud of young people denouncing inequalities, but was “completely stunned” that people could think of fighting racism and injustice by using hateful words.\n\nOn November 23, Frémont delivered a statement to the University of Ottawa Senate titled “correcting the record.” He said the facts had been validated by several sources: Lieutenant-Duval used the n-word; a student emailed her; the professor apologized and offered the student an opportunity to lead an in-class discussion; this generated tension, with students complaining that the request was inappropriate and that the professor had put the onus on students to educate others and argue for their right to dignity; and the class discussion became very difficult, including a statement perceived as threatening by some participants. He said the dean removed the professor pending an investigation, met with her along with her union representatives and lawyer under the APTPUO Collective Agreement, arranged equity, diversity, and inclusion (EDI) training, an EDI-led class discussion, and a separate section of the course. He also announced the dissolution of the President’s Advisory Committee on Anti-Racism and Inclusion and the launch of a new, more action-oriented Action Committee on Anti-Racism and Inclusion with a mandate to review resources, provide recommendations to further the inclusion of BIPOC members, and eliminate barriers to diversity and inclusion efforts.\n\nHowever, subsequent reporting by La Presse and statements from the Association des professeurs à temps partiel de l’Université d’Ottawa (APTPUO) disputed parts of Frémont’s account. Lieutenant-Duval said that, apart from a meeting with the dean on October 6, nobody had ever asked her for her version of the facts. APTPUO said that nothing in the email exchange indicated that many students felt hurt by the word; the student in question, who is of Arab origin, wrote in her email that hearing the word “did not affect her personally,” and she thanked the professor and said she looked forward to the next class. The union also said that the Zoom recording and chat did not corroborate that the professor had made any statement that could reasonably be perceived as threatening. Lieutenant-Duval said she had retained all the emails and recordings and was calling for an independent investigation. She said she felt like the “great forgotten” person in an affair that bears her name.']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>class - gender - complaint - word - rights - investigation - views - complaints - 2015 - expression</t>
+          <t>letter - comments - expression - wrote - saying - views - social - statement - racism - class</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2_health_consent_medical_committee</t>
+          <t>2_report_clinical_records_committee</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
+          <t>['report', 'clinical', 'records', 'committee', 'consent', 'health', 'confidentiality', 'patients', 'medical', 'information']</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['A prolonged and acrimonious dispute in Toronto involving internationally acclaimed blood researcher Dr. Nancy Olivieri, the Hospital for Sick Children (HSC), the University of Toronto, and the pharmaceutical manufacturer Apotex Inc. was resolved in a face-saving compromise in late January 1999, after earlier events had ignited a controversy over research ethics, patient safety, and academic freedom.\n\nThe dispute centred on clinical trials of deferiprone (L1), an experimental orally active iron-chelating agent being tested as an alternative to the standard but onerous deferoxamine (DFO) therapy for patients with thalassemia major, a transfusion-dependent blood disorder causing progressive iron loading of major organs. Dr. Olivieri, a specialist in hematology and internal medicine, was principal investigator of two Toronto trials: LA-03, a long-term efficacy and safety study, and LA-01, a randomized comparison trial versus DFO, co-sponsored by the Medical Research Council and Apotex. In 1996, Dr. Olivieri identified an unexpected risk in the LA-03 data: loss of sustained efficacy of L1 in a substantial proportion of patients, with hepatic iron concentrations (HIC) stabilizing or rising into ranges associated with iron-induced complications. Apotex disputed her interpretation and opposed informing patients. When HSC\'s Research Ethics Board (REB) directed Dr. Olivieri to revise patient information and consent forms to disclose this risk, Apotex abruptly terminated both Toronto trials on May 24, 1996, withdrew its drug from the hospital pharmacy, and issued legal warnings threatening legal action if she communicated the risk to patients, regulators, or the scientific community.\n\nFollowing the trial terminations, Dean Arnold Aberman of the University of Toronto\'s Faculty of Medicine mediated a new arrangement under Health Canada\'s Emergency Drug Release (EDR) program. Patients who had been in the former trial cohorts and wished to continue on L1 and were still considered to be benefiting could do so as patients under Dr. Olivieri\'s care, provided they were fully informed of the newly identified risk, accepted it, and agreed to monitoring tests including annual liver biopsy. The REB had no jurisdiction over this non-trial EDR treatment arrangement, and Dr. Olivieri, as "the practitioner" under EDR regulations, had reporting obligations only to patients, Apotex, and the Health Protection Branch. She nonetheless informed the REB that the trials had been terminated, and she later reported the loss-of-efficacy finding directly to the regulators despite continued legal warnings from Apotex.\n\nIn early February 1997, Dr. Olivieri and her collaborators, liver pathologist Dr. Ross Cameron and Dr. Gary Brittenham, identified a second, more serious unexpected risk through review of serial liver biopsy slides: progression of liver fibrosis in some patients, making L1 the probable cause of a "severe adverse reaction." She informed patients immediately, counselled them to interrupt use of the drug, and transferred them back to standard therapy in a timely and orderly fashion. She also informed Apotex and the federal regulators, sending her report to the FDA, HPB, and the health ministries of Italy and India. Apotex responded with further legal warnings, and Dr. Hugh O\'Brodovich, HSC\'s Pediatrician-in-Chief, intervened on February 19, 1997, questioning whether Dr. Olivieri had failed in an obligation to report the risk to the REB and to her department chief. Dr. Aideen Moore, the REB Chair, provided incorrect information suggesting that a research trial of L1 continued after May 1996, although both trials had in fact been terminated and patients were under EDR. Subsequent investigations determined that Dr. Olivieri had no obligation to report to the REB in these circumstances and that she had acted "in the best interests of her patients."\n\nThe controversy became public in August 1998 after Dr. Olivieri published her findings on loss of efficacy and toxicity in the New England Journal of Medicine. In September 1998, the HSC Board of Trustees unilaterally established a review conducted by Dr. Arnold Naimark. The Naimark Report, released December 9, 1998, incorrectly concluded that Dr. Olivieri had failed to report her concerns about L1 toxicity to the REB in a timely fashion. On the same day, the HSC Board directed its Medical Advisory Committee (MAC) to inquire into her conduct. On January 6, 1999, HSC removed Dr. Olivieri from her position as director of the hemoglobinopathy program without due process and issued "gag orders" to her and three supporters, Drs. Helen Chan, Peter Durie, and Brenda Gallie, restricting communication with the media. These actions prompted interventions by the Canadian Association of University Teachers (CAUT), the University of Toronto Faculty Association (UTFA), leading scientists Sir David Weatherall and Dr. David Nathan, and University President Robert Prichard. A marathon negotiating session on January 25, 1999 produced a settlement that restored Dr. Olivieri\'s full responsibility and authority over clinical care and research in hemoglobinopathies, withdrew the gag orders, changed her reporting relationships, and provided her with legal indemnification of $150,000 and coverage for potential legal action by Apotex.\n\nThe Medical Advisory Committee, using undisclosed allegations and testimony, principally from Dr. Gideon Koren, Dr. Olivieri\'s former co-investigator, and Dr. O\'Brodovich, referred a series of "concerns" about her conduct to the College of Physicians and Surgeons of Ontario (CPSO) and the University of Toronto in April 2000. Dr. Koren was later disciplined by HSC and the University on April 11, 2000 for "gross misconduct," including persistently lying about his authorship of anonymous letters disparaging Dr. Olivieri and her supporters; he admitted responsibility only after being identified by DNA evidence. The Health Professions Appeal and Review Board subsequently found that Dr. Koren\'s anonymous letter-writing campaign constituted "serious professional misconduct" and directed that the matter be referred to the CPSO Discipline Committee.\n\nIn October 2001, the independent CAUT Committee of Inquiry, chaired by Jon Thompson with Patricia Baird and Jocelyn Downie, published a detailed report exonerating Dr. Olivieri, faulting Apotex for attempting to suppress information on risks and to discredit her, faulting HSC and the University for failing to protect her academic freedom, and criticizing the Naimark Review and MAC proceedings for relying on incorrect and false information. On December 19, 2001, the CPSO Complaints Committee, assisted by an independent expert panel, concluded that "no further action is warranted against Dr. Olivieri," finding she did not fall below a reasonable standard of care in continuing to administer L1, in ordering liver biopsies, or in communicating with her department chief. The Committee specifically found her judgment in advising patients to undergo biopsies "not only reasonable, but commendable in the circumstances." On January 7, 2002, Dean David Naylor of the University of Toronto\'s Faculty of Medicine dismissed all related allegations, including the claim that Dr. Olivieri should have reported her conclusions on L1 toxicity to the REB.\n\nThe case was ultimately recognized for its impact on a critically important issue: the growing dependence of researchers, universities, and hospitals on corporate research funding and the need for policy safeguards to ensure that sponsors cannot restrict communication of identified risks, that confidentiality clauses in research contracts are not used to suppress findings of risk, and that research ethics boards, universities, and hospitals act robustly to defend academic freedom and the safety of trial participants and patients.', 'The Canadian Association of University Teachers (CAUT) established an Independent Committee of Inquiry, chaired by Professor Trudo Lemmens, with Dr. Thomas A. Ban and Dr. Louis C. Charland, to investigate the seizure of research records from the offices of Dr. Anne Duffy at the Institute of Mental Health Research (IMHR) in Ottawa on March 22, 2005. The Committee was mandated to investigate the sequence of events leading to and following the seizure, the institutional relationships between the University of Ottawa, the IMHR, and the Royal Ottawa Hospital (ROH), whether breaches of institutional responsibility or research ethics standards occurred, the impact on academic freedom and integrity, the impact on researchers, research subjects and institutions, and to make recommendations to prevent recurrence. The final report was submitted in March 2013 after delays caused by court proceedings and health issues.\n\nThe events began on March 11, 2005, when Dr. Duffy’s research coordinator told Sharyn Szick, Administrative Director of the IMHR, that a research assistant was scanning clinical charts and inserting printed copies into research records, and that informed consent forms were missing from some research records or had been signed after study initiation and backdated. Ms. Szick reported this to Dr. Zul Merali, President and CEO of the IMHR. On March 22, 2005, after a meeting attended by Ms. Szick, Dr. Keith Busby, Suzan Crozier, Carolyn Belzile, and Sharon Purvis, the decision was made to remove clinical charts from Dr. Duffy’s office and chart room. Dr. Paul Dagg, Director of Clinical Services, and Mr. Bruce Swan, CEO of the Royal Ottawa Health Care Group (ROHCG), authorized the removal of clinical charts based on allegations that clinical charts had been scanned and downloaded to hospital network drives, contrary to ROH policy and the Personal Health Information Protection Act (PHIPA). Once the clinical charts were relocated, Dr. Busby, at Dr. Merali’s request, conducted a “spot check” of approximately 20 research binders and reported that about five lacked consent forms behind the tab marked “consent.” Dr. Merali then ordered the immediate transfer of the research records of the bipolar team to a “secure location” at the ROH. Neither Dr. Duffy nor any member of her research team was present. Dr. Duffy learned of the removal the next morning from a note on her door.\n\nThe seized material included clinical charts, research records, personal files, and computer discs. According to Drs. Duffy and Grof, the records concerned more than 2,000 research subjects, including current and former patients and controls from Ontario and Nova Scotia. The records included studies conducted by Drs. Alda, Grof, and Duffy, involving long-term follow-up of families with bipolar disorder. The ROHCG Research Ethics Board (REB), chaired by Dr. Alan B. Douglass, was not consulted in advance, had received no complaint, and had not authorized the removal. Dr. Dagg’s investigation concluded on April 13, 2005 that no serious breaches of privacy with clinical charts had occurred, though he apologized for the removal.\n\nDrs. Duffy and Grof retained legal counsel on March 23, 2005, and commenced court proceedings for the return of the research records. They also filed a complaint with the Information and Privacy Commissioner of Ontario. On April 15, 2005, proceedings were adjourned and on April 18, 2005 an agreement was reached: the research records would be copied, originals returned, copies turned over to the REB without review, Dr. Merali would outline concerns, and the REB would appoint an independent reviewer. However, Dr. Duffy learned that Dr. Busby had already reviewed some records, contrary to her understanding of the agreement. Dr. Duffy then informed research subjects by e-mail that IMHR personnel had accessed personal information. The Information and Privacy Commissioner’s investigation was put on hold after objections from Dr. Duffy’s lawyers.\n\nIn May 2005, Drs. Duffy and Grof contacted CAUT, which established the Independent Committee of Inquiry. Committee interviews began in late summer 2005. Most institutional officials declined to participate on legal advice. A settlement was reached on October 19, 2005, which allowed Dr. Douglass to invite Dr. Padraig Darby, Chair of the REB of the Centre for Addiction and Mental Health, to review copies of the research records. Dr. Darby’s report, submitted November 10, 2006, found that only one of six studies had REB approval and that informed consent forms were missing from 77 of 252 records (30.5%). It was later clarified that all studies had approval letters on file that had not been provided to Dr. Darby. Drs. Duffy and Grof disputed the findings, reporting that only 11% of records lacked consent forms based on their review of the originals, and suggested that a former research assistant had failed to add consent forms to files. The Darby Report led to a second round of litigation, which ended in 2008 when the Canadian Medical Protective Association declined further funding and Drs. Duffy and Grof agreed to pay the other party’s legal costs.\n\nThe Committee’s own review of the original research records found that some consent forms identified as missing by Dr. Darby were present in the originals, and that new signed consent forms were present in records where originals were absent. Interviews with research subjects and parents of subjects whose original consent forms were missing showed that all were fully aware that they or their children were participating in Dr. Duffy’s research, understood the nature and purpose of the research, and had strong confidence in Dr. Duffy’s integrity.\n\nThe Committee concluded that the seizure of research records was in violation of research ethics standards. It emphasized a key distinction between informed consent obtained to protect research subjects from physical or psychological harm, and informed consent obtained to protect the privacy of research subjects and the confidentiality of sensitive health information. In the studies at issue, the consent forms represented a pledge by researchers to protect confidentiality. Seizing records in response to allegations of missing consent forms therefore violated the very essence of the informed consent. The “spot check” conducted by Dr. Busby was not a proper audit, as it lacked advance notice, defined objectives, scope, and researcher involvement, and was not carried out by the REB. The Committee found that the seizure was a disproportionate response, contrary to the principle of “proportionate review” under the Tri-Council Policy Statement (TCPS), and that institutional officials breached their responsibility by prioritizing the establishment of alleged wrongdoing over the protection of research subject privacy. The Committee attributed the seizure to ongoing tensions between Drs. Duffy and Grof and Drs. Merali and Bradwejn, and to the confounding of informed consent for privacy protection with informed consent for protection from harm.\n\nThe Committee’s recommendations included: clarifying that research records are in principle the property of the researcher; clearly defining the position of self-funded research teams and renegotiating responsibilities regularly; identifying for each research project whether informed consent is for protection from harm or for privacy and confidentiality; clarifying institutional responsibilities so that the REB that approved a project, not other institutional officials, ensures adherence to research ethics standards; and ensuring that seizure of research records is only a last resort when there is an immediate and serious threat to the wellbeing of research subjects, with procedures designed to respect the privacy and confidentiality of health information.', '# Summary: Suspension and Termination of Dr. Francis Christian\n\nDr. Francis Christian, a clinical professor of general surgery at the University of Saskatchewan (USask) and a practicing surgeon in Saskatoon with more than 20 years of experience, was suspended and terminated from his positions after publicly raising concerns about COVID-19 vaccination of children. As of June 2021, Christian served as Director of the Surgical Humanities Program (which he co-founded), Director of Quality and Patient Safety in the Department of Surgery, and Editor of the Journal of the Surgical Humanities. His roles overlapped with a contract position with the Saskatchewan Health Authority (SHA).\n\nOn June 17, 2021, Christian released a prepared statement to over 200 doctors and spoke at a press conference outside Walter Murray Collegiate in Saskatoon, appearing with a group called Concerned Parents Saskatchewan while a vaccine clinic was taking place at the high school. He declined to take questions from journalists. In his statement, Christian emphasized that he is a "very pro-vaccine physician" and is "pro-vaccine for my own family, including myself," citing the elimination of smallpox through vaccination. He stated he spoke "directly to parents and children" as "a physician, a surgeon and a fellow human being" and did not represent any group, the SHA, or the university.\n\nChristian invoked the "sacrosanct principle" of informed consent, arguing that patients must be made "fully aware of the risks of the medical intervention, the benefits of the intervention and if any alternatives exist to the intervention," particularly for "a new vaccine that has never before been tried in humans." He asserted this principle was "being consistently violated in this province for the m-RNA vaccine for our kids," claiming he had not met "a single vaccinated child or parent who has been adequately informed."\n\nChristian articulated eight points he argued parents and children must know before consenting: (1) that the mRNA vaccine is "a new, experimental vaccine design" never used in humans; (2) that the vaccines have not been fully authorized by Health Canada or the CDC, being under "interim authorization" in Canada and "emergency use authorization" in the US; (3) that while there is an emergency for the elderly, vulnerable, and health care workers—given that the mean age of COVID-19 deaths in Canada is 83.8—"Covid-19 does not pose a threat to our kids," with a death risk of less than 0.003%; (4) that children do not readily transmit the virus to adults; (5) that the mRNA vaccines have been "associated with several thousand deaths" in the US government\'s Vaccine Adverse Reporting System, which he called "a strong signal" that could not be ignored; (6) that there is a "real and significantly increased risk" of myocarditis (heart inflammation) in vaccinated children, leading the German national vaccine agency and the UK vaccine agency to not recommend the vaccine for healthy children; (7) that the benefit of the vaccine for children is "marginal at best," with an Absolute Risk Reduction of less than 2%; and (8) that Ivermectin is an alternative treatment. He urged authorities "to call a pause in the m-RNA vaccine roll-out to our kids" and stated that without informed consent, "the Nuremberg code is being violated." He also appeared in a video posted to the website BitChute that received nearly 70,000 views, in which he questioned the mainstream narrative about the pandemic, mocked restrictions, and called the vaccines "experimental injections."\n\nOn June 21, 2021, the Saskatchewan Health Authority and the College of Medicine wrote to Christian alleging they had "received information that you are engaging in activities designed to discourage and prevent children and adolescents from receiving Covid-19 vaccination contrary to the recommendations and pandemic-response efforts of Saskatchewan and Canadian public health authorities."\n\nOn June 23, 2021, Christian was called into a meeting with Dr. Preston Smith, Dean of the College of Medicine; Dr. Susan Shaw, Chief Medical Officer of the Saskatchewan Health Authority; and Dr. Brian Ulmer, Head of the Department of Surgery. He was informed of his immediate suspension from all faculty responsibilities and academic administrative roles, and that he would be fired from the university as of September 2021. The SHA terminated its contract with Christian, which was set to expire on September 21 following the required 90 days\' notice. Christian remained able to practice medicine and the university said it was not suspending payment for services he would have otherwise received during the investigation period. Christian recorded the 22-minute meeting and posted the audio online.\n\nDuring the meeting, Christian said, "You\'ve basically read indictments against me. These are the sort of panels that were set up in the Soviet Union and Nazi Germany against academics," adding, "I\'m not saying that you\'re Nazis or Soviets, but it\'s really disturbing, isn\'t it?" He stated he was one of many doctors being "silenced and censored," and told the officials, "You guys are living in a dystopian bubble. The truth will come out and when that bubble bursts, you guys are going to be in big trouble." Shaw expressed concern that Christian was "a highly intelligent man" who was "not making intelligent decisions," and Christian was offered supports if he was feeling distressed, which he declined.\n\nIn a statement, Dean Smith said the University "encourages public debate of important societal issues," but noted that per USask\'s Medical Faculty Policy, "our medical faculty are subject to the ethical and professional standards governing the practice of medicine." Smith told Global News that "when somebody is saying things that are at such great variance with all of our experts and worldwide experts and public safety is involved and could be jeopardized through these differences of view, I think we have to recognize that that\'s a special situation that requires urgent and extraordinary action." The SHA stated that "health system leaders are expected to be committed to fact-based, scientifically driven public messaging" and that leaders who depart "in favour of conspiracy theories put lives at risk by potentially discouraging uptake on life-saving vaccines."\n\nThe Justice Centre for Constitutional Freedoms announced it was representing Christian in his appeals and before the College of Physicians and Surgeons of Saskatchewan, against a complaint objecting to his advocacy for informed consent. Litigation Director Jay Cameron said the termination was "a violation of his charter-protected right to freedom of thought, belief, opinion and expression, and a betrayal of the principles of scientific inquiry," and described "a clear pattern of highly competent and skilled medical doctors in very esteemed positions being taken down and censored or even fired, for practicing proper science and medicine." The Justice Centre also drew comparisons to its representation of Dr. Chris Milburn in Nova Scotia, who faced disciplinary proceedings over an opinion column.\n\nOn June 30, 2021, the Society for Academic Freedom and Scholarship (SAFS), through its president Mark Mercer, wrote to Dean Smith requesting an explanation of "how Dr Christian\'s suspension is not a violation of his academic freedom and how his suspension will not tend to create a chilly climate for expression on campus." SAFS argued that "nothing that has been reported should draw any discipline at all" and that "academic freedom protects his rights to have them and to express them publicly," noting the importance of professors being "free to question received wisdom and official policy" during a pandemic.']</t>
+          <t>['A prolonged and acrimonious dispute in Toronto involving internationally acclaimed blood researcher Dr. Nancy Olivieri, the Hospital for Sick Children (HSC), the University of Toronto, and the pharmaceutical manufacturer Apotex Inc. was resolved in a face-saving compromise in late January 1999, after earlier events had ignited a controversy over research ethics, patient safety, and academic freedom.\n\nThe dispute centred on clinical trials of deferiprone (L1), an experimental orally active iron-chelating agent being tested as an alternative to the standard but onerous deferoxamine (DFO) therapy for patients with thalassemia major, a transfusion-dependent blood disorder causing progressive iron loading of major organs. Dr. Olivieri, a specialist in hematology and internal medicine, was principal investigator of two Toronto trials: LA-03, a long-term efficacy and safety study, and LA-01, a randomized comparison trial versus DFO, co-sponsored by the Medical Research Council and Apotex. In 1996, Dr. Olivieri identified an unexpected risk in the LA-03 data: loss of sustained efficacy of L1 in a substantial proportion of patients, with hepatic iron concentrations (HIC) stabilizing or rising into ranges associated with iron-induced complications. Apotex disputed her interpretation and opposed informing patients. When HSC\'s Research Ethics Board (REB) directed Dr. Olivieri to revise patient information and consent forms to disclose this risk, Apotex abruptly terminated both Toronto trials on May 24, 1996, withdrew its drug from the hospital pharmacy, and issued legal warnings threatening legal action if she communicated the risk to patients, regulators, or the scientific community.\n\nFollowing the trial terminations, Dean Arnold Aberman of the University of Toronto\'s Faculty of Medicine mediated a new arrangement under Health Canada\'s Emergency Drug Release (EDR) program. Patients who had been in the former trial cohorts and wished to continue on L1 and were still considered to be benefiting could do so as patients under Dr. Olivieri\'s care, provided they were fully informed of the newly identified risk, accepted it, and agreed to monitoring tests including annual liver biopsy. The REB had no jurisdiction over this non-trial EDR treatment arrangement, and Dr. Olivieri, as "the practitioner" under EDR regulations, had reporting obligations only to patients, Apotex, and the Health Protection Branch. She nonetheless informed the REB that the trials had been terminated, and she later reported the loss-of-efficacy finding directly to the regulators despite continued legal warnings from Apotex.\n\nIn early February 1997, Dr. Olivieri and her collaborators, liver pathologist Dr. Ross Cameron and Dr. Gary Brittenham, identified a second, more serious unexpected risk through review of serial liver biopsy slides: progression of liver fibrosis in some patients, making L1 the probable cause of a "severe adverse reaction." She informed patients immediately, counselled them to interrupt use of the drug, and transferred them back to standard therapy in a timely and orderly fashion. She also informed Apotex and the federal regulators, sending her report to the FDA, HPB, and the health ministries of Italy and India. Apotex responded with further legal warnings, and Dr. Hugh O\'Brodovich, HSC\'s Pediatrician-in-Chief, intervened on February 19, 1997, questioning whether Dr. Olivieri had failed in an obligation to report the risk to the REB and to her department chief. Dr. Aideen Moore, the REB Chair, provided incorrect information suggesting that a research trial of L1 continued after May 1996, although both trials had in fact been terminated and patients were under EDR. Subsequent investigations determined that Dr. Olivieri had no obligation to report to the REB in these circumstances and that she had acted "in the best interests of her patients."\n\nThe controversy became public in August 1998 after Dr. Olivieri published her findings on loss of efficacy and toxicity in the New England Journal of Medicine. In September 1998, the HSC Board of Trustees unilaterally established a review conducted by Dr. Arnold Naimark. The Naimark Report, released December 9, 1998, incorrectly concluded that Dr. Olivieri had failed to report her concerns about L1 toxicity to the REB in a timely fashion. On the same day, the HSC Board directed its Medical Advisory Committee (MAC) to inquire into her conduct. On January 6, 1999, HSC removed Dr. Olivieri from her position as director of the hemoglobinopathy program without due process and issued "gag orders" to her and three supporters, Drs. Helen Chan, Peter Durie, and Brenda Gallie, restricting communication with the media. These actions prompted interventions by the Canadian Association of University Teachers (CAUT), the University of Toronto Faculty Association (UTFA), leading scientists Sir David Weatherall and Dr. David Nathan, and University President Robert Prichard. A marathon negotiating session on January 25, 1999 produced a settlement that restored Dr. Olivieri\'s full responsibility and authority over clinical care and research in hemoglobinopathies, withdrew the gag orders, changed her reporting relationships, and provided her with legal indemnification of $150,000 and coverage for potential legal action by Apotex.\n\nThe Medical Advisory Committee, using undisclosed allegations and testimony, principally from Dr. Gideon Koren, Dr. Olivieri\'s former co-investigator, and Dr. O\'Brodovich, referred a series of "concerns" about her conduct to the College of Physicians and Surgeons of Ontario (CPSO) and the University of Toronto in April 2000. Dr. Koren was later disciplined by HSC and the University on April 11, 2000 for "gross misconduct," including persistently lying about his authorship of anonymous letters disparaging Dr. Olivieri and her supporters; he admitted responsibility only after being identified by DNA evidence. The Health Professions Appeal and Review Board subsequently found that Dr. Koren\'s anonymous letter-writing campaign constituted "serious professional misconduct" and directed that the matter be referred to the CPSO Discipline Committee.\n\nIn October 2001, the independent CAUT Committee of Inquiry, chaired by Jon Thompson with Patricia Baird and Jocelyn Downie, published a detailed report exonerating Dr. Olivieri, faulting Apotex for attempting to suppress information on risks and to discredit her, faulting HSC and the University for failing to protect her academic freedom, and criticizing the Naimark Review and MAC proceedings for relying on incorrect and false information. On December 19, 2001, the CPSO Complaints Committee, assisted by an independent expert panel, concluded that "no further action is warranted against Dr. Olivieri," finding she did not fall below a reasonable standard of care in continuing to administer L1, in ordering liver biopsies, or in communicating with her department chief. The Committee specifically found her judgment in advising patients to undergo biopsies "not only reasonable, but commendable in the circumstances." On January 7, 2002, Dean David Naylor of the University of Toronto\'s Faculty of Medicine dismissed all related allegations, including the claim that Dr. Olivieri should have reported her conclusions on L1 toxicity to the REB.\n\nThe case was ultimately recognized for its impact on a critically important issue: the growing dependence of researchers, universities, and hospitals on corporate research funding and the need for policy safeguards to ensure that sponsors cannot restrict communication of identified risks, that confidentiality clauses in research contracts are not used to suppress findings of risk, and that research ethics boards, universities, and hospitals act robustly to defend academic freedom and the safety of trial participants and patients.', 'The Canadian Association of University Teachers (CAUT) established an Independent Committee of Inquiry, chaired by Professor Trudo Lemmens, with Dr. Thomas A. Ban and Dr. Louis C. Charland, to investigate the seizure of research records from the offices of Dr. Anne Duffy at the Institute of Mental Health Research (IMHR) in Ottawa on March 22, 2005. The Committee was mandated to investigate the sequence of events leading to and following the seizure, the institutional relationships between the University of Ottawa, the IMHR, and the Royal Ottawa Hospital (ROH), whether breaches of institutional responsibility or research ethics standards occurred, the impact on academic freedom and integrity, the impact on researchers, research subjects and institutions, and to make recommendations to prevent recurrence. The final report was submitted in March 2013 after delays caused by court proceedings and health issues.\n\nThe events began on March 11, 2005, when Dr. Duffy’s research coordinator told Sharyn Szick, Administrative Director of the IMHR, that a research assistant was scanning clinical charts and inserting printed copies into research records, and that informed consent forms were missing from some research records or had been signed after study initiation and backdated. Ms. Szick reported this to Dr. Zul Merali, President and CEO of the IMHR. On March 22, 2005, after a meeting attended by Ms. Szick, Dr. Keith Busby, Suzan Crozier, Carolyn Belzile, and Sharon Purvis, the decision was made to remove clinical charts from Dr. Duffy’s office and chart room. Dr. Paul Dagg, Director of Clinical Services, and Mr. Bruce Swan, CEO of the Royal Ottawa Health Care Group (ROHCG), authorized the removal of clinical charts based on allegations that clinical charts had been scanned and downloaded to hospital network drives, contrary to ROH policy and the Personal Health Information Protection Act (PHIPA). Once the clinical charts were relocated, Dr. Busby, at Dr. Merali’s request, conducted a “spot check” of approximately 20 research binders and reported that about five lacked consent forms behind the tab marked “consent.” Dr. Merali then ordered the immediate transfer of the research records of the bipolar team to a “secure location” at the ROH. Neither Dr. Duffy nor any member of her research team was present. Dr. Duffy learned of the removal the next morning from a note on her door.\n\nThe seized material included clinical charts, research records, personal files, and computer discs. According to Drs. Duffy and Grof, the records concerned more than 2,000 research subjects, including current and former patients and controls from Ontario and Nova Scotia. The records included studies conducted by Drs. Alda, Grof, and Duffy, involving long-term follow-up of families with bipolar disorder. The ROHCG Research Ethics Board (REB), chaired by Dr. Alan B. Douglass, was not consulted in advance, had received no complaint, and had not authorized the removal. Dr. Dagg’s investigation concluded on April 13, 2005 that no serious breaches of privacy with clinical charts had occurred, though he apologized for the removal.\n\nDrs. Duffy and Grof retained legal counsel on March 23, 2005, and commenced court proceedings for the return of the research records. They also filed a complaint with the Information and Privacy Commissioner of Ontario. On April 15, 2005, proceedings were adjourned and on April 18, 2005 an agreement was reached: the research records would be copied, originals returned, copies turned over to the REB without review, Dr. Merali would outline concerns, and the REB would appoint an independent reviewer. However, Dr. Duffy learned that Dr. Busby had already reviewed some records, contrary to her understanding of the agreement. Dr. Duffy then informed research subjects by e-mail that IMHR personnel had accessed personal information. The Information and Privacy Commissioner’s investigation was put on hold after objections from Dr. Duffy’s lawyers.\n\nIn May 2005, Drs. Duffy and Grof contacted CAUT, which established the Independent Committee of Inquiry. Committee interviews began in late summer 2005. Most institutional officials declined to participate on legal advice. A settlement was reached on October 19, 2005, which allowed Dr. Douglass to invite Dr. Padraig Darby, Chair of the REB of the Centre for Addiction and Mental Health, to review copies of the research records. Dr. Darby’s report, submitted November 10, 2006, found that only one of six studies had REB approval and that informed consent forms were missing from 77 of 252 records (30.5%). It was later clarified that all studies had approval letters on file that had not been provided to Dr. Darby. Drs. Duffy and Grof disputed the findings, reporting that only 11% of records lacked consent forms based on their review of the originals, and suggested that a former research assistant had failed to add consent forms to files. The Darby Report led to a second round of litigation, which ended in 2008 when the Canadian Medical Protective Association declined further funding and Drs. Duffy and Grof agreed to pay the other party’s legal costs.\n\nThe Committee’s own review of the original research records found that some consent forms identified as missing by Dr. Darby were present in the originals, and that new signed consent forms were present in records where originals were absent. Interviews with research subjects and parents of subjects whose original consent forms were missing showed that all were fully aware that they or their children were participating in Dr. Duffy’s research, understood the nature and purpose of the research, and had strong confidence in Dr. Duffy’s integrity.\n\nThe Committee concluded that the seizure of research records was in violation of research ethics standards. It emphasized a key distinction between informed consent obtained to protect research subjects from physical or psychological harm, and informed consent obtained to protect the privacy of research subjects and the confidentiality of sensitive health information. In the studies at issue, the consent forms represented a pledge by researchers to protect confidentiality. Seizing records in response to allegations of missing consent forms therefore violated the very essence of the informed consent. The “spot check” conducted by Dr. Busby was not a proper audit, as it lacked advance notice, defined objectives, scope, and researcher involvement, and was not carried out by the REB. The Committee found that the seizure was a disproportionate response, contrary to the principle of “proportionate review” under the Tri-Council Policy Statement (TCPS), and that institutional officials breached their responsibility by prioritizing the establishment of alleged wrongdoing over the protection of research subject privacy. The Committee attributed the seizure to ongoing tensions between Drs. Duffy and Grof and Drs. Merali and Bradwejn, and to the confounding of informed consent for privacy protection with informed consent for protection from harm.\n\nThe Committee’s recommendations included: clarifying that research records are in principle the property of the researcher; clearly defining the position of self-funded research teams and renegotiating responsibilities regularly; identifying for each research project whether informed consent is for protection from harm or for privacy and confidentiality; clarifying institutional responsibilities so that the REB that approved a project, not other institutional officials, ensures adherence to research ethics standards; and ensuring that seizure of research records is only a last resort when there is an immediate and serious threat to the wellbeing of research subjects, with procedures designed to respect the privacy and confidentiality of health information.', 'A prolonged and bitter dispute at Halifax’s Capital District Health Authority (CDHA) and Dalhousie University involved three physicians—Drs. Gabrielle Horne, Michael Goodyear, and Bassam A. Nassar. All held joint academic and hospital appointments. An Independent Committee of Inquiry established by the Canadian Association of University Teachers found that their cases arose from “interpersonal disagreements” that escalated because of serious flaws in bylaws, policies, procedures, and institutional culture. The Committee concluded that the damage was caused by a “collective and systemic failure” at CDHA/Dalhousie, not by individual errors, and that none of the three doctors was ultimately found to have committed wrongdoing when their cases received fair hearings.\n\nA central problem was the absence of academic freedom from the Affiliation Agreement between Dalhousie and CDHA. This meant academic freedom had no formal role in the relationship, leaving clinical faculty vulnerable. The Committee also found that “collegiality” was undefined and misused; it was applied in vague, personality-based ways that related to perceptions of “congeniality” rather than professional competence. In all three cases, allegations of lacking collegiality were used against the doctors. The doctors’ remuneration came through the Alternate Funding Plan (AFP) or group practice plans, which gave Department Chiefs extraordinary power over income with inadequate appeal rights. Appointments were not tenured, but were Continuing Appointments with Periodic Review (CAPR), which did not protect academic freedom.\n\nThe CDHA Medical Staff (Disciplinary) Bylaws were central to the cases of Drs. Horne and Goodyear. The Bylaws allowed summary variation of privileges by a Department Chief, but did not require natural justice or procedural fairness at the District Medical Advisory Committee (DMAC) or Privileges Review Committee (PRC) stages. Only the CDHA Board hearing provided those protections. The Bylaws set a maximum of fifty-one days before a case would go to the Board, but in practice the processes lasted years because the parties agreed to waive time limits. The Committee found that the Bylaws were “in many ways unsuited to productive solutions” and that variations of privileges should be reserved for egregious cases. It also criticized the lack of grievance procedures, income maintenance, and any binding process to implement Board rulings.\n\nIn Dr. Nassar’s case, the Disciplinary Bylaws were not invoked. His problems began with conflicts with the Chief of Pathology over privatized laboratory services and perceived conflicts of interest. He faced a letter of reprimand, a harassment complaint that was quashed by the Nova Scotia Supreme Court because no valid bylaws were in force, and a recommendation that his CAPR appointment not be renewed based on allegations about “collegiality” and “personal integrity.” His complaint of a hostile work environment was not resolved, and he spent years in litigation. An addendum to the Inquiry report later noted that Dr. Nassar reached a “mutually satisfactory settlement” with the Capital District Health Authority.\n\nDr. Horne was a cardiologist and clinical researcher whose privileges were summarily varied on October 21, 2002, by the Chief of Medicine. She was removed from clinical services where team care was the model, including the Heart Function Clinic, and enrollment in her research clinical trials was halted. The stated reason was concern about her ability to maintain “appropriate professional interaction in a team care model of service delivery.” Her research had all required Research Ethics Board approvals, and when her protocols were eventually presented to a special meeting of the clinical trials group, no safety issues were identified. A mediated settlement was reached in June 2003, but CDHA did not implement it; the PRC asserted the CEO lacked authority, and the courts agreed. The CDHA Board ruled in September 2006 that there was insufficient reason to invoke the “emergency variation” and ordered Dr. Horne restored to the status she held before the variation. By then, her research program had been destroyed. Dr. Horne subsequently won a jury verdict in the Nova Scotia Supreme Court of $1.4 million—described as the highest amount ever awarded in Canadian history for “loss of reputation and career”—plus more than $167,000 in legal fees. The jury found that her loss of privileges constituted “bad faith or malice.” Dr. Ken West called it “a classic case of workplace bullying.” The Nova Scotia Court of Appeal later reduced the award to $800,000, while the $167,000 for legal fees remained.\n\nDr. Goodyear, a medical oncologist, had his privileges restricted on October 10, 2002, and then suspended on January 9, 2003, after disagreements with colleagues over new cancer treatment protocols, including use of the “Douillard protocol” rather than the “Saltz regimen.” He was accused of failure to function in a “collegial team framework” and of exposing patients to risk. His income was reduced to 15% of its previous level through the AFP while the case was still pending. The CDHA Board did not rule until January 26, 2009—more than six years after the original variation—finding that there was “no basis to vary or suspend the privileges of Dr. Michael Goodyear” and ordering him restored to his October 9, 2002 status. However, by then he had been out of practice so long that a reintegration plan was required. Two CDHA oncologists who had testified against him were appointed as mentors, creating a reasonable apprehension of bias. Dr. Goodyear was ultimately denied a full medical licence and his oncology career was ended.\n\nThe provincial government later released documents showing that over $1 million in taxpayer money was spent on outside lawyers during the disciplinary process involving Dr. Horne, from 2002 onwards. The $1,024,649.67 was shared among four Halifax law firms: Boyne Clarke, Patterson Palmer, Stewart McKelvey, and Wickwire Holm. The Nova Scotia government had long refused to release the figures until Information Commissioner Tricia Ralph found the Department of Health “did not meet its burden to prove the information was exempt from disclosure.” The costs of defending the subsequent lawsuit and appeal remained secret, with the Nova Scotia Health Organizations Protective Association refusing to disclose “commercially sensitive information.” Dr. Horne said the figure was “extremely upsetting” and that it was likely “a small fraction of what was actually spent.”\n\nThe Independent Committee of Inquiry made numerous recommendations, including replacing the Affiliation Agreement with a “Cooperative Partnership,” protecting academic freedom, converting CAPR appointments into tenure-stream appointments, creating a formal Policy on Variation of Privileges, establishing discipline and grievance policies with final and binding arbitration, and ensuring effective representation for medical staff. It also recommended new external independent resources for defining and assessing clinical practice standards, and prompt fair settlements for the three doctors. The Committee concluded that “justice has been too long delayed.”']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>health - consent - medical - committee - public - records - christian - informed - medicine - covid</t>
+          <t>report - clinical - records - committee - consent - health - confidentiality - patients - medical - information</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1306,16 +1306,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4_board_media_journals_release</t>
+          <t>3_media_board_release_journals</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>['board', 'media', 'journals', 'release', 'trustees', 'governance', 'wall', 'suspension', 'president', 'grievance']</t>
+          <t>['media', 'board', 'release', 'journals', 'trustees', 'governance', 'wall', 'suspension', 'committee', 'grievance']</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1325,11 +1325,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>board - media - journals - release - trustees - governance - wall - suspension - president - grievance</t>
+          <t>media - board - release - journals - trustees - governance - wall - suspension - committee - grievance</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.5667731802665151</v>
+        <v>0.6324743110128644</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1353,30 +1353,30 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0_committee_president_board_hall</t>
+          <t>1_committee_president_board_public</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>['committee', 'president', 'board', 'hall', 'grievor', 'caut', 'public', 'applicants', 'school', 'search']</t>
+          <t>['committee', 'president', 'board', 'public', 'caut', 'applicants', 'hall', 'grievor', 'school', 'search']</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['The grievor, Chad Thompson, had been employed as an Assistant Professor at University College of the North (UCN) for approximately two years when he was terminated in August 2011 for insubordination, insolence and defiant behaviour in the context of his involvement on a search committee. The termination occurred following his role as Chair of the Selection Board for Competition No. 3145, a search to fill a full-time, regular Social Science Instructor position in the Faculty of Arts and Sciences. The grievor held a full-time tenure track position within the bargaining unit represented by the Manitoba Government and General Employees\' Union.\n\nNorma Baker, the grievor\'s spouse and Dean of the Faculty of Arts and Sciences, was initially involved in preparing the posting and reviewing applications, but then went on sick leave. Because of concern about delay, the Vice-President - Academic, Kathryn McNaughton, requested that the grievor chair the search committee. The committee shortlisted two candidates, Aaron Crowe and Jason Hildebrandt. Crowe was interviewed, while Hildebrandt was unavailable due to an injury. The search committee unanimously endorsed Crowe, pending reference checks. Although UCN policy provided that Human Resources would check references, there was discussion by the committee and it was decided that Baker, as an academic, should conduct the reference checks, with the input of Human Resources committee member Linda Hunt. Baker did conduct the reference checks of Crowe. Linda Hunt prepared the Selection Board Report and submitted it to Interim President Konrad Jonasson with the committee\'s recommendation to hire Crowe.\n\nBy e-mail of July 14, 2011, Jonasson refused to approve the recommendation. He raised concerns including an appearance of conflict of interest by having both Baker and the grievor involved, questions about the second candidate\'s inability to interview, the educational qualifications of the recommended candidate, and whether information regarding the candidate\'s PhD program was current. Jonasson offered two options: consider the search failed and start anew, or go back and review all candidates to determine if any of the three not granted interviews should be interviewed and whether the second candidate remained interested. The e-mail concluded that if the other three did not merit an interview and candidate 2 could not go forward, the search should be declared failed and restarted. Baker, the grievor, committee member Sandra Barber, and McNaughton interpreted this e-mail as a declaration of failed search. Jonasson testified that it was designed to indicate concerns and solicit additional information, and that he did not declare a failed search until a subsequent e-mail on July 15.\n\nOn July 15, 2011 at 8:54 a.m., the grievor directed an e-mail to Linda Hunt stating that he would not be submitting his notes and ratings for the LTF hiring process, that given the actions of the Interim President regarding competition 3145 he had no confidence that Mr. Jonasson would respect the policies and procedures of HR, and that he was unwilling to participate any further in this or any other hiring committee until he regained confidence in the process. The e-mail was copied to the head of Human Resources and to McNaughton, but not to Jonasson. The grievor testified that he was not attempting to hide anything, that he felt it was part of his role to speak out where he believed the governance of the institution to be in error, and that he did not regret sending the message, although he wished he had worded it more carefully.\n\nAt 9:14 a.m. on July 15, approximately twenty minutes after the e-mail to Hunt, the grievor sent an e-mail directly to Aaron Crowe, advising him that, as Chair of the Selection Committee, he was writing with deepest regret to inform him of the decision by Interim President Mr. Konrad Jonasson to reject the unanimous recommendation of the Selection Committee to offer him the position. The e-mail suggested that Crowe might wish to speak with Human Resources regarding UCN policy HR-03-0 and with MGEU regarding Article 11:04 in the collective agreement, and was copied to the Manager of Human Resources and two Union staff representatives, including Nelson. Jonasson considered this a violation of protocol and a breach of confidentiality of the selection process. The grievor acknowledged he was angry, that he felt Jonasson\'s decision was not just, that sending the e-mail was a "very stupid thing to do," and that he regretted having done so. Crowe, an internal candidate, subsequently grieved the failure to award him the position.\n\nBy letter of August 10, 2011, Jonasson issued Baker a disciplinary reprimand for various misconduct, including her involvement on the search committee, her involvement in contacting references, and her e-mail of July 15. Baker was out of scope and not in a position to grieve that discipline; she subsequently resigned her position with UCN. Jonasson met with the grievor and Union representative Nelson on July 27, 2011 to review concerns. There was an issue as to whether the grievor offered regret or an apology; Jonasson had no recollection of an apology, while the grievor believed he showed regret and offered an apology, and Nelson testified that the grievor apologized at least twice or perhaps three times. Subsequent to that meeting, the grievor\'s position was terminated by letter of August 17, 2011.\n\nThe letter of termination stated that the grievor\'s actions relating to competition no. 3145 were in fundamental breach of his employment obligations. It cited three reasons: first, without the knowledge or approval of Human Resources, he allowed Baker to continue to participate on the Selection Board after she withdrew and allowed her to contact references on behalf of UCN, which was a significant breach of trust and a clear breach of policy; second, the grievor made insolent allegations against the Interim President in his e-mail to Hunt, stating he had no confidence that Jonasson would respect HR policies and procedures; and third, the grievor violated UCN policy by sending an e-mail directly to the recommended candidate advising him of the rejection, copying representatives of the MGEU Union who were not employees of UCN, and highlighting sections of the Collective Agreement for the unsuccessful applicant. The letter asserted that the grievor\'s conduct was clearly intended to undermine the authority of the Interim President.\n\nThe Employer argued that the grievor was a short term employee who had been insubordinate, insolent and defiant without justification, that his evidence was misleading in an attempt to minimize what he had done, and that the e-mails were inappropriate and sent without justification. The Employer submitted that this was extreme insubordination striking at the heart of the employment relationship, that none of the normal factors of mitigation were present, and that dismissal was the appropriate response. The Employer noted that the grievor had not demonstrated exceptional financial hardship other than what one would normally anticipate from a termination, and argued that even if academic freedom were engaged, it was not used responsibly.\n\nThe Union asserted that while there was conduct deserving of discipline, there had been no progressive discipline and termination was simply too severe. The Union pointed out that the grievor had an unblemished record, that Jonasson acknowledged he had not looked at the grievor\'s prior clear record, and that another individual, Baker, had received only a written reprimand for similar conduct, demonstrating inconsistency in the application of discipline. The Union argued that the e-mail to Crowe was written in the heat of the moment, that the grievor accepted responsibility for his actions, that the reference checks were done with the involvement of Human Resources, and that the e-mail to Hunt was an expression of concern over the hiring process, related to the service component of his role and potentially within academic freedom under Article 72 of the Collective Agreement. The Union requested reinstatement and compensation, with a letter of reprimand as the appropriate discipline.\n\nThe arbitrator, R.A. Simpson, found that while the grievor\'s conduct was insubordinate and warranted discipline, termination was not justified. The arbitrator noted that although the grievor was entitled to consider the July 14 e-mail equivalent to a declaration of failed search, that did not excuse his subsequent conduct. The e-mail to Hunt, containing comments about the Interim President\'s respect for HR policies, had a degree of insolence amounting to insubordination and was not within the service component of the grievor\'s role or within the parameters of academic freedom, but considered in isolation, it could have been dealt with through perhaps a verbal or at most a written reprimand. The e-mail to Crowe was clearly insubordinate, involving a breach of confidentiality, disclosure of confidential information, an invitation to challenge the Employer\'s decision, and a defiance of and challenge to the Employer\'s authority. However, the arbitrator was not satisfied that the employment relationship was irreparably harmed or could not be successfully rehabilitated. The grievor was not a long term employee, but his record over two years was without blemish, he was not challenged on his evidence as to exceptional services he had provided, and dismissal would have a significant adverse effect upon his career. There was no evidence that progressive discipline short of termination was considered. The arbitrator accepted the Employer\'s argument that there was a significant difference between Baker\'s situation and the grievor\'s, with Baker communicating with colleagues and advocating for faculty and students, as opposed to the grievor communicating with an unsuccessful candidate and disclosing confidential information. Nevertheless, a lesser discipline could well have been sufficient to rehabilitate the employment relationship. The arbitrator substituted a two-month suspension without pay for the termination, stating that this was a significant penalty that should send a message that such behaviour would not be tolerated. The grievance was allowed, the termination rescinded, and a two-month suspension without pay substituted.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.']</t>
+          <t>['Between March 2011 and July 2012, the University of Calgary (U of C) worked to secure a sponsorship from Enbridge, a Calgary-based oil and gas pipeline company, to establish a research institute at the Haskayne School of Business (HSB). Dr. Joe Arvai, a recently appointed faculty member, was asked to be director of what became the Enbridge Centre for Corporate Sustainability (ECCS). The sponsorship agreement, dated July 1, 2011, was between Enbridge and “The Governors of the University of Calgary,” committing $225,000 annually over ten years. However, planned activities were based on an annual budget of $500,000, more than double Enbridge’s financial outlay, creating an immediate funding shortfall that was supposed to be made up by additional corporate fundraising.\n\nDuring the establishment and launch of the ECCS, Arvai repeatedly raised concerns about Enbridge’s influence over the Centre’s academic mission. Emails disclosed through freedom of information requests showed that Enbridge exerted influence over the Centre’s name, the selection of partner institutions, the planning of the public launch, and the role of the director. Enbridge pressed for Central Michigan University (CMU) as a partner, in part because CMU had given Enbridge "very valuable advice" after the 2010 Kalamazoo River oil spill in Michigan; Arvai objected on academic grounds, saying CMU had only one faculty member in the relevant field, but was pressured to accept. HSB Dean Len Waverman told Arvai that “the monies we give to CMU are tiny – it won’t be viewed as a payoff,” and that “Elizabeth [Cannon] will have a fit if she sees this.” Enbridge also expressed concerns about Arvai’s appointment to a U.S. Environmental Protection Agency (EPA) Scientific Advisory Board, and the university delayed its announcement of that appointment so as not to “piss off Enbridge any more.” Arvai stated that “we cannot maintain our credibility as serious scholars/researchers if the sponsors can dictate the Centre’s agenda,” and that he could not serve as director if sponsors were allowed to meddle in academic activities.\n\nArvai was removed as ECCS director in March 2012. He later told the CAUT committee that he was removed one week after he informed Enbridge’s public relations firm, National Public Relations, of his opposition on scientific grounds to the Northern Gateway pipeline. In an email of March 19, 2012, Dean Waverman told Enbridge officials: “Joe Arvai is no longer Director of the Centre, there are too many conflicts and demands!” Arvai subsequently left the U of C and is now at the University of Michigan.\n\nA CBC News investigation in November 2015 prompted the Canadian Association of University Teachers (CAUT) to establish an Ad Hoc Investigatory Committee. In his first public statement, an opinion piece reprinted by CBC News, Arvai said the CBC had done “an exceptional job of getting the facts correct,” and that the post hoc suggestions that decisions setting up the Enbridge Centre were “transparent, legitimate, and free of corporate interference or conflict-of-interest” were as difficult for him to accept as they were in 2012. He said donors should be able to suggest, but not select, advisory individuals, and should have a voice in a centre’s name and mission, but should not require that support be limited to those sharing their “core values.”\n\nThe CAUT report, released in October 2017, made findings on conflict of interest, academic freedom, external influence, funding, governance, and the McMahon review. It found a “clear appearance of a conflict of interest” on the part of U of C President Elizabeth Cannon, who served on the Enbridge Income Fund Holdings Board for significant remuneration while president, and who failed to publicly recuse herself from Enbridge-related matters. The report found that Cannon intervened directly with Dean Waverman, telling him that Enbridge was “not very happy,” that she wanted a good relationship with Enbridge, and emphasizing “I am on one of their Boards!” The report also found that the U of C Board of Governors failed to review or approve the sponsorship agreement, despite being a party to it, and that Cannon’s reliance on an “administrative lapse” was an “unacceptable evasion of responsibility.”\n\nThe CAUT committee concluded that Dr. Arvai’s academic freedom was compromised as a result of the U of C’s mishandling of the Enbridge Centre, appearing to be due to a desire on the part of senior leadership to please a significant donor. It found that Enbridge sought to influence the Centre’s establishment and launch, and that university administrators failed to convey that this influence was inappropriate. The report found that Enbridge was given special access to academic staff, was allowed to recommend partners, and had extensive influence over the public launch. The committee found Arvai’s explanation for his departure credible and troubling. It also found that the sponsorship was “skewed in Enbridge’s favour” from the start, with unfunded promises made at the university’s risk and expense, creating a “cycle of dependency” and pressures to compromise academic integrity. It identified a “significant failure of collegial governance, accountability and oversight,” and warned of “worrying signs of a culture of silencing and reprisal at the U of C.”\n\nThe CAUT report was highly critical of the university’s own review, led by retired Justice Terrence McMahon. The Board of Governors had commissioned the McMahon review in November 2015; McMahon found no wrongdoing and cleared university officials, including President Cannon, and the board considered the matter closed. The CAUT committee, however, stated that it was misleading to describe the McMahon review as “independent” and “transparent,” because it was established, mandated, and staffed by the Board or its counsel, and because it did not acknowledge or discuss the central role of academic freedom. The committee said McMahon gave the benefit of the doubt to senior officials while subjecting Arvai and Waverman to damaging criticism, and that the review’s selective approach to confidentiality was inconsistent with fairness and thoroughness. The CAUT report made recommendations including prohibiting university presidents and senior officials from serving for remuneration on external corporate boards, reviewing Board governance, and releasing all documents provided to the McMahon review.\n\nFollowing the CAUT report, the University of Calgary Faculty Association, chaired by Sandra Hoenle, called on the provincial government to probe governance at the university. Hoenle wrote that one of the greatest concerns was “the domination of the senior administration in the governance processes,” and that the Board of Governors and Senior Administration had misapplied “for-profit corporate structures within a university collegial setting,” keeping decision-making behind closed doors. She said, “We’re not a corporation. Universities are not corporations.” Arvai welcomed the CAUT report and said it was “wholly appropriate for the faculty association to be asking for a provincial review.” Alberta’s Ministry of Advanced Education stated that conflict of interest was being examined at public boards, including academic freedom, through a review of agencies, boards, and commissions, and that “Academic freedom is a cornerstone of any university.” Hoenle said the provincial governance review had been truncated and should be expanded to specifically deal with issues identified in the CAUT and CBC investigations.', 'Simon Fraser University has acknowledged mistakes and expressed “sincere regret” to York University professor David Noble over the handling of his candidacy for the J.S. Woodsworth Chair in 2001. The apology was part of an out-of-court settlement reached between SFU and Noble, who was denied the appointment despite overwhelming support from the faculty. Noble said he was “pleased at the outcome” and that Simon Fraser recognized the consequences of its actions. No settlement terms were released, and Noble said he is prohibited from discussing the deal.\n\nIn the winter of 2000, the department of humanities at Simon Fraser University invited Professor David Noble to apply for the J.S. Woodsworth Chair, a permanent position recently created by agreement between the department and the dean of arts. The department appointed a search committee that eventually selected Noble as its first choice and ultimately recommended his appointment to the entire department. The department endorsed the search committee’s recommendation, initially by a vote of nine in favour with one abstention, and later approved forwarding Noble’s name to the dean of arts by a vote of seven in favour, one opposed, and two abstentions. The search committee generated a short list of four potential nominees, and Noble visited the campus for interviews between Jan. 11–14, 2001. During his visit, Noble asked whether Michael Stevenson, the newly appointed president of SFU, would have a role in the selection process, and noted that any involvement by President Stevenson would not bode well for his candidacy. There was also discussion of the recent faculty strike at York University, during which Noble was critical of Stevenson’s role in the negotiations while the latter was vice president academic at York.\n\nDespite the department’s strong endorsement, senior officials from the dean of arts all the way up to the president became involved in trying to stop Noble’s appointment. Dean John Pierce was initially supportive, but one week after the search committee’s decision, he informed department chair Stephen Duguid that severe concerns had been raised at a Deans’ meeting about Noble’s “collegiality” and an accusation that he tended to attack individuals with whom he disagreed. Dean Pierce had heard from Dean Ron Marteniuk of applied sciences an allegation that Noble had behaved rudely at a conference on technology and distance education at SFU’s Harbour Centre, including allegedly shouting “Nuremberg, Nuremberg” and not allowing a speaker to finish. The committee of inquiry later found there was no foundation to these allegations; the alleged victim, Tom Calvert, said the exchange had been “heated” but civil and focused on issues, not personalities. President Stevenson told Dean Pierce there was need for a thorough background check on Noble’s style of interaction, and wrote an email to Vice President Academic John Waterhouse saying, “I touched base with John Pierce this afternoon. I would be glad to discuss in detail, but I’d avoid this appointment like the plague.”\n\nDean Pierce commissioned a private consultant, Libby Dybikowski of Provence Consulting, to do a due diligence check on Noble. The dean wanted to know how Noble would interact with people who took opposing views, particularly faculty members engaged in IT work, the business community, and the press, and wanted the chair to build bridges to other faculties and the external community, including business. When Dybikowski contacted Noble for permission to contact individuals he did not know, Noble refused, saying the individuals listed knew neither him nor his work, and that he could suggest others who would be more appropriate. After consulting with Dean Pierce, Dybikowski again contacted Noble, who informed her that his lawyer advised him not to cooperate further because of the unusual nature of the request. Dybikowski then contacted Noble’s named referees and submitted a confidential report to Dean Pierce on Feb. 7. The Provence Consulting report was overwhelmingly positive, with referees describing Noble as creative, multi-disciplinary, a gifted organizer, a good team player, a principled activist, a superb speaker, and an educator loved by his students.\n\nOn Feb. 20, 2001, Dean Pierce informed Dr. Duguid that he would not support Noble’s nomination. In a March 12 memorandum, Dean Pierce stated that given the high-profile nature of the position, in particular representing the university to the wider public and building bridges to other departments and faculties such as applied sciences, he had decided to proceed with further background checks or due diligence. He cited Noble’s refusal to give permission to talk to a number of current or former senior academic administrators at York University and one other academic from SFU. The department reconsidered and reaffirmed its choice of Noble on March 22, 2001, with a vote of seven in favour, one opposed, and two abstentions. Vice President Waterhouse did not support the department’s recommendation and submitted the file to the University Appointments Committee (UAC), raising concerns about equity, permission to nominate, documentation, and representing the university. The UAC returned the file to the department in May 2001 with instructions to supply additional information, including a fuller CV, a statement of interest, a statement of teaching ability, and employment equity documentation. Dean Pierce then proposed terminating the search and starting a new search in fall 2001, despite the UAC’s indication that the deficiencies could be supplied without major difficulty. The process was suspended.\n\nPresident Stevenson later announced that he had appointed Lyman Robinson, a retired professor of law, to inquire into the search process. The Robinson report, delivered July 30, 2001, recommended lifting the suspension and allowing the department to respond to the UAC, but concluded that Noble’s academic freedom was not violated, reasoning in part that there was no employment relationship between Noble and Simon Fraser University. The department of humanities resumed the process, but support within the department had declined. In November 2001, the UAC returned the file again, concluding that the appointment recommendation failed to meet all the documentary requirements of the university’s appointment policies and recommending a new search. Noble requested a review, and a Special University Appointments Committee (SUAC) dismissed his appeal, finding no procedural irregularities, no bias on grounds of personal prejudice, and no discrimination contrary to the Human Rights Act of British Columbia. The SUAC characterized President Stevenson’s “plague email” as the expression of a personal opinion in an informal email exchange.\n\nThe Canadian Association of University Teachers (CAUT) Academic Freedom and Tenure Committee had established a committee of inquiry, composed of the Hon. Howard Pawley and Professor Gordon Shrimpton. The committee issued a damning report in 2003, determining that interventions by SFU administrators, particularly the dean of applied arts and the university president, had violated Noble’s academic freedom. The committee found that administrators imposed unreasonable requirements that concerned Noble’s style of engaging with academics and institutions he criticized, and may even have raised concerns about his professional opinions on tele-learning and university-corporate relations. The committee identified specific violations: the imposition of a requirement to “represent the university,” which is inconsistent with freedom to criticize the university; penalizing Noble for exercising his legal rights as a citizen when he refused to allow additional background-check contacts; raising concerns about his research and publications on university-corporate relations and educational technology; and inquiries into his style of interaction and collegiality, which violated freedom of discussion. The committee found bias or reasonable apprehension of bias on the part of the president and the dean of arts, and concluded that the appointment process failed to adhere to established academic practice and violated CAUT policies. It recommended that SFU acknowledge that the department of humanities conducted a fair and thorough process and offer Noble an appointment with tenure to the J.S. Woodsworth Chair. SFU officials disputed the report’s findings, saying the university’s appointment process had worked properly. Noble filed a lawsuit against SFU. The university ultimately reached an out-of-court settlement, issuing a statement recognizing that it made mistakes when applying its policies to Noble’s candidacy and acknowledging that the mistakes had a personal impact on him, while noting that the outcome of the candidacy, had the mistakes not been made, remains uncertain.', 'According to the CAUT Ad Hoc Investigatory Committee Report, in 2001 Professor George Nader was denied reappointment as principal or “master” of Peter Robinson College at Trent University. The search committee had recommended him by a six-one plurality, with two abstentions, and he had stated his willingness to serve. The denial followed a period of controversy during which the survival of Peter Robinson College was in question. On November 12, 1999, Trent’s board of governors agreed to President Bonnie Patterson’s proposal that her administration be authorized to close or relocate Peter Robinson College and Traill College, the university’s two downtown colleges. Opponents believed the closures would undermine Trent’s historic mission, and the Trent University Faculty Association shared that view.\n\nNader, then principal of Peter Robinson College and a tenured faculty member in geography, was centrally important in discussions of the administration’s plans. He criticized the policy of the Trent administration through letters and memoranda to university officials, contributions to senate and board proceedings, open letters to the board, organization of a society devoted to the college’s survival, communications with the press, and public utterances. He also forwarded motions passed by the Peter Robinson College Council, including a motion calling for the college to continue in its traditional downtown location. He produced a “Business Analysis” arguing that closure made little sense even on a strict cost-benefit basis. He became a trustee of the “Friends of Trent Colleges,” an association that raised funds for legal action against the board. Along with others, he acquired support from the senate, faculty association, students, staff, and members of the public. Nader also worked to ensure a judicial review once the closure decision was ratified by the board.\n\nIn late 2000, President Patterson and Vice-President Graham Taylor reprimanded Nader for his activities as a public critic of administration policy. Taylor’s letter of September 21, 2000 charged that Nader was conflating his academic role with his administrative role as an appointee of the Board of Governors, and that he was making statements to the public media, purportedly as Principal, that “must be recognized as detrimental to the well-being of the university.” Taylor objected to Nader’s use of his title in fund-raising for the Friends of Trent Colleges, to his use of college facilities, to his distribution of an open letter using a confidential list of board members’ addresses, and to his release of financial data and calculations that had been prepared on a confidential basis. President Patterson’s letter of October 26, 2000 reiterated the administration’s concerns and stated that Nader’s intervention had “not been fully constructive.” She also mentioned the upcoming college head search and expressed hope that Nader would fulfil his role as expected during transition issues.\n\nDespite the reprimands, the search committee for a new principal recommended Nader’s reappointment. On April 24, 2001, the chair of the search committee welcomed news that Nader was prepared to accept a two-year reappointment. On May 6, 2001, Vice-President Taylor wrote to the committee chair that he did not think this was an appropriate recommendation and asked the committee to consider its options more thoroughly. According to Nader’s notes of a June 26, 2001 meeting with the president and vice-president, President Patterson offered three reasons for denying reappointment: Nader’s opposition in published reports and public statements to the board’s capital development plan; his role as trustee of the Friends of Trent Colleges; and her belief that students and faculty were divided on relocation, and that therefore the college should be relocated. She noted that the chair of the board agreed with her. Nader’s term ended June 30, 2001, and he returned to full-time academic work in the geography department.\n\nThe faculty association launched an unsuccessful grievance on Nader’s behalf relying on the collective agreement clause on academic freedom, but the grievance was not pursued because Nader had not been a member of the faculty association at the time of the claimed abridgement. A judicial review application seeking to quash the board’s resolution was denied by the Divisional Court; the Ontario Court of Appeal dismissed an appeal in Kulchyski v. Trent University, and the Supreme Court of Canada refused leave to appeal. Peter Robinson College was eventually closed, some of its operations moved to the main campus, and Sadleir House was sold.\n\nIn October 2003, CAUT’s Academic Freedom and Tenure Committee appointed an ad hoc investigatory committee, composed of William Bruneau and Timothy Quigley, to investigate whether there were breaches of or threats to academic freedom. The committee had access to substantial documentation and interviewed ten individuals on February 8 and 9, 2005. President Patterson declined to participate and instructed her administration not to participate; former Vice-President Taylor also declined to be interviewed. The committee concluded there was a prima facie case that Nader’s academic freedom had been abridged.\n\nThe committee found that Nader was a tenured academic holding an academic teaching appointment, and that his work as principal of his college was academic in scope and purpose. The position was an academic appointment by the senate, akin to a department head, and carried a responsibility to advocate on behalf of the college. The committee found no evidence that Nader’s public utterances materially threatened the administration’s ability to make or execute policy. Nader did not rely on secret materials, betrayed no administration secrets, and told the public nothing that a determined member of the public could not have found out for herself. The committee found no evidence that Trent funds were misdirected to the Friends of Trent Colleges, and no evidence that Nader was denied reappointment for just cause.\n\nThe committee concluded that Nader’s academic freedom was infringed by the administration’s reprimands in 2000 and by the subsequent and consequent refusal to reappoint him as principal. It rejected the argument that a frank criticism of administration policy “must be recognized as detrimental to the well-being of the university,” noting that administrative embarrassment is not the same as harm to the university. The committee also argued that academic freedom is not divisible according to type of duties, and that mid-level academic administrators such as a college principal, department chair, or associate dean should have the right to criticize policy without fear of reprimand or punitive changes in their conditions of employment. It stated that even more senior administrators should enjoy academic freedom protection for good-faith criticism, subject to legitimate constraints. The committee recommended that CAUT and AUCC study and develop a policy on academic freedom protection for senior university personnel, and recommended that the university administration apologize to Nader for infringing his academic freedom.']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>committee - president - board - hall - grievor - caut - public - applicants - school - search</t>
+          <t>committee - president - board - public - caut - applicants - hall - grievor - school - search</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.7363327494236253</v>
+        <v>0.9412156192866595</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1_law_indigenous_dean_report</t>
+          <t>-1_law_indigenous_september_rights</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>['law', 'indigenous', 'dean', 'report', 'association', 'letter', 'harassment', 'process', 'work', 'hiring']</t>
+          <t>['law', 'indigenous', 'september', 'rights', 'work', 'harassment', 'dean', 'hiring', 'law school', 'process']</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.']</t>
+          <t>['## Summary\n\nThe events concern the hiring process for the Director of the International Human Rights Program (IHRP) at the University of Toronto Faculty of Law, and the subsequent fallout involving allegations of external interference, academic freedom violations, and institutional responses.\n\nThe IHRP was established by the Faculty of Law in 1987 to advance international human rights law, offering experiential learning, a clinic, a speaker series, internships, and advocacy work. It had won awards, including a Lexpert Zenith award and the Ludwik and Estelle Jus Memorial Human Rights Prize. In 2020, following a competitive search for the vacant Director position, a three-person hiring committee consisting of Assistant Dean Alexis Archbold, Professor Audrey Macklin, and IHRP Research Associate Vincent Wong unanimously selected Dr. Valentina Azarova as its top choice. Dr. Azarova was a highly recognized international legal practitioner, educator, and researcher specializing in legal and human rights issues arising from immigration detention, the arms trade, and occupation and annexation, including published work on Israel’s occupation of the Palestinian Territories.\n\nThe hiring process initially proceeded smoothly. In early August 2020, Assistant Dean Archbold said she had a meeting booked with University Human Resources to “discuss our offer to Valentina.” On August 11, Archbold verbally offered Dr. Azarova the directorship by videoconference, discussing salary, pension, starting date, and contract term. Dr. Azarova accepted verbally on August 19. The University proposed initially hiring Dr. Azarova as an independent contractor or consultant while her Canadian work permit was being obtained, and University employment lawyers confirmed this arrangement was permissible. An immigration lawyer, Peter Rekai, was retained to assist with the work permit application. On September 3, Assistant Dean Archbold wrote that she was progressing with drafting a summary of terms for a subsequent employment contract and working on work permit processes.\n\nThe situation changed abruptly on September 4, 2020. A sitting judge of the Tax Court of Canada, who was also a University of Toronto alumnus and major donor, contacted a University fundraising official and expressed objections to Dr. Azarova’s appointment because of her work on Israel and Palestine. The judge indicated he intended to call the Dean of the Faculty of Law, Edward Iacobucci. Professor Macklin recorded her alarm about possible donor influence. On September 6, Dean Iacobucci called Macklin and announced that the hiring process was being terminated. He gave two reasons: first, that it was improper to hire Dr. Azarova as an independent contractor before her work permit was secured; second, that she had requested permission to pursue overseas work during part of the summer vacation period. When Macklin raised the issue of Azarova’s Israel/Palestine work, the Dean reportedly replied, “it is an issue, but given the other two issues, I don’t need to get to the third issue.”\n\nOn September 10, Assistant Dean Archbold informed Vincent Wong that “Valentina’s immigration situation turned out to be more complicated than we thought” and that the Faculty could not proceed with her candidacy. Dr. Azarova was told “we hit a wall,” and that immigration lawyers had indicated “very high risks” to the University in engaging her on a short-term consultancy, despite the University having initially suggested that arrangement. No written contract was ever provided.\n\nThe decision triggered a series of resignations. Professor Audrey Macklin resigned from the hiring committee and as chair of the IHRP Faculty Advisory Committee on September 11. The other members of the Faculty Advisory Committee, Professors Vincent Chiao, Anna Su, and Trudo Lemmens, also resigned. Vincent Wong resigned from his paid Research Associate position on September 16, citing concerns about abuse of process, improper external influence, and academic freedom. Two former IHRP directors wrote to the Dean expressing alarm about improper external interference and a serious breach of confidentiality in the hiring process.\n\nDean Iacobucci publicly denied the allegations. In a September 17 message to the law school, he asserted that “assertions that outside influence affected the outcome of the search are untrue and objectionable,” and that “no offer of employment was made because of legal constraints on cross-border hiring.” The University’s Office of the President similarly stated that no offer was made and no offer was revoked. Students, however, expressed deep concern. The Students’ Law Society published an open letter saying the allegations suggested the Faculty had compromised its commitment to academic freedom. Individual students said the IHRP’s independence and reputation were central to its human rights work, that the program had already been without a permanent director for a year, and that the hiring controversy exposed a “disturbing general tendency to clamp down on any criticism of Israel.” Nine law faculty members wrote to the Provost on October 7, arguing that the Dean had subverted the collegial hiring process and that the immigration rationale was “pretextual.”\n\nThe Canadian Association of University Teachers (CAUT) conducted a review and issued a report in October 2020. CAUT’s Academic Freedom and Tenure Committee concluded that there was sufficient evidence to support allegations of a serious breach of Dr. Azarova’s academic freedom and that censure of the University of Toronto Administration was warranted. The report found that a verbal employment contract was entered into on August 19 and that the subsequent decision not to proceed amounted to a breach of that contract. It found that the University’s stated grounds related to immigration and the summer work request were not plausible and appeared pretextual. It rejected the University’s characterization of the Director position as non-academic, holding that academic freedom is “indivisible and undiminished” for academic administrators. Finally, based on a balance of probabilities, CAUT concluded that the rescinding of Dr. Azarova’s appointment was motivated by her research and political views regarding Israel and Palestine, and that collegial hiring practices in the Faculty of Law were breached.\n\nAmnesty International also became involved. In an official correspondence dated 18 May 2021, Amnesty International Canada and Amnesty International’s Crisis Response Programme wrote to University of Toronto President Gertler and Dean Brunnée, regretfully informing them that Amnesty was pausing its relationship with the Faculty of Law and its International Human Rights Law Program with immediate effect. This action was taken in support of CAUT’s censure decision. Amnesty noted its more than four-year partnership with the IHRP through the Digital Verification Corps, an award-winning flagship programme. Amnesty stated that, having read the report by retired Supreme Court of Canada Justice Thomas Cromwell, it was “unable to take at face value the claim that the hire was frozen solely due to immigration issues, rather than external influence from a major university donor critical of Dr Azarova’s academic work on Israel and Palestine.” Amnesty indicated it would suspend its relationship until the CAUT censure was lifted and a sustainable roadmap for the IHRP’s future was in place.', 'In April 2021, Stéphane Sérafin, a law professor at the University of Ottawa’s Common Law Section, received an email from his Vice-Dean asking to speak about “many comments/complaints/preoccupations” regarding his property law class. Sérafin immediately understood the subject: he had taught a module on aboriginal law, a customary part of Canadian property law courses, examining the long-established rule, still reflected in case law, that the English Crown affirmed sovereignty over the land now Canada in the 18th century, with indigenous rights in some circumstances surviving as an “encumbrance” on that Crown title. During the lecture, a small group of students interjected, asserting that these doctrines were simply “racist” and “colonialist.” Sérafin pushed back “ever so slightly,” telling students that such conclusions rested on assumptions associated with critical legal studies and its progeny, that they could not be taken for granted without further argument, and that his job was to help them understand the law as a prelude to critiquing or changing it.\n\nThe complaints eventually became a formal human rights complaint filed with the Dean through the law school’s “Indigenous Learner Advocate.” The students objected both to Sérafin’s remarks and to his allowing discussion of “sensitive” issues at all. They singled out another student’s correct observation that indigenous groups frequently fought each other prior to European contact as a “problematic statement.” The complainants demanded that the law school act on its “commitments to the indigenous community” by requiring the module be taught by an indigenous person, preceded by a trigger warning, that faculty undergo mandatory anti-colonialism training, and that Sérafin issue a formal apology and “deepen” his knowledge of indigenous issues. Sérafin decided to stand his ground. Because professors at the institution are unionized, and the collective agreement formally enshrines academic freedom in the classroom, he forwarded the email to a union representative and asserted his rights. When he pressed the Vice-Dean for a written outline of the complaints, the Vice-Dean dodged; once Sérafin invoked the collective agreement, the Vice-Dean backed off. Because the formal complaint process was still in progress, Sérafin was able to escape sanction entirely.\n\nSérafin describes this as part of a broader transformation of Canadian universities. When he graduated from the same law school in 2014, signs of capture by “wokeness,” “critical social justice,” or the “successor ideology” were minimal. Between 2014 and 2019, the law school took largely symbolic steps. Most important was its commitment to implementing the 28th “call to action” of the Truth and Reconciliation Commission, which mandated that Canadian law schools require all students to take a course on Aboriginal people and the law, including the history and legacy of residential schools, the United Nations Declaration on the Rights of Indigenous Peoples, Treaties and Aboriginal rights, Indigenous law, and Aboriginal–Crown relations, with skills-based training in intercultural competency, conflict resolution, human rights, and anti-racism. Law schools hired indigenous faculty and administrators, including an “Indigenous Learner Advocate.” Around the same time, the Law Society of Ontario mandated that all practising lawyers abide by a “statement of principles” committing them to “equity, diversity and inclusion.” Though lawyers elected to the Law Society’s governing body subsequently repealed that requirement by a 28-20 vote in 2019, the law school adopted a similar policy for students. Sérafin initially accepted these initiatives as largely symbolic, and he had spent two years working for First Nations communities, so he valued indigenous legal traditions.\n\nThen came the summer of 2020. The George Floyd story was “totalizing” in Anglo-Canadian culture, and per the ideology’s proponents, Canada’s systemic racism had been exposed, justifying mass protests and demands that universities implement their commitments. The Dean began sending schoolwide emails, and student groups made many demands, including mandatory anti-bias training for faculty and an anonymous complaint process directed at faculty and students. In October 2020, an adjunct professor in the Faculty of Arts used the n-word descriptively while lecturing on language reclamation by marginalized groups. A single student complained, and the professor was suspended from teaching on the spot. Some professors mobilized, writing a letter condemning the treatment; the union issued a similar statement. Then a group calling itself the “BIPOC Caucus” replied that the professors’ letter “reveals the depth of anti-Black racism in this country,” and a social media pile-on ensued. The union walked back its email and apologized. Another letter supporting the professor, prepared by law school colleagues and signed by legal scholars from other universities, was pulled before publication. A professor who had circulated it was forced to resign as president of the Canadian Association of Law Teachers, and the Association apologized for circulating the letter.\n\nBy the time of the Vice-Dean’s 2021 email, Sérafin writes, the law school had been paying lip service to the ideology and hiring administrators to implement its symbolic gestures. The ideology’s adherents then called in those promises. The next phase was reconciling these commitments with the traditional purpose of the university. Sérafin notes that as a result of the lack of institutional support, he cut all reference to indigenous issues from his property law syllabus this year—a tragedy, since the material is challenging and important, but necessary because it had become effectively impossible to touch unless one toes the ideological line. His hopes of avoiding controversy were dashed when a committee exploring a new mandatory indigenous law course returned recommendations far worse than expected. The new course would not focus on indigenous legal traditions; instead, it would be a full course aimed squarely at “anti-racism” and “decolonization,” focused on “dismantling” traditional law school curriculum content. Moreover, the course would not be confined to one class: a portion of every other first-year course would be explicitly set aside for teaching similar ideas. These recommendations were approved as a pilot project, which Sérafin assumes will become permanent. This means professors will be expected to teach controversial material in precisely the way the ideology demands, and side-stepping it will no longer be an option.\n\nSérafin therefore asked to be relieved of any obligation to teach first-year courses, and the request was granted. He also decided to be public about the situation, since he has little faith that academic freedom will prevail from within and expects further reprisals.\n\nWesley Yang’s introduction frames this account as a case study in “ideological succession”: install ideological enforcers within the administration to police “controversial” views—including the substance of existing law—out of circulation by labelling them harm and harassment, forcing professors to tiptoe around “sensitive” subjects and inducing a wider chilling effect. Yang notes the process is the same in the US and Canada.\n\nThe third document is a letter from Mark Mercer, president of the Society for Academic Freedom and Scholarship (SAFS), to Kristen Boon, Dean of the Faculty of Law. The letter states that academic freedom is a foundation stone of the contemporary university, and that a vice-dean who wishes to serve the university well would explain to complaining students that a professor is free to use his or her judgment in pedagogical matters. Instead, the Vice-Dean in this case failed in his duty to protect the law school and university. SAFS condemned the law school’s response, saying that having Sérafin no longer teach introductory courses constitutes a victory for “anti-intellectual, anti-academic forces,” and that the law school “capitulated to threats and ignorance.” The letter also compares the case to Ottawa U’s handling of the Verushka Lieutenant-Duval case and former law dean Adam Dodek’s persecution of student Nikolay Stanchulov. SAFS requested a response to be posted on its website.', 'Frances Widdowson, a tenured associate professor in the Department of Economics, Justice, and Policy Studies at Mount Royal University (MRU) in Calgary, was dismissed from her position on December 20, 2021, effective immediately. Widdowson, who joined MRU in 2008 and received tenure in 2011, was a political scientist with a specialization in Indigenous peoples’ policy and affairs. She authored and co-authored books including *Disrobing the Aboriginal Industry: The Deception Behind Indigenous Cultural Preservation* (2008), *Separate but Unequal: How Parallelist Ideology Conceals Indigenous Dependency* (2019), and edited *Indigenizing the University: Diverse Perspectives* (2021). She was also a board member of the Society for Academic Freedom and Scholarship (SAFS) and a core member of the Rational Space Network, a faculty group promoting “open inquiry, critical thinking, and evidence-based approaches in post-secondary education.”\n\nWiddowson described herself as a left-wing critic of Indigenous policies and other “woke” initiatives. She was known for publicly criticizing “wokeism” and what she called “identity politics that has become totalitarian.” She argued that universities had embraced “reified postmodernism,” an anti-Enlightenment position that rejects objectivity and universal truth, and that this created an environment where questioning the claims of oppressed groups was treated as harassment or discrimination.\n\nIn 2020, Widdowson made public statements that drew wide attention. She said the Black Lives Matter movement had “destroyed” the culture at MRU, and she suggested that residential schools gave Indigenous children an education that “normally they wouldn’t have received.” These remarks led to an online petition calling for her firing, which garnered more than 6,000 signatures. Widdowson said there was a campaign by about 30 faculty members to have her terminated, and that the petition called for her to be fired for “racist remarks” and “racist actions.” MRU president Tim Rahilly at the time said the school was “reviewing the concerns in light of our strong commitment to academic freedom and freedom of expression.”\n\nA central event in Widdowson’s account occurred in September 2019, when she attended a talk by Dr. Gregory Cajete, a professor of Native American studies at the University of New Mexico, who discussed Indigenous “star knowledge.” During the question period, Widdowson asked whether Indigenous star knowledge could be incorporated into astronomy or other science classes at MRU, or whether it was about how Indigenous people historically understood the stars. She noted that astronomy had advanced tremendously since Galileo and the development of the telescope, and asked how stories from cultures without telescopes could contribute to actual science courses. In December 2020, this question became the subject of a harassment complaint. An Indigenous studies professor who attended the talk alleged that Widdowson had “asked Dr. Cajete what Indigenous science was and said that Indigenous science was not science,” and that her remarks were “racist and discriminatory” and “very disrespectful.” Although the complainant later said she could not remember word-for-word what Widdowson had said, she maintained that the question acted to “invalidate the technologies of Indigenous peoples and denigrate the work of Dr. Cajete.” Because a recording of Widdowson’s question existed, she was not found to have engaged in harassment or discrimination with respect to that allegation.\n\nThe matter continued at an Arts Faculty Council meeting in March 2021. Widdowson asked the Dean of Arts whether arguments such as those made by Massimo Pigliucci in her edited volume—which argued that there is no such thing as Indigenous science—could still have space at MRU without being perceived as racist. In response, another Indigenous studies professor, who identified himself as Mayan, said he felt “insulted” by the previous speaker’s statement that Indigenous people have no science, called the argument “laughable,” and said he had been teaching Indigenous contributions to science for years. Widdowson then posted the words “Insulted? Laughable?” in the meeting chat. Six faculty members responded saying “yes insulted” and thanked the professor. A faculty member from Sociology and Anthropology said it was “a little bit nonsensical” to talk about “some guy’s view on Mayan science or lack thereof” and said such “nonsense” should not be allowed at the Arts Faculty Council. Widdowson raised a Point of Privilege, declaring “there is a terrible double standard in the Faculty of Arts,” and said she was tired of being smeared as a racist for making academic arguments.\n\nThis Arts Faculty Council incident became part of another harassment complaint, made by Indigenous studies professor Renae Watchman, who alleged that Widdowson “publicly announced that there is no such thing as Indigenous Science and used the chat to ridicule an Indigenous faculty member.” During a six-hour investigation, Widdowson read out the transcript, and the investigator found she was not at fault. According to Widdowson, the investigator said her comments and behaviour were not inappropriate and that other faculty members at the meeting “seem[ed] to illustrate some unduly disrespectful and dismissive behaviour of others.” Despite this, MRU later cited her conduct at that meeting as one of the reasons for her firing, stating that it was “so disruptive that it was a significant contributing factor to the development of new procedures at Arts Faculty Council meetings as well as the disabling of the chat function during these meetings.”\n\nWiddowson and several colleagues also engaged in what the arbitrator later described as a full-on “Twitter war.” Over several months, they traded complaints of harassment and bullying. Some of Widdowson’s tweets were found to constitute harassment. In July 2021, she made a complaint against a colleague for his tweets; an investigation in November 2021 found that none of those tweets constituted harassment and characterized her complaint “as being malicious, frivolous, vexatious and made in bad faith.” Her termination followed in December 2021.\n\nMRU confirmed that Widdowson was no longer a faculty member but did not give a specific reason, citing personnel matters. The university issued statements asserting that it is “committed to fostering expression and free speech” and that it “unequivocally supports academic debate,” but that “academic freedom does not justify harassment or discrimination.” It said employees have the right to work in an environment that is respectful and free from harassment and that decisions were made following rigorous due process.\n\nWiddowson said she was “pretty shocked” by the firing and planned to take the case to arbitration through her union. She argued that the university had “failed to implement the campus free speech policy they were required to adopt by the Alberta government in 2019,” and accused MRU of spending “hundreds of thousands of dollars policing Twitter.” She said her stance on Indigenous issues and trans activism contributed to an “academic mob” that tried to have her removed. David Robinson, executive director of the Canadian Association of University Teachers, said it is rare for tenured professors to be fired because tenure is a guarantee that dismissal requires just cause, meaning gross negligence or misconduct, and that professors cannot be dismissed for political or disciplinary views.\n\nThe Society for Academic Freedom and Scholarship, in a letter from president Mark Mercer to MRU president Tim Rahilly, said there was no public evidence of any good reason for Widdowson’s termination. The letter described her as a distinguished scholar and defender of academic freedom, and expressed concern that her firing would send a chilling message to professors and students not to speak certain views. Commentator Bruce Gilley, in an opinion piece, described the firing as a “Stalinist purge” and accused the university of embracing “indigenization” and “decolonization” ideologies at the expense of science, debate, and truth-seeking.\n\nThe case proceeded to arbitration before arbitrator David Phillip Jones. His decision, issued in July 2024, ran more than 300 pages and dealt with 10 grievances filed by Widdowson and the Mount Royal Faculty Association. The hearing took 30 days spread over 10 months, with 25 witnesses and thousands of pages of exhibits. Jones dismissed the eight procedural grievances, finding the investigation was fair. He found that while some of Widdowson’s tweets constituted harassment and there was just cause for discipline, the penalties—both the two-week suspension and the termination—were disproportionate. He substituted a letter of reprimand for the suspension and awarded a monetary payment in lieu of reinstatement. He declined to order reinstatement because of the irreparable damage to the employment relationship, the hostility between Widdowson and her colleagues, and her persistence in arguing that the tweets did not constitute harassment. Financial details remained to be determined. Widdowson said she was pleased the arbitrator found she had been wrongfully terminated but remained upset that the decision treated some of her conduct as harassment. MRU said it understood the ongoing impact of the process and would have no further comment. The Mount Royal Faculty Association noted the possibility of a judicial review.']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>law - indigenous - dean - report - association - letter - harassment - process - work - hiring</t>
+          <t>law - indigenous - september - rights - work - harassment - dean - hiring - law school - process</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1456,29 +1456,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2_health_consent_medical_committee</t>
+          <t>2_report_clinical_records_committee</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>['health', 'consent', 'medical', 'committee', 'public', 'records', 'christian', 'informed', 'medicine', 'covid']</t>
+          <t>['report', 'clinical', 'records', 'committee', 'consent', 'health', 'confidentiality', 'patients', 'medical', 'information']</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['A prolonged and acrimonious dispute in Toronto involving internationally acclaimed blood researcher Dr. Nancy Olivieri, the Hospital for Sick Children (HSC), the University of Toronto, and the pharmaceutical manufacturer Apotex Inc. was resolved in a face-saving compromise in late January 1999, after earlier events had ignited a controversy over research ethics, patient safety, and academic freedom.\n\nThe dispute centred on clinical trials of deferiprone (L1), an experimental orally active iron-chelating agent being tested as an alternative to the standard but onerous deferoxamine (DFO) therapy for patients with thalassemia major, a transfusion-dependent blood disorder causing progressive iron loading of major organs. Dr. Olivieri, a specialist in hematology and internal medicine, was principal investigator of two Toronto trials: LA-03, a long-term efficacy and safety study, and LA-01, a randomized comparison trial versus DFO, co